--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44A4CCB2-8159-4A08-B623-D5ED8FAB6DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC70EBF-5F6B-41C7-8827-768DD1FCB4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -48,184 +48,172 @@
     <t xml:space="preserve">Anexo </t>
   </si>
   <si>
-    <t>Processar</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 27.10.2025</t>
-  </si>
-  <si>
-    <t>134984579</t>
-  </si>
-  <si>
-    <t>134995372</t>
-  </si>
-  <si>
-    <t>134991107</t>
-  </si>
-  <si>
-    <t>134998390</t>
-  </si>
-  <si>
-    <t>135006701</t>
-  </si>
-  <si>
-    <t>135018319</t>
-  </si>
-  <si>
-    <t>135032010</t>
-  </si>
-  <si>
-    <t>135056767</t>
-  </si>
-  <si>
-    <t>135058405</t>
-  </si>
-  <si>
-    <t>135050313</t>
-  </si>
-  <si>
-    <t>135054937</t>
-  </si>
-  <si>
-    <t>135056538</t>
-  </si>
-  <si>
-    <t>135053027</t>
-  </si>
-  <si>
-    <t>135039021</t>
-  </si>
-  <si>
-    <t>135047710</t>
-  </si>
-  <si>
-    <t>135062441</t>
-  </si>
-  <si>
-    <t>135064406</t>
-  </si>
-  <si>
-    <t>135070644</t>
-  </si>
-  <si>
-    <t>135078285</t>
-  </si>
-  <si>
-    <t>135063404</t>
-  </si>
-  <si>
-    <t>135079165</t>
-  </si>
-  <si>
-    <t>135063790</t>
-  </si>
-  <si>
-    <t>135078940</t>
-  </si>
-  <si>
-    <t>135077212</t>
-  </si>
-  <si>
-    <t>135063411</t>
-  </si>
-  <si>
-    <t>135098510</t>
-  </si>
-  <si>
-    <t>135102621</t>
-  </si>
-  <si>
-    <t>135091822</t>
-  </si>
-  <si>
-    <t>135096144</t>
-  </si>
-  <si>
-    <t>135091519</t>
-  </si>
-  <si>
-    <t>135073395</t>
-  </si>
-  <si>
-    <t>134926489</t>
-  </si>
-  <si>
-    <t>135047658</t>
-  </si>
-  <si>
-    <t>135029860</t>
-  </si>
-  <si>
-    <t>135055114</t>
-  </si>
-  <si>
-    <t>135113829</t>
-  </si>
-  <si>
-    <t>135023805</t>
-  </si>
-  <si>
-    <t>135114518</t>
-  </si>
-  <si>
-    <t>130972090</t>
-  </si>
-  <si>
-    <t>131954898</t>
-  </si>
-  <si>
-    <t>135016899</t>
-  </si>
-  <si>
-    <t>135014545</t>
-  </si>
-  <si>
-    <t>135117053</t>
-  </si>
-  <si>
-    <t>134994271</t>
-  </si>
-  <si>
-    <t>134995698</t>
-  </si>
-  <si>
-    <t>134996070</t>
-  </si>
-  <si>
-    <t>134997240</t>
-  </si>
-  <si>
-    <t>134997276</t>
-  </si>
-  <si>
-    <t>134998211</t>
-  </si>
-  <si>
-    <t>135118623</t>
-  </si>
-  <si>
-    <t>134938757</t>
-  </si>
-  <si>
-    <t>134945513</t>
-  </si>
-  <si>
-    <t>135119781</t>
-  </si>
-  <si>
-    <t>135059226</t>
-  </si>
-  <si>
-    <t>134987833</t>
-  </si>
-  <si>
-    <t>134481525</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_27.10.2025</t>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 28.10.2025</t>
+  </si>
+  <si>
+    <t>135007586</t>
+  </si>
+  <si>
+    <t>135011190</t>
+  </si>
+  <si>
+    <t>135058394</t>
+  </si>
+  <si>
+    <t>135054008</t>
+  </si>
+  <si>
+    <t>135080147</t>
+  </si>
+  <si>
+    <t>135079870</t>
+  </si>
+  <si>
+    <t>135078594</t>
+  </si>
+  <si>
+    <t>135070329</t>
+  </si>
+  <si>
+    <t>135068167</t>
+  </si>
+  <si>
+    <t>135075372</t>
+  </si>
+  <si>
+    <t>135101363</t>
+  </si>
+  <si>
+    <t>135103213</t>
+  </si>
+  <si>
+    <t>135100501</t>
+  </si>
+  <si>
+    <t>135096207</t>
+  </si>
+  <si>
+    <t>135044067</t>
+  </si>
+  <si>
+    <t>135117159</t>
+  </si>
+  <si>
+    <t>130462486</t>
+  </si>
+  <si>
+    <t>135120282</t>
+  </si>
+  <si>
+    <t>135119201</t>
+  </si>
+  <si>
+    <t>134926439</t>
+  </si>
+  <si>
+    <t>134940641</t>
+  </si>
+  <si>
+    <t>135059827</t>
+  </si>
+  <si>
+    <t>135127330</t>
+  </si>
+  <si>
+    <t>135127962</t>
+  </si>
+  <si>
+    <t>134950647</t>
+  </si>
+  <si>
+    <t>135068467</t>
+  </si>
+  <si>
+    <t>135059444</t>
+  </si>
+  <si>
+    <t>135130475</t>
+  </si>
+  <si>
+    <t>135070618</t>
+  </si>
+  <si>
+    <t>135030570</t>
+  </si>
+  <si>
+    <t>135037342</t>
+  </si>
+  <si>
+    <t>135132770</t>
+  </si>
+  <si>
+    <t>135132648</t>
+  </si>
+  <si>
+    <t>135076470</t>
+  </si>
+  <si>
+    <t>132194311</t>
+  </si>
+  <si>
+    <t>135133279</t>
+  </si>
+  <si>
+    <t>135134206</t>
+  </si>
+  <si>
+    <t>135058668</t>
+  </si>
+  <si>
+    <t>135070235</t>
+  </si>
+  <si>
+    <t>135136487</t>
+  </si>
+  <si>
+    <t>135050767</t>
+  </si>
+  <si>
+    <t>134923144</t>
+  </si>
+  <si>
+    <t>135005541</t>
+  </si>
+  <si>
+    <t>135012281</t>
+  </si>
+  <si>
+    <t>135077754</t>
+  </si>
+  <si>
+    <t>135017899</t>
+  </si>
+  <si>
+    <t>135139887</t>
+  </si>
+  <si>
+    <t>132723100</t>
+  </si>
+  <si>
+    <t>135002855</t>
+  </si>
+  <si>
+    <t>135141237</t>
+  </si>
+  <si>
+    <t>135054016</t>
+  </si>
+  <si>
+    <t>135018578</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_28.10.2025</t>
   </si>
 </sst>
 </file>
@@ -630,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -662,19 +650,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134916660</v>
+        <v>134979721</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2"/>
     </row>
@@ -683,16 +671,16 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3"/>
     </row>
@@ -701,935 +689,918 @@
         <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F19"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F21"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F37"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F38"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F41"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F47"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F48"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F49"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F50"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F51"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F52"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F53"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="F54"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1645,31 +1616,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC70EBF-5F6B-41C7-8827-768DD1FCB4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE6772A-A505-43E4-A1C8-ABE6DB65D1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="79">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,169 +51,220 @@
     <t>971</t>
   </si>
   <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 28.10.2025</t>
-  </si>
-  <si>
-    <t>135007586</t>
-  </si>
-  <si>
-    <t>135011190</t>
-  </si>
-  <si>
-    <t>135058394</t>
-  </si>
-  <si>
-    <t>135054008</t>
-  </si>
-  <si>
-    <t>135080147</t>
-  </si>
-  <si>
-    <t>135079870</t>
-  </si>
-  <si>
-    <t>135078594</t>
-  </si>
-  <si>
-    <t>135070329</t>
-  </si>
-  <si>
-    <t>135068167</t>
-  </si>
-  <si>
-    <t>135075372</t>
-  </si>
-  <si>
-    <t>135101363</t>
-  </si>
-  <si>
-    <t>135103213</t>
-  </si>
-  <si>
-    <t>135100501</t>
-  </si>
-  <si>
-    <t>135096207</t>
-  </si>
-  <si>
-    <t>135044067</t>
-  </si>
-  <si>
-    <t>135117159</t>
-  </si>
-  <si>
-    <t>130462486</t>
-  </si>
-  <si>
-    <t>135120282</t>
-  </si>
-  <si>
-    <t>135119201</t>
-  </si>
-  <si>
-    <t>134926439</t>
-  </si>
-  <si>
-    <t>134940641</t>
-  </si>
-  <si>
-    <t>135059827</t>
-  </si>
-  <si>
-    <t>135127330</t>
-  </si>
-  <si>
-    <t>135127962</t>
-  </si>
-  <si>
-    <t>134950647</t>
-  </si>
-  <si>
-    <t>135068467</t>
-  </si>
-  <si>
-    <t>135059444</t>
-  </si>
-  <si>
-    <t>135130475</t>
-  </si>
-  <si>
-    <t>135070618</t>
-  </si>
-  <si>
-    <t>135030570</t>
-  </si>
-  <si>
-    <t>135037342</t>
-  </si>
-  <si>
-    <t>135132770</t>
-  </si>
-  <si>
-    <t>135132648</t>
-  </si>
-  <si>
-    <t>135076470</t>
-  </si>
-  <si>
-    <t>132194311</t>
-  </si>
-  <si>
-    <t>135133279</t>
-  </si>
-  <si>
-    <t>135134206</t>
-  </si>
-  <si>
-    <t>135058668</t>
-  </si>
-  <si>
-    <t>135070235</t>
-  </si>
-  <si>
-    <t>135136487</t>
-  </si>
-  <si>
-    <t>135050767</t>
-  </si>
-  <si>
-    <t>134923144</t>
-  </si>
-  <si>
-    <t>135005541</t>
-  </si>
-  <si>
-    <t>135012281</t>
-  </si>
-  <si>
-    <t>135077754</t>
-  </si>
-  <si>
-    <t>135017899</t>
-  </si>
-  <si>
-    <t>135139887</t>
-  </si>
-  <si>
-    <t>132723100</t>
-  </si>
-  <si>
-    <t>135002855</t>
-  </si>
-  <si>
-    <t>135141237</t>
-  </si>
-  <si>
-    <t>135054016</t>
-  </si>
-  <si>
-    <t>135018578</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_28.10.2025</t>
+    <t>Processar</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 29.10.2025</t>
+  </si>
+  <si>
+    <t>134979484</t>
+  </si>
+  <si>
+    <t>134962145</t>
+  </si>
+  <si>
+    <t>135030358</t>
+  </si>
+  <si>
+    <t>135028379</t>
+  </si>
+  <si>
+    <t>135024994</t>
+  </si>
+  <si>
+    <t>135025576</t>
+  </si>
+  <si>
+    <t>130956880</t>
+  </si>
+  <si>
+    <t>135059853</t>
+  </si>
+  <si>
+    <t>135070326</t>
+  </si>
+  <si>
+    <t>135062482</t>
+  </si>
+  <si>
+    <t>135101455</t>
+  </si>
+  <si>
+    <t>135097429</t>
+  </si>
+  <si>
+    <t>135098943</t>
+  </si>
+  <si>
+    <t>135100523</t>
+  </si>
+  <si>
+    <t>135101752</t>
+  </si>
+  <si>
+    <t>135099365</t>
+  </si>
+  <si>
+    <t>135085517</t>
+  </si>
+  <si>
+    <t>135078885</t>
+  </si>
+  <si>
+    <t>135042913</t>
+  </si>
+  <si>
+    <t>135085215</t>
+  </si>
+  <si>
+    <t>135120312</t>
+  </si>
+  <si>
+    <t>135121374</t>
+  </si>
+  <si>
+    <t>135119631</t>
+  </si>
+  <si>
+    <t>135134316</t>
+  </si>
+  <si>
+    <t>135131641</t>
+  </si>
+  <si>
+    <t>135088744</t>
+  </si>
+  <si>
+    <t>135133876</t>
+  </si>
+  <si>
+    <t>135102311</t>
+  </si>
+  <si>
+    <t>135133611</t>
+  </si>
+  <si>
+    <t>134950623</t>
+  </si>
+  <si>
+    <t>134952079</t>
+  </si>
+  <si>
+    <t>131805468</t>
+  </si>
+  <si>
+    <t>135138340</t>
+  </si>
+  <si>
+    <t>135086755</t>
+  </si>
+  <si>
+    <t>135072175</t>
+  </si>
+  <si>
+    <t>135038093</t>
+  </si>
+  <si>
+    <t>135026153</t>
+  </si>
+  <si>
+    <t>135149510</t>
+  </si>
+  <si>
+    <t>133038530</t>
+  </si>
+  <si>
+    <t>135077298</t>
+  </si>
+  <si>
+    <t>135028866</t>
+  </si>
+  <si>
+    <t>131985416</t>
+  </si>
+  <si>
+    <t>135055444</t>
+  </si>
+  <si>
+    <t>131738740</t>
+  </si>
+  <si>
+    <t>135148583</t>
+  </si>
+  <si>
+    <t>134892696</t>
+  </si>
+  <si>
+    <t>134990202</t>
+  </si>
+  <si>
+    <t>135070064</t>
+  </si>
+  <si>
+    <t>135055483</t>
+  </si>
+  <si>
+    <t>135153117</t>
+  </si>
+  <si>
+    <t>135091081</t>
+  </si>
+  <si>
+    <t>133422656</t>
+  </si>
+  <si>
+    <t>135089000</t>
+  </si>
+  <si>
+    <t>134974400</t>
+  </si>
+  <si>
+    <t>134980258</t>
+  </si>
+  <si>
+    <t>134981898</t>
+  </si>
+  <si>
+    <t>134987823</t>
+  </si>
+  <si>
+    <t>135096804</t>
+  </si>
+  <si>
+    <t>135032162</t>
+  </si>
+  <si>
+    <t>135037003</t>
+  </si>
+  <si>
+    <t>135022784</t>
+  </si>
+  <si>
+    <t>133952637</t>
+  </si>
+  <si>
+    <t>131368021</t>
+  </si>
+  <si>
+    <t>133819202</t>
+  </si>
+  <si>
+    <t>135048759</t>
+  </si>
+  <si>
+    <t>135157596</t>
+  </si>
+  <si>
+    <t>134962553</t>
+  </si>
+  <si>
+    <t>135008504</t>
+  </si>
+  <si>
+    <t>130464424</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_29.10.2025</t>
   </si>
 </sst>
 </file>
@@ -618,7 +669,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -650,7 +701,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134979721</v>
+        <v>134970102</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -659,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -677,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -695,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -713,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -731,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -749,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -767,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -785,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -803,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -821,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -839,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -857,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -875,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -893,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -911,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -929,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -947,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -965,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -983,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1001,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1019,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1037,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1055,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1073,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1091,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1109,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1127,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1145,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1163,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1181,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1199,7 +1250,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1217,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1235,7 +1286,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1253,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1271,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1289,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1307,7 +1358,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1325,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1343,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1361,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1379,7 +1430,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1397,7 +1448,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1415,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1433,7 +1484,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1451,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1469,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1487,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1505,7 +1556,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1523,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1541,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1559,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1577,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1595,12 +1646,301 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54"/>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1616,31 +1956,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BE6772A-A505-43E4-A1C8-ABE6DB65D1ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59A411F-7530-4FC3-992E-01A2E9BF41D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,217 +54,163 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 29.10.2025</t>
-  </si>
-  <si>
-    <t>134979484</t>
-  </si>
-  <si>
-    <t>134962145</t>
-  </si>
-  <si>
-    <t>135030358</t>
-  </si>
-  <si>
-    <t>135028379</t>
-  </si>
-  <si>
-    <t>135024994</t>
-  </si>
-  <si>
-    <t>135025576</t>
-  </si>
-  <si>
-    <t>130956880</t>
-  </si>
-  <si>
-    <t>135059853</t>
-  </si>
-  <si>
-    <t>135070326</t>
-  </si>
-  <si>
-    <t>135062482</t>
-  </si>
-  <si>
-    <t>135101455</t>
-  </si>
-  <si>
-    <t>135097429</t>
-  </si>
-  <si>
-    <t>135098943</t>
-  </si>
-  <si>
-    <t>135100523</t>
-  </si>
-  <si>
-    <t>135101752</t>
-  </si>
-  <si>
-    <t>135099365</t>
-  </si>
-  <si>
-    <t>135085517</t>
-  </si>
-  <si>
-    <t>135078885</t>
-  </si>
-  <si>
-    <t>135042913</t>
-  </si>
-  <si>
-    <t>135085215</t>
-  </si>
-  <si>
-    <t>135120312</t>
-  </si>
-  <si>
-    <t>135121374</t>
-  </si>
-  <si>
-    <t>135119631</t>
-  </si>
-  <si>
-    <t>135134316</t>
-  </si>
-  <si>
-    <t>135131641</t>
-  </si>
-  <si>
-    <t>135088744</t>
-  </si>
-  <si>
-    <t>135133876</t>
-  </si>
-  <si>
-    <t>135102311</t>
-  </si>
-  <si>
-    <t>135133611</t>
-  </si>
-  <si>
-    <t>134950623</t>
-  </si>
-  <si>
-    <t>134952079</t>
-  </si>
-  <si>
-    <t>131805468</t>
-  </si>
-  <si>
-    <t>135138340</t>
-  </si>
-  <si>
-    <t>135086755</t>
-  </si>
-  <si>
-    <t>135072175</t>
-  </si>
-  <si>
-    <t>135038093</t>
-  </si>
-  <si>
-    <t>135026153</t>
-  </si>
-  <si>
-    <t>135149510</t>
-  </si>
-  <si>
-    <t>133038530</t>
-  </si>
-  <si>
-    <t>135077298</t>
-  </si>
-  <si>
-    <t>135028866</t>
-  </si>
-  <si>
-    <t>131985416</t>
-  </si>
-  <si>
-    <t>135055444</t>
-  </si>
-  <si>
-    <t>131738740</t>
-  </si>
-  <si>
-    <t>135148583</t>
-  </si>
-  <si>
-    <t>134892696</t>
-  </si>
-  <si>
-    <t>134990202</t>
-  </si>
-  <si>
-    <t>135070064</t>
-  </si>
-  <si>
-    <t>135055483</t>
-  </si>
-  <si>
-    <t>135153117</t>
-  </si>
-  <si>
-    <t>135091081</t>
-  </si>
-  <si>
-    <t>133422656</t>
-  </si>
-  <si>
-    <t>135089000</t>
-  </si>
-  <si>
-    <t>134974400</t>
-  </si>
-  <si>
-    <t>134980258</t>
-  </si>
-  <si>
-    <t>134981898</t>
-  </si>
-  <si>
-    <t>134987823</t>
-  </si>
-  <si>
-    <t>135096804</t>
-  </si>
-  <si>
-    <t>135032162</t>
-  </si>
-  <si>
-    <t>135037003</t>
-  </si>
-  <si>
-    <t>135022784</t>
-  </si>
-  <si>
-    <t>133952637</t>
-  </si>
-  <si>
-    <t>131368021</t>
-  </si>
-  <si>
-    <t>133819202</t>
-  </si>
-  <si>
-    <t>135048759</t>
-  </si>
-  <si>
-    <t>135157596</t>
-  </si>
-  <si>
-    <t>134962553</t>
-  </si>
-  <si>
-    <t>135008504</t>
-  </si>
-  <si>
-    <t>130464424</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_29.10.2025</t>
+    <t>Relatório de Recusa Sicredi 30.10.2025</t>
+  </si>
+  <si>
+    <t>134980049</t>
+  </si>
+  <si>
+    <t>134997746</t>
+  </si>
+  <si>
+    <t>135045899</t>
+  </si>
+  <si>
+    <t>135096084</t>
+  </si>
+  <si>
+    <t>135097342</t>
+  </si>
+  <si>
+    <t>135085990</t>
+  </si>
+  <si>
+    <t>135076835</t>
+  </si>
+  <si>
+    <t>135108701</t>
+  </si>
+  <si>
+    <t>135113221</t>
+  </si>
+  <si>
+    <t>135119469</t>
+  </si>
+  <si>
+    <t>135152642</t>
+  </si>
+  <si>
+    <t>135155601</t>
+  </si>
+  <si>
+    <t>135158914</t>
+  </si>
+  <si>
+    <t>135155772</t>
+  </si>
+  <si>
+    <t>135152939</t>
+  </si>
+  <si>
+    <t>135155922</t>
+  </si>
+  <si>
+    <t>135161695</t>
+  </si>
+  <si>
+    <t>135161865</t>
+  </si>
+  <si>
+    <t>135151936</t>
+  </si>
+  <si>
+    <t>134907893</t>
+  </si>
+  <si>
+    <t>134971163</t>
+  </si>
+  <si>
+    <t>134990549</t>
+  </si>
+  <si>
+    <t>134944480</t>
+  </si>
+  <si>
+    <t>135166404</t>
+  </si>
+  <si>
+    <t>135077339</t>
+  </si>
+  <si>
+    <t>135115838</t>
+  </si>
+  <si>
+    <t>135078859</t>
+  </si>
+  <si>
+    <t>135172360</t>
+  </si>
+  <si>
+    <t>131813732</t>
+  </si>
+  <si>
+    <t>135085785</t>
+  </si>
+  <si>
+    <t>131364532</t>
+  </si>
+  <si>
+    <t>135078578</t>
+  </si>
+  <si>
+    <t>135065484</t>
+  </si>
+  <si>
+    <t>135172278</t>
+  </si>
+  <si>
+    <t>132137878</t>
+  </si>
+  <si>
+    <t>135175575</t>
+  </si>
+  <si>
+    <t>135069844</t>
+  </si>
+  <si>
+    <t>135176287</t>
+  </si>
+  <si>
+    <t>135170085</t>
+  </si>
+  <si>
+    <t>135028527</t>
+  </si>
+  <si>
+    <t>134964751</t>
+  </si>
+  <si>
+    <t>134944967</t>
+  </si>
+  <si>
+    <t>135091351</t>
+  </si>
+  <si>
+    <t>135175592</t>
+  </si>
+  <si>
+    <t>135139983</t>
+  </si>
+  <si>
+    <t>135055339</t>
+  </si>
+  <si>
+    <t>135168958</t>
+  </si>
+  <si>
+    <t>135173637</t>
+  </si>
+  <si>
+    <t>135052175</t>
+  </si>
+  <si>
+    <t>135055410</t>
+  </si>
+  <si>
+    <t>135059344</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_30.10.2025</t>
   </si>
 </sst>
 </file>
@@ -669,7 +615,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -701,7 +647,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134970102</v>
+        <v>134995916</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -710,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -728,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -746,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -764,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -782,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -800,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -818,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -836,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -854,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -872,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -890,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -908,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -926,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -944,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -962,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -980,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -998,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -1016,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1034,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1052,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1070,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1088,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1106,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1124,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1142,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1160,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1178,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1196,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1214,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1232,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1250,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1268,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1286,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1304,7 +1250,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1322,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1340,7 +1286,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1358,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1376,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1394,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1412,7 +1358,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1430,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1448,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1466,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1484,7 +1430,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1502,7 +1448,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1520,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1538,7 +1484,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1556,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1574,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1592,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1610,7 +1556,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1628,319 +1574,12 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F53"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1956,31 +1595,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C59A411F-7530-4FC3-992E-01A2E9BF41D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A55E108-7F7D-4BB9-A998-D08763915B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="86">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,163 +54,238 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 30.10.2025</t>
-  </si>
-  <si>
-    <t>134980049</t>
-  </si>
-  <si>
-    <t>134997746</t>
-  </si>
-  <si>
-    <t>135045899</t>
-  </si>
-  <si>
-    <t>135096084</t>
-  </si>
-  <si>
-    <t>135097342</t>
-  </si>
-  <si>
-    <t>135085990</t>
-  </si>
-  <si>
-    <t>135076835</t>
-  </si>
-  <si>
-    <t>135108701</t>
-  </si>
-  <si>
-    <t>135113221</t>
-  </si>
-  <si>
-    <t>135119469</t>
-  </si>
-  <si>
-    <t>135152642</t>
-  </si>
-  <si>
-    <t>135155601</t>
-  </si>
-  <si>
-    <t>135158914</t>
-  </si>
-  <si>
-    <t>135155772</t>
-  </si>
-  <si>
-    <t>135152939</t>
-  </si>
-  <si>
-    <t>135155922</t>
-  </si>
-  <si>
-    <t>135161695</t>
-  </si>
-  <si>
-    <t>135161865</t>
-  </si>
-  <si>
-    <t>135151936</t>
-  </si>
-  <si>
-    <t>134907893</t>
-  </si>
-  <si>
-    <t>134971163</t>
-  </si>
-  <si>
-    <t>134990549</t>
-  </si>
-  <si>
-    <t>134944480</t>
-  </si>
-  <si>
-    <t>135166404</t>
-  </si>
-  <si>
-    <t>135077339</t>
-  </si>
-  <si>
-    <t>135115838</t>
-  </si>
-  <si>
-    <t>135078859</t>
-  </si>
-  <si>
-    <t>135172360</t>
-  </si>
-  <si>
-    <t>131813732</t>
-  </si>
-  <si>
-    <t>135085785</t>
-  </si>
-  <si>
-    <t>131364532</t>
-  </si>
-  <si>
-    <t>135078578</t>
-  </si>
-  <si>
-    <t>135065484</t>
-  </si>
-  <si>
-    <t>135172278</t>
-  </si>
-  <si>
-    <t>132137878</t>
-  </si>
-  <si>
-    <t>135175575</t>
-  </si>
-  <si>
-    <t>135069844</t>
-  </si>
-  <si>
-    <t>135176287</t>
-  </si>
-  <si>
-    <t>135170085</t>
-  </si>
-  <si>
-    <t>135028527</t>
-  </si>
-  <si>
-    <t>134964751</t>
-  </si>
-  <si>
-    <t>134944967</t>
-  </si>
-  <si>
-    <t>135091351</t>
-  </si>
-  <si>
-    <t>135175592</t>
-  </si>
-  <si>
-    <t>135139983</t>
-  </si>
-  <si>
-    <t>135055339</t>
-  </si>
-  <si>
-    <t>135168958</t>
-  </si>
-  <si>
-    <t>135173637</t>
-  </si>
-  <si>
-    <t>135052175</t>
-  </si>
-  <si>
-    <t>135055410</t>
-  </si>
-  <si>
-    <t>135059344</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_30.10.2025</t>
+    <t>Relatório de Recusa Sicredi 01.11.2025</t>
+  </si>
+  <si>
+    <t>135014830</t>
+  </si>
+  <si>
+    <t>135032128</t>
+  </si>
+  <si>
+    <t>133016532</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 31.10.2025</t>
+  </si>
+  <si>
+    <t>135060123</t>
+  </si>
+  <si>
+    <t>135065829</t>
+  </si>
+  <si>
+    <t>135077193</t>
+  </si>
+  <si>
+    <t>135073231</t>
+  </si>
+  <si>
+    <t>135070603</t>
+  </si>
+  <si>
+    <t>135071144</t>
+  </si>
+  <si>
+    <t>135071378</t>
+  </si>
+  <si>
+    <t>135075931</t>
+  </si>
+  <si>
+    <t>135073934</t>
+  </si>
+  <si>
+    <t>135097112</t>
+  </si>
+  <si>
+    <t>135062766</t>
+  </si>
+  <si>
+    <t>135076181</t>
+  </si>
+  <si>
+    <t>135093195</t>
+  </si>
+  <si>
+    <t>135130244</t>
+  </si>
+  <si>
+    <t>135133652</t>
+  </si>
+  <si>
+    <t>135144221</t>
+  </si>
+  <si>
+    <t>135138466</t>
+  </si>
+  <si>
+    <t>135137894</t>
+  </si>
+  <si>
+    <t>135127801</t>
+  </si>
+  <si>
+    <t>135070387</t>
+  </si>
+  <si>
+    <t>133422656</t>
+  </si>
+  <si>
+    <t>135162668</t>
+  </si>
+  <si>
+    <t>135174075</t>
+  </si>
+  <si>
+    <t>135182826</t>
+  </si>
+  <si>
+    <t>135172287</t>
+  </si>
+  <si>
+    <t>135170263</t>
+  </si>
+  <si>
+    <t>134989358</t>
+  </si>
+  <si>
+    <t>134996299</t>
+  </si>
+  <si>
+    <t>134999018</t>
+  </si>
+  <si>
+    <t>135006674</t>
+  </si>
+  <si>
+    <t>135088134</t>
+  </si>
+  <si>
+    <t>135017342</t>
+  </si>
+  <si>
+    <t>135187762</t>
+  </si>
+  <si>
+    <t>135189420</t>
+  </si>
+  <si>
+    <t>135090501</t>
+  </si>
+  <si>
+    <t>135190933</t>
+  </si>
+  <si>
+    <t>135033068</t>
+  </si>
+  <si>
+    <t>135048187</t>
+  </si>
+  <si>
+    <t>135084695</t>
+  </si>
+  <si>
+    <t>130836298</t>
+  </si>
+  <si>
+    <t>135070662</t>
+  </si>
+  <si>
+    <t>135195834</t>
+  </si>
+  <si>
+    <t>130496860</t>
+  </si>
+  <si>
+    <t>131353766</t>
+  </si>
+  <si>
+    <t>135090968</t>
+  </si>
+  <si>
+    <t>135062454</t>
+  </si>
+  <si>
+    <t>135062495</t>
+  </si>
+  <si>
+    <t>135065376</t>
+  </si>
+  <si>
+    <t>135065537</t>
+  </si>
+  <si>
+    <t>135065657</t>
+  </si>
+  <si>
+    <t>135068649</t>
+  </si>
+  <si>
+    <t>135195249</t>
+  </si>
+  <si>
+    <t>135070544</t>
+  </si>
+  <si>
+    <t>135073273</t>
+  </si>
+  <si>
+    <t>135078244</t>
+  </si>
+  <si>
+    <t>131578702</t>
+  </si>
+  <si>
+    <t>135074435</t>
+  </si>
+  <si>
+    <t>135074441</t>
+  </si>
+  <si>
+    <t>135075408</t>
+  </si>
+  <si>
+    <t>135197745</t>
+  </si>
+  <si>
+    <t>135077093</t>
+  </si>
+  <si>
+    <t>135077158</t>
+  </si>
+  <si>
+    <t>135195113</t>
+  </si>
+  <si>
+    <t>135097150</t>
+  </si>
+  <si>
+    <t>135058339</t>
+  </si>
+  <si>
+    <t>135199594</t>
+  </si>
+  <si>
+    <t>135197582</t>
+  </si>
+  <si>
+    <t>135196813</t>
+  </si>
+  <si>
+    <t>135015251</t>
+  </si>
+  <si>
+    <t>135201278</t>
+  </si>
+  <si>
+    <t>135201923</t>
+  </si>
+  <si>
+    <t>135201800</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_01.11.2025</t>
   </si>
 </sst>
 </file>
@@ -615,7 +690,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -647,7 +722,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134995916</v>
+        <v>135014240</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -656,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -674,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -692,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -707,10 +782,10 @@
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -719,16 +794,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -737,16 +812,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -755,16 +830,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -773,16 +848,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -791,16 +866,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -809,16 +884,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -827,16 +902,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -845,16 +920,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -863,16 +938,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -881,16 +956,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -899,16 +974,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -917,16 +992,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -935,16 +1010,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -953,16 +1028,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -971,16 +1046,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -989,16 +1064,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1007,16 +1082,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1025,16 +1100,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1043,16 +1118,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1061,16 +1136,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1079,16 +1154,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1097,16 +1172,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1115,16 +1190,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1133,16 +1208,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1151,16 +1226,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1169,16 +1244,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1187,16 +1262,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1205,16 +1280,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1223,16 +1298,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1241,16 +1316,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1259,16 +1334,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1277,16 +1352,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1295,16 +1370,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1313,16 +1388,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1331,16 +1406,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1349,16 +1424,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1367,16 +1442,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1385,16 +1460,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1403,16 +1478,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1421,16 +1496,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1439,16 +1514,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1457,16 +1532,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1475,16 +1550,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1493,16 +1568,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1511,16 +1586,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1529,16 +1604,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1547,16 +1622,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1565,21 +1640,429 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F53"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1595,31 +2078,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A55E108-7F7D-4BB9-A998-D08763915B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E59B6D-364E-4830-9172-018EAB6D92AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,238 +54,181 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 01.11.2025</t>
-  </si>
-  <si>
-    <t>135014830</t>
-  </si>
-  <si>
-    <t>135032128</t>
-  </si>
-  <si>
-    <t>133016532</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 31.10.2025</t>
-  </si>
-  <si>
-    <t>135060123</t>
-  </si>
-  <si>
-    <t>135065829</t>
-  </si>
-  <si>
-    <t>135077193</t>
-  </si>
-  <si>
-    <t>135073231</t>
-  </si>
-  <si>
-    <t>135070603</t>
-  </si>
-  <si>
-    <t>135071144</t>
-  </si>
-  <si>
-    <t>135071378</t>
-  </si>
-  <si>
-    <t>135075931</t>
-  </si>
-  <si>
-    <t>135073934</t>
-  </si>
-  <si>
-    <t>135097112</t>
-  </si>
-  <si>
-    <t>135062766</t>
-  </si>
-  <si>
-    <t>135076181</t>
-  </si>
-  <si>
-    <t>135093195</t>
-  </si>
-  <si>
-    <t>135130244</t>
-  </si>
-  <si>
-    <t>135133652</t>
-  </si>
-  <si>
-    <t>135144221</t>
-  </si>
-  <si>
-    <t>135138466</t>
-  </si>
-  <si>
-    <t>135137894</t>
-  </si>
-  <si>
-    <t>135127801</t>
-  </si>
-  <si>
-    <t>135070387</t>
-  </si>
-  <si>
-    <t>133422656</t>
-  </si>
-  <si>
-    <t>135162668</t>
-  </si>
-  <si>
-    <t>135174075</t>
-  </si>
-  <si>
-    <t>135182826</t>
-  </si>
-  <si>
-    <t>135172287</t>
-  </si>
-  <si>
-    <t>135170263</t>
-  </si>
-  <si>
-    <t>134989358</t>
-  </si>
-  <si>
-    <t>134996299</t>
-  </si>
-  <si>
-    <t>134999018</t>
-  </si>
-  <si>
-    <t>135006674</t>
-  </si>
-  <si>
-    <t>135088134</t>
-  </si>
-  <si>
-    <t>135017342</t>
-  </si>
-  <si>
-    <t>135187762</t>
-  </si>
-  <si>
-    <t>135189420</t>
-  </si>
-  <si>
-    <t>135090501</t>
-  </si>
-  <si>
-    <t>135190933</t>
-  </si>
-  <si>
-    <t>135033068</t>
-  </si>
-  <si>
-    <t>135048187</t>
-  </si>
-  <si>
-    <t>135084695</t>
-  </si>
-  <si>
-    <t>130836298</t>
-  </si>
-  <si>
-    <t>135070662</t>
-  </si>
-  <si>
-    <t>135195834</t>
-  </si>
-  <si>
     <t>130496860</t>
   </si>
   <si>
-    <t>131353766</t>
-  </si>
-  <si>
-    <t>135090968</t>
-  </si>
-  <si>
-    <t>135062454</t>
-  </si>
-  <si>
-    <t>135062495</t>
-  </si>
-  <si>
-    <t>135065376</t>
-  </si>
-  <si>
-    <t>135065537</t>
-  </si>
-  <si>
-    <t>135065657</t>
-  </si>
-  <si>
-    <t>135068649</t>
-  </si>
-  <si>
-    <t>135195249</t>
-  </si>
-  <si>
-    <t>135070544</t>
-  </si>
-  <si>
-    <t>135073273</t>
-  </si>
-  <si>
-    <t>135078244</t>
-  </si>
-  <si>
-    <t>131578702</t>
-  </si>
-  <si>
-    <t>135074435</t>
-  </si>
-  <si>
-    <t>135074441</t>
-  </si>
-  <si>
-    <t>135075408</t>
-  </si>
-  <si>
-    <t>135197745</t>
-  </si>
-  <si>
-    <t>135077093</t>
-  </si>
-  <si>
-    <t>135077158</t>
-  </si>
-  <si>
-    <t>135195113</t>
-  </si>
-  <si>
-    <t>135097150</t>
-  </si>
-  <si>
-    <t>135058339</t>
-  </si>
-  <si>
-    <t>135199594</t>
-  </si>
-  <si>
-    <t>135197582</t>
-  </si>
-  <si>
-    <t>135196813</t>
-  </si>
-  <si>
-    <t>135015251</t>
-  </si>
-  <si>
-    <t>135201278</t>
-  </si>
-  <si>
-    <t>135201923</t>
-  </si>
-  <si>
-    <t>135201800</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_01.11.2025</t>
+    <t>Relatório de Recusa Sicredi 03/11/2025</t>
+  </si>
+  <si>
+    <t>135108917</t>
+  </si>
+  <si>
+    <t>135121033</t>
+  </si>
+  <si>
+    <t>135134371</t>
+  </si>
+  <si>
+    <t>135139416</t>
+  </si>
+  <si>
+    <t>135128502</t>
+  </si>
+  <si>
+    <t>135135758</t>
+  </si>
+  <si>
+    <t>135127175</t>
+  </si>
+  <si>
+    <t>135128181</t>
+  </si>
+  <si>
+    <t>135128072</t>
+  </si>
+  <si>
+    <t>130885467</t>
+  </si>
+  <si>
+    <t>135134289</t>
+  </si>
+  <si>
+    <t>135154950</t>
+  </si>
+  <si>
+    <t>135156822</t>
+  </si>
+  <si>
+    <t>135141081</t>
+  </si>
+  <si>
+    <t>135151375</t>
+  </si>
+  <si>
+    <t>135150909</t>
+  </si>
+  <si>
+    <t>135154035</t>
+  </si>
+  <si>
+    <t>135162396</t>
+  </si>
+  <si>
+    <t>135175060</t>
+  </si>
+  <si>
+    <t>135180829</t>
+  </si>
+  <si>
+    <t>135149781</t>
+  </si>
+  <si>
+    <t>135188585</t>
+  </si>
+  <si>
+    <t>135188940</t>
+  </si>
+  <si>
+    <t>132680873</t>
+  </si>
+  <si>
+    <t>135191990</t>
+  </si>
+  <si>
+    <t>135133079</t>
+  </si>
+  <si>
+    <t>135198688</t>
+  </si>
+  <si>
+    <t>130914561</t>
+  </si>
+  <si>
+    <t>131465358</t>
+  </si>
+  <si>
+    <t>131305604</t>
+  </si>
+  <si>
+    <t>130972090</t>
+  </si>
+  <si>
+    <t>135085552</t>
+  </si>
+  <si>
+    <t>133162355</t>
+  </si>
+  <si>
+    <t>135148384</t>
+  </si>
+  <si>
+    <t>130042850</t>
+  </si>
+  <si>
+    <t>135112484</t>
+  </si>
+  <si>
+    <t>133900965</t>
+  </si>
+  <si>
+    <t>135148094</t>
+  </si>
+  <si>
+    <t>130592947</t>
+  </si>
+  <si>
+    <t>135148052</t>
+  </si>
+  <si>
+    <t>133265930</t>
+  </si>
+  <si>
+    <t>135130564</t>
+  </si>
+  <si>
+    <t>135055495</t>
+  </si>
+  <si>
+    <t>135099722</t>
+  </si>
+  <si>
+    <t>134149529</t>
+  </si>
+  <si>
+    <t>135203792</t>
+  </si>
+  <si>
+    <t>132703005</t>
+  </si>
+  <si>
+    <t>135217823</t>
+  </si>
+  <si>
+    <t>135212528</t>
+  </si>
+  <si>
+    <t>135098784</t>
+  </si>
+  <si>
+    <t>135129911</t>
+  </si>
+  <si>
+    <t>135143965</t>
+  </si>
+  <si>
+    <t>134208028</t>
+  </si>
+  <si>
+    <t>134755454</t>
+  </si>
+  <si>
+    <t>135047869</t>
+  </si>
+  <si>
+    <t>135101324</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_03.11.2025</t>
   </si>
 </sst>
 </file>
@@ -690,7 +633,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -722,16 +665,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135014240</v>
+        <v>131744635</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -740,16 +683,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -758,16 +701,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -776,16 +719,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -800,10 +743,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -818,10 +761,10 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -836,10 +779,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -854,10 +797,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -872,10 +815,10 @@
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -890,10 +833,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -908,10 +851,10 @@
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -926,10 +869,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -944,10 +887,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -962,10 +905,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -980,10 +923,10 @@
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -998,10 +941,10 @@
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -1016,10 +959,10 @@
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -1034,10 +977,10 @@
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1052,10 +995,10 @@
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1070,10 +1013,10 @@
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1088,10 +1031,10 @@
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1106,10 +1049,10 @@
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1124,10 +1067,10 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1142,10 +1085,10 @@
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1160,10 +1103,10 @@
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1178,10 +1121,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1190,16 +1133,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1208,16 +1151,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1226,16 +1169,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1244,16 +1187,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1262,16 +1205,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1280,16 +1223,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1298,16 +1241,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1316,16 +1259,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1334,16 +1277,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1352,16 +1295,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1370,16 +1313,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1388,16 +1331,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1406,16 +1349,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1424,16 +1367,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1442,16 +1385,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1460,16 +1403,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1478,16 +1421,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1496,16 +1439,16 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1514,16 +1457,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1532,16 +1475,16 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1550,16 +1493,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1568,16 +1511,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1586,16 +1529,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1604,16 +1547,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1622,16 +1565,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1640,16 +1583,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1658,16 +1601,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1675,16 +1618,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1692,16 +1635,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1709,16 +1652,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1726,16 +1669,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1743,324 +1686,18 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E77" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2078,31 +1715,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E59B6D-364E-4830-9172-018EAB6D92AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E41FBA-43D9-482E-9F5D-79680D6931E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="97">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,181 +54,271 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>130496860</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 03/11/2025</t>
-  </si>
-  <si>
-    <t>135108917</t>
-  </si>
-  <si>
-    <t>135121033</t>
-  </si>
-  <si>
-    <t>135134371</t>
-  </si>
-  <si>
-    <t>135139416</t>
-  </si>
-  <si>
-    <t>135128502</t>
-  </si>
-  <si>
-    <t>135135758</t>
-  </si>
-  <si>
-    <t>135127175</t>
-  </si>
-  <si>
-    <t>135128181</t>
-  </si>
-  <si>
-    <t>135128072</t>
-  </si>
-  <si>
-    <t>130885467</t>
-  </si>
-  <si>
-    <t>135134289</t>
-  </si>
-  <si>
-    <t>135154950</t>
-  </si>
-  <si>
-    <t>135156822</t>
-  </si>
-  <si>
-    <t>135141081</t>
-  </si>
-  <si>
-    <t>135151375</t>
-  </si>
-  <si>
-    <t>135150909</t>
-  </si>
-  <si>
-    <t>135154035</t>
-  </si>
-  <si>
-    <t>135162396</t>
-  </si>
-  <si>
-    <t>135175060</t>
-  </si>
-  <si>
-    <t>135180829</t>
-  </si>
-  <si>
-    <t>135149781</t>
-  </si>
-  <si>
-    <t>135188585</t>
-  </si>
-  <si>
-    <t>135188940</t>
-  </si>
-  <si>
-    <t>132680873</t>
-  </si>
-  <si>
-    <t>135191990</t>
-  </si>
-  <si>
-    <t>135133079</t>
-  </si>
-  <si>
-    <t>135198688</t>
-  </si>
-  <si>
-    <t>130914561</t>
-  </si>
-  <si>
-    <t>131465358</t>
-  </si>
-  <si>
-    <t>131305604</t>
-  </si>
-  <si>
-    <t>130972090</t>
-  </si>
-  <si>
-    <t>135085552</t>
-  </si>
-  <si>
-    <t>133162355</t>
-  </si>
-  <si>
-    <t>135148384</t>
-  </si>
-  <si>
-    <t>130042850</t>
-  </si>
-  <si>
-    <t>135112484</t>
-  </si>
-  <si>
-    <t>133900965</t>
-  </si>
-  <si>
-    <t>135148094</t>
-  </si>
-  <si>
-    <t>130592947</t>
-  </si>
-  <si>
-    <t>135148052</t>
-  </si>
-  <si>
-    <t>133265930</t>
-  </si>
-  <si>
-    <t>135130564</t>
-  </si>
-  <si>
-    <t>135055495</t>
-  </si>
-  <si>
-    <t>135099722</t>
-  </si>
-  <si>
-    <t>134149529</t>
-  </si>
-  <si>
-    <t>135203792</t>
-  </si>
-  <si>
-    <t>132703005</t>
-  </si>
-  <si>
-    <t>135217823</t>
-  </si>
-  <si>
-    <t>135212528</t>
-  </si>
-  <si>
-    <t>135098784</t>
-  </si>
-  <si>
-    <t>135129911</t>
-  </si>
-  <si>
-    <t>135143965</t>
-  </si>
-  <si>
-    <t>134208028</t>
-  </si>
-  <si>
-    <t>134755454</t>
-  </si>
-  <si>
-    <t>135047869</t>
-  </si>
-  <si>
-    <t>135101324</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_03.11.2025</t>
+    <t>Relatório de Recusa Sicredi 04/11/2025</t>
+  </si>
+  <si>
+    <t>131923198</t>
+  </si>
+  <si>
+    <t>135037722</t>
+  </si>
+  <si>
+    <t>135058831</t>
+  </si>
+  <si>
+    <t>135048906</t>
+  </si>
+  <si>
+    <t>135085465</t>
+  </si>
+  <si>
+    <t>135118239</t>
+  </si>
+  <si>
+    <t>135113420</t>
+  </si>
+  <si>
+    <t>135127484</t>
+  </si>
+  <si>
+    <t>135118989</t>
+  </si>
+  <si>
+    <t>135170330</t>
+  </si>
+  <si>
+    <t>135173763</t>
+  </si>
+  <si>
+    <t>135177260</t>
+  </si>
+  <si>
+    <t>135166647</t>
+  </si>
+  <si>
+    <t>135177872</t>
+  </si>
+  <si>
+    <t>135035687</t>
+  </si>
+  <si>
+    <t>135176532</t>
+  </si>
+  <si>
+    <t>135180551</t>
+  </si>
+  <si>
+    <t>135176872</t>
+  </si>
+  <si>
+    <t>135171224</t>
+  </si>
+  <si>
+    <t>135178078</t>
+  </si>
+  <si>
+    <t>135153935</t>
+  </si>
+  <si>
+    <t>130888756</t>
+  </si>
+  <si>
+    <t>135200354</t>
+  </si>
+  <si>
+    <t>135121082</t>
+  </si>
+  <si>
+    <t>135192174</t>
+  </si>
+  <si>
+    <t>134887168</t>
+  </si>
+  <si>
+    <t>135144233</t>
+  </si>
+  <si>
+    <t>135211653</t>
+  </si>
+  <si>
+    <t>131727427</t>
+  </si>
+  <si>
+    <t>135200950</t>
+  </si>
+  <si>
+    <t>135223101</t>
+  </si>
+  <si>
+    <t>135212916</t>
+  </si>
+  <si>
+    <t>135033222</t>
+  </si>
+  <si>
+    <t>135033420</t>
+  </si>
+  <si>
+    <t>135034294</t>
+  </si>
+  <si>
+    <t>135046676</t>
+  </si>
+  <si>
+    <t>135049687</t>
+  </si>
+  <si>
+    <t>135050642</t>
+  </si>
+  <si>
+    <t>135051210</t>
+  </si>
+  <si>
+    <t>135051525</t>
+  </si>
+  <si>
+    <t>135051851</t>
+  </si>
+  <si>
+    <t>135056600</t>
+  </si>
+  <si>
+    <t>135057495</t>
+  </si>
+  <si>
+    <t>135057639</t>
+  </si>
+  <si>
+    <t>135043876</t>
+  </si>
+  <si>
+    <t>135047940</t>
+  </si>
+  <si>
+    <t>135052614</t>
+  </si>
+  <si>
+    <t>135227754</t>
+  </si>
+  <si>
+    <t>132870164</t>
+  </si>
+  <si>
+    <t>135056089</t>
+  </si>
+  <si>
+    <t>133311618</t>
+  </si>
+  <si>
+    <t>135230613</t>
+  </si>
+  <si>
+    <t>135233462</t>
+  </si>
+  <si>
+    <t>135113255</t>
+  </si>
+  <si>
+    <t>135139001</t>
+  </si>
+  <si>
+    <t>135160012</t>
+  </si>
+  <si>
+    <t>135121201</t>
+  </si>
+  <si>
+    <t>135120804</t>
+  </si>
+  <si>
+    <t>135234114</t>
+  </si>
+  <si>
+    <t>135143171</t>
+  </si>
+  <si>
+    <t>135116173</t>
+  </si>
+  <si>
+    <t>135139128</t>
+  </si>
+  <si>
+    <t>135150501</t>
+  </si>
+  <si>
+    <t>135132905</t>
+  </si>
+  <si>
+    <t>135142494</t>
+  </si>
+  <si>
+    <t>135172847</t>
+  </si>
+  <si>
+    <t>135235308</t>
+  </si>
+  <si>
+    <t>135109970</t>
+  </si>
+  <si>
+    <t>135110222</t>
+  </si>
+  <si>
+    <t>135110929</t>
+  </si>
+  <si>
+    <t>135174968</t>
+  </si>
+  <si>
+    <t>135113414</t>
+  </si>
+  <si>
+    <t>135114251</t>
+  </si>
+  <si>
+    <t>135074080</t>
+  </si>
+  <si>
+    <t>132546677</t>
+  </si>
+  <si>
+    <t>135170891</t>
+  </si>
+  <si>
+    <t>135117275</t>
+  </si>
+  <si>
+    <t>135123083</t>
+  </si>
+  <si>
+    <t>135238828</t>
+  </si>
+  <si>
+    <t>135239562</t>
+  </si>
+  <si>
+    <t>135169882</t>
+  </si>
+  <si>
+    <t>135237705</t>
+  </si>
+  <si>
+    <t>131573026</t>
+  </si>
+  <si>
+    <t>135195960</t>
+  </si>
+  <si>
+    <t>135243331</t>
+  </si>
+  <si>
+    <t>135243799</t>
+  </si>
+  <si>
+    <t>135147808</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_04.11.2025</t>
   </si>
 </sst>
 </file>
@@ -633,7 +723,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -665,16 +755,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>131744635</v>
+        <v>131284278</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -683,16 +773,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -701,16 +791,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -719,16 +809,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -737,16 +827,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -755,16 +845,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -773,16 +863,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -791,16 +881,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -809,16 +899,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -827,16 +917,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -845,16 +935,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -863,16 +953,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -881,16 +971,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -899,16 +989,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -917,16 +1007,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -935,16 +1025,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -953,16 +1043,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -971,16 +1061,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -989,16 +1079,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1007,16 +1097,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1025,16 +1115,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1043,16 +1133,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1061,16 +1151,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1079,16 +1169,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1097,16 +1187,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1115,16 +1205,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1133,16 +1223,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1157,10 +1247,10 @@
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1175,10 +1265,10 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1193,10 +1283,10 @@
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1211,10 +1301,10 @@
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1229,10 +1319,10 @@
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1247,10 +1337,10 @@
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1265,10 +1355,10 @@
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1283,10 +1373,10 @@
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1301,10 +1391,10 @@
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1319,10 +1409,10 @@
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1337,10 +1427,10 @@
         <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1355,10 +1445,10 @@
         <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1373,10 +1463,10 @@
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1391,10 +1481,10 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1409,10 +1499,10 @@
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1427,10 +1517,10 @@
         <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1445,10 +1535,10 @@
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1463,10 +1553,10 @@
         <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1481,10 +1571,10 @@
         <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1499,10 +1589,10 @@
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1517,10 +1607,10 @@
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1535,10 +1625,10 @@
         <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1553,10 +1643,10 @@
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1571,10 +1661,10 @@
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1589,10 +1679,10 @@
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1607,10 +1697,10 @@
         <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1624,10 +1714,10 @@
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1641,10 +1731,10 @@
         <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1658,10 +1748,10 @@
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1675,10 +1765,10 @@
         <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1692,12 +1782,522 @@
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1715,31 +2315,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8E41FBA-43D9-482E-9F5D-79680D6931E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D58BAE1-58EE-45A4-B5F5-B769FDC3861D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="77">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,271 +54,211 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 04/11/2025</t>
-  </si>
-  <si>
-    <t>131923198</t>
-  </si>
-  <si>
-    <t>135037722</t>
-  </si>
-  <si>
-    <t>135058831</t>
-  </si>
-  <si>
-    <t>135048906</t>
-  </si>
-  <si>
-    <t>135085465</t>
-  </si>
-  <si>
-    <t>135118239</t>
-  </si>
-  <si>
-    <t>135113420</t>
-  </si>
-  <si>
-    <t>135127484</t>
-  </si>
-  <si>
-    <t>135118989</t>
-  </si>
-  <si>
-    <t>135170330</t>
-  </si>
-  <si>
-    <t>135173763</t>
-  </si>
-  <si>
-    <t>135177260</t>
-  </si>
-  <si>
-    <t>135166647</t>
-  </si>
-  <si>
-    <t>135177872</t>
-  </si>
-  <si>
-    <t>135035687</t>
-  </si>
-  <si>
-    <t>135176532</t>
-  </si>
-  <si>
-    <t>135180551</t>
-  </si>
-  <si>
-    <t>135176872</t>
-  </si>
-  <si>
-    <t>135171224</t>
-  </si>
-  <si>
-    <t>135178078</t>
-  </si>
-  <si>
-    <t>135153935</t>
-  </si>
-  <si>
-    <t>130888756</t>
-  </si>
-  <si>
-    <t>135200354</t>
-  </si>
-  <si>
-    <t>135121082</t>
-  </si>
-  <si>
-    <t>135192174</t>
-  </si>
-  <si>
-    <t>134887168</t>
-  </si>
-  <si>
-    <t>135144233</t>
-  </si>
-  <si>
-    <t>135211653</t>
-  </si>
-  <si>
-    <t>131727427</t>
-  </si>
-  <si>
-    <t>135200950</t>
-  </si>
-  <si>
-    <t>135223101</t>
-  </si>
-  <si>
-    <t>135212916</t>
-  </si>
-  <si>
-    <t>135033222</t>
-  </si>
-  <si>
-    <t>135033420</t>
-  </si>
-  <si>
-    <t>135034294</t>
-  </si>
-  <si>
-    <t>135046676</t>
-  </si>
-  <si>
-    <t>135049687</t>
-  </si>
-  <si>
-    <t>135050642</t>
-  </si>
-  <si>
-    <t>135051210</t>
-  </si>
-  <si>
-    <t>135051525</t>
-  </si>
-  <si>
-    <t>135051851</t>
-  </si>
-  <si>
-    <t>135056600</t>
-  </si>
-  <si>
-    <t>135057495</t>
-  </si>
-  <si>
-    <t>135057639</t>
-  </si>
-  <si>
-    <t>135043876</t>
-  </si>
-  <si>
-    <t>135047940</t>
-  </si>
-  <si>
-    <t>135052614</t>
-  </si>
-  <si>
-    <t>135227754</t>
-  </si>
-  <si>
-    <t>132870164</t>
-  </si>
-  <si>
-    <t>135056089</t>
-  </si>
-  <si>
-    <t>133311618</t>
-  </si>
-  <si>
-    <t>135230613</t>
-  </si>
-  <si>
-    <t>135233462</t>
-  </si>
-  <si>
-    <t>135113255</t>
-  </si>
-  <si>
-    <t>135139001</t>
-  </si>
-  <si>
-    <t>135160012</t>
-  </si>
-  <si>
-    <t>135121201</t>
-  </si>
-  <si>
-    <t>135120804</t>
-  </si>
-  <si>
-    <t>135234114</t>
-  </si>
-  <si>
-    <t>135143171</t>
-  </si>
-  <si>
-    <t>135116173</t>
-  </si>
-  <si>
-    <t>135139128</t>
-  </si>
-  <si>
-    <t>135150501</t>
-  </si>
-  <si>
-    <t>135132905</t>
-  </si>
-  <si>
-    <t>135142494</t>
-  </si>
-  <si>
-    <t>135172847</t>
-  </si>
-  <si>
-    <t>135235308</t>
-  </si>
-  <si>
-    <t>135109970</t>
-  </si>
-  <si>
-    <t>135110222</t>
-  </si>
-  <si>
-    <t>135110929</t>
-  </si>
-  <si>
-    <t>135174968</t>
-  </si>
-  <si>
-    <t>135113414</t>
-  </si>
-  <si>
-    <t>135114251</t>
-  </si>
-  <si>
-    <t>135074080</t>
-  </si>
-  <si>
-    <t>132546677</t>
-  </si>
-  <si>
-    <t>135170891</t>
-  </si>
-  <si>
-    <t>135117275</t>
-  </si>
-  <si>
-    <t>135123083</t>
-  </si>
-  <si>
-    <t>135238828</t>
-  </si>
-  <si>
-    <t>135239562</t>
-  </si>
-  <si>
-    <t>135169882</t>
-  </si>
-  <si>
-    <t>135237705</t>
-  </si>
-  <si>
-    <t>131573026</t>
-  </si>
-  <si>
-    <t>135195960</t>
-  </si>
-  <si>
-    <t>135243331</t>
-  </si>
-  <si>
-    <t>135243799</t>
-  </si>
-  <si>
-    <t>135147808</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_04.11.2025</t>
+    <t>Relatório de Recusa Sicredi 05/11/2025</t>
+  </si>
+  <si>
+    <t>135078633</t>
+  </si>
+  <si>
+    <t>135094926</t>
+  </si>
+  <si>
+    <t>135131204</t>
+  </si>
+  <si>
+    <t>135132937</t>
+  </si>
+  <si>
+    <t>135132613</t>
+  </si>
+  <si>
+    <t>135133947</t>
+  </si>
+  <si>
+    <t>135141448</t>
+  </si>
+  <si>
+    <t>135144071</t>
+  </si>
+  <si>
+    <t>135137142</t>
+  </si>
+  <si>
+    <t>135143624</t>
+  </si>
+  <si>
+    <t>135155054</t>
+  </si>
+  <si>
+    <t>135175448</t>
+  </si>
+  <si>
+    <t>135172876</t>
+  </si>
+  <si>
+    <t>135181763</t>
+  </si>
+  <si>
+    <t>135181035</t>
+  </si>
+  <si>
+    <t>135193553</t>
+  </si>
+  <si>
+    <t>135157105</t>
+  </si>
+  <si>
+    <t>135189479</t>
+  </si>
+  <si>
+    <t>135198146</t>
+  </si>
+  <si>
+    <t>135200391</t>
+  </si>
+  <si>
+    <t>135217129</t>
+  </si>
+  <si>
+    <t>135211497</t>
+  </si>
+  <si>
+    <t>131030192</t>
+  </si>
+  <si>
+    <t>135174748</t>
+  </si>
+  <si>
+    <t>135049062</t>
+  </si>
+  <si>
+    <t>135055335</t>
+  </si>
+  <si>
+    <t>135058152</t>
+  </si>
+  <si>
+    <t>135080312</t>
+  </si>
+  <si>
+    <t>132020739</t>
+  </si>
+  <si>
+    <t>135200199</t>
+  </si>
+  <si>
+    <t>135139179</t>
+  </si>
+  <si>
+    <t>135182263</t>
+  </si>
+  <si>
+    <t>135175687</t>
+  </si>
+  <si>
+    <t>135178657</t>
+  </si>
+  <si>
+    <t>130665369</t>
+  </si>
+  <si>
+    <t>135170325</t>
+  </si>
+  <si>
+    <t>135249024</t>
+  </si>
+  <si>
+    <t>135250196</t>
+  </si>
+  <si>
+    <t>135253094</t>
+  </si>
+  <si>
+    <t>135069769</t>
+  </si>
+  <si>
+    <t>135254553</t>
+  </si>
+  <si>
+    <t>135180089</t>
+  </si>
+  <si>
+    <t>135088791</t>
+  </si>
+  <si>
+    <t>135258418</t>
+  </si>
+  <si>
+    <t>135092676</t>
+  </si>
+  <si>
+    <t>135152640</t>
+  </si>
+  <si>
+    <t>130388019</t>
+  </si>
+  <si>
+    <t>135162008</t>
+  </si>
+  <si>
+    <t>135260113</t>
+  </si>
+  <si>
+    <t>135179452</t>
+  </si>
+  <si>
+    <t>135169984</t>
+  </si>
+  <si>
+    <t>135076343</t>
+  </si>
+  <si>
+    <t>135253270</t>
+  </si>
+  <si>
+    <t>135129342</t>
+  </si>
+  <si>
+    <t>131100515</t>
+  </si>
+  <si>
+    <t>135193569</t>
+  </si>
+  <si>
+    <t>135134236</t>
+  </si>
+  <si>
+    <t>135136956</t>
+  </si>
+  <si>
+    <t>135137112</t>
+  </si>
+  <si>
+    <t>135138142</t>
+  </si>
+  <si>
+    <t>135138697</t>
+  </si>
+  <si>
+    <t>135138988</t>
+  </si>
+  <si>
+    <t>135143239</t>
+  </si>
+  <si>
+    <t>135143378</t>
+  </si>
+  <si>
+    <t>135143415</t>
+  </si>
+  <si>
+    <t>135143600</t>
+  </si>
+  <si>
+    <t>135144077</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_05.11.2025</t>
   </si>
 </sst>
 </file>
@@ -723,7 +663,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -755,7 +695,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>131284278</v>
+        <v>135068962</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -764,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -782,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -800,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -818,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -836,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -854,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -872,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -890,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -908,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -926,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -944,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -962,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -980,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -998,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -1016,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -1034,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -1052,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -1070,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1088,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1106,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1124,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1142,7 +1082,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1160,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1178,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1196,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1214,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1232,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1250,7 +1190,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1268,7 +1208,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1286,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1304,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1322,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1340,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1358,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1376,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1394,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1412,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1430,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1448,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1466,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1484,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1502,7 +1442,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1520,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1538,7 +1478,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1556,7 +1496,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1574,7 +1514,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1592,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1610,7 +1550,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1628,7 +1568,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1646,7 +1586,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1664,7 +1604,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1682,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1700,7 +1640,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1717,7 +1657,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1734,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1751,7 +1691,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1768,7 +1708,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1785,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1802,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1819,7 +1759,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
@@ -1836,7 +1776,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>7</v>
@@ -1853,7 +1793,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>7</v>
@@ -1870,7 +1810,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>7</v>
@@ -1887,7 +1827,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>7</v>
@@ -1904,7 +1844,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>7</v>
@@ -1921,7 +1861,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>7</v>
@@ -1938,7 +1878,7 @@
         <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>7</v>
@@ -1955,349 +1895,9 @@
         <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E89" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2315,31 +1915,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46FD910B-DDF6-47A7-9791-D2822545B9A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E0CD3D-4F17-435F-B020-86C2CE6DF69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="80">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,220 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 08/11/2025</t>
-  </si>
-  <si>
-    <t>135121938</t>
-  </si>
-  <si>
-    <t>135117409</t>
-  </si>
-  <si>
-    <t>135124873</t>
-  </si>
-  <si>
-    <t>135143481</t>
-  </si>
-  <si>
-    <t>135256434</t>
-  </si>
-  <si>
-    <t>135127864</t>
-  </si>
-  <si>
-    <t>135151383</t>
-  </si>
-  <si>
-    <t>135117334</t>
-  </si>
-  <si>
-    <t>135139762</t>
-  </si>
-  <si>
-    <t>133738722</t>
-  </si>
-  <si>
-    <t>131748141</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_07.11.2025</t>
-  </si>
-  <si>
-    <t>135108135</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_08.11.2025</t>
+    <t>Relatório de Recusa Sicredi 10/11/2025</t>
+  </si>
+  <si>
+    <t>135201345</t>
+  </si>
+  <si>
+    <t>135200147</t>
+  </si>
+  <si>
+    <t>135192618</t>
+  </si>
+  <si>
+    <t>135231330</t>
+  </si>
+  <si>
+    <t>135233947</t>
+  </si>
+  <si>
+    <t>135242453</t>
+  </si>
+  <si>
+    <t>135241203</t>
+  </si>
+  <si>
+    <t>135239434</t>
+  </si>
+  <si>
+    <t>135260335</t>
+  </si>
+  <si>
+    <t>135261216</t>
+  </si>
+  <si>
+    <t>135265316</t>
+  </si>
+  <si>
+    <t>135202546</t>
+  </si>
+  <si>
+    <t>135247981</t>
+  </si>
+  <si>
+    <t>135274442</t>
+  </si>
+  <si>
+    <t>135253472</t>
+  </si>
+  <si>
+    <t>135308588</t>
+  </si>
+  <si>
+    <t>135310549</t>
+  </si>
+  <si>
+    <t>135310779</t>
+  </si>
+  <si>
+    <t>135301588</t>
+  </si>
+  <si>
+    <t>135306040</t>
+  </si>
+  <si>
+    <t>135305515</t>
+  </si>
+  <si>
+    <t>135314208</t>
+  </si>
+  <si>
+    <t>135235956</t>
+  </si>
+  <si>
+    <t>135108721</t>
+  </si>
+  <si>
+    <t>135199917</t>
+  </si>
+  <si>
+    <t>135187161</t>
+  </si>
+  <si>
+    <t>135135034</t>
+  </si>
+  <si>
+    <t>135239039</t>
+  </si>
+  <si>
+    <t>135127390</t>
+  </si>
+  <si>
+    <t>135197636</t>
+  </si>
+  <si>
+    <t>135320181</t>
+  </si>
+  <si>
+    <t>133075161</t>
+  </si>
+  <si>
+    <t>135323439</t>
+  </si>
+  <si>
+    <t>135216386</t>
+  </si>
+  <si>
+    <t>135220527</t>
+  </si>
+  <si>
+    <t>135242674</t>
+  </si>
+  <si>
+    <t>132322277</t>
+  </si>
+  <si>
+    <t>135321533</t>
+  </si>
+  <si>
+    <t>135238761</t>
+  </si>
+  <si>
+    <t>135212987</t>
+  </si>
+  <si>
+    <t>131814119</t>
+  </si>
+  <si>
+    <t>132587252</t>
+  </si>
+  <si>
+    <t>135128177</t>
+  </si>
+  <si>
+    <t>135188744</t>
+  </si>
+  <si>
+    <t>135189003</t>
+  </si>
+  <si>
+    <t>135190814</t>
+  </si>
+  <si>
+    <t>135192353</t>
+  </si>
+  <si>
+    <t>135192752</t>
+  </si>
+  <si>
+    <t>135194768</t>
+  </si>
+  <si>
+    <t>135196607</t>
+  </si>
+  <si>
+    <t>135196668</t>
+  </si>
+  <si>
+    <t>135196768</t>
+  </si>
+  <si>
+    <t>135196992</t>
+  </si>
+  <si>
+    <t>135197056</t>
+  </si>
+  <si>
+    <t>135197326</t>
+  </si>
+  <si>
+    <t>135198787</t>
+  </si>
+  <si>
+    <t>135198892</t>
+  </si>
+  <si>
+    <t>135199592</t>
+  </si>
+  <si>
+    <t>135199767</t>
+  </si>
+  <si>
+    <t>135199781</t>
+  </si>
+  <si>
+    <t>135200503</t>
+  </si>
+  <si>
+    <t>135201074</t>
+  </si>
+  <si>
+    <t>135201903</t>
+  </si>
+  <si>
+    <t>135202006</t>
+  </si>
+  <si>
+    <t>135202126</t>
+  </si>
+  <si>
+    <t>135202357</t>
+  </si>
+  <si>
+    <t>135202531</t>
+  </si>
+  <si>
+    <t>135202870</t>
+  </si>
+  <si>
+    <t>135142756</t>
+  </si>
+  <si>
+    <t>135251350</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_10.11.2025</t>
   </si>
 </sst>
 </file>
@@ -501,7 +672,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -533,7 +704,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135108135</v>
+        <v>135185803</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -542,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -560,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -578,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -596,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -614,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -632,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -650,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -668,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -686,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -704,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -722,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -740,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -749,7 +920,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -758,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -767,7 +938,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
@@ -776,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -785,7 +956,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
@@ -794,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -803,7 +974,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
@@ -812,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -821,7 +992,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
@@ -830,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -839,7 +1010,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -848,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -857,7 +1028,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
@@ -866,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -875,7 +1046,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
@@ -884,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -893,7 +1064,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
@@ -902,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -911,7 +1082,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
@@ -920,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -929,7 +1100,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
@@ -938,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -947,7 +1118,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
@@ -956,12 +1127,811 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>22</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -977,31 +1947,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E0CD3D-4F17-435F-B020-86C2CE6DF69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CAFF68-F294-4995-AFF7-BDB180F7837F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="88">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,220 +54,244 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 10/11/2025</t>
-  </si>
-  <si>
-    <t>135201345</t>
-  </si>
-  <si>
-    <t>135200147</t>
-  </si>
-  <si>
-    <t>135192618</t>
-  </si>
-  <si>
-    <t>135231330</t>
-  </si>
-  <si>
-    <t>135233947</t>
-  </si>
-  <si>
-    <t>135242453</t>
-  </si>
-  <si>
-    <t>135241203</t>
-  </si>
-  <si>
-    <t>135239434</t>
-  </si>
-  <si>
-    <t>135260335</t>
-  </si>
-  <si>
-    <t>135261216</t>
-  </si>
-  <si>
-    <t>135265316</t>
-  </si>
-  <si>
-    <t>135202546</t>
-  </si>
-  <si>
-    <t>135247981</t>
-  </si>
-  <si>
-    <t>135274442</t>
-  </si>
-  <si>
-    <t>135253472</t>
-  </si>
-  <si>
-    <t>135308588</t>
-  </si>
-  <si>
-    <t>135310549</t>
-  </si>
-  <si>
-    <t>135310779</t>
-  </si>
-  <si>
-    <t>135301588</t>
-  </si>
-  <si>
-    <t>135306040</t>
-  </si>
-  <si>
-    <t>135305515</t>
-  </si>
-  <si>
-    <t>135314208</t>
-  </si>
-  <si>
-    <t>135235956</t>
-  </si>
-  <si>
-    <t>135108721</t>
-  </si>
-  <si>
-    <t>135199917</t>
-  </si>
-  <si>
-    <t>135187161</t>
-  </si>
-  <si>
-    <t>135135034</t>
-  </si>
-  <si>
-    <t>135239039</t>
-  </si>
-  <si>
-    <t>135127390</t>
-  </si>
-  <si>
-    <t>135197636</t>
-  </si>
-  <si>
-    <t>135320181</t>
-  </si>
-  <si>
-    <t>133075161</t>
-  </si>
-  <si>
-    <t>135323439</t>
-  </si>
-  <si>
-    <t>135216386</t>
-  </si>
-  <si>
-    <t>135220527</t>
-  </si>
-  <si>
-    <t>135242674</t>
-  </si>
-  <si>
-    <t>132322277</t>
-  </si>
-  <si>
-    <t>135321533</t>
-  </si>
-  <si>
-    <t>135238761</t>
-  </si>
-  <si>
-    <t>135212987</t>
-  </si>
-  <si>
-    <t>131814119</t>
-  </si>
-  <si>
-    <t>132587252</t>
-  </si>
-  <si>
-    <t>135128177</t>
-  </si>
-  <si>
-    <t>135188744</t>
-  </si>
-  <si>
-    <t>135189003</t>
-  </si>
-  <si>
-    <t>135190814</t>
-  </si>
-  <si>
-    <t>135192353</t>
-  </si>
-  <si>
-    <t>135192752</t>
-  </si>
-  <si>
-    <t>135194768</t>
-  </si>
-  <si>
-    <t>135196607</t>
-  </si>
-  <si>
-    <t>135196668</t>
-  </si>
-  <si>
-    <t>135196768</t>
-  </si>
-  <si>
-    <t>135196992</t>
-  </si>
-  <si>
-    <t>135197056</t>
-  </si>
-  <si>
-    <t>135197326</t>
-  </si>
-  <si>
-    <t>135198787</t>
-  </si>
-  <si>
-    <t>135198892</t>
-  </si>
-  <si>
-    <t>135199592</t>
-  </si>
-  <si>
-    <t>135199767</t>
-  </si>
-  <si>
-    <t>135199781</t>
-  </si>
-  <si>
-    <t>135200503</t>
-  </si>
-  <si>
-    <t>135201074</t>
-  </si>
-  <si>
-    <t>135201903</t>
-  </si>
-  <si>
-    <t>135202006</t>
-  </si>
-  <si>
-    <t>135202126</t>
-  </si>
-  <si>
-    <t>135202357</t>
-  </si>
-  <si>
-    <t>135202531</t>
-  </si>
-  <si>
-    <t>135202870</t>
-  </si>
-  <si>
-    <t>135142756</t>
-  </si>
-  <si>
-    <t>135251350</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_10.11.2025</t>
+    <t>Relatório de Recusa Sicredi 11.11.2025</t>
+  </si>
+  <si>
+    <t>135154881</t>
+  </si>
+  <si>
+    <t>135177215</t>
+  </si>
+  <si>
+    <t>135179760</t>
+  </si>
+  <si>
+    <t>135180010</t>
+  </si>
+  <si>
+    <t>135217086</t>
+  </si>
+  <si>
+    <t>135210284</t>
+  </si>
+  <si>
+    <t>135244169</t>
+  </si>
+  <si>
+    <t>135262156</t>
+  </si>
+  <si>
+    <t>135254576</t>
+  </si>
+  <si>
+    <t>135265765</t>
+  </si>
+  <si>
+    <t>135264894</t>
+  </si>
+  <si>
+    <t>135247559</t>
+  </si>
+  <si>
+    <t>135263153</t>
+  </si>
+  <si>
+    <t>135260222</t>
+  </si>
+  <si>
+    <t>135277910</t>
+  </si>
+  <si>
+    <t>135280323</t>
+  </si>
+  <si>
+    <t>135280240</t>
+  </si>
+  <si>
+    <t>135273343</t>
+  </si>
+  <si>
+    <t>135277238</t>
+  </si>
+  <si>
+    <t>135293915</t>
+  </si>
+  <si>
+    <t>135299671</t>
+  </si>
+  <si>
+    <t>135302681</t>
+  </si>
+  <si>
+    <t>135307795</t>
+  </si>
+  <si>
+    <t>135302385</t>
+  </si>
+  <si>
+    <t>135301411</t>
+  </si>
+  <si>
+    <t>135310068</t>
+  </si>
+  <si>
+    <t>135283998</t>
+  </si>
+  <si>
+    <t>135292463</t>
+  </si>
+  <si>
+    <t>135305262</t>
+  </si>
+  <si>
+    <t>135330835</t>
+  </si>
+  <si>
+    <t>135330267</t>
+  </si>
+  <si>
+    <t>135170338</t>
+  </si>
+  <si>
+    <t>135082925</t>
+  </si>
+  <si>
+    <t>135128841</t>
+  </si>
+  <si>
+    <t>135133577</t>
+  </si>
+  <si>
+    <t>135156636</t>
+  </si>
+  <si>
+    <t>135162941</t>
+  </si>
+  <si>
+    <t>135242630</t>
+  </si>
+  <si>
+    <t>135337612</t>
+  </si>
+  <si>
+    <t>135239347</t>
+  </si>
+  <si>
+    <t>135259512</t>
+  </si>
+  <si>
+    <t>135255299</t>
+  </si>
+  <si>
+    <t>132455787</t>
+  </si>
+  <si>
+    <t>135274642</t>
+  </si>
+  <si>
+    <t>134551993</t>
+  </si>
+  <si>
+    <t>135341271</t>
+  </si>
+  <si>
+    <t>135263773</t>
+  </si>
+  <si>
+    <t>135230059</t>
+  </si>
+  <si>
+    <t>135262199</t>
+  </si>
+  <si>
+    <t>135301145</t>
+  </si>
+  <si>
+    <t>135214461</t>
+  </si>
+  <si>
+    <t>135343100</t>
+  </si>
+  <si>
+    <t>135179721</t>
+  </si>
+  <si>
+    <t>135284497</t>
+  </si>
+  <si>
+    <t>135256559</t>
+  </si>
+  <si>
+    <t>135231230</t>
+  </si>
+  <si>
+    <t>132062974</t>
+  </si>
+  <si>
+    <t>134026375</t>
+  </si>
+  <si>
+    <t>135240985</t>
+  </si>
+  <si>
+    <t>135219717</t>
+  </si>
+  <si>
+    <t>135269873</t>
+  </si>
+  <si>
+    <t>135168752</t>
+  </si>
+  <si>
+    <t>135250393</t>
+  </si>
+  <si>
+    <t>135273552</t>
+  </si>
+  <si>
+    <t>133866453</t>
+  </si>
+  <si>
+    <t>135200381</t>
+  </si>
+  <si>
+    <t>135169228</t>
+  </si>
+  <si>
+    <t>135242667</t>
+  </si>
+  <si>
+    <t>135249985</t>
+  </si>
+  <si>
+    <t>135349902</t>
+  </si>
+  <si>
+    <t>135236348</t>
+  </si>
+  <si>
+    <t>135347501</t>
+  </si>
+  <si>
+    <t>135232684</t>
+  </si>
+  <si>
+    <t>135253419</t>
+  </si>
+  <si>
+    <t>135265207</t>
+  </si>
+  <si>
+    <t>135250494</t>
+  </si>
+  <si>
+    <t>135187879</t>
+  </si>
+  <si>
+    <t>135169148</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_11.11.2025</t>
   </si>
 </sst>
 </file>
@@ -672,7 +696,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -704,7 +728,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135185803</v>
+        <v>135160549</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -713,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -731,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -749,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -767,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -785,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -803,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -821,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -839,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -857,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -875,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -893,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -911,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -929,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -947,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -965,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -983,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -1001,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -1019,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1037,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1055,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1073,7 +1097,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1091,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1109,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1127,7 +1151,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1145,7 +1169,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1162,7 +1186,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1179,7 +1203,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1196,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1213,7 +1237,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1230,7 +1254,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1247,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1264,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1281,7 +1305,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1298,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1315,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1332,7 +1356,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1349,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1366,7 +1390,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1383,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1400,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1417,7 +1441,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1434,7 +1458,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1451,7 +1475,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1468,7 +1492,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1485,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1502,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1519,7 +1543,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1536,7 +1560,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1553,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1570,7 +1594,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1587,7 +1611,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1604,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1621,7 +1645,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1638,7 +1662,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1655,7 +1679,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1672,7 +1696,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1689,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1706,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1723,7 +1747,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1740,7 +1764,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
@@ -1757,7 +1781,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>7</v>
@@ -1774,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>7</v>
@@ -1791,7 +1815,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>7</v>
@@ -1808,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>7</v>
@@ -1825,7 +1849,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>7</v>
@@ -1842,7 +1866,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>7</v>
@@ -1859,7 +1883,7 @@
         <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>7</v>
@@ -1876,7 +1900,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>7</v>
@@ -1893,7 +1917,7 @@
         <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>7</v>
@@ -1910,7 +1934,7 @@
         <v>8</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>7</v>
@@ -1927,9 +1951,145 @@
         <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1947,31 +2107,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CAFF68-F294-4995-AFF7-BDB180F7837F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6DA993-D986-4FA5-BF82-FC69FF946181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="72">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,244 +54,196 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 11.11.2025</t>
-  </si>
-  <si>
-    <t>135154881</t>
-  </si>
-  <si>
-    <t>135177215</t>
-  </si>
-  <si>
-    <t>135179760</t>
-  </si>
-  <si>
-    <t>135180010</t>
-  </si>
-  <si>
-    <t>135217086</t>
-  </si>
-  <si>
-    <t>135210284</t>
-  </si>
-  <si>
-    <t>135244169</t>
-  </si>
-  <si>
-    <t>135262156</t>
-  </si>
-  <si>
-    <t>135254576</t>
-  </si>
-  <si>
-    <t>135265765</t>
-  </si>
-  <si>
-    <t>135264894</t>
-  </si>
-  <si>
-    <t>135247559</t>
-  </si>
-  <si>
-    <t>135263153</t>
-  </si>
-  <si>
-    <t>135260222</t>
-  </si>
-  <si>
-    <t>135277910</t>
-  </si>
-  <si>
-    <t>135280323</t>
-  </si>
-  <si>
-    <t>135280240</t>
-  </si>
-  <si>
-    <t>135273343</t>
-  </si>
-  <si>
-    <t>135277238</t>
-  </si>
-  <si>
-    <t>135293915</t>
-  </si>
-  <si>
-    <t>135299671</t>
-  </si>
-  <si>
-    <t>135302681</t>
-  </si>
-  <si>
-    <t>135307795</t>
-  </si>
-  <si>
-    <t>135302385</t>
-  </si>
-  <si>
-    <t>135301411</t>
-  </si>
-  <si>
-    <t>135310068</t>
-  </si>
-  <si>
-    <t>135283998</t>
-  </si>
-  <si>
-    <t>135292463</t>
-  </si>
-  <si>
-    <t>135305262</t>
-  </si>
-  <si>
-    <t>135330835</t>
-  </si>
-  <si>
-    <t>135330267</t>
-  </si>
-  <si>
-    <t>135170338</t>
-  </si>
-  <si>
-    <t>135082925</t>
-  </si>
-  <si>
-    <t>135128841</t>
-  </si>
-  <si>
-    <t>135133577</t>
-  </si>
-  <si>
-    <t>135156636</t>
-  </si>
-  <si>
-    <t>135162941</t>
-  </si>
-  <si>
-    <t>135242630</t>
-  </si>
-  <si>
-    <t>135337612</t>
-  </si>
-  <si>
-    <t>135239347</t>
-  </si>
-  <si>
-    <t>135259512</t>
-  </si>
-  <si>
-    <t>135255299</t>
-  </si>
-  <si>
-    <t>132455787</t>
-  </si>
-  <si>
-    <t>135274642</t>
-  </si>
-  <si>
-    <t>134551993</t>
-  </si>
-  <si>
-    <t>135341271</t>
-  </si>
-  <si>
-    <t>135263773</t>
-  </si>
-  <si>
-    <t>135230059</t>
-  </si>
-  <si>
-    <t>135262199</t>
-  </si>
-  <si>
-    <t>135301145</t>
-  </si>
-  <si>
-    <t>135214461</t>
-  </si>
-  <si>
-    <t>135343100</t>
-  </si>
-  <si>
-    <t>135179721</t>
-  </si>
-  <si>
-    <t>135284497</t>
-  </si>
-  <si>
-    <t>135256559</t>
-  </si>
-  <si>
-    <t>135231230</t>
-  </si>
-  <si>
-    <t>132062974</t>
-  </si>
-  <si>
-    <t>134026375</t>
-  </si>
-  <si>
-    <t>135240985</t>
-  </si>
-  <si>
-    <t>135219717</t>
-  </si>
-  <si>
-    <t>135269873</t>
-  </si>
-  <si>
-    <t>135168752</t>
-  </si>
-  <si>
-    <t>135250393</t>
-  </si>
-  <si>
-    <t>135273552</t>
-  </si>
-  <si>
-    <t>133866453</t>
-  </si>
-  <si>
-    <t>135200381</t>
-  </si>
-  <si>
-    <t>135169228</t>
-  </si>
-  <si>
-    <t>135242667</t>
-  </si>
-  <si>
-    <t>135249985</t>
-  </si>
-  <si>
-    <t>135349902</t>
-  </si>
-  <si>
-    <t>135236348</t>
-  </si>
-  <si>
-    <t>135347501</t>
-  </si>
-  <si>
-    <t>135232684</t>
-  </si>
-  <si>
-    <t>135253419</t>
-  </si>
-  <si>
-    <t>135265207</t>
-  </si>
-  <si>
-    <t>135250494</t>
-  </si>
-  <si>
-    <t>135187879</t>
-  </si>
-  <si>
-    <t>135169148</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_11.11.2025</t>
+    <t>Relatório de Recusa Sicredi 12.11.2025</t>
+  </si>
+  <si>
+    <t>135159447</t>
+  </si>
+  <si>
+    <t>135182159</t>
+  </si>
+  <si>
+    <t>135219695</t>
+  </si>
+  <si>
+    <t>135221464</t>
+  </si>
+  <si>
+    <t>135265035</t>
+  </si>
+  <si>
+    <t>135259371</t>
+  </si>
+  <si>
+    <t>135265194</t>
+  </si>
+  <si>
+    <t>135258374</t>
+  </si>
+  <si>
+    <t>135248049</t>
+  </si>
+  <si>
+    <t>135276675</t>
+  </si>
+  <si>
+    <t>135286829</t>
+  </si>
+  <si>
+    <t>135284082</t>
+  </si>
+  <si>
+    <t>135278335</t>
+  </si>
+  <si>
+    <t>135273212</t>
+  </si>
+  <si>
+    <t>135282326</t>
+  </si>
+  <si>
+    <t>135274615</t>
+  </si>
+  <si>
+    <t>135269218</t>
+  </si>
+  <si>
+    <t>135300425</t>
+  </si>
+  <si>
+    <t>135291039</t>
+  </si>
+  <si>
+    <t>135332280</t>
+  </si>
+  <si>
+    <t>135332217</t>
+  </si>
+  <si>
+    <t>135327335</t>
+  </si>
+  <si>
+    <t>135338982</t>
+  </si>
+  <si>
+    <t>135308275</t>
+  </si>
+  <si>
+    <t>135350687</t>
+  </si>
+  <si>
+    <t>135356166</t>
+  </si>
+  <si>
+    <t>135157589</t>
+  </si>
+  <si>
+    <t>135168242</t>
+  </si>
+  <si>
+    <t>135236855</t>
+  </si>
+  <si>
+    <t>135346821</t>
+  </si>
+  <si>
+    <t>135281676</t>
+  </si>
+  <si>
+    <t>135242903</t>
+  </si>
+  <si>
+    <t>135281904</t>
+  </si>
+  <si>
+    <t>135360380</t>
+  </si>
+  <si>
+    <t>135254425</t>
+  </si>
+  <si>
+    <t>135260014</t>
+  </si>
+  <si>
+    <t>133185706</t>
+  </si>
+  <si>
+    <t>134999783</t>
+  </si>
+  <si>
+    <t>135265775</t>
+  </si>
+  <si>
+    <t>135273629</t>
+  </si>
+  <si>
+    <t>135168517</t>
+  </si>
+  <si>
+    <t>135240579</t>
+  </si>
+  <si>
+    <t>135296123</t>
+  </si>
+  <si>
+    <t>135303916</t>
+  </si>
+  <si>
+    <t>135234525</t>
+  </si>
+  <si>
+    <t>135274771</t>
+  </si>
+  <si>
+    <t>135366800</t>
+  </si>
+  <si>
+    <t>135266107</t>
+  </si>
+  <si>
+    <t>135275425</t>
+  </si>
+  <si>
+    <t>135367614</t>
+  </si>
+  <si>
+    <t>135286226</t>
+  </si>
+  <si>
+    <t>135292796</t>
+  </si>
+  <si>
+    <t>130580410</t>
+  </si>
+  <si>
+    <t>135369578</t>
+  </si>
+  <si>
+    <t>135359954</t>
+  </si>
+  <si>
+    <t>135260315</t>
+  </si>
+  <si>
+    <t>135260753</t>
+  </si>
+  <si>
+    <t>135255034</t>
+  </si>
+  <si>
+    <t>135371833</t>
+  </si>
+  <si>
+    <t>135189767</t>
+  </si>
+  <si>
+    <t>135294322</t>
+  </si>
+  <si>
+    <t>135199896</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_12.11.2025</t>
   </si>
 </sst>
 </file>
@@ -696,7 +648,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -728,7 +680,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135160549</v>
+        <v>135166636</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -737,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -755,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -773,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -791,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -809,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -827,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -845,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -863,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -881,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -899,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -917,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -935,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -953,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -971,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -989,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -1007,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -1025,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -1043,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1061,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1079,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1097,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1115,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1133,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1151,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1169,7 +1121,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1186,7 +1138,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1203,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1220,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1237,7 +1189,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1254,7 +1206,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1271,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1288,7 +1240,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1305,7 +1257,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1322,7 +1274,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1339,7 +1291,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1356,7 +1308,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1373,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1390,7 +1342,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1407,7 +1359,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1424,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1441,7 +1393,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1458,7 +1410,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1475,7 +1427,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1492,7 +1444,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1509,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1526,7 +1478,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1543,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1560,7 +1512,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1577,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1594,7 +1546,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1611,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1628,7 +1580,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1645,7 +1597,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1662,7 +1614,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1679,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1696,7 +1648,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1713,7 +1665,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1730,7 +1682,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1747,7 +1699,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1764,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
@@ -1781,7 +1733,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>7</v>
@@ -1798,7 +1750,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>7</v>
@@ -1815,281 +1767,9 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E80" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2107,31 +1787,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6DA993-D986-4FA5-BF82-FC69FF946181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40771CD-9BAA-426C-9402-C3D2731DA52A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="119">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,24 +57,6 @@
     <t>Relatório de Recusa Sicredi 12.11.2025</t>
   </si>
   <si>
-    <t>135159447</t>
-  </si>
-  <si>
-    <t>135182159</t>
-  </si>
-  <si>
-    <t>135219695</t>
-  </si>
-  <si>
-    <t>135221464</t>
-  </si>
-  <si>
-    <t>135265035</t>
-  </si>
-  <si>
-    <t>135259371</t>
-  </si>
-  <si>
     <t>135265194</t>
   </si>
   <si>
@@ -244,6 +226,165 @@
   </si>
   <si>
     <t>Relatório Recusa _ SICREDI_12.11.2025</t>
+  </si>
+  <si>
+    <t>135218789</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 13/11/2025</t>
+  </si>
+  <si>
+    <t>135259836</t>
+  </si>
+  <si>
+    <t>135257116</t>
+  </si>
+  <si>
+    <t>135201091</t>
+  </si>
+  <si>
+    <t>135283518</t>
+  </si>
+  <si>
+    <t>135284171</t>
+  </si>
+  <si>
+    <t>135286414</t>
+  </si>
+  <si>
+    <t>135293292</t>
+  </si>
+  <si>
+    <t>135304929</t>
+  </si>
+  <si>
+    <t>135307879</t>
+  </si>
+  <si>
+    <t>135308947</t>
+  </si>
+  <si>
+    <t>135294090</t>
+  </si>
+  <si>
+    <t>135296369</t>
+  </si>
+  <si>
+    <t>135308202</t>
+  </si>
+  <si>
+    <t>135303895</t>
+  </si>
+  <si>
+    <t>135252744</t>
+  </si>
+  <si>
+    <t>135332602</t>
+  </si>
+  <si>
+    <t>135359279</t>
+  </si>
+  <si>
+    <t>135359926</t>
+  </si>
+  <si>
+    <t>135366308</t>
+  </si>
+  <si>
+    <t>135368206</t>
+  </si>
+  <si>
+    <t>135368301</t>
+  </si>
+  <si>
+    <t>135362854</t>
+  </si>
+  <si>
+    <t>135358468</t>
+  </si>
+  <si>
+    <t>135180264</t>
+  </si>
+  <si>
+    <t>133470461</t>
+  </si>
+  <si>
+    <t>135381124</t>
+  </si>
+  <si>
+    <t>135260748</t>
+  </si>
+  <si>
+    <t>135298274</t>
+  </si>
+  <si>
+    <t>135291591</t>
+  </si>
+  <si>
+    <t>135262533</t>
+  </si>
+  <si>
+    <t>135238893</t>
+  </si>
+  <si>
+    <t>135170086</t>
+  </si>
+  <si>
+    <t>135273977</t>
+  </si>
+  <si>
+    <t>135293744</t>
+  </si>
+  <si>
+    <t>135281567</t>
+  </si>
+  <si>
+    <t>135278558</t>
+  </si>
+  <si>
+    <t>135231088</t>
+  </si>
+  <si>
+    <t>135242972</t>
+  </si>
+  <si>
+    <t>135276435</t>
+  </si>
+  <si>
+    <t>135293214</t>
+  </si>
+  <si>
+    <t>135385739</t>
+  </si>
+  <si>
+    <t>135262936</t>
+  </si>
+  <si>
+    <t>135258998</t>
+  </si>
+  <si>
+    <t>135273398</t>
+  </si>
+  <si>
+    <t>135382138</t>
+  </si>
+  <si>
+    <t>135276823</t>
+  </si>
+  <si>
+    <t>135219064</t>
+  </si>
+  <si>
+    <t>135268693</t>
+  </si>
+  <si>
+    <t>135306319</t>
+  </si>
+  <si>
+    <t>135391990</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_13.11.2025</t>
   </si>
 </sst>
 </file>
@@ -648,7 +789,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -680,7 +821,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135166636</v>
+        <v>135259371</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -689,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -707,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -725,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -743,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -761,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -779,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -797,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -815,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -833,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -851,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -869,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -887,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -905,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -923,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -941,7 +1082,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -959,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -977,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -995,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1013,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1031,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1049,7 +1190,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1067,7 +1208,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1085,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1103,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1121,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1138,7 +1279,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1155,7 +1296,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1172,7 +1313,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1189,7 +1330,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1206,7 +1347,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1223,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1240,7 +1381,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1257,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1274,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1291,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1308,7 +1449,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1325,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1342,7 +1483,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1359,7 +1500,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1376,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1393,7 +1534,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1410,7 +1551,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1427,7 +1568,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1444,7 +1585,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1461,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1478,7 +1619,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1495,7 +1636,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1512,7 +1653,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1529,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1546,7 +1687,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1563,7 +1704,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1580,7 +1721,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1597,7 +1738,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1614,7 +1755,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1631,7 +1772,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1648,7 +1789,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1665,7 +1806,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1673,16 +1814,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1690,16 +1831,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1707,16 +1848,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
@@ -1724,16 +1865,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>7</v>
@@ -1741,16 +1882,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>7</v>
@@ -1758,18 +1899,783 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>8</v>
+        <v>67</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492F7387-CC16-4D24-87FD-68CCC62796DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F4C543C-AF71-42AB-A50F-7B10EA63047A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24120" yWindow="1770" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26640" yWindow="1725" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="218">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,631 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 15/11/2025</t>
-  </si>
-  <si>
-    <t>135223414</t>
-  </si>
-  <si>
-    <t>135219642</t>
-  </si>
-  <si>
-    <t>135208697</t>
-  </si>
-  <si>
-    <t>135227656</t>
-  </si>
-  <si>
-    <t>135236306</t>
-  </si>
-  <si>
-    <t>135209529</t>
-  </si>
-  <si>
-    <t>135213076</t>
-  </si>
-  <si>
-    <t>135213375</t>
-  </si>
-  <si>
-    <t>135213602</t>
-  </si>
-  <si>
-    <t>135216399</t>
-  </si>
-  <si>
-    <t>135217782</t>
-  </si>
-  <si>
-    <t>135220589</t>
-  </si>
-  <si>
-    <t>135221004</t>
-  </si>
-  <si>
-    <t>135222384</t>
-  </si>
-  <si>
-    <t>135223621</t>
-  </si>
-  <si>
-    <t>135234746</t>
-  </si>
-  <si>
-    <t>135236107</t>
-  </si>
-  <si>
-    <t>135237102</t>
-  </si>
-  <si>
-    <t>135238048</t>
-  </si>
-  <si>
-    <t>131506326</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_15.11.2025</t>
-  </si>
-  <si>
-    <t>135215624</t>
+    <t>Recusas Sicredi 17/11/2025</t>
+  </si>
+  <si>
+    <t>133040728</t>
+  </si>
+  <si>
+    <t>133666271</t>
+  </si>
+  <si>
+    <t>135223403</t>
+  </si>
+  <si>
+    <t>135254420</t>
+  </si>
+  <si>
+    <t>135250604</t>
+  </si>
+  <si>
+    <t>135248020</t>
+  </si>
+  <si>
+    <t>135248739</t>
+  </si>
+  <si>
+    <t>135276263</t>
+  </si>
+  <si>
+    <t>135279473</t>
+  </si>
+  <si>
+    <t>135287238</t>
+  </si>
+  <si>
+    <t>135285004</t>
+  </si>
+  <si>
+    <t>135285667</t>
+  </si>
+  <si>
+    <t>135290975</t>
+  </si>
+  <si>
+    <t>135311007</t>
+  </si>
+  <si>
+    <t>135295161</t>
+  </si>
+  <si>
+    <t>135322533</t>
+  </si>
+  <si>
+    <t>135322062</t>
+  </si>
+  <si>
+    <t>135326734</t>
+  </si>
+  <si>
+    <t>135329053</t>
+  </si>
+  <si>
+    <t>135296314</t>
+  </si>
+  <si>
+    <t>135323740</t>
+  </si>
+  <si>
+    <t>135349015</t>
+  </si>
+  <si>
+    <t>135352531</t>
+  </si>
+  <si>
+    <t>135346066</t>
+  </si>
+  <si>
+    <t>135306564</t>
+  </si>
+  <si>
+    <t>135351883</t>
+  </si>
+  <si>
+    <t>135330086</t>
+  </si>
+  <si>
+    <t>132035683</t>
+  </si>
+  <si>
+    <t>135344832</t>
+  </si>
+  <si>
+    <t>135368535</t>
+  </si>
+  <si>
+    <t>135356635</t>
+  </si>
+  <si>
+    <t>135357533</t>
+  </si>
+  <si>
+    <t>135352428</t>
+  </si>
+  <si>
+    <t>135387434</t>
+  </si>
+  <si>
+    <t>135388166</t>
+  </si>
+  <si>
+    <t>135378415</t>
+  </si>
+  <si>
+    <t>135307219</t>
+  </si>
+  <si>
+    <t>135411319</t>
+  </si>
+  <si>
+    <t>135263798</t>
+  </si>
+  <si>
+    <t>135410379</t>
+  </si>
+  <si>
+    <t>135402014</t>
+  </si>
+  <si>
+    <t>135408419</t>
+  </si>
+  <si>
+    <t>135233761</t>
+  </si>
+  <si>
+    <t>135220016</t>
+  </si>
+  <si>
+    <t>135348375</t>
+  </si>
+  <si>
+    <t>133208144</t>
+  </si>
+  <si>
+    <t>135241379</t>
+  </si>
+  <si>
+    <t>133140726</t>
+  </si>
+  <si>
+    <t>135241387</t>
+  </si>
+  <si>
+    <t>135284067</t>
+  </si>
+  <si>
+    <t>135241701</t>
+  </si>
+  <si>
+    <t>135309276</t>
+  </si>
+  <si>
+    <t>135316479</t>
+  </si>
+  <si>
+    <t>135242838</t>
+  </si>
+  <si>
+    <t>135233315</t>
+  </si>
+  <si>
+    <t>135426209</t>
+  </si>
+  <si>
+    <t>135426029</t>
+  </si>
+  <si>
+    <t>135280248</t>
+  </si>
+  <si>
+    <t>135230543</t>
+  </si>
+  <si>
+    <t>135231253</t>
+  </si>
+  <si>
+    <t>135424635</t>
+  </si>
+  <si>
+    <t>135238253</t>
+  </si>
+  <si>
+    <t>135239073</t>
+  </si>
+  <si>
+    <t>135129673</t>
+  </si>
+  <si>
+    <t>135332896</t>
+  </si>
+  <si>
+    <t>135298608</t>
+  </si>
+  <si>
+    <t>135428111</t>
+  </si>
+  <si>
+    <t>135351428</t>
+  </si>
+  <si>
+    <t>135285779</t>
+  </si>
+  <si>
+    <t>135352415</t>
+  </si>
+  <si>
+    <t>135257611</t>
+  </si>
+  <si>
+    <t>135260111</t>
+  </si>
+  <si>
+    <t>135350646</t>
+  </si>
+  <si>
+    <t>135260506</t>
+  </si>
+  <si>
+    <t>135431145</t>
+  </si>
+  <si>
+    <t>135431294</t>
+  </si>
+  <si>
+    <t>135422641</t>
+  </si>
+  <si>
+    <t>131210989</t>
+  </si>
+  <si>
+    <t>132733171</t>
+  </si>
+  <si>
+    <t>135387752</t>
+  </si>
+  <si>
+    <t>133467883</t>
+  </si>
+  <si>
+    <t>133609393</t>
+  </si>
+  <si>
+    <t>135248503</t>
+  </si>
+  <si>
+    <t>135250771</t>
+  </si>
+  <si>
+    <t>135258264</t>
+  </si>
+  <si>
+    <t>135260698</t>
+  </si>
+  <si>
+    <t>135262204</t>
+  </si>
+  <si>
+    <t>135263032</t>
+  </si>
+  <si>
+    <t>135264896</t>
+  </si>
+  <si>
+    <t>135265402</t>
+  </si>
+  <si>
+    <t>135274979</t>
+  </si>
+  <si>
+    <t>135269176</t>
+  </si>
+  <si>
+    <t>135269357</t>
+  </si>
+  <si>
+    <t>135270449</t>
+  </si>
+  <si>
+    <t>135273610</t>
+  </si>
+  <si>
+    <t>135271755</t>
+  </si>
+  <si>
+    <t>135273221</t>
+  </si>
+  <si>
+    <t>135279476</t>
+  </si>
+  <si>
+    <t>135279912</t>
+  </si>
+  <si>
+    <t>135281237</t>
+  </si>
+  <si>
+    <t>135281890</t>
+  </si>
+  <si>
+    <t>135282036</t>
+  </si>
+  <si>
+    <t>135282492</t>
+  </si>
+  <si>
+    <t>135282844</t>
+  </si>
+  <si>
+    <t>135285394</t>
+  </si>
+  <si>
+    <t>135285800</t>
+  </si>
+  <si>
+    <t>135292805</t>
+  </si>
+  <si>
+    <t>135293629</t>
+  </si>
+  <si>
+    <t>135293702</t>
+  </si>
+  <si>
+    <t>135294951</t>
+  </si>
+  <si>
+    <t>135295522</t>
+  </si>
+  <si>
+    <t>135298097</t>
+  </si>
+  <si>
+    <t>135298396</t>
+  </si>
+  <si>
+    <t>135299381</t>
+  </si>
+  <si>
+    <t>135301398</t>
+  </si>
+  <si>
+    <t>135301945</t>
+  </si>
+  <si>
+    <t>135302360</t>
+  </si>
+  <si>
+    <t>135302757</t>
+  </si>
+  <si>
+    <t>135302761</t>
+  </si>
+  <si>
+    <t>135303979</t>
+  </si>
+  <si>
+    <t>135304883</t>
+  </si>
+  <si>
+    <t>135305594</t>
+  </si>
+  <si>
+    <t>135306819</t>
+  </si>
+  <si>
+    <t>135306908</t>
+  </si>
+  <si>
+    <t>135307477</t>
+  </si>
+  <si>
+    <t>135307521</t>
+  </si>
+  <si>
+    <t>135307603</t>
+  </si>
+  <si>
+    <t>135307759</t>
+  </si>
+  <si>
+    <t>135367099</t>
+  </si>
+  <si>
+    <t>135308252</t>
+  </si>
+  <si>
+    <t>135308315</t>
+  </si>
+  <si>
+    <t>135309650</t>
+  </si>
+  <si>
+    <t>135310242</t>
+  </si>
+  <si>
+    <t>135310400</t>
+  </si>
+  <si>
+    <t>135310807</t>
+  </si>
+  <si>
+    <t>135320339</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_17.11.2025</t>
+  </si>
+  <si>
+    <t>135221510</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 14/11/2025</t>
+  </si>
+  <si>
+    <t>135263800</t>
+  </si>
+  <si>
+    <t>135287207</t>
+  </si>
+  <si>
+    <t>135281063</t>
+  </si>
+  <si>
+    <t>135282367</t>
+  </si>
+  <si>
+    <t>135293095</t>
+  </si>
+  <si>
+    <t>135262233</t>
+  </si>
+  <si>
+    <t>131080088</t>
+  </si>
+  <si>
+    <t>135330565</t>
+  </si>
+  <si>
+    <t>135325691</t>
+  </si>
+  <si>
+    <t>135319962</t>
+  </si>
+  <si>
+    <t>135321443</t>
+  </si>
+  <si>
+    <t>135323320</t>
+  </si>
+  <si>
+    <t>135321250</t>
+  </si>
+  <si>
+    <t>135323047</t>
+  </si>
+  <si>
+    <t>135333394</t>
+  </si>
+  <si>
+    <t>135316045</t>
+  </si>
+  <si>
+    <t>135300342</t>
+  </si>
+  <si>
+    <t>135308037</t>
+  </si>
+  <si>
+    <t>135300192</t>
+  </si>
+  <si>
+    <t>135350435</t>
+  </si>
+  <si>
+    <t>135345296</t>
+  </si>
+  <si>
+    <t>135331405</t>
+  </si>
+  <si>
+    <t>135365432</t>
+  </si>
+  <si>
+    <t>135367671</t>
+  </si>
+  <si>
+    <t>135377037</t>
+  </si>
+  <si>
+    <t>135380112</t>
+  </si>
+  <si>
+    <t>135382360</t>
+  </si>
+  <si>
+    <t>135290629</t>
+  </si>
+  <si>
+    <t>135391601</t>
+  </si>
+  <si>
+    <t>135388823</t>
+  </si>
+  <si>
+    <t>135197451</t>
+  </si>
+  <si>
+    <t>135204216</t>
+  </si>
+  <si>
+    <t>135196907</t>
+  </si>
+  <si>
+    <t>135398027</t>
+  </si>
+  <si>
+    <t>135395880</t>
+  </si>
+  <si>
+    <t>135309279</t>
+  </si>
+  <si>
+    <t>132444484</t>
+  </si>
+  <si>
+    <t>135212284</t>
+  </si>
+  <si>
+    <t>135212304</t>
+  </si>
+  <si>
+    <t>135212771</t>
+  </si>
+  <si>
+    <t>135398869</t>
+  </si>
+  <si>
+    <t>135280741</t>
+  </si>
+  <si>
+    <t>135399604</t>
+  </si>
+  <si>
+    <t>135309586</t>
+  </si>
+  <si>
+    <t>135400515</t>
+  </si>
+  <si>
+    <t>135398238</t>
+  </si>
+  <si>
+    <t>135218134</t>
+  </si>
+  <si>
+    <t>135221567</t>
+  </si>
+  <si>
+    <t>135402656</t>
+  </si>
+  <si>
+    <t>135230036</t>
+  </si>
+  <si>
+    <t>135366618</t>
+  </si>
+  <si>
+    <t>135254531</t>
+  </si>
+  <si>
+    <t>135284046</t>
+  </si>
+  <si>
+    <t>135341800</t>
+  </si>
+  <si>
+    <t>135257127</t>
+  </si>
+  <si>
+    <t>135300111</t>
+  </si>
+  <si>
+    <t>135406440</t>
+  </si>
+  <si>
+    <t>135302389</t>
+  </si>
+  <si>
+    <t>135408322</t>
+  </si>
+  <si>
+    <t>135262676</t>
+  </si>
+  <si>
+    <t>135305579</t>
+  </si>
+  <si>
+    <t>135326308</t>
+  </si>
+  <si>
+    <t>135323049</t>
+  </si>
+  <si>
+    <t>135332271</t>
+  </si>
+  <si>
+    <t>135309477</t>
+  </si>
+  <si>
+    <t>135283214</t>
+  </si>
+  <si>
+    <t>135411477</t>
+  </si>
+  <si>
+    <t>135279658</t>
+  </si>
+  <si>
+    <t>135305825</t>
   </si>
   <si>
     <t>Relatório Recusa _ SICREDI_14.11.2025</t>
@@ -528,7 +1086,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F208"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -560,7 +1118,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135215624</v>
+        <v>130654291</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -569,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -587,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -605,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -623,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -641,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -659,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -677,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -695,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -713,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -731,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -749,7 +1307,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -767,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -785,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -803,7 +1361,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -821,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -839,7 +1397,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -857,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -875,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -893,7 +1451,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -911,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -929,7 +1487,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -938,7 +1496,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
@@ -947,7 +1505,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -955,7 +1513,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
@@ -964,7 +1522,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -972,7 +1530,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
@@ -981,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -989,7 +1547,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
@@ -998,7 +1556,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1006,7 +1564,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
@@ -1015,7 +1573,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1023,7 +1581,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
@@ -1032,7 +1590,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1040,7 +1598,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
@@ -1049,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1057,7 +1615,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
@@ -1066,7 +1624,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1074,7 +1632,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
@@ -1083,7 +1641,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1091,7 +1649,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
@@ -1100,7 +1658,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1108,7 +1666,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
@@ -1117,7 +1675,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1125,7 +1683,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
@@ -1134,7 +1692,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1142,7 +1700,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
@@ -1151,7 +1709,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1159,7 +1717,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
@@ -1168,7 +1726,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1176,7 +1734,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
@@ -1185,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1193,7 +1751,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
@@ -1202,7 +1760,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1210,7 +1768,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
@@ -1219,7 +1777,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1227,7 +1785,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
@@ -1236,7 +1794,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1244,7 +1802,7 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
@@ -1253,7 +1811,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1261,7 +1819,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
@@ -1270,7 +1828,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1278,7 +1836,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>6</v>
@@ -1287,9 +1845,2814 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E208" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B367AE67-C427-49EF-AB4D-ED1641AE1AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56618E84-371D-4F92-B1D0-A5FDF2F130F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="70">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>135408514</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -686,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -704,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -722,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -740,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -758,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -776,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -794,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -812,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -830,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -848,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -866,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -884,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -902,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -920,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -938,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -956,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -974,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -992,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1010,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1028,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1046,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1064,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1081,7 +1078,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1098,7 +1095,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1115,7 +1112,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1132,7 +1129,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1149,7 +1146,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1166,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1183,7 +1180,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1200,7 +1197,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1217,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1234,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1251,7 +1248,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1268,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1285,7 +1282,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1302,7 +1299,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1319,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1336,7 +1333,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1353,7 +1350,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1370,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1387,7 +1384,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1404,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1421,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1438,7 +1435,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1455,7 +1452,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1472,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1489,7 +1486,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1506,7 +1503,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1523,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1540,7 +1537,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1557,7 +1554,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1574,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1591,7 +1588,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1608,7 +1605,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1625,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1642,7 +1639,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1659,7 +1656,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1676,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1693,7 +1690,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1710,7 +1707,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
@@ -1727,7 +1724,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>7</v>
@@ -1744,7 +1741,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>7</v>
@@ -1764,31 +1761,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56618E84-371D-4F92-B1D0-A5FDF2F130F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA72666E-D7A5-48C7-A0E9-BAC1629F0F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1761,31 +1761,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA72666E-D7A5-48C7-A0E9-BAC1629F0F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EC937E-4B42-43AC-9B9C-74D88A4AA9A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="71">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>135408514</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_18.11.2025</t>
   </si>
 </sst>
 </file>
@@ -683,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -701,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -719,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -737,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -755,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -773,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -791,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -809,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -827,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -845,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -863,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -881,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -899,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -917,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -935,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -953,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -971,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -989,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1007,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1025,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1043,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1061,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1078,7 +1081,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1095,7 +1098,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1112,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1129,7 +1132,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1146,7 +1149,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1163,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1180,7 +1183,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1197,7 +1200,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1214,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1231,7 +1234,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1248,7 +1251,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1265,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1282,7 +1285,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1299,7 +1302,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1316,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1333,7 +1336,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1350,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1367,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1384,7 +1387,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1401,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1418,7 +1421,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1435,7 +1438,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1452,7 +1455,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1469,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1486,7 +1489,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1503,7 +1506,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1520,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1537,7 +1540,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1554,7 +1557,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1571,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1588,7 +1591,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1605,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1622,7 +1625,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1639,7 +1642,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1656,7 +1659,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1673,7 +1676,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1690,7 +1693,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1707,7 +1710,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
@@ -1724,7 +1727,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>7</v>
@@ -1741,7 +1744,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>7</v>
@@ -1761,31 +1764,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E37AB9-FD30-47BD-816F-A343DAE2B3CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E720FED-F708-4CBA-8F40-C6A9301C3122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="190">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,49 +54,550 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 20/11/2025</t>
-  </si>
-  <si>
-    <t>135394861</t>
-  </si>
-  <si>
-    <t>135401611</t>
-  </si>
-  <si>
-    <t>135408773</t>
-  </si>
-  <si>
-    <t>135421139</t>
-  </si>
-  <si>
-    <t>135302337</t>
-  </si>
-  <si>
-    <t>135277538</t>
-  </si>
-  <si>
-    <t>135280631</t>
-  </si>
-  <si>
-    <t>135378019</t>
-  </si>
-  <si>
-    <t>135379478</t>
-  </si>
-  <si>
-    <t>135382408</t>
-  </si>
-  <si>
-    <t>135387536</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_20.11.2025</t>
-  </si>
-  <si>
-    <t>135283779</t>
-  </si>
-  <si>
     <t>Relatório Recusa _ SICREDI_19.11.2025</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 19/11/2025</t>
+  </si>
+  <si>
+    <t>135264631</t>
+  </si>
+  <si>
+    <t>135280090</t>
+  </si>
+  <si>
+    <t>135291193</t>
+  </si>
+  <si>
+    <t>135307071</t>
+  </si>
+  <si>
+    <t>135330580</t>
+  </si>
+  <si>
+    <t>135330582</t>
+  </si>
+  <si>
+    <t>135332148</t>
+  </si>
+  <si>
+    <t>135331339</t>
+  </si>
+  <si>
+    <t>135349493</t>
+  </si>
+  <si>
+    <t>135357177</t>
+  </si>
+  <si>
+    <t>135370370</t>
+  </si>
+  <si>
+    <t>135261416</t>
+  </si>
+  <si>
+    <t>135264026</t>
+  </si>
+  <si>
+    <t>135386666</t>
+  </si>
+  <si>
+    <t>135240382</t>
+  </si>
+  <si>
+    <t>135381141</t>
+  </si>
+  <si>
+    <t>135387325</t>
+  </si>
+  <si>
+    <t>135398001</t>
+  </si>
+  <si>
+    <t>135406652</t>
+  </si>
+  <si>
+    <t>135399966</t>
+  </si>
+  <si>
+    <t>135412391</t>
+  </si>
+  <si>
+    <t>135299325</t>
+  </si>
+  <si>
+    <t>135429752</t>
+  </si>
+  <si>
+    <t>135445024</t>
+  </si>
+  <si>
+    <t>135429152</t>
+  </si>
+  <si>
+    <t>135398893</t>
+  </si>
+  <si>
+    <t>135452188</t>
+  </si>
+  <si>
+    <t>135444616</t>
+  </si>
+  <si>
+    <t>135200314</t>
+  </si>
+  <si>
+    <t>135248482</t>
+  </si>
+  <si>
+    <t>135252755</t>
+  </si>
+  <si>
+    <t>135263551</t>
+  </si>
+  <si>
+    <t>135262267</t>
+  </si>
+  <si>
+    <t>135282974</t>
+  </si>
+  <si>
+    <t>135263830</t>
+  </si>
+  <si>
+    <t>132455787</t>
+  </si>
+  <si>
+    <t>135275162</t>
+  </si>
+  <si>
+    <t>135279014</t>
+  </si>
+  <si>
+    <t>135389528</t>
+  </si>
+  <si>
+    <t>135325655</t>
+  </si>
+  <si>
+    <t>135273046</t>
+  </si>
+  <si>
+    <t>135337440</t>
+  </si>
+  <si>
+    <t>135464005</t>
+  </si>
+  <si>
+    <t>135363014</t>
+  </si>
+  <si>
+    <t>135467389</t>
+  </si>
+  <si>
+    <t>135362476</t>
+  </si>
+  <si>
+    <t>135292592</t>
+  </si>
+  <si>
+    <t>135326754</t>
+  </si>
+  <si>
+    <t>135305574</t>
+  </si>
+  <si>
+    <t>135249049</t>
+  </si>
+  <si>
+    <t>135290483</t>
+  </si>
+  <si>
+    <t>131497615</t>
+  </si>
+  <si>
+    <t>135295124</t>
+  </si>
+  <si>
+    <t>135390017</t>
+  </si>
+  <si>
+    <t>135296507</t>
+  </si>
+  <si>
+    <t>135470208</t>
+  </si>
+  <si>
+    <t>135299693</t>
+  </si>
+  <si>
+    <t>135359394</t>
+  </si>
+  <si>
+    <t>135473466</t>
+  </si>
+  <si>
+    <t>135474529</t>
+  </si>
+  <si>
+    <t>135469935</t>
+  </si>
+  <si>
+    <t>135346680</t>
+  </si>
+  <si>
+    <t>133809902</t>
+  </si>
+  <si>
+    <t>135361483</t>
+  </si>
+  <si>
+    <t>134890224</t>
+  </si>
+  <si>
+    <t>134971789</t>
+  </si>
+  <si>
+    <t>135317381</t>
+  </si>
+  <si>
+    <t>135318439</t>
+  </si>
+  <si>
+    <t>135319060</t>
+  </si>
+  <si>
+    <t>135319682</t>
+  </si>
+  <si>
+    <t>135319890</t>
+  </si>
+  <si>
+    <t>135320195</t>
+  </si>
+  <si>
+    <t>135323203</t>
+  </si>
+  <si>
+    <t>135325412</t>
+  </si>
+  <si>
+    <t>135325452</t>
+  </si>
+  <si>
+    <t>135326162</t>
+  </si>
+  <si>
+    <t>135327777</t>
+  </si>
+  <si>
+    <t>135328326</t>
+  </si>
+  <si>
+    <t>135329897</t>
+  </si>
+  <si>
+    <t>135330231</t>
+  </si>
+  <si>
+    <t>135251441</t>
+  </si>
+  <si>
+    <t>135261592</t>
+  </si>
+  <si>
+    <t>135356731</t>
+  </si>
+  <si>
+    <t>135357016</t>
+  </si>
+  <si>
+    <t>135359775</t>
+  </si>
+  <si>
+    <t>135360161</t>
+  </si>
+  <si>
+    <t>135361505</t>
+  </si>
+  <si>
+    <t>135363195</t>
+  </si>
+  <si>
+    <t>135365868</t>
+  </si>
+  <si>
+    <t>135366173</t>
+  </si>
+  <si>
+    <t>135367588</t>
+  </si>
+  <si>
+    <t>135368577</t>
+  </si>
+  <si>
+    <t>135370788</t>
+  </si>
+  <si>
+    <t>135289681</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 22/11/2025</t>
+  </si>
+  <si>
+    <t>135329597</t>
+  </si>
+  <si>
+    <t>135352154</t>
+  </si>
+  <si>
+    <t>135345732</t>
+  </si>
+  <si>
+    <t>135293984</t>
+  </si>
+  <si>
+    <t>135290595</t>
+  </si>
+  <si>
+    <t>135321504</t>
+  </si>
+  <si>
+    <t>135323846</t>
+  </si>
+  <si>
+    <t>135329451</t>
+  </si>
+  <si>
+    <t>135337016</t>
+  </si>
+  <si>
+    <t>135338063</t>
+  </si>
+  <si>
+    <t>135340148</t>
+  </si>
+  <si>
+    <t>135342318</t>
+  </si>
+  <si>
+    <t>135342435</t>
+  </si>
+  <si>
+    <t>135346928</t>
+  </si>
+  <si>
+    <t>135350364</t>
+  </si>
+  <si>
+    <t>135296950</t>
+  </si>
+  <si>
+    <t>135303544</t>
+  </si>
+  <si>
+    <t>133470461</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.11.2025</t>
+  </si>
+  <si>
+    <t>135348691</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 21/11/2025</t>
+  </si>
+  <si>
+    <t>135366278</t>
+  </si>
+  <si>
+    <t>135381734</t>
+  </si>
+  <si>
+    <t>135390438</t>
+  </si>
+  <si>
+    <t>135390054</t>
+  </si>
+  <si>
+    <t>131966018</t>
+  </si>
+  <si>
+    <t>135391409</t>
+  </si>
+  <si>
+    <t>135401134</t>
+  </si>
+  <si>
+    <t>135424994</t>
+  </si>
+  <si>
+    <t>135427272</t>
+  </si>
+  <si>
+    <t>135422446</t>
+  </si>
+  <si>
+    <t>135427946</t>
+  </si>
+  <si>
+    <t>135417548</t>
+  </si>
+  <si>
+    <t>135430623</t>
+  </si>
+  <si>
+    <t>135433109</t>
+  </si>
+  <si>
+    <t>135436596</t>
+  </si>
+  <si>
+    <t>135382932</t>
+  </si>
+  <si>
+    <t>135444488</t>
+  </si>
+  <si>
+    <t>135444047</t>
+  </si>
+  <si>
+    <t>135437039</t>
+  </si>
+  <si>
+    <t>135431661</t>
+  </si>
+  <si>
+    <t>135474238</t>
+  </si>
+  <si>
+    <t>135477553</t>
+  </si>
+  <si>
+    <t>135292373</t>
+  </si>
+  <si>
+    <t>135303459</t>
+  </si>
+  <si>
+    <t>135303908</t>
+  </si>
+  <si>
+    <t>135307352</t>
+  </si>
+  <si>
+    <t>135324171</t>
+  </si>
+  <si>
+    <t>135326064</t>
+  </si>
+  <si>
+    <t>135323596</t>
+  </si>
+  <si>
+    <t>135330778</t>
+  </si>
+  <si>
+    <t>135347437</t>
+  </si>
+  <si>
+    <t>135408532</t>
+  </si>
+  <si>
+    <t>133391139</t>
+  </si>
+  <si>
+    <t>135342058</t>
+  </si>
+  <si>
+    <t>135348223</t>
+  </si>
+  <si>
+    <t>135350142</t>
+  </si>
+  <si>
+    <t>135351206</t>
+  </si>
+  <si>
+    <t>135351740</t>
+  </si>
+  <si>
+    <t>135485855</t>
+  </si>
+  <si>
+    <t>135348333</t>
+  </si>
+  <si>
+    <t>135486363</t>
+  </si>
+  <si>
+    <t>135381190</t>
+  </si>
+  <si>
+    <t>131240727</t>
+  </si>
+  <si>
+    <t>135428952</t>
+  </si>
+  <si>
+    <t>135320365</t>
+  </si>
+  <si>
+    <t>135494523</t>
+  </si>
+  <si>
+    <t>135388178</t>
+  </si>
+  <si>
+    <t>132035683</t>
+  </si>
+  <si>
+    <t>135374899</t>
+  </si>
+  <si>
+    <t>135379654</t>
+  </si>
+  <si>
+    <t>131693659</t>
+  </si>
+  <si>
+    <t>135380760</t>
+  </si>
+  <si>
+    <t>135496252</t>
+  </si>
+  <si>
+    <t>135385731</t>
+  </si>
+  <si>
+    <t>135402227</t>
+  </si>
+  <si>
+    <t>135387044</t>
+  </si>
+  <si>
+    <t>135310791</t>
+  </si>
+  <si>
+    <t>132124895</t>
+  </si>
+  <si>
+    <t>134012141</t>
+  </si>
+  <si>
+    <t>135390106</t>
+  </si>
+  <si>
+    <t>135391092</t>
+  </si>
+  <si>
+    <t>135395973</t>
+  </si>
+  <si>
+    <t>135501017</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_21.11.2025</t>
   </si>
 </sst>
 </file>
@@ -501,8 +1002,8 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F180"/>
+  <sheetFormatPr defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
     <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
@@ -533,16 +1034,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135283779</v>
+        <v>135263886</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -551,16 +1052,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -569,16 +1070,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -587,16 +1088,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -605,16 +1106,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -623,16 +1124,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -641,16 +1142,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -659,16 +1160,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -677,16 +1178,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -695,16 +1196,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -713,16 +1214,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -731,16 +1232,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -755,10 +1256,10 @@
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -766,16 +1267,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -783,16 +1284,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -800,16 +1301,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -817,16 +1318,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -834,16 +1335,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -851,16 +1352,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -868,16 +1369,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -885,16 +1386,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -902,16 +1403,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -919,16 +1420,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -936,19 +1437,2630 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D179" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D180" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -965,31 +4077,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554D1BE0-81FF-4576-B10B-79193D96618D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6415AA80-7252-4099-8D93-65A346702965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21270" yWindow="780" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="69">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,202 +54,187 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>131240727</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_21.11.2025</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 24/11/2025</t>
-  </si>
-  <si>
-    <t>133016532</t>
-  </si>
-  <si>
-    <t>135346293</t>
-  </si>
-  <si>
-    <t>135357000</t>
-  </si>
-  <si>
-    <t>135389669</t>
-  </si>
-  <si>
-    <t>135377330</t>
-  </si>
-  <si>
-    <t>135385192</t>
-  </si>
-  <si>
-    <t>135410012</t>
-  </si>
-  <si>
-    <t>135394950</t>
-  </si>
-  <si>
-    <t>135406244</t>
-  </si>
-  <si>
-    <t>135409035</t>
-  </si>
-  <si>
-    <t>135454857</t>
-  </si>
-  <si>
-    <t>135446922</t>
-  </si>
-  <si>
-    <t>135442949</t>
-  </si>
-  <si>
-    <t>135460789</t>
-  </si>
-  <si>
-    <t>135490576</t>
-  </si>
-  <si>
-    <t>135489600</t>
-  </si>
-  <si>
-    <t>135488404</t>
-  </si>
-  <si>
-    <t>135496203</t>
-  </si>
-  <si>
-    <t>135499710</t>
-  </si>
-  <si>
-    <t>135473459</t>
-  </si>
-  <si>
-    <t>135495807</t>
-  </si>
-  <si>
-    <t>135491171</t>
-  </si>
-  <si>
-    <t>135500390</t>
-  </si>
-  <si>
-    <t>135505759</t>
-  </si>
-  <si>
-    <t>135350511</t>
-  </si>
-  <si>
-    <t>135426603</t>
-  </si>
-  <si>
-    <t>135453066</t>
-  </si>
-  <si>
-    <t>135300755</t>
-  </si>
-  <si>
-    <t>135513038</t>
-  </si>
-  <si>
-    <t>135444007</t>
-  </si>
-  <si>
-    <t>135397713</t>
-  </si>
-  <si>
-    <t>133139710</t>
-  </si>
-  <si>
-    <t>135515903</t>
-  </si>
-  <si>
-    <t>135516971</t>
-  </si>
-  <si>
-    <t>135449425</t>
-  </si>
-  <si>
-    <t>135332095</t>
-  </si>
-  <si>
-    <t>135340852</t>
-  </si>
-  <si>
-    <t>135446779</t>
-  </si>
-  <si>
-    <t>135428970</t>
-  </si>
-  <si>
-    <t>135519444</t>
-  </si>
-  <si>
-    <t>132062974</t>
-  </si>
-  <si>
-    <t>135519913</t>
-  </si>
-  <si>
-    <t>135425898</t>
-  </si>
-  <si>
-    <t>135461741</t>
-  </si>
-  <si>
-    <t>135349899</t>
-  </si>
-  <si>
-    <t>135352465</t>
-  </si>
-  <si>
-    <t>135522139</t>
-  </si>
-  <si>
-    <t>135395052</t>
-  </si>
-  <si>
-    <t>135399053</t>
-  </si>
-  <si>
-    <t>135399898</t>
-  </si>
-  <si>
-    <t>135400020</t>
-  </si>
-  <si>
-    <t>135400785</t>
-  </si>
-  <si>
-    <t>135402383</t>
-  </si>
-  <si>
-    <t>135408845</t>
-  </si>
-  <si>
-    <t>135409107</t>
-  </si>
-  <si>
-    <t>135405264</t>
-  </si>
-  <si>
-    <t>135405326</t>
-  </si>
-  <si>
-    <t>135405522</t>
-  </si>
-  <si>
-    <t>135407334</t>
-  </si>
-  <si>
-    <t>135407825</t>
-  </si>
-  <si>
-    <t>135408156</t>
-  </si>
-  <si>
-    <t>135411731</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_24.11.2025</t>
+    <t>Recusas Sicredi 25/11/2025</t>
+  </si>
+  <si>
+    <t>135391105</t>
+  </si>
+  <si>
+    <t>135387657</t>
+  </si>
+  <si>
+    <t>135425887</t>
+  </si>
+  <si>
+    <t>135431765</t>
+  </si>
+  <si>
+    <t>135441456</t>
+  </si>
+  <si>
+    <t>135449921</t>
+  </si>
+  <si>
+    <t>135454426</t>
+  </si>
+  <si>
+    <t>135438723</t>
+  </si>
+  <si>
+    <t>135440349</t>
+  </si>
+  <si>
+    <t>135450121</t>
+  </si>
+  <si>
+    <t>135395930</t>
+  </si>
+  <si>
+    <t>135467452</t>
+  </si>
+  <si>
+    <t>135494203</t>
+  </si>
+  <si>
+    <t>135487552</t>
+  </si>
+  <si>
+    <t>135489024</t>
+  </si>
+  <si>
+    <t>135505297</t>
+  </si>
+  <si>
+    <t>135348651</t>
+  </si>
+  <si>
+    <t>135464451</t>
+  </si>
+  <si>
+    <t>135519975</t>
+  </si>
+  <si>
+    <t>135522669</t>
+  </si>
+  <si>
+    <t>135524692</t>
+  </si>
+  <si>
+    <t>135523918</t>
+  </si>
+  <si>
+    <t>135523686</t>
+  </si>
+  <si>
+    <t>135327396</t>
+  </si>
+  <si>
+    <t>135364158</t>
+  </si>
+  <si>
+    <t>135367410</t>
+  </si>
+  <si>
+    <t>135402399</t>
+  </si>
+  <si>
+    <t>135403681</t>
+  </si>
+  <si>
+    <t>135466334</t>
+  </si>
+  <si>
+    <t>135464235</t>
+  </si>
+  <si>
+    <t>135368246</t>
+  </si>
+  <si>
+    <t>135530500</t>
+  </si>
+  <si>
+    <t>135433461</t>
+  </si>
+  <si>
+    <t>135365536</t>
+  </si>
+  <si>
+    <t>135389011</t>
+  </si>
+  <si>
+    <t>135418704</t>
+  </si>
+  <si>
+    <t>135532533</t>
+  </si>
+  <si>
+    <t>135533450</t>
+  </si>
+  <si>
+    <t>135447364</t>
+  </si>
+  <si>
+    <t>135461257</t>
+  </si>
+  <si>
+    <t>135441260</t>
+  </si>
+  <si>
+    <t>135458838</t>
+  </si>
+  <si>
+    <t>135447066</t>
+  </si>
+  <si>
+    <t>135443405</t>
+  </si>
+  <si>
+    <t>135539129</t>
+  </si>
+  <si>
+    <t>135540952</t>
+  </si>
+  <si>
+    <t>135440653</t>
+  </si>
+  <si>
+    <t>135478386</t>
+  </si>
+  <si>
+    <t>135440946</t>
+  </si>
+  <si>
+    <t>135477773</t>
+  </si>
+  <si>
+    <t>135015633</t>
+  </si>
+  <si>
+    <t>135431766</t>
+  </si>
+  <si>
+    <t>135424935</t>
+  </si>
+  <si>
+    <t>135544711</t>
+  </si>
+  <si>
+    <t>135541134</t>
+  </si>
+  <si>
+    <t>135448756</t>
+  </si>
+  <si>
+    <t>135375068</t>
+  </si>
+  <si>
+    <t>135381493</t>
+  </si>
+  <si>
+    <t>135399314</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_25.11.2025</t>
   </si>
 </sst>
 </file>
@@ -686,16 +671,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>130654291</v>
+        <v>135349500</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -704,16 +689,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -722,16 +707,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -740,16 +725,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -758,16 +743,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -776,16 +761,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -794,16 +779,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -812,16 +797,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -830,16 +815,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -848,16 +833,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -866,16 +851,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -884,16 +869,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -902,16 +887,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -919,16 +904,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -936,16 +921,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -953,16 +938,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -970,16 +955,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -987,16 +972,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1004,16 +989,16 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1021,16 +1006,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1038,16 +1023,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1055,16 +1040,16 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1072,16 +1057,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1089,16 +1074,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1106,16 +1091,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1123,16 +1108,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1140,16 +1125,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1157,16 +1142,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1174,16 +1159,16 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1191,16 +1176,16 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1208,16 +1193,16 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1225,16 +1210,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1242,16 +1227,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1259,16 +1244,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1276,16 +1261,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1293,16 +1278,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1310,16 +1295,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1327,16 +1312,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1344,16 +1329,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1361,16 +1346,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1378,16 +1363,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1395,16 +1380,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1412,16 +1397,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1429,16 +1414,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1446,16 +1431,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1463,16 +1448,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1480,16 +1465,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1497,16 +1482,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1514,16 +1499,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1531,16 +1516,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1548,16 +1533,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1565,16 +1550,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1582,16 +1567,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1599,16 +1584,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1616,16 +1601,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1633,16 +1618,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1650,16 +1635,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1667,16 +1652,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1684,16 +1669,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1701,112 +1686,40 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D66" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="D67" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="65" x14ac:dyDescent="0.25"/>
+    <row r="66" x14ac:dyDescent="0.25"/>
+    <row r="67" x14ac:dyDescent="0.25"/>
+    <row r="68" x14ac:dyDescent="0.25"/>
+    <row r="69" x14ac:dyDescent="0.25"/>
+    <row r="70" x14ac:dyDescent="0.25"/>
+    <row r="71" x14ac:dyDescent="0.25"/>
+    <row r="72" x14ac:dyDescent="0.25"/>
+    <row r="73" x14ac:dyDescent="0.25"/>
+    <row r="74" x14ac:dyDescent="0.25"/>
+    <row r="75" x14ac:dyDescent="0.25"/>
+    <row r="76" x14ac:dyDescent="0.25"/>
+    <row r="77" x14ac:dyDescent="0.25"/>
+    <row r="78" x14ac:dyDescent="0.25"/>
+    <row r="79" x14ac:dyDescent="0.25"/>
+    <row r="80" x14ac:dyDescent="0.25"/>
     <row r="81" x14ac:dyDescent="0.25"/>
     <row r="82" x14ac:dyDescent="0.25"/>
     <row r="83" x14ac:dyDescent="0.25"/>
@@ -1921,31 +1834,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6415AA80-7252-4099-8D93-65A346702965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6809BEE-4BE4-448A-8FAA-2B3716C90415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="86">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,187 +54,238 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 25/11/2025</t>
-  </si>
-  <si>
-    <t>135391105</t>
-  </si>
-  <si>
-    <t>135387657</t>
-  </si>
-  <si>
-    <t>135425887</t>
-  </si>
-  <si>
-    <t>135431765</t>
-  </si>
-  <si>
-    <t>135441456</t>
-  </si>
-  <si>
-    <t>135449921</t>
-  </si>
-  <si>
-    <t>135454426</t>
-  </si>
-  <si>
-    <t>135438723</t>
-  </si>
-  <si>
-    <t>135440349</t>
-  </si>
-  <si>
-    <t>135450121</t>
-  </si>
-  <si>
-    <t>135395930</t>
-  </si>
-  <si>
-    <t>135467452</t>
-  </si>
-  <si>
-    <t>135494203</t>
-  </si>
-  <si>
-    <t>135487552</t>
-  </si>
-  <si>
-    <t>135489024</t>
-  </si>
-  <si>
-    <t>135505297</t>
-  </si>
-  <si>
-    <t>135348651</t>
-  </si>
-  <si>
-    <t>135464451</t>
-  </si>
-  <si>
-    <t>135519975</t>
-  </si>
-  <si>
-    <t>135522669</t>
-  </si>
-  <si>
-    <t>135524692</t>
-  </si>
-  <si>
-    <t>135523918</t>
-  </si>
-  <si>
-    <t>135523686</t>
-  </si>
-  <si>
-    <t>135327396</t>
-  </si>
-  <si>
-    <t>135364158</t>
-  </si>
-  <si>
-    <t>135367410</t>
-  </si>
-  <si>
-    <t>135402399</t>
-  </si>
-  <si>
-    <t>135403681</t>
-  </si>
-  <si>
-    <t>135466334</t>
-  </si>
-  <si>
-    <t>135464235</t>
-  </si>
-  <si>
-    <t>135368246</t>
-  </si>
-  <si>
-    <t>135530500</t>
-  </si>
-  <si>
-    <t>135433461</t>
-  </si>
-  <si>
-    <t>135365536</t>
-  </si>
-  <si>
-    <t>135389011</t>
-  </si>
-  <si>
-    <t>135418704</t>
-  </si>
-  <si>
-    <t>135532533</t>
-  </si>
-  <si>
-    <t>135533450</t>
-  </si>
-  <si>
-    <t>135447364</t>
-  </si>
-  <si>
-    <t>135461257</t>
-  </si>
-  <si>
-    <t>135441260</t>
-  </si>
-  <si>
-    <t>135458838</t>
-  </si>
-  <si>
-    <t>135447066</t>
-  </si>
-  <si>
-    <t>135443405</t>
-  </si>
-  <si>
-    <t>135539129</t>
-  </si>
-  <si>
-    <t>135540952</t>
-  </si>
-  <si>
-    <t>135440653</t>
-  </si>
-  <si>
-    <t>135478386</t>
-  </si>
-  <si>
-    <t>135440946</t>
-  </si>
-  <si>
-    <t>135477773</t>
-  </si>
-  <si>
-    <t>135015633</t>
-  </si>
-  <si>
-    <t>135431766</t>
-  </si>
-  <si>
-    <t>135424935</t>
-  </si>
-  <si>
-    <t>135544711</t>
-  </si>
-  <si>
-    <t>135541134</t>
-  </si>
-  <si>
-    <t>135448756</t>
-  </si>
-  <si>
-    <t>135375068</t>
-  </si>
-  <si>
-    <t>135381493</t>
-  </si>
-  <si>
-    <t>135399314</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_25.11.2025</t>
+    <t>Recusas Sicredi 26/11/2025</t>
+  </si>
+  <si>
+    <t>135396315</t>
+  </si>
+  <si>
+    <t>135403847</t>
+  </si>
+  <si>
+    <t>135432285</t>
+  </si>
+  <si>
+    <t>135433576</t>
+  </si>
+  <si>
+    <t>135370202</t>
+  </si>
+  <si>
+    <t>135443848</t>
+  </si>
+  <si>
+    <t>135445972</t>
+  </si>
+  <si>
+    <t>135431472</t>
+  </si>
+  <si>
+    <t>135467575</t>
+  </si>
+  <si>
+    <t>135471653</t>
+  </si>
+  <si>
+    <t>135486164</t>
+  </si>
+  <si>
+    <t>135491428</t>
+  </si>
+  <si>
+    <t>135497637</t>
+  </si>
+  <si>
+    <t>135493325</t>
+  </si>
+  <si>
+    <t>135490003</t>
+  </si>
+  <si>
+    <t>135477106</t>
+  </si>
+  <si>
+    <t>135513535</t>
+  </si>
+  <si>
+    <t>135516074</t>
+  </si>
+  <si>
+    <t>135509319</t>
+  </si>
+  <si>
+    <t>135351071</t>
+  </si>
+  <si>
+    <t>135336146</t>
+  </si>
+  <si>
+    <t>135402255</t>
+  </si>
+  <si>
+    <t>135532867</t>
+  </si>
+  <si>
+    <t>135536223</t>
+  </si>
+  <si>
+    <t>135534807</t>
+  </si>
+  <si>
+    <t>135538133</t>
+  </si>
+  <si>
+    <t>135546019</t>
+  </si>
+  <si>
+    <t>135544044</t>
+  </si>
+  <si>
+    <t>135545416</t>
+  </si>
+  <si>
+    <t>135538141</t>
+  </si>
+  <si>
+    <t>135539929</t>
+  </si>
+  <si>
+    <t>135366084</t>
+  </si>
+  <si>
+    <t>135360231</t>
+  </si>
+  <si>
+    <t>135363145</t>
+  </si>
+  <si>
+    <t>135364964</t>
+  </si>
+  <si>
+    <t>135366478</t>
+  </si>
+  <si>
+    <t>135368431</t>
+  </si>
+  <si>
+    <t>135386381</t>
+  </si>
+  <si>
+    <t>131252986</t>
+  </si>
+  <si>
+    <t>135538029</t>
+  </si>
+  <si>
+    <t>135552373</t>
+  </si>
+  <si>
+    <t>135552702</t>
+  </si>
+  <si>
+    <t>133208144</t>
+  </si>
+  <si>
+    <t>135432735</t>
+  </si>
+  <si>
+    <t>135556338</t>
+  </si>
+  <si>
+    <t>135555811</t>
+  </si>
+  <si>
+    <t>135557073</t>
+  </si>
+  <si>
+    <t>135557475</t>
+  </si>
+  <si>
+    <t>135556214</t>
+  </si>
+  <si>
+    <t>135558440</t>
+  </si>
+  <si>
+    <t>135558243</t>
+  </si>
+  <si>
+    <t>135449138</t>
+  </si>
+  <si>
+    <t>135452727</t>
+  </si>
+  <si>
+    <t>135560303</t>
+  </si>
+  <si>
+    <t>135560150</t>
+  </si>
+  <si>
+    <t>135472962</t>
+  </si>
+  <si>
+    <t>135561283</t>
+  </si>
+  <si>
+    <t>135561616</t>
+  </si>
+  <si>
+    <t>135396987</t>
+  </si>
+  <si>
+    <t>135559931</t>
+  </si>
+  <si>
+    <t>135562051</t>
+  </si>
+  <si>
+    <t>135448789</t>
+  </si>
+  <si>
+    <t>135493523</t>
+  </si>
+  <si>
+    <t>135557169</t>
+  </si>
+  <si>
+    <t>135561006</t>
+  </si>
+  <si>
+    <t>135429668</t>
+  </si>
+  <si>
+    <t>135444653</t>
+  </si>
+  <si>
+    <t>135568606</t>
+  </si>
+  <si>
+    <t>135468882</t>
+  </si>
+  <si>
+    <t>135438105</t>
+  </si>
+  <si>
+    <t>135568704</t>
+  </si>
+  <si>
+    <t>135568460</t>
+  </si>
+  <si>
+    <t>135568225</t>
+  </si>
+  <si>
+    <t>135569187</t>
+  </si>
+  <si>
+    <t>135463563</t>
+  </si>
+  <si>
+    <t>135449460</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_26.11.2025</t>
   </si>
 </sst>
 </file>
@@ -671,7 +722,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135349500</v>
+        <v>135370049</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -680,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -698,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -716,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -734,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -752,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -770,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -788,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -806,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -824,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -842,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -860,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -878,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -896,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -913,7 +964,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -930,7 +981,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -947,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -964,7 +1015,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -981,7 +1032,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -998,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1015,7 +1066,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1032,7 +1083,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1049,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1066,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1083,7 +1134,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1100,7 +1151,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1117,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1134,7 +1185,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1151,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1168,7 +1219,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1185,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1202,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1219,7 +1270,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1236,7 +1287,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1253,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1270,7 +1321,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1287,7 +1338,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1304,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1321,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1338,7 +1389,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1355,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1372,7 +1423,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1389,7 +1440,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1406,7 +1457,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1423,7 +1474,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1440,7 +1491,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1457,7 +1508,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1474,7 +1525,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1491,7 +1542,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1508,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1525,7 +1576,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1542,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1559,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1576,7 +1627,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1593,7 +1644,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1610,7 +1661,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1627,7 +1678,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1644,7 +1695,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1661,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1678,7 +1729,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1695,31 +1746,303 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25"/>
-    <row r="65" x14ac:dyDescent="0.25"/>
-    <row r="66" x14ac:dyDescent="0.25"/>
-    <row r="67" x14ac:dyDescent="0.25"/>
-    <row r="68" x14ac:dyDescent="0.25"/>
-    <row r="69" x14ac:dyDescent="0.25"/>
-    <row r="70" x14ac:dyDescent="0.25"/>
-    <row r="71" x14ac:dyDescent="0.25"/>
-    <row r="72" x14ac:dyDescent="0.25"/>
-    <row r="73" x14ac:dyDescent="0.25"/>
-    <row r="74" x14ac:dyDescent="0.25"/>
-    <row r="75" x14ac:dyDescent="0.25"/>
-    <row r="76" x14ac:dyDescent="0.25"/>
-    <row r="77" x14ac:dyDescent="0.25"/>
-    <row r="78" x14ac:dyDescent="0.25"/>
-    <row r="79" x14ac:dyDescent="0.25"/>
-    <row r="80" x14ac:dyDescent="0.25"/>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25"/>
     <row r="81" x14ac:dyDescent="0.25"/>
     <row r="82" x14ac:dyDescent="0.25"/>
     <row r="83" x14ac:dyDescent="0.25"/>
@@ -1834,31 +2157,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E3CAF0-D7EA-4EBB-BB9D-520692B5CF4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{528365AB-521C-48C9-AFAD-2C8286CD5A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="143">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -48,12 +48,183 @@
     <t xml:space="preserve">Anexo </t>
   </si>
   <si>
-    <t>Processado</t>
-  </si>
-  <si>
     <t>971</t>
   </si>
   <si>
+    <t>Recusas Sicredi 28/11/2025</t>
+  </si>
+  <si>
+    <t>135446213</t>
+  </si>
+  <si>
+    <t>135454415</t>
+  </si>
+  <si>
+    <t>135454509</t>
+  </si>
+  <si>
+    <t>135469303</t>
+  </si>
+  <si>
+    <t>135476654</t>
+  </si>
+  <si>
+    <t>135510358</t>
+  </si>
+  <si>
+    <t>135542795</t>
+  </si>
+  <si>
+    <t>135541442</t>
+  </si>
+  <si>
+    <t>135552925</t>
+  </si>
+  <si>
+    <t>135561842</t>
+  </si>
+  <si>
+    <t>135410746</t>
+  </si>
+  <si>
+    <t>135556926</t>
+  </si>
+  <si>
+    <t>135584066</t>
+  </si>
+  <si>
+    <t>135588680</t>
+  </si>
+  <si>
+    <t>135588788</t>
+  </si>
+  <si>
+    <t>135587883</t>
+  </si>
+  <si>
+    <t>135397552</t>
+  </si>
+  <si>
+    <t>135422017</t>
+  </si>
+  <si>
+    <t>135452625</t>
+  </si>
+  <si>
+    <t>135449564</t>
+  </si>
+  <si>
+    <t>135418148</t>
+  </si>
+  <si>
+    <t>135441391</t>
+  </si>
+  <si>
+    <t>135597714</t>
+  </si>
+  <si>
+    <t>135466412</t>
+  </si>
+  <si>
+    <t>135602268</t>
+  </si>
+  <si>
+    <t>135448304</t>
+  </si>
+  <si>
+    <t>135602339</t>
+  </si>
+  <si>
+    <t>135454043</t>
+  </si>
+  <si>
+    <t>135603314</t>
+  </si>
+  <si>
+    <t>135497962</t>
+  </si>
+  <si>
+    <t>135604159</t>
+  </si>
+  <si>
+    <t>135604829</t>
+  </si>
+  <si>
+    <t>135604260</t>
+  </si>
+  <si>
+    <t>135595376</t>
+  </si>
+  <si>
+    <t>135055041</t>
+  </si>
+  <si>
+    <t>135463403</t>
+  </si>
+  <si>
+    <t>135485567</t>
+  </si>
+  <si>
+    <t>135518401</t>
+  </si>
+  <si>
+    <t>135608362</t>
+  </si>
+  <si>
+    <t>135432748</t>
+  </si>
+  <si>
+    <t>135610707</t>
+  </si>
+  <si>
+    <t>135608931</t>
+  </si>
+  <si>
+    <t>135608732</t>
+  </si>
+  <si>
+    <t>135438112</t>
+  </si>
+  <si>
+    <t>135614812</t>
+  </si>
+  <si>
+    <t>135440975</t>
+  </si>
+  <si>
+    <t>135443061</t>
+  </si>
+  <si>
+    <t>135443127</t>
+  </si>
+  <si>
+    <t>135494457</t>
+  </si>
+  <si>
+    <t>135616478</t>
+  </si>
+  <si>
+    <t>135448408</t>
+  </si>
+  <si>
+    <t>135448998</t>
+  </si>
+  <si>
+    <t>135616584</t>
+  </si>
+  <si>
+    <t>135496456</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_28.11.2025</t>
+  </si>
+  <si>
+    <t>Processar</t>
+  </si>
+  <si>
+    <t>135383961</t>
+  </si>
+  <si>
     <t>Recusas Sicredi 27/11/2025</t>
   </si>
   <si>
@@ -216,91 +387,76 @@
     <t>135425066</t>
   </si>
   <si>
-    <t>135576572</t>
-  </si>
-  <si>
-    <t>135446654</t>
-  </si>
-  <si>
-    <t>135575036</t>
-  </si>
-  <si>
-    <t>135469267</t>
-  </si>
-  <si>
-    <t>135466683</t>
-  </si>
-  <si>
-    <t>135444532</t>
-  </si>
-  <si>
-    <t>135497520</t>
-  </si>
-  <si>
-    <t>135579789</t>
-  </si>
-  <si>
-    <t>135458813</t>
-  </si>
-  <si>
-    <t>135420857</t>
-  </si>
-  <si>
-    <t>135421784</t>
-  </si>
-  <si>
-    <t>135422657</t>
-  </si>
-  <si>
-    <t>135425129</t>
-  </si>
-  <si>
-    <t>135581661</t>
-  </si>
-  <si>
-    <t>135574905</t>
-  </si>
-  <si>
-    <t>135583157</t>
-  </si>
-  <si>
-    <t>135499929</t>
-  </si>
-  <si>
-    <t>135584189</t>
-  </si>
-  <si>
-    <t>133651314</t>
-  </si>
-  <si>
-    <t>135585355</t>
-  </si>
-  <si>
-    <t>135587721</t>
-  </si>
-  <si>
-    <t>135585060</t>
-  </si>
-  <si>
-    <t>135587184</t>
-  </si>
-  <si>
-    <t>135588363</t>
-  </si>
-  <si>
-    <t>135474293</t>
-  </si>
-  <si>
-    <t>135578560</t>
-  </si>
-  <si>
-    <t>135453294</t>
-  </si>
-  <si>
-    <t>135402553</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_27.11.2025</t>
+    <t>135427268</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 29/11/2025</t>
+  </si>
+  <si>
+    <t>135424186</t>
+  </si>
+  <si>
+    <t>135450141</t>
+  </si>
+  <si>
+    <t>135451960</t>
+  </si>
+  <si>
+    <t>135425117</t>
+  </si>
+  <si>
+    <t>135519828</t>
+  </si>
+  <si>
+    <t>135532843</t>
+  </si>
+  <si>
+    <t>135569157</t>
+  </si>
+  <si>
+    <t>135586076</t>
+  </si>
+  <si>
+    <t>135553993</t>
+  </si>
+  <si>
+    <t>135410914</t>
+  </si>
+  <si>
+    <t>135417347</t>
+  </si>
+  <si>
+    <t>135419284</t>
+  </si>
+  <si>
+    <t>135429567</t>
+  </si>
+  <si>
+    <t>135443917</t>
+  </si>
+  <si>
+    <t>135446280</t>
+  </si>
+  <si>
+    <t>135451825</t>
+  </si>
+  <si>
+    <t>135422940</t>
+  </si>
+  <si>
+    <t>135484174</t>
+  </si>
+  <si>
+    <t>135492457</t>
+  </si>
+  <si>
+    <t>135509845</t>
+  </si>
+  <si>
+    <t>135489098</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_29.11.2025</t>
   </si>
 </sst>
 </file>
@@ -705,7 +861,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -737,1452 +893,2284 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135383961</v>
+        <v>135444351</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F32"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F33"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F35"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F36"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F37"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F38"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F43"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F45"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F47"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F48"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F49"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F50"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F51"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F52"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F54"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F55"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
       <c r="F56"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57"/>
+        <v>63</v>
+      </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>6</v>
+        <v>63</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2199,31 +3187,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A542C7F-4599-4FD6-9003-D2740ED2037A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5344D743-C886-4C22-8F61-1B59ACE8E743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,241 +54,133 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 01/12/2025</t>
-  </si>
-  <si>
-    <t>135472047</t>
-  </si>
-  <si>
-    <t>135490039</t>
-  </si>
-  <si>
-    <t>135501286</t>
-  </si>
-  <si>
-    <t>135514633</t>
-  </si>
-  <si>
-    <t>135523713</t>
-  </si>
-  <si>
-    <t>135517414</t>
-  </si>
-  <si>
-    <t>135512474</t>
-  </si>
-  <si>
-    <t>135521719</t>
-  </si>
-  <si>
-    <t>135541521</t>
-  </si>
-  <si>
-    <t>135488049</t>
-  </si>
-  <si>
-    <t>135532045</t>
-  </si>
-  <si>
-    <t>135534559</t>
-  </si>
-  <si>
-    <t>135537316</t>
-  </si>
-  <si>
-    <t>135529273</t>
-  </si>
-  <si>
-    <t>135533356</t>
-  </si>
-  <si>
-    <t>135562217</t>
-  </si>
-  <si>
-    <t>135563262</t>
-  </si>
-  <si>
-    <t>135485801</t>
-  </si>
-  <si>
-    <t>135553226</t>
-  </si>
-  <si>
-    <t>135562700</t>
-  </si>
-  <si>
-    <t>135498180</t>
-  </si>
-  <si>
-    <t>135558532</t>
-  </si>
-  <si>
-    <t>135555029</t>
-  </si>
-  <si>
-    <t>135544536</t>
-  </si>
-  <si>
-    <t>135613950</t>
-  </si>
-  <si>
-    <t>135613149</t>
-  </si>
-  <si>
-    <t>135609419</t>
-  </si>
-  <si>
-    <t>135609941</t>
-  </si>
-  <si>
-    <t>135563992</t>
-  </si>
-  <si>
-    <t>135609084</t>
-  </si>
-  <si>
-    <t>135618900</t>
-  </si>
-  <si>
-    <t>132408495</t>
-  </si>
-  <si>
-    <t>135627056</t>
-  </si>
-  <si>
-    <t>135522821</t>
-  </si>
-  <si>
-    <t>135470141</t>
-  </si>
-  <si>
-    <t>135441125</t>
-  </si>
-  <si>
-    <t>135517023</t>
-  </si>
-  <si>
-    <t>135452695</t>
-  </si>
-  <si>
-    <t>135472634</t>
-  </si>
-  <si>
-    <t>135478372</t>
-  </si>
-  <si>
-    <t>135631479</t>
-  </si>
-  <si>
-    <t>135483998</t>
-  </si>
-  <si>
-    <t>135631474</t>
-  </si>
-  <si>
-    <t>135501647</t>
-  </si>
-  <si>
-    <t>135632731</t>
-  </si>
-  <si>
-    <t>135520597</t>
-  </si>
-  <si>
-    <t>135631985</t>
-  </si>
-  <si>
-    <t>135523036</t>
-  </si>
-  <si>
-    <t>135490863</t>
-  </si>
-  <si>
-    <t>135443409</t>
-  </si>
-  <si>
-    <t>135638152</t>
-  </si>
-  <si>
-    <t>134458545</t>
-  </si>
-  <si>
-    <t>131122287</t>
-  </si>
-  <si>
-    <t>135516163</t>
-  </si>
-  <si>
-    <t>135489408</t>
-  </si>
-  <si>
-    <t>135522033</t>
-  </si>
-  <si>
-    <t>135517720</t>
-  </si>
-  <si>
-    <t>135161788</t>
-  </si>
-  <si>
-    <t>135487579</t>
-  </si>
-  <si>
-    <t>135568239</t>
-  </si>
-  <si>
-    <t>135457536</t>
-  </si>
-  <si>
-    <t>135448447</t>
-  </si>
-  <si>
-    <t>135569330</t>
-  </si>
-  <si>
-    <t>135465838</t>
-  </si>
-  <si>
-    <t>135466738</t>
-  </si>
-  <si>
-    <t>135469984</t>
-  </si>
-  <si>
-    <t>135472988</t>
-  </si>
-  <si>
-    <t>135473891</t>
-  </si>
-  <si>
-    <t>135475429</t>
-  </si>
-  <si>
-    <t>135475782</t>
-  </si>
-  <si>
-    <t>135475841</t>
-  </si>
-  <si>
-    <t>135488752</t>
-  </si>
-  <si>
-    <t>135490393</t>
-  </si>
-  <si>
-    <t>135490688</t>
-  </si>
-  <si>
-    <t>135491158</t>
-  </si>
-  <si>
-    <t>135498520</t>
-  </si>
-  <si>
-    <t>135499266</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_01.12.2025</t>
+    <t>Recusas Sicredi 02/12/2025</t>
+  </si>
+  <si>
+    <t>135539348</t>
+  </si>
+  <si>
+    <t>135530843</t>
+  </si>
+  <si>
+    <t>135568590</t>
+  </si>
+  <si>
+    <t>135577465</t>
+  </si>
+  <si>
+    <t>135551254</t>
+  </si>
+  <si>
+    <t>135583837</t>
+  </si>
+  <si>
+    <t>135534020</t>
+  </si>
+  <si>
+    <t>135576694</t>
+  </si>
+  <si>
+    <t>135573436</t>
+  </si>
+  <si>
+    <t>135579950</t>
+  </si>
+  <si>
+    <t>135588642</t>
+  </si>
+  <si>
+    <t>135604817</t>
+  </si>
+  <si>
+    <t>135610953</t>
+  </si>
+  <si>
+    <t>135590273</t>
+  </si>
+  <si>
+    <t>135608574</t>
+  </si>
+  <si>
+    <t>135608356</t>
+  </si>
+  <si>
+    <t>135632899</t>
+  </si>
+  <si>
+    <t>135631221</t>
+  </si>
+  <si>
+    <t>135539696</t>
+  </si>
+  <si>
+    <t>135643719</t>
+  </si>
+  <si>
+    <t>135642346</t>
+  </si>
+  <si>
+    <t>135642668</t>
+  </si>
+  <si>
+    <t>135631268</t>
+  </si>
+  <si>
+    <t>135439215</t>
+  </si>
+  <si>
+    <t>135487306</t>
+  </si>
+  <si>
+    <t>135641746</t>
+  </si>
+  <si>
+    <t>135547610</t>
+  </si>
+  <si>
+    <t>135648732</t>
+  </si>
+  <si>
+    <t>135529796</t>
+  </si>
+  <si>
+    <t>135562245</t>
+  </si>
+  <si>
+    <t>135458473</t>
+  </si>
+  <si>
+    <t>135555958</t>
+  </si>
+  <si>
+    <t>135543008</t>
+  </si>
+  <si>
+    <t>135464960</t>
+  </si>
+  <si>
+    <t>135514175</t>
+  </si>
+  <si>
+    <t>135514080</t>
+  </si>
+  <si>
+    <t>135658260</t>
+  </si>
+  <si>
+    <t>135658977</t>
+  </si>
+  <si>
+    <t>135659492</t>
+  </si>
+  <si>
+    <t>135437162</t>
+  </si>
+  <si>
+    <t>134597350</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_02.12.2025</t>
   </si>
 </sst>
 </file>
@@ -693,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -725,7 +617,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135450974</v>
+        <v>135465959</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -734,7 +626,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -752,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -770,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -788,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -806,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -824,7 +716,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -842,7 +734,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -860,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -878,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -896,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -914,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -932,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -950,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -968,7 +860,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -986,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -1004,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -1022,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -1040,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1058,7 +950,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1076,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1094,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1112,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1130,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1148,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1166,7 +1058,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1184,7 +1076,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1202,7 +1094,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1220,7 +1112,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1238,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1256,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1274,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1292,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1310,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1328,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1346,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1364,7 +1256,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1382,7 +1274,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1400,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1418,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1436,7 +1328,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1454,7 +1346,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1472,637 +1364,12 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F43"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50"/>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>7</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -2118,31 +1385,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5344D743-C886-4C22-8F61-1B59ACE8E743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2C3545-DD29-4548-935A-EE0E5731EE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="54">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,133 +54,142 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 02/12/2025</t>
-  </si>
-  <si>
-    <t>135539348</t>
-  </si>
-  <si>
-    <t>135530843</t>
-  </si>
-  <si>
-    <t>135568590</t>
-  </si>
-  <si>
-    <t>135577465</t>
-  </si>
-  <si>
-    <t>135551254</t>
-  </si>
-  <si>
-    <t>135583837</t>
-  </si>
-  <si>
-    <t>135534020</t>
-  </si>
-  <si>
-    <t>135576694</t>
-  </si>
-  <si>
-    <t>135573436</t>
-  </si>
-  <si>
-    <t>135579950</t>
-  </si>
-  <si>
-    <t>135588642</t>
-  </si>
-  <si>
-    <t>135604817</t>
-  </si>
-  <si>
-    <t>135610953</t>
-  </si>
-  <si>
-    <t>135590273</t>
-  </si>
-  <si>
-    <t>135608574</t>
-  </si>
-  <si>
-    <t>135608356</t>
-  </si>
-  <si>
-    <t>135632899</t>
-  </si>
-  <si>
-    <t>135631221</t>
-  </si>
-  <si>
-    <t>135539696</t>
-  </si>
-  <si>
-    <t>135643719</t>
-  </si>
-  <si>
-    <t>135642346</t>
-  </si>
-  <si>
-    <t>135642668</t>
-  </si>
-  <si>
-    <t>135631268</t>
-  </si>
-  <si>
-    <t>135439215</t>
-  </si>
-  <si>
-    <t>135487306</t>
-  </si>
-  <si>
-    <t>135641746</t>
-  </si>
-  <si>
-    <t>135547610</t>
-  </si>
-  <si>
-    <t>135648732</t>
-  </si>
-  <si>
-    <t>135529796</t>
-  </si>
-  <si>
-    <t>135562245</t>
-  </si>
-  <si>
-    <t>135458473</t>
-  </si>
-  <si>
-    <t>135555958</t>
-  </si>
-  <si>
-    <t>135543008</t>
-  </si>
-  <si>
-    <t>135464960</t>
-  </si>
-  <si>
-    <t>135514175</t>
-  </si>
-  <si>
-    <t>135514080</t>
-  </si>
-  <si>
-    <t>135658260</t>
-  </si>
-  <si>
-    <t>135658977</t>
-  </si>
-  <si>
-    <t>135659492</t>
-  </si>
-  <si>
-    <t>135437162</t>
-  </si>
-  <si>
-    <t>134597350</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_02.12.2025</t>
+    <t>Recusas Sicredi 03/12/2025</t>
+  </si>
+  <si>
+    <t>135528358</t>
+  </si>
+  <si>
+    <t>135566813</t>
+  </si>
+  <si>
+    <t>135583851</t>
+  </si>
+  <si>
+    <t>135586799</t>
+  </si>
+  <si>
+    <t>135588850</t>
+  </si>
+  <si>
+    <t>135611761</t>
+  </si>
+  <si>
+    <t>135607313</t>
+  </si>
+  <si>
+    <t>135586688</t>
+  </si>
+  <si>
+    <t>135633290</t>
+  </si>
+  <si>
+    <t>135630732</t>
+  </si>
+  <si>
+    <t>135652787</t>
+  </si>
+  <si>
+    <t>135656745</t>
+  </si>
+  <si>
+    <t>135656897</t>
+  </si>
+  <si>
+    <t>133621984</t>
+  </si>
+  <si>
+    <t>135664362</t>
+  </si>
+  <si>
+    <t>135655437</t>
+  </si>
+  <si>
+    <t>135321420</t>
+  </si>
+  <si>
+    <t>135474615</t>
+  </si>
+  <si>
+    <t>135425810</t>
+  </si>
+  <si>
+    <t>135443818</t>
+  </si>
+  <si>
+    <t>135459171</t>
+  </si>
+  <si>
+    <t>135461207</t>
+  </si>
+  <si>
+    <t>135461275</t>
+  </si>
+  <si>
+    <t>135477354</t>
+  </si>
+  <si>
+    <t>135473032</t>
+  </si>
+  <si>
+    <t>135473117</t>
+  </si>
+  <si>
+    <t>135514182</t>
+  </si>
+  <si>
+    <t>135670321</t>
+  </si>
+  <si>
+    <t>135673340</t>
+  </si>
+  <si>
+    <t>135677005</t>
+  </si>
+  <si>
+    <t>135555753</t>
+  </si>
+  <si>
+    <t>135429489</t>
+  </si>
+  <si>
+    <t>135555829</t>
+  </si>
+  <si>
+    <t>135679561</t>
+  </si>
+  <si>
+    <t>135679763</t>
+  </si>
+  <si>
+    <t>135680480</t>
+  </si>
+  <si>
+    <t>135612367</t>
+  </si>
+  <si>
+    <t>135488179</t>
+  </si>
+  <si>
+    <t>135523792</t>
+  </si>
+  <si>
+    <t>135673055</t>
+  </si>
+  <si>
+    <t>135685158</t>
+  </si>
+  <si>
+    <t>135577311</t>
+  </si>
+  <si>
+    <t>135291399</t>
+  </si>
+  <si>
+    <t>135679619</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_03.12.2025</t>
   </si>
 </sst>
 </file>
@@ -585,7 +594,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -617,7 +626,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135465959</v>
+        <v>135466152</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -626,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -644,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -662,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -680,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -698,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -716,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -734,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -752,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -770,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -788,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -806,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -824,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -842,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -860,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -878,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -896,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -914,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -932,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -950,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -968,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -986,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1004,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1022,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1040,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1058,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1076,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1094,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1112,7 +1121,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1130,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1148,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1166,7 +1175,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1184,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1202,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1220,7 +1229,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1238,7 +1247,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1256,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1274,7 +1283,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1292,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1310,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1328,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1346,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1364,12 +1373,63 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43"/>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1385,31 +1445,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C2C3545-DD29-4548-935A-EE0E5731EE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2108A3C6-1097-4570-86FD-3866B6E6A35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="55">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,142 +54,145 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 03/12/2025</t>
-  </si>
-  <si>
-    <t>135528358</t>
-  </si>
-  <si>
-    <t>135566813</t>
-  </si>
-  <si>
-    <t>135583851</t>
-  </si>
-  <si>
-    <t>135586799</t>
-  </si>
-  <si>
-    <t>135588850</t>
-  </si>
-  <si>
-    <t>135611761</t>
-  </si>
-  <si>
-    <t>135607313</t>
-  </si>
-  <si>
-    <t>135586688</t>
-  </si>
-  <si>
-    <t>135633290</t>
-  </si>
-  <si>
-    <t>135630732</t>
-  </si>
-  <si>
-    <t>135652787</t>
-  </si>
-  <si>
-    <t>135656745</t>
-  </si>
-  <si>
-    <t>135656897</t>
-  </si>
-  <si>
-    <t>133621984</t>
-  </si>
-  <si>
-    <t>135664362</t>
-  </si>
-  <si>
-    <t>135655437</t>
-  </si>
-  <si>
-    <t>135321420</t>
-  </si>
-  <si>
-    <t>135474615</t>
-  </si>
-  <si>
-    <t>135425810</t>
-  </si>
-  <si>
-    <t>135443818</t>
-  </si>
-  <si>
-    <t>135459171</t>
-  </si>
-  <si>
-    <t>135461207</t>
-  </si>
-  <si>
-    <t>135461275</t>
-  </si>
-  <si>
-    <t>135477354</t>
-  </si>
-  <si>
-    <t>135473032</t>
-  </si>
-  <si>
-    <t>135473117</t>
-  </si>
-  <si>
-    <t>135514182</t>
-  </si>
-  <si>
-    <t>135670321</t>
-  </si>
-  <si>
-    <t>135673340</t>
-  </si>
-  <si>
-    <t>135677005</t>
-  </si>
-  <si>
-    <t>135555753</t>
-  </si>
-  <si>
-    <t>135429489</t>
-  </si>
-  <si>
-    <t>135555829</t>
-  </si>
-  <si>
-    <t>135679561</t>
-  </si>
-  <si>
-    <t>135679763</t>
-  </si>
-  <si>
-    <t>135680480</t>
-  </si>
-  <si>
-    <t>135612367</t>
-  </si>
-  <si>
-    <t>135488179</t>
-  </si>
-  <si>
-    <t>135523792</t>
-  </si>
-  <si>
-    <t>135673055</t>
-  </si>
-  <si>
-    <t>135685158</t>
-  </si>
-  <si>
-    <t>135577311</t>
-  </si>
-  <si>
-    <t>135291399</t>
-  </si>
-  <si>
-    <t>135679619</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_03.12.2025</t>
+    <t>Recusas Sicredi 04/12/2025</t>
+  </si>
+  <si>
+    <t>135521966</t>
+  </si>
+  <si>
+    <t>135528897</t>
+  </si>
+  <si>
+    <t>135565655</t>
+  </si>
+  <si>
+    <t>135572811</t>
+  </si>
+  <si>
+    <t>135607687</t>
+  </si>
+  <si>
+    <t>135614419</t>
+  </si>
+  <si>
+    <t>135614799</t>
+  </si>
+  <si>
+    <t>135615941</t>
+  </si>
+  <si>
+    <t>135643907</t>
+  </si>
+  <si>
+    <t>135641477</t>
+  </si>
+  <si>
+    <t>135636132</t>
+  </si>
+  <si>
+    <t>135658960</t>
+  </si>
+  <si>
+    <t>135663335</t>
+  </si>
+  <si>
+    <t>135588104</t>
+  </si>
+  <si>
+    <t>135672126</t>
+  </si>
+  <si>
+    <t>135677140</t>
+  </si>
+  <si>
+    <t>135520147</t>
+  </si>
+  <si>
+    <t>135484057</t>
+  </si>
+  <si>
+    <t>135493793</t>
+  </si>
+  <si>
+    <t>135698743</t>
+  </si>
+  <si>
+    <t>135695606</t>
+  </si>
+  <si>
+    <t>135701198</t>
+  </si>
+  <si>
+    <t>135701343</t>
+  </si>
+  <si>
+    <t>135551363</t>
+  </si>
+  <si>
+    <t>135693581</t>
+  </si>
+  <si>
+    <t>135701557</t>
+  </si>
+  <si>
+    <t>135704115</t>
+  </si>
+  <si>
+    <t>135700733</t>
+  </si>
+  <si>
+    <t>135576824</t>
+  </si>
+  <si>
+    <t>135585082</t>
+  </si>
+  <si>
+    <t>135596748</t>
+  </si>
+  <si>
+    <t>135704498</t>
+  </si>
+  <si>
+    <t>135574843</t>
+  </si>
+  <si>
+    <t>135591146</t>
+  </si>
+  <si>
+    <t>133809902</t>
+  </si>
+  <si>
+    <t>135507983</t>
+  </si>
+  <si>
+    <t>135509087</t>
+  </si>
+  <si>
+    <t>135510591</t>
+  </si>
+  <si>
+    <t>135521527</t>
+  </si>
+  <si>
+    <t>135522409</t>
+  </si>
+  <si>
+    <t>135525101</t>
+  </si>
+  <si>
+    <t>135499501</t>
+  </si>
+  <si>
+    <t>135494016</t>
+  </si>
+  <si>
+    <t>135498726</t>
+  </si>
+  <si>
+    <t>131578702</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_04.12.2025</t>
   </si>
 </sst>
 </file>
@@ -594,7 +597,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -626,7 +629,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135466152</v>
+        <v>135496334</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -635,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -653,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -671,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -689,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -707,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -725,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -743,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -761,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -779,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -797,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -815,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -833,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -851,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -869,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -887,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -905,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -923,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -941,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -959,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -977,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -995,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1013,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1031,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1049,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1067,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1085,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1103,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1121,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1139,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1157,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1175,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1193,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1211,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1229,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1247,7 +1250,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1265,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1283,7 +1286,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1301,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1319,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1337,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1355,7 +1358,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1373,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1391,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1408,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1425,9 +1428,26 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1445,31 +1465,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2108A3C6-1097-4570-86FD-3866B6E6A35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC602C5F-DE9A-4306-9A53-87944BDD2025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="52">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,145 +54,136 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 04/12/2025</t>
-  </si>
-  <si>
-    <t>135521966</t>
-  </si>
-  <si>
-    <t>135528897</t>
-  </si>
-  <si>
-    <t>135565655</t>
-  </si>
-  <si>
-    <t>135572811</t>
-  </si>
-  <si>
-    <t>135607687</t>
-  </si>
-  <si>
-    <t>135614419</t>
-  </si>
-  <si>
-    <t>135614799</t>
-  </si>
-  <si>
-    <t>135615941</t>
-  </si>
-  <si>
-    <t>135643907</t>
-  </si>
-  <si>
-    <t>135641477</t>
-  </si>
-  <si>
-    <t>135636132</t>
-  </si>
-  <si>
-    <t>135658960</t>
-  </si>
-  <si>
-    <t>135663335</t>
-  </si>
-  <si>
-    <t>135588104</t>
-  </si>
-  <si>
-    <t>135672126</t>
-  </si>
-  <si>
-    <t>135677140</t>
-  </si>
-  <si>
-    <t>135520147</t>
-  </si>
-  <si>
-    <t>135484057</t>
-  </si>
-  <si>
-    <t>135493793</t>
-  </si>
-  <si>
-    <t>135698743</t>
-  </si>
-  <si>
-    <t>135695606</t>
-  </si>
-  <si>
-    <t>135701198</t>
-  </si>
-  <si>
-    <t>135701343</t>
-  </si>
-  <si>
-    <t>135551363</t>
-  </si>
-  <si>
-    <t>135693581</t>
-  </si>
-  <si>
-    <t>135701557</t>
-  </si>
-  <si>
-    <t>135704115</t>
-  </si>
-  <si>
-    <t>135700733</t>
-  </si>
-  <si>
-    <t>135576824</t>
-  </si>
-  <si>
-    <t>135585082</t>
-  </si>
-  <si>
-    <t>135596748</t>
-  </si>
-  <si>
-    <t>135704498</t>
-  </si>
-  <si>
-    <t>135574843</t>
-  </si>
-  <si>
-    <t>135591146</t>
-  </si>
-  <si>
-    <t>133809902</t>
-  </si>
-  <si>
-    <t>135507983</t>
-  </si>
-  <si>
-    <t>135509087</t>
-  </si>
-  <si>
-    <t>135510591</t>
-  </si>
-  <si>
-    <t>135521527</t>
-  </si>
-  <si>
-    <t>135522409</t>
-  </si>
-  <si>
-    <t>135525101</t>
-  </si>
-  <si>
-    <t>135499501</t>
-  </si>
-  <si>
-    <t>135494016</t>
-  </si>
-  <si>
-    <t>135498726</t>
-  </si>
-  <si>
-    <t>131578702</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_04.12.2025</t>
+    <t>Recusas Sicredi 05/12/2025</t>
+  </si>
+  <si>
+    <t>135540081</t>
+  </si>
+  <si>
+    <t>135544612</t>
+  </si>
+  <si>
+    <t>135561667</t>
+  </si>
+  <si>
+    <t>135560658</t>
+  </si>
+  <si>
+    <t>135580171</t>
+  </si>
+  <si>
+    <t>135545974</t>
+  </si>
+  <si>
+    <t>135606709</t>
+  </si>
+  <si>
+    <t>135633506</t>
+  </si>
+  <si>
+    <t>135654189</t>
+  </si>
+  <si>
+    <t>135610258</t>
+  </si>
+  <si>
+    <t>135662918</t>
+  </si>
+  <si>
+    <t>135683254</t>
+  </si>
+  <si>
+    <t>135678575</t>
+  </si>
+  <si>
+    <t>135684221</t>
+  </si>
+  <si>
+    <t>135676921</t>
+  </si>
+  <si>
+    <t>135686571</t>
+  </si>
+  <si>
+    <t>135697581</t>
+  </si>
+  <si>
+    <t>135705795</t>
+  </si>
+  <si>
+    <t>135704928</t>
+  </si>
+  <si>
+    <t>135715035</t>
+  </si>
+  <si>
+    <t>135463200</t>
+  </si>
+  <si>
+    <t>135486944</t>
+  </si>
+  <si>
+    <t>135562750</t>
+  </si>
+  <si>
+    <t>135615516</t>
+  </si>
+  <si>
+    <t>135545671</t>
+  </si>
+  <si>
+    <t>135545670</t>
+  </si>
+  <si>
+    <t>135715465</t>
+  </si>
+  <si>
+    <t>135566194</t>
+  </si>
+  <si>
+    <t>135718758</t>
+  </si>
+  <si>
+    <t>135720221</t>
+  </si>
+  <si>
+    <t>135582190</t>
+  </si>
+  <si>
+    <t>135558889</t>
+  </si>
+  <si>
+    <t>135725718</t>
+  </si>
+  <si>
+    <t>135560304</t>
+  </si>
+  <si>
+    <t>135726531</t>
+  </si>
+  <si>
+    <t>135599675</t>
+  </si>
+  <si>
+    <t>135531262</t>
+  </si>
+  <si>
+    <t>135726823</t>
+  </si>
+  <si>
+    <t>135609861</t>
+  </si>
+  <si>
+    <t>135611594</t>
+  </si>
+  <si>
+    <t>135544931</t>
+  </si>
+  <si>
+    <t>135735797</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_05.12.2025</t>
   </si>
 </sst>
 </file>
@@ -597,7 +588,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -629,7 +620,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135496334</v>
+        <v>135510217</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -638,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -656,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -674,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -692,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -710,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -728,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -746,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -764,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -782,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -800,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -818,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -836,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -854,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -872,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -890,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -908,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -926,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -944,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -962,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -980,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -998,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1016,7 +1007,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1034,7 +1025,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1052,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1070,7 +1061,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1088,7 +1079,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1106,7 +1097,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1124,7 +1115,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1142,7 +1133,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1160,7 +1151,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1178,7 +1169,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1196,7 +1187,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1214,7 +1205,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1232,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1250,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1268,7 +1259,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1286,7 +1277,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1304,7 +1295,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1322,7 +1313,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1340,7 +1331,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1358,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1376,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1394,60 +1385,9 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1465,31 +1405,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC602C5F-DE9A-4306-9A53-87944BDD2025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{601FBBF3-4B49-4278-B4AA-B0868882DCDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="1230" windowWidth="15375" windowHeight="7965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,136 +54,166 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 05/12/2025</t>
-  </si>
-  <si>
-    <t>135540081</t>
-  </si>
-  <si>
-    <t>135544612</t>
-  </si>
-  <si>
-    <t>135561667</t>
-  </si>
-  <si>
-    <t>135560658</t>
-  </si>
-  <si>
-    <t>135580171</t>
-  </si>
-  <si>
-    <t>135545974</t>
-  </si>
-  <si>
-    <t>135606709</t>
-  </si>
-  <si>
-    <t>135633506</t>
-  </si>
-  <si>
-    <t>135654189</t>
-  </si>
-  <si>
-    <t>135610258</t>
-  </si>
-  <si>
-    <t>135662918</t>
-  </si>
-  <si>
-    <t>135683254</t>
-  </si>
-  <si>
-    <t>135678575</t>
-  </si>
-  <si>
-    <t>135684221</t>
-  </si>
-  <si>
-    <t>135676921</t>
-  </si>
-  <si>
-    <t>135686571</t>
-  </si>
-  <si>
-    <t>135697581</t>
-  </si>
-  <si>
-    <t>135705795</t>
-  </si>
-  <si>
-    <t>135704928</t>
-  </si>
-  <si>
-    <t>135715035</t>
-  </si>
-  <si>
-    <t>135463200</t>
-  </si>
-  <si>
-    <t>135486944</t>
-  </si>
-  <si>
-    <t>135562750</t>
-  </si>
-  <si>
-    <t>135615516</t>
-  </si>
-  <si>
-    <t>135545671</t>
-  </si>
-  <si>
-    <t>135545670</t>
-  </si>
-  <si>
-    <t>135715465</t>
-  </si>
-  <si>
-    <t>135566194</t>
-  </si>
-  <si>
-    <t>135718758</t>
-  </si>
-  <si>
-    <t>135720221</t>
-  </si>
-  <si>
-    <t>135582190</t>
-  </si>
-  <si>
-    <t>135558889</t>
-  </si>
-  <si>
-    <t>135725718</t>
-  </si>
-  <si>
-    <t>135560304</t>
-  </si>
-  <si>
-    <t>135726531</t>
-  </si>
-  <si>
-    <t>135599675</t>
-  </si>
-  <si>
-    <t>135531262</t>
-  </si>
-  <si>
-    <t>135726823</t>
-  </si>
-  <si>
-    <t>135609861</t>
-  </si>
-  <si>
-    <t>135611594</t>
-  </si>
-  <si>
-    <t>135544931</t>
-  </si>
-  <si>
-    <t>135735797</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_05.12.2025</t>
+    <t>Recusas Sicredi 08/12/2025</t>
+  </si>
+  <si>
+    <t>135590898</t>
+  </si>
+  <si>
+    <t>135590431</t>
+  </si>
+  <si>
+    <t>135602438</t>
+  </si>
+  <si>
+    <t>135629334</t>
+  </si>
+  <si>
+    <t>135626634</t>
+  </si>
+  <si>
+    <t>135638043</t>
+  </si>
+  <si>
+    <t>135576325</t>
+  </si>
+  <si>
+    <t>135633147</t>
+  </si>
+  <si>
+    <t>135630312</t>
+  </si>
+  <si>
+    <t>135657611</t>
+  </si>
+  <si>
+    <t>135656680</t>
+  </si>
+  <si>
+    <t>135651747</t>
+  </si>
+  <si>
+    <t>135662583</t>
+  </si>
+  <si>
+    <t>135660106</t>
+  </si>
+  <si>
+    <t>135657854</t>
+  </si>
+  <si>
+    <t>135674005</t>
+  </si>
+  <si>
+    <t>135587651</t>
+  </si>
+  <si>
+    <t>135552499</t>
+  </si>
+  <si>
+    <t>135683623</t>
+  </si>
+  <si>
+    <t>135650356</t>
+  </si>
+  <si>
+    <t>135695738</t>
+  </si>
+  <si>
+    <t>135709787</t>
+  </si>
+  <si>
+    <t>135697313</t>
+  </si>
+  <si>
+    <t>135722821</t>
+  </si>
+  <si>
+    <t>135633944</t>
+  </si>
+  <si>
+    <t>135721064</t>
+  </si>
+  <si>
+    <t>135731261</t>
+  </si>
+  <si>
+    <t>135743197</t>
+  </si>
+  <si>
+    <t>135743238</t>
+  </si>
+  <si>
+    <t>135608506</t>
+  </si>
+  <si>
+    <t>135538218</t>
+  </si>
+  <si>
+    <t>135539765</t>
+  </si>
+  <si>
+    <t>135675481</t>
+  </si>
+  <si>
+    <t>135631317</t>
+  </si>
+  <si>
+    <t>135656663</t>
+  </si>
+  <si>
+    <t>135750179</t>
+  </si>
+  <si>
+    <t>135580933</t>
+  </si>
+  <si>
+    <t>135642087</t>
+  </si>
+  <si>
+    <t>135582581</t>
+  </si>
+  <si>
+    <t>135591018</t>
+  </si>
+  <si>
+    <t>135596929</t>
+  </si>
+  <si>
+    <t>135642316</t>
+  </si>
+  <si>
+    <t>135610939</t>
+  </si>
+  <si>
+    <t>135633187</t>
+  </si>
+  <si>
+    <t>135594498</t>
+  </si>
+  <si>
+    <t>135606985</t>
+  </si>
+  <si>
+    <t>135754583</t>
+  </si>
+  <si>
+    <t>135589524</t>
+  </si>
+  <si>
+    <t>135638140</t>
+  </si>
+  <si>
+    <t>135606643</t>
+  </si>
+  <si>
+    <t>134098180</t>
+  </si>
+  <si>
+    <t>135745661</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_08.12.2025</t>
   </si>
 </sst>
 </file>
@@ -588,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,7 +650,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135510217</v>
+        <v>135563697</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -629,7 +659,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -647,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -665,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -683,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -701,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -719,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -737,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -755,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -773,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -791,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -809,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -827,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -845,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -863,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -881,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -899,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -917,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -935,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -953,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -971,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -989,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1007,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1025,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1043,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1061,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1079,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1097,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1115,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1133,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1151,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1169,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1187,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1205,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1223,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1241,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1259,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1277,7 +1307,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1295,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1313,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1331,7 +1361,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1349,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1367,7 +1397,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1385,9 +1415,179 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1405,31 +1605,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC70EBF-5F6B-41C7-8827-768DD1FCB4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D6D45E-CD06-476B-AEF7-A6D1DD0F2EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="122">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,169 +51,349 @@
     <t>971</t>
   </si>
   <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 28.10.2025</t>
-  </si>
-  <si>
-    <t>135007586</t>
-  </si>
-  <si>
-    <t>135011190</t>
-  </si>
-  <si>
-    <t>135058394</t>
-  </si>
-  <si>
-    <t>135054008</t>
-  </si>
-  <si>
-    <t>135080147</t>
-  </si>
-  <si>
-    <t>135079870</t>
-  </si>
-  <si>
-    <t>135078594</t>
-  </si>
-  <si>
-    <t>135070329</t>
-  </si>
-  <si>
-    <t>135068167</t>
-  </si>
-  <si>
-    <t>135075372</t>
-  </si>
-  <si>
-    <t>135101363</t>
-  </si>
-  <si>
-    <t>135103213</t>
-  </si>
-  <si>
-    <t>135100501</t>
-  </si>
-  <si>
-    <t>135096207</t>
-  </si>
-  <si>
-    <t>135044067</t>
-  </si>
-  <si>
-    <t>135117159</t>
-  </si>
-  <si>
-    <t>130462486</t>
-  </si>
-  <si>
-    <t>135120282</t>
-  </si>
-  <si>
-    <t>135119201</t>
-  </si>
-  <si>
-    <t>134926439</t>
-  </si>
-  <si>
-    <t>134940641</t>
-  </si>
-  <si>
-    <t>135059827</t>
-  </si>
-  <si>
-    <t>135127330</t>
-  </si>
-  <si>
-    <t>135127962</t>
-  </si>
-  <si>
-    <t>134950647</t>
-  </si>
-  <si>
-    <t>135068467</t>
-  </si>
-  <si>
-    <t>135059444</t>
-  </si>
-  <si>
-    <t>135130475</t>
-  </si>
-  <si>
-    <t>135070618</t>
-  </si>
-  <si>
-    <t>135030570</t>
-  </si>
-  <si>
-    <t>135037342</t>
-  </si>
-  <si>
-    <t>135132770</t>
-  </si>
-  <si>
-    <t>135132648</t>
-  </si>
-  <si>
-    <t>135076470</t>
-  </si>
-  <si>
-    <t>132194311</t>
-  </si>
-  <si>
-    <t>135133279</t>
-  </si>
-  <si>
-    <t>135134206</t>
-  </si>
-  <si>
-    <t>135058668</t>
-  </si>
-  <si>
-    <t>135070235</t>
-  </si>
-  <si>
-    <t>135136487</t>
-  </si>
-  <si>
-    <t>135050767</t>
-  </si>
-  <si>
-    <t>134923144</t>
-  </si>
-  <si>
-    <t>135005541</t>
-  </si>
-  <si>
-    <t>135012281</t>
-  </si>
-  <si>
-    <t>135077754</t>
-  </si>
-  <si>
-    <t>135017899</t>
-  </si>
-  <si>
-    <t>135139887</t>
-  </si>
-  <si>
-    <t>132723100</t>
-  </si>
-  <si>
-    <t>135002855</t>
-  </si>
-  <si>
-    <t>135141237</t>
-  </si>
-  <si>
-    <t>135054016</t>
-  </si>
-  <si>
-    <t>135018578</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_28.10.2025</t>
+    <t>Processar</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 19/12/2025</t>
+  </si>
+  <si>
+    <t>135773438</t>
+  </si>
+  <si>
+    <t>135791168</t>
+  </si>
+  <si>
+    <t>135791953</t>
+  </si>
+  <si>
+    <t>135790131</t>
+  </si>
+  <si>
+    <t>135818392</t>
+  </si>
+  <si>
+    <t>135827858</t>
+  </si>
+  <si>
+    <t>135836063</t>
+  </si>
+  <si>
+    <t>135825915</t>
+  </si>
+  <si>
+    <t>135832545</t>
+  </si>
+  <si>
+    <t>135841003</t>
+  </si>
+  <si>
+    <t>135830930</t>
+  </si>
+  <si>
+    <t>135834935</t>
+  </si>
+  <si>
+    <t>135834282</t>
+  </si>
+  <si>
+    <t>135813130</t>
+  </si>
+  <si>
+    <t>135766375</t>
+  </si>
+  <si>
+    <t>135858962</t>
+  </si>
+  <si>
+    <t>135839236</t>
+  </si>
+  <si>
+    <t>135890142</t>
+  </si>
+  <si>
+    <t>135834993</t>
+  </si>
+  <si>
+    <t>135911149</t>
+  </si>
+  <si>
+    <t>135915391</t>
+  </si>
+  <si>
+    <t>135923348</t>
+  </si>
+  <si>
+    <t>135904354</t>
+  </si>
+  <si>
+    <t>135431532</t>
+  </si>
+  <si>
+    <t>135936739</t>
+  </si>
+  <si>
+    <t>135926278</t>
+  </si>
+  <si>
+    <t>135674970</t>
+  </si>
+  <si>
+    <t>135679357</t>
+  </si>
+  <si>
+    <t>135705195</t>
+  </si>
+  <si>
+    <t>135716804</t>
+  </si>
+  <si>
+    <t>135716833</t>
+  </si>
+  <si>
+    <t>135724817</t>
+  </si>
+  <si>
+    <t>135726542</t>
+  </si>
+  <si>
+    <t>135731476</t>
+  </si>
+  <si>
+    <t>135734298</t>
+  </si>
+  <si>
+    <t>135942443</t>
+  </si>
+  <si>
+    <t>135943009</t>
+  </si>
+  <si>
+    <t>135943826</t>
+  </si>
+  <si>
+    <t>135944084</t>
+  </si>
+  <si>
+    <t>135821046</t>
+  </si>
+  <si>
+    <t>135944620</t>
+  </si>
+  <si>
+    <t>135840804</t>
+  </si>
+  <si>
+    <t>135835945</t>
+  </si>
+  <si>
+    <t>135777360</t>
+  </si>
+  <si>
+    <t>135946644</t>
+  </si>
+  <si>
+    <t>135797896</t>
+  </si>
+  <si>
+    <t>132941813</t>
+  </si>
+  <si>
+    <t>134203021</t>
+  </si>
+  <si>
+    <t>135866321</t>
+  </si>
+  <si>
+    <t>135834446</t>
+  </si>
+  <si>
+    <t>135762938</t>
+  </si>
+  <si>
+    <t>135764664</t>
+  </si>
+  <si>
+    <t>135952362</t>
+  </si>
+  <si>
+    <t>135772132</t>
+  </si>
+  <si>
+    <t>135773253</t>
+  </si>
+  <si>
+    <t>135833054</t>
+  </si>
+  <si>
+    <t>135819891</t>
+  </si>
+  <si>
+    <t>135782827</t>
+  </si>
+  <si>
+    <t>134622583</t>
+  </si>
+  <si>
+    <t>135777406</t>
+  </si>
+  <si>
+    <t>135777739</t>
+  </si>
+  <si>
+    <t>135778698</t>
+  </si>
+  <si>
+    <t>135944378</t>
+  </si>
+  <si>
+    <t>135953881</t>
+  </si>
+  <si>
+    <t>135855482</t>
+  </si>
+  <si>
+    <t>135826369</t>
+  </si>
+  <si>
+    <t>135884642</t>
+  </si>
+  <si>
+    <t>135958075</t>
+  </si>
+  <si>
+    <t>132675616</t>
+  </si>
+  <si>
+    <t>135745115</t>
+  </si>
+  <si>
+    <t>135745899</t>
+  </si>
+  <si>
+    <t>135958254</t>
+  </si>
+  <si>
+    <t>135755051</t>
+  </si>
+  <si>
+    <t>135844150</t>
+  </si>
+  <si>
+    <t>135861033</t>
+  </si>
+  <si>
+    <t>135785914</t>
+  </si>
+  <si>
+    <t>135837443</t>
+  </si>
+  <si>
+    <t>135832134</t>
+  </si>
+  <si>
+    <t>135799399</t>
+  </si>
+  <si>
+    <t>135813872</t>
+  </si>
+  <si>
+    <t>135956550</t>
+  </si>
+  <si>
+    <t>135946609</t>
+  </si>
+  <si>
+    <t>134727124</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_19.12.2025</t>
+  </si>
+  <si>
+    <t>135721220</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 20/12/2025</t>
+  </si>
+  <si>
+    <t>135721566</t>
+  </si>
+  <si>
+    <t>135728407</t>
+  </si>
+  <si>
+    <t>135729933</t>
+  </si>
+  <si>
+    <t>135754138</t>
+  </si>
+  <si>
+    <t>135721133</t>
+  </si>
+  <si>
+    <t>135839993</t>
+  </si>
+  <si>
+    <t>135895837</t>
+  </si>
+  <si>
+    <t>135747139</t>
+  </si>
+  <si>
+    <t>135701250</t>
+  </si>
+  <si>
+    <t>135716087</t>
+  </si>
+  <si>
+    <t>135716424</t>
+  </si>
+  <si>
+    <t>135721589</t>
+  </si>
+  <si>
+    <t>135725540</t>
+  </si>
+  <si>
+    <t>135743669</t>
+  </si>
+  <si>
+    <t>135746624</t>
+  </si>
+  <si>
+    <t>135749053</t>
+  </si>
+  <si>
+    <t>135750855</t>
+  </si>
+  <si>
+    <t>135754381</t>
+  </si>
+  <si>
+    <t>135756049</t>
+  </si>
+  <si>
+    <t>135834121</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_20.12.2025</t>
+  </si>
+  <si>
+    <t>135816302</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 21/12/2025</t>
+  </si>
+  <si>
+    <t>135818619</t>
+  </si>
+  <si>
+    <t>135816489</t>
+  </si>
+  <si>
+    <t>135866049</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_21.12.2025</t>
   </si>
 </sst>
 </file>
@@ -618,7 +798,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -650,7 +830,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134979721</v>
+        <v>135681689</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -659,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -677,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -695,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -713,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -731,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -749,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -767,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -785,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -803,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -821,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -839,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -857,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -875,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -893,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -911,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -929,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -947,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -965,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -983,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1001,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1019,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1037,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1055,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1073,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1091,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1109,7 +1289,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1127,7 +1307,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1145,7 +1325,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1163,7 +1343,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1181,7 +1361,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1199,7 +1379,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1217,7 +1397,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1235,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1253,7 +1433,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1271,7 +1451,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1289,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1307,7 +1487,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1325,7 +1505,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1343,7 +1523,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1361,7 +1541,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1379,7 +1559,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1397,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1415,7 +1595,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1433,7 +1613,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1451,7 +1631,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1469,7 +1649,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1487,7 +1667,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1505,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1523,7 +1703,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1541,7 +1721,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1559,7 +1739,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1577,7 +1757,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1595,12 +1775,964 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54"/>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1616,31 +2748,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D6D45E-CD06-476B-AEF7-A6D1DD0F2EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907311B1-9A38-48FF-BF17-969EE27C0DED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="91">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,346 +54,253 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusas Sicredi 19/12/2025</t>
-  </si>
-  <si>
-    <t>135773438</t>
-  </si>
-  <si>
-    <t>135791168</t>
-  </si>
-  <si>
-    <t>135791953</t>
-  </si>
-  <si>
-    <t>135790131</t>
-  </si>
-  <si>
-    <t>135818392</t>
-  </si>
-  <si>
-    <t>135827858</t>
-  </si>
-  <si>
-    <t>135836063</t>
-  </si>
-  <si>
-    <t>135825915</t>
-  </si>
-  <si>
-    <t>135832545</t>
-  </si>
-  <si>
-    <t>135841003</t>
-  </si>
-  <si>
-    <t>135830930</t>
-  </si>
-  <si>
-    <t>135834935</t>
-  </si>
-  <si>
-    <t>135834282</t>
-  </si>
-  <si>
-    <t>135813130</t>
-  </si>
-  <si>
-    <t>135766375</t>
-  </si>
-  <si>
-    <t>135858962</t>
-  </si>
-  <si>
-    <t>135839236</t>
-  </si>
-  <si>
-    <t>135890142</t>
-  </si>
-  <si>
-    <t>135834993</t>
-  </si>
-  <si>
-    <t>135911149</t>
-  </si>
-  <si>
-    <t>135915391</t>
-  </si>
-  <si>
-    <t>135923348</t>
-  </si>
-  <si>
-    <t>135904354</t>
-  </si>
-  <si>
-    <t>135431532</t>
-  </si>
-  <si>
-    <t>135936739</t>
-  </si>
-  <si>
-    <t>135926278</t>
-  </si>
-  <si>
-    <t>135674970</t>
-  </si>
-  <si>
-    <t>135679357</t>
-  </si>
-  <si>
-    <t>135705195</t>
-  </si>
-  <si>
-    <t>135716804</t>
-  </si>
-  <si>
-    <t>135716833</t>
-  </si>
-  <si>
-    <t>135724817</t>
-  </si>
-  <si>
-    <t>135726542</t>
-  </si>
-  <si>
-    <t>135731476</t>
-  </si>
-  <si>
-    <t>135734298</t>
-  </si>
-  <si>
-    <t>135942443</t>
-  </si>
-  <si>
-    <t>135943009</t>
-  </si>
-  <si>
-    <t>135943826</t>
-  </si>
-  <si>
-    <t>135944084</t>
-  </si>
-  <si>
-    <t>135821046</t>
-  </si>
-  <si>
-    <t>135944620</t>
-  </si>
-  <si>
-    <t>135840804</t>
-  </si>
-  <si>
-    <t>135835945</t>
-  </si>
-  <si>
-    <t>135777360</t>
-  </si>
-  <si>
-    <t>135946644</t>
-  </si>
-  <si>
-    <t>135797896</t>
-  </si>
-  <si>
-    <t>132941813</t>
-  </si>
-  <si>
-    <t>134203021</t>
-  </si>
-  <si>
-    <t>135866321</t>
-  </si>
-  <si>
-    <t>135834446</t>
-  </si>
-  <si>
-    <t>135762938</t>
-  </si>
-  <si>
-    <t>135764664</t>
-  </si>
-  <si>
-    <t>135952362</t>
-  </si>
-  <si>
-    <t>135772132</t>
-  </si>
-  <si>
-    <t>135773253</t>
-  </si>
-  <si>
-    <t>135833054</t>
-  </si>
-  <si>
-    <t>135819891</t>
-  </si>
-  <si>
-    <t>135782827</t>
-  </si>
-  <si>
-    <t>134622583</t>
-  </si>
-  <si>
-    <t>135777406</t>
-  </si>
-  <si>
-    <t>135777739</t>
-  </si>
-  <si>
-    <t>135778698</t>
-  </si>
-  <si>
-    <t>135944378</t>
-  </si>
-  <si>
-    <t>135953881</t>
-  </si>
-  <si>
-    <t>135855482</t>
-  </si>
-  <si>
-    <t>135826369</t>
-  </si>
-  <si>
-    <t>135884642</t>
-  </si>
-  <si>
-    <t>135958075</t>
-  </si>
-  <si>
-    <t>132675616</t>
-  </si>
-  <si>
-    <t>135745115</t>
-  </si>
-  <si>
-    <t>135745899</t>
-  </si>
-  <si>
-    <t>135958254</t>
-  </si>
-  <si>
-    <t>135755051</t>
-  </si>
-  <si>
-    <t>135844150</t>
-  </si>
-  <si>
-    <t>135861033</t>
-  </si>
-  <si>
-    <t>135785914</t>
-  </si>
-  <si>
-    <t>135837443</t>
-  </si>
-  <si>
-    <t>135832134</t>
-  </si>
-  <si>
-    <t>135799399</t>
-  </si>
-  <si>
-    <t>135813872</t>
-  </si>
-  <si>
-    <t>135956550</t>
-  </si>
-  <si>
-    <t>135946609</t>
-  </si>
-  <si>
-    <t>134727124</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_19.12.2025</t>
-  </si>
-  <si>
-    <t>135721220</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 20/12/2025</t>
-  </si>
-  <si>
-    <t>135721566</t>
-  </si>
-  <si>
-    <t>135728407</t>
-  </si>
-  <si>
-    <t>135729933</t>
-  </si>
-  <si>
-    <t>135754138</t>
-  </si>
-  <si>
-    <t>135721133</t>
-  </si>
-  <si>
-    <t>135839993</t>
-  </si>
-  <si>
-    <t>135895837</t>
-  </si>
-  <si>
-    <t>135747139</t>
-  </si>
-  <si>
-    <t>135701250</t>
-  </si>
-  <si>
-    <t>135716087</t>
-  </si>
-  <si>
-    <t>135716424</t>
-  </si>
-  <si>
-    <t>135721589</t>
-  </si>
-  <si>
-    <t>135725540</t>
-  </si>
-  <si>
-    <t>135743669</t>
-  </si>
-  <si>
-    <t>135746624</t>
-  </si>
-  <si>
-    <t>135749053</t>
-  </si>
-  <si>
-    <t>135750855</t>
-  </si>
-  <si>
-    <t>135754381</t>
-  </si>
-  <si>
-    <t>135756049</t>
-  </si>
-  <si>
-    <t>135834121</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_20.12.2025</t>
-  </si>
-  <si>
-    <t>135816302</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 21/12/2025</t>
-  </si>
-  <si>
-    <t>135818619</t>
-  </si>
-  <si>
-    <t>135816489</t>
-  </si>
-  <si>
-    <t>135866049</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_21.12.2025</t>
+    <t>Recusas Sicredi 22/12/2025</t>
+  </si>
+  <si>
+    <t>135797924</t>
+  </si>
+  <si>
+    <t>135807951</t>
+  </si>
+  <si>
+    <t>135828472</t>
+  </si>
+  <si>
+    <t>135844223</t>
+  </si>
+  <si>
+    <t>135844288</t>
+  </si>
+  <si>
+    <t>135836027</t>
+  </si>
+  <si>
+    <t>135838857</t>
+  </si>
+  <si>
+    <t>135847129</t>
+  </si>
+  <si>
+    <t>135819122</t>
+  </si>
+  <si>
+    <t>135820917</t>
+  </si>
+  <si>
+    <t>135815668</t>
+  </si>
+  <si>
+    <t>135818050</t>
+  </si>
+  <si>
+    <t>135808458</t>
+  </si>
+  <si>
+    <t>135852497</t>
+  </si>
+  <si>
+    <t>135859433</t>
+  </si>
+  <si>
+    <t>135820028</t>
+  </si>
+  <si>
+    <t>135856701</t>
+  </si>
+  <si>
+    <t>135877007</t>
+  </si>
+  <si>
+    <t>135875838</t>
+  </si>
+  <si>
+    <t>135883965</t>
+  </si>
+  <si>
+    <t>135891869</t>
+  </si>
+  <si>
+    <t>135881150</t>
+  </si>
+  <si>
+    <t>135900927</t>
+  </si>
+  <si>
+    <t>135901047</t>
+  </si>
+  <si>
+    <t>135913593</t>
+  </si>
+  <si>
+    <t>135897755</t>
+  </si>
+  <si>
+    <t>135919009</t>
+  </si>
+  <si>
+    <t>135927518</t>
+  </si>
+  <si>
+    <t>135935887</t>
+  </si>
+  <si>
+    <t>135927478</t>
+  </si>
+  <si>
+    <t>135931155</t>
+  </si>
+  <si>
+    <t>135936123</t>
+  </si>
+  <si>
+    <t>135926744</t>
+  </si>
+  <si>
+    <t>135933542</t>
+  </si>
+  <si>
+    <t>135963077</t>
+  </si>
+  <si>
+    <t>135961940</t>
+  </si>
+  <si>
+    <t>135961456</t>
+  </si>
+  <si>
+    <t>135946648</t>
+  </si>
+  <si>
+    <t>135883096</t>
+  </si>
+  <si>
+    <t>135806606</t>
+  </si>
+  <si>
+    <t>135815418</t>
+  </si>
+  <si>
+    <t>135769350</t>
+  </si>
+  <si>
+    <t>135842681</t>
+  </si>
+  <si>
+    <t>135976215</t>
+  </si>
+  <si>
+    <t>135881000</t>
+  </si>
+  <si>
+    <t>135977362</t>
+  </si>
+  <si>
+    <t>135797857</t>
+  </si>
+  <si>
+    <t>135981291</t>
+  </si>
+  <si>
+    <t>135982077</t>
+  </si>
+  <si>
+    <t>135982504</t>
+  </si>
+  <si>
+    <t>135840983</t>
+  </si>
+  <si>
+    <t>135754903</t>
+  </si>
+  <si>
+    <t>135764249</t>
+  </si>
+  <si>
+    <t>135815643</t>
+  </si>
+  <si>
+    <t>135810685</t>
+  </si>
+  <si>
+    <t>135763451</t>
+  </si>
+  <si>
+    <t>135975375</t>
+  </si>
+  <si>
+    <t>135854752</t>
+  </si>
+  <si>
+    <t>135913227</t>
+  </si>
+  <si>
+    <t>132126371</t>
+  </si>
+  <si>
+    <t>135858823</t>
+  </si>
+  <si>
+    <t>135838514</t>
+  </si>
+  <si>
+    <t>135984348</t>
+  </si>
+  <si>
+    <t>135833685</t>
+  </si>
+  <si>
+    <t>135776248</t>
+  </si>
+  <si>
+    <t>135772201</t>
+  </si>
+  <si>
+    <t>135829081</t>
+  </si>
+  <si>
+    <t>133297809</t>
+  </si>
+  <si>
+    <t>135786554</t>
+  </si>
+  <si>
+    <t>135788625</t>
+  </si>
+  <si>
+    <t>135789768</t>
+  </si>
+  <si>
+    <t>135789931</t>
+  </si>
+  <si>
+    <t>135795802</t>
+  </si>
+  <si>
+    <t>135796978</t>
+  </si>
+  <si>
+    <t>135797823</t>
+  </si>
+  <si>
+    <t>135800223</t>
+  </si>
+  <si>
+    <t>135803478</t>
+  </si>
+  <si>
+    <t>135808027</t>
+  </si>
+  <si>
+    <t>135808244</t>
+  </si>
+  <si>
+    <t>135808376</t>
+  </si>
+  <si>
+    <t>135812293</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.12.2025</t>
   </si>
 </sst>
 </file>
@@ -798,7 +705,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -830,7 +737,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135681689</v>
+        <v>135765403</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
@@ -839,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
@@ -857,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
@@ -875,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>7</v>
@@ -893,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>7</v>
@@ -911,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>7</v>
@@ -929,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>7</v>
@@ -947,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>7</v>
@@ -965,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>7</v>
@@ -983,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>7</v>
@@ -1001,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>7</v>
@@ -1019,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>7</v>
@@ -1037,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>7</v>
@@ -1055,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>7</v>
@@ -1073,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>7</v>
@@ -1091,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>7</v>
@@ -1109,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>7</v>
@@ -1127,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>7</v>
@@ -1145,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>7</v>
@@ -1163,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>7</v>
@@ -1181,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>7</v>
@@ -1199,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>7</v>
@@ -1217,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>7</v>
@@ -1235,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>7</v>
@@ -1253,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>7</v>
@@ -1271,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>7</v>
@@ -1289,7 +1196,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>7</v>
@@ -1307,7 +1214,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>7</v>
@@ -1325,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>7</v>
@@ -1343,7 +1250,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>7</v>
@@ -1361,7 +1268,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>7</v>
@@ -1379,7 +1286,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>7</v>
@@ -1397,7 +1304,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>7</v>
@@ -1415,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -1433,7 +1340,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>7</v>
@@ -1451,7 +1358,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>7</v>
@@ -1469,7 +1376,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -1487,7 +1394,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>7</v>
@@ -1505,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>7</v>
@@ -1523,7 +1430,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -1541,7 +1448,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>7</v>
@@ -1559,7 +1466,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>7</v>
@@ -1577,7 +1484,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -1595,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>7</v>
@@ -1613,7 +1520,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>7</v>
@@ -1631,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>7</v>
@@ -1649,7 +1556,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>7</v>
@@ -1667,7 +1574,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>7</v>
@@ -1685,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>7</v>
@@ -1703,7 +1610,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>7</v>
@@ -1721,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>7</v>
@@ -1739,7 +1646,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>7</v>
@@ -1757,7 +1664,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>7</v>
@@ -1775,7 +1682,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>7</v>
@@ -1793,7 +1700,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -1810,7 +1717,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>7</v>
@@ -1827,7 +1734,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>7</v>
@@ -1844,7 +1751,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>7</v>
@@ -1861,7 +1768,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>7</v>
@@ -1878,7 +1785,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>7</v>
@@ -1895,7 +1802,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>7</v>
@@ -1912,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>7</v>
@@ -1929,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>7</v>
@@ -1946,7 +1853,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>7</v>
@@ -1963,7 +1870,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>7</v>
@@ -1980,7 +1887,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>7</v>
@@ -1997,7 +1904,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>7</v>
@@ -2014,7 +1921,7 @@
         <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>7</v>
@@ -2031,7 +1938,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>7</v>
@@ -2048,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>7</v>
@@ -2065,7 +1972,7 @@
         <v>8</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>7</v>
@@ -2082,7 +1989,7 @@
         <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>7</v>
@@ -2099,7 +2006,7 @@
         <v>8</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>7</v>
@@ -2116,7 +2023,7 @@
         <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>7</v>
@@ -2133,7 +2040,7 @@
         <v>8</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>7</v>
@@ -2150,7 +2057,7 @@
         <v>8</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>7</v>
@@ -2167,7 +2074,7 @@
         <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>7</v>
@@ -2184,7 +2091,7 @@
         <v>8</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>7</v>
@@ -2201,7 +2108,7 @@
         <v>8</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>7</v>
@@ -2218,7 +2125,7 @@
         <v>8</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>7</v>
@@ -2235,7 +2142,7 @@
         <v>8</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>7</v>
@@ -2252,7 +2159,7 @@
         <v>8</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>7</v>
@@ -2269,468 +2176,9 @@
         <v>8</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B96" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B97" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B102" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B106" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B107" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E110" s="2" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2748,31 +2196,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05555340-37DB-4843-B9C2-95B389594BC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E930504F-7B1A-46F0-8C11-E77AB3BBBF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="190">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,555 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 24.12.2025</t>
+  </si>
+  <si>
+    <t>135803565</t>
+  </si>
+  <si>
+    <t>135797519</t>
+  </si>
+  <si>
+    <t>135873070</t>
+  </si>
+  <si>
+    <t>135862572</t>
+  </si>
+  <si>
+    <t>135861662</t>
+  </si>
+  <si>
+    <t>135892257</t>
+  </si>
+  <si>
+    <t>135886892</t>
+  </si>
+  <si>
+    <t>135893499</t>
+  </si>
+  <si>
+    <t>135907860</t>
+  </si>
+  <si>
+    <t>135883668</t>
+  </si>
+  <si>
+    <t>135905733</t>
+  </si>
+  <si>
+    <t>135922388</t>
+  </si>
+  <si>
+    <t>135919468</t>
+  </si>
+  <si>
+    <t>135930396</t>
+  </si>
+  <si>
+    <t>135921630</t>
+  </si>
+  <si>
+    <t>135943426</t>
+  </si>
+  <si>
+    <t>135929788</t>
+  </si>
+  <si>
+    <t>135868690</t>
+  </si>
+  <si>
+    <t>135997740</t>
+  </si>
+  <si>
+    <t>135998909</t>
+  </si>
+  <si>
+    <t>135787533</t>
+  </si>
+  <si>
+    <t>135881459</t>
+  </si>
+  <si>
+    <t>136012941</t>
+  </si>
+  <si>
+    <t>136012526</t>
+  </si>
+  <si>
+    <t>136013908</t>
+  </si>
+  <si>
+    <t>136014872</t>
+  </si>
+  <si>
+    <t>136013505</t>
+  </si>
+  <si>
+    <t>136014374</t>
+  </si>
+  <si>
+    <t>135899343</t>
+  </si>
+  <si>
+    <t>135865147</t>
+  </si>
+  <si>
+    <t>135867078</t>
+  </si>
+  <si>
+    <t>135880622</t>
+  </si>
+  <si>
+    <t>135889468</t>
+  </si>
+  <si>
+    <t>135284295</t>
+  </si>
+  <si>
+    <t>135907271</t>
+  </si>
+  <si>
+    <t>135908899</t>
+  </si>
+  <si>
+    <t>135904320</t>
+  </si>
+  <si>
+    <t>135909882</t>
+  </si>
+  <si>
+    <t>135858382</t>
+  </si>
+  <si>
+    <t>135901487</t>
+  </si>
+  <si>
+    <t>131651261</t>
+  </si>
+  <si>
+    <t>135882321</t>
+  </si>
+  <si>
+    <t>135889934</t>
+  </si>
+  <si>
+    <t>135902878</t>
+  </si>
+  <si>
+    <t>135910956</t>
+  </si>
+  <si>
+    <t>135168026</t>
+  </si>
+  <si>
+    <t>135876842</t>
+  </si>
+  <si>
+    <t>135873218</t>
+  </si>
+  <si>
+    <t>131203867</t>
+  </si>
+  <si>
+    <t>Macro 24. 12 Sicred</t>
+  </si>
+  <si>
+    <t>135786657</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 23.12.2025</t>
+  </si>
+  <si>
+    <t>135799651</t>
+  </si>
+  <si>
+    <t>135793552</t>
+  </si>
+  <si>
+    <t>135817420</t>
+  </si>
+  <si>
+    <t>135814609</t>
+  </si>
+  <si>
+    <t>135846339</t>
+  </si>
+  <si>
+    <t>135839448</t>
+  </si>
+  <si>
+    <t>135841784</t>
+  </si>
+  <si>
+    <t>135844098</t>
+  </si>
+  <si>
+    <t>135824981</t>
+  </si>
+  <si>
+    <t>135825494</t>
+  </si>
+  <si>
+    <t>135841241</t>
+  </si>
+  <si>
+    <t>135845938</t>
+  </si>
+  <si>
+    <t>135824561</t>
+  </si>
+  <si>
+    <t>135807193</t>
+  </si>
+  <si>
+    <t>135814570</t>
+  </si>
+  <si>
+    <t>135816255</t>
+  </si>
+  <si>
+    <t>135869062</t>
+  </si>
+  <si>
+    <t>135873776</t>
+  </si>
+  <si>
+    <t>135891112</t>
+  </si>
+  <si>
+    <t>135890743</t>
+  </si>
+  <si>
+    <t>135892355</t>
+  </si>
+  <si>
+    <t>135885034</t>
+  </si>
+  <si>
+    <t>135884408</t>
+  </si>
+  <si>
+    <t>135908334</t>
+  </si>
+  <si>
+    <t>135912363</t>
+  </si>
+  <si>
+    <t>135898220</t>
+  </si>
+  <si>
+    <t>135900509</t>
+  </si>
+  <si>
+    <t>135907986</t>
+  </si>
+  <si>
+    <t>135897696</t>
+  </si>
+  <si>
+    <t>135899640</t>
+  </si>
+  <si>
+    <t>135920516</t>
+  </si>
+  <si>
+    <t>135922320</t>
+  </si>
+  <si>
+    <t>135928195</t>
+  </si>
+  <si>
+    <t>135935855</t>
+  </si>
+  <si>
+    <t>135929413</t>
+  </si>
+  <si>
+    <t>135947126</t>
+  </si>
+  <si>
+    <t>135947422</t>
+  </si>
+  <si>
+    <t>135958504</t>
+  </si>
+  <si>
+    <t>135940896</t>
+  </si>
+  <si>
+    <t>135948589</t>
+  </si>
+  <si>
+    <t>135954391</t>
+  </si>
+  <si>
+    <t>135883063</t>
+  </si>
+  <si>
+    <t>135859626</t>
+  </si>
+  <si>
+    <t>135950989</t>
+  </si>
+  <si>
+    <t>135962150</t>
+  </si>
+  <si>
+    <t>135861415</t>
+  </si>
+  <si>
+    <t>135901511</t>
+  </si>
+  <si>
+    <t>135976813</t>
+  </si>
+  <si>
+    <t>135985376</t>
+  </si>
+  <si>
+    <t>135983281</t>
+  </si>
+  <si>
+    <t>135813044</t>
+  </si>
+  <si>
+    <t>135814171</t>
+  </si>
+  <si>
+    <t>135777217</t>
+  </si>
+  <si>
+    <t>135816438</t>
+  </si>
+  <si>
+    <t>135817621</t>
+  </si>
+  <si>
+    <t>135818953</t>
+  </si>
+  <si>
+    <t>135819240</t>
+  </si>
+  <si>
+    <t>135819327</t>
+  </si>
+  <si>
+    <t>135820319</t>
+  </si>
+  <si>
+    <t>135821148</t>
+  </si>
+  <si>
+    <t>135821936</t>
+  </si>
+  <si>
+    <t>135825479</t>
+  </si>
+  <si>
+    <t>135826844</t>
+  </si>
+  <si>
+    <t>135830423</t>
+  </si>
+  <si>
+    <t>135831403</t>
+  </si>
+  <si>
+    <t>135832538</t>
+  </si>
+  <si>
+    <t>135833328</t>
+  </si>
+  <si>
+    <t>135835238</t>
+  </si>
+  <si>
+    <t>135837814</t>
+  </si>
+  <si>
+    <t>135837860</t>
+  </si>
+  <si>
+    <t>135838333</t>
+  </si>
+  <si>
+    <t>135839133</t>
+  </si>
+  <si>
+    <t>135979898</t>
+  </si>
+  <si>
+    <t>135841319</t>
+  </si>
+  <si>
+    <t>135841942</t>
+  </si>
+  <si>
+    <t>135842346</t>
+  </si>
+  <si>
+    <t>135841523</t>
+  </si>
+  <si>
+    <t>135841546</t>
+  </si>
+  <si>
+    <t>135843710</t>
+  </si>
+  <si>
+    <t>135845274</t>
+  </si>
+  <si>
+    <t>135845297</t>
+  </si>
+  <si>
+    <t>135772583</t>
+  </si>
+  <si>
+    <t>135844139</t>
+  </si>
+  <si>
+    <t>135773298</t>
+  </si>
+  <si>
+    <t>135845913</t>
+  </si>
+  <si>
+    <t>135768260</t>
+  </si>
+  <si>
+    <t>135776410</t>
+  </si>
+  <si>
+    <t>135777481</t>
+  </si>
+  <si>
+    <t>135795729</t>
+  </si>
+  <si>
+    <t>135844834</t>
+  </si>
+  <si>
+    <t>135990436</t>
+  </si>
+  <si>
+    <t>135831620</t>
+  </si>
+  <si>
+    <t>135857254</t>
+  </si>
+  <si>
+    <t>134737221</t>
+  </si>
+  <si>
+    <t>135806354</t>
+  </si>
+  <si>
+    <t>135903286</t>
+  </si>
+  <si>
+    <t>133320663</t>
+  </si>
+  <si>
+    <t>135861265</t>
+  </si>
+  <si>
+    <t>135995209</t>
+  </si>
+  <si>
+    <t>131967144</t>
+  </si>
+  <si>
+    <t>135866811</t>
+  </si>
+  <si>
+    <t>135997732</t>
+  </si>
+  <si>
+    <t>135952367</t>
+  </si>
+  <si>
+    <t>135903935</t>
+  </si>
+  <si>
+    <t>135791059</t>
+  </si>
+  <si>
+    <t>136001426</t>
+  </si>
+  <si>
+    <t>135484297</t>
+  </si>
+  <si>
+    <t>136002181</t>
+  </si>
+  <si>
+    <t>135992170</t>
+  </si>
+  <si>
+    <t>134664469</t>
+  </si>
+  <si>
+    <t>135881072</t>
+  </si>
+  <si>
+    <t>135796703</t>
+  </si>
+  <si>
+    <t>136005560</t>
+  </si>
+  <si>
+    <t>135907086</t>
+  </si>
+  <si>
+    <t>135797505</t>
+  </si>
+  <si>
+    <t>135819617</t>
+  </si>
+  <si>
+    <t>135820442</t>
+  </si>
+  <si>
+    <t>135876167</t>
+  </si>
+  <si>
+    <t>135832853</t>
+  </si>
+  <si>
+    <t>135858044</t>
+  </si>
+  <si>
+    <t>135887758</t>
+  </si>
+  <si>
+    <t>135880315</t>
+  </si>
+  <si>
+    <t>135883336</t>
+  </si>
+  <si>
+    <t>135862374</t>
+  </si>
+  <si>
+    <t>135859844</t>
+  </si>
+  <si>
+    <t>135875464</t>
+  </si>
+  <si>
+    <t>135906042</t>
+  </si>
+  <si>
+    <t>135832425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indexação FG Sicred 23.12 </t>
   </si>
 </sst>
 </file>
@@ -453,7 +1002,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F180"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,466 +1033,3098 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>135797706</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F46"/>
     </row>
-    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F47"/>
     </row>
-    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="5:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>189</v>
+      </c>
       <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E180" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E930504F-7B1A-46F0-8C11-E77AB3BBBF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA0D8FA-FE87-4453-A176-968C5B6021AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="171">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,550 +54,493 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 24.12.2025</t>
-  </si>
-  <si>
-    <t>135803565</t>
-  </si>
-  <si>
-    <t>135797519</t>
-  </si>
-  <si>
-    <t>135873070</t>
-  </si>
-  <si>
-    <t>135862572</t>
-  </si>
-  <si>
-    <t>135861662</t>
-  </si>
-  <si>
-    <t>135892257</t>
-  </si>
-  <si>
-    <t>135886892</t>
-  </si>
-  <si>
-    <t>135893499</t>
-  </si>
-  <si>
-    <t>135907860</t>
-  </si>
-  <si>
-    <t>135883668</t>
-  </si>
-  <si>
-    <t>135905733</t>
-  </si>
-  <si>
-    <t>135922388</t>
-  </si>
-  <si>
-    <t>135919468</t>
-  </si>
-  <si>
-    <t>135930396</t>
-  </si>
-  <si>
-    <t>135921630</t>
-  </si>
-  <si>
-    <t>135943426</t>
-  </si>
-  <si>
-    <t>135929788</t>
-  </si>
-  <si>
-    <t>135868690</t>
-  </si>
-  <si>
-    <t>135997740</t>
-  </si>
-  <si>
-    <t>135998909</t>
-  </si>
-  <si>
-    <t>135787533</t>
-  </si>
-  <si>
-    <t>135881459</t>
-  </si>
-  <si>
-    <t>136012941</t>
-  </si>
-  <si>
-    <t>136012526</t>
-  </si>
-  <si>
-    <t>136013908</t>
-  </si>
-  <si>
-    <t>136014872</t>
-  </si>
-  <si>
-    <t>136013505</t>
-  </si>
-  <si>
-    <t>136014374</t>
-  </si>
-  <si>
-    <t>135899343</t>
-  </si>
-  <si>
-    <t>135865147</t>
-  </si>
-  <si>
-    <t>135867078</t>
-  </si>
-  <si>
-    <t>135880622</t>
-  </si>
-  <si>
-    <t>135889468</t>
-  </si>
-  <si>
-    <t>135284295</t>
-  </si>
-  <si>
-    <t>135907271</t>
-  </si>
-  <si>
-    <t>135908899</t>
-  </si>
-  <si>
-    <t>135904320</t>
-  </si>
-  <si>
-    <t>135909882</t>
-  </si>
-  <si>
-    <t>135858382</t>
-  </si>
-  <si>
-    <t>135901487</t>
-  </si>
-  <si>
-    <t>131651261</t>
-  </si>
-  <si>
-    <t>135882321</t>
-  </si>
-  <si>
-    <t>135889934</t>
-  </si>
-  <si>
-    <t>135902878</t>
-  </si>
-  <si>
-    <t>135910956</t>
-  </si>
-  <si>
-    <t>135168026</t>
-  </si>
-  <si>
-    <t>135876842</t>
-  </si>
-  <si>
-    <t>135873218</t>
-  </si>
-  <si>
-    <t>131203867</t>
-  </si>
-  <si>
-    <t>Macro 24. 12 Sicred</t>
-  </si>
-  <si>
-    <t>135786657</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 23.12.2025</t>
-  </si>
-  <si>
-    <t>135799651</t>
-  </si>
-  <si>
-    <t>135793552</t>
-  </si>
-  <si>
-    <t>135817420</t>
-  </si>
-  <si>
-    <t>135814609</t>
-  </si>
-  <si>
-    <t>135846339</t>
-  </si>
-  <si>
-    <t>135839448</t>
-  </si>
-  <si>
-    <t>135841784</t>
-  </si>
-  <si>
-    <t>135844098</t>
-  </si>
-  <si>
-    <t>135824981</t>
-  </si>
-  <si>
-    <t>135825494</t>
-  </si>
-  <si>
-    <t>135841241</t>
-  </si>
-  <si>
-    <t>135845938</t>
-  </si>
-  <si>
-    <t>135824561</t>
-  </si>
-  <si>
-    <t>135807193</t>
-  </si>
-  <si>
-    <t>135814570</t>
-  </si>
-  <si>
-    <t>135816255</t>
-  </si>
-  <si>
-    <t>135869062</t>
-  </si>
-  <si>
-    <t>135873776</t>
-  </si>
-  <si>
-    <t>135891112</t>
-  </si>
-  <si>
-    <t>135890743</t>
-  </si>
-  <si>
-    <t>135892355</t>
-  </si>
-  <si>
-    <t>135885034</t>
-  </si>
-  <si>
-    <t>135884408</t>
-  </si>
-  <si>
-    <t>135908334</t>
-  </si>
-  <si>
-    <t>135912363</t>
-  </si>
-  <si>
-    <t>135898220</t>
-  </si>
-  <si>
-    <t>135900509</t>
-  </si>
-  <si>
-    <t>135907986</t>
-  </si>
-  <si>
-    <t>135897696</t>
-  </si>
-  <si>
-    <t>135899640</t>
-  </si>
-  <si>
-    <t>135920516</t>
-  </si>
-  <si>
-    <t>135922320</t>
-  </si>
-  <si>
-    <t>135928195</t>
-  </si>
-  <si>
-    <t>135935855</t>
-  </si>
-  <si>
-    <t>135929413</t>
-  </si>
-  <si>
-    <t>135947126</t>
-  </si>
-  <si>
-    <t>135947422</t>
-  </si>
-  <si>
-    <t>135958504</t>
-  </si>
-  <si>
-    <t>135940896</t>
-  </si>
-  <si>
-    <t>135948589</t>
-  </si>
-  <si>
-    <t>135954391</t>
-  </si>
-  <si>
-    <t>135883063</t>
-  </si>
-  <si>
-    <t>135859626</t>
-  </si>
-  <si>
-    <t>135950989</t>
-  </si>
-  <si>
-    <t>135962150</t>
-  </si>
-  <si>
-    <t>135861415</t>
-  </si>
-  <si>
-    <t>135901511</t>
-  </si>
-  <si>
-    <t>135976813</t>
-  </si>
-  <si>
-    <t>135985376</t>
-  </si>
-  <si>
-    <t>135983281</t>
-  </si>
-  <si>
-    <t>135813044</t>
-  </si>
-  <si>
-    <t>135814171</t>
-  </si>
-  <si>
-    <t>135777217</t>
-  </si>
-  <si>
-    <t>135816438</t>
-  </si>
-  <si>
-    <t>135817621</t>
-  </si>
-  <si>
-    <t>135818953</t>
-  </si>
-  <si>
-    <t>135819240</t>
-  </si>
-  <si>
-    <t>135819327</t>
-  </si>
-  <si>
-    <t>135820319</t>
-  </si>
-  <si>
-    <t>135821148</t>
-  </si>
-  <si>
-    <t>135821936</t>
-  </si>
-  <si>
-    <t>135825479</t>
-  </si>
-  <si>
-    <t>135826844</t>
-  </si>
-  <si>
-    <t>135830423</t>
-  </si>
-  <si>
-    <t>135831403</t>
-  </si>
-  <si>
-    <t>135832538</t>
-  </si>
-  <si>
-    <t>135833328</t>
-  </si>
-  <si>
-    <t>135835238</t>
-  </si>
-  <si>
-    <t>135837814</t>
-  </si>
-  <si>
-    <t>135837860</t>
-  </si>
-  <si>
-    <t>135838333</t>
-  </si>
-  <si>
-    <t>135839133</t>
-  </si>
-  <si>
-    <t>135979898</t>
-  </si>
-  <si>
-    <t>135841319</t>
-  </si>
-  <si>
-    <t>135841942</t>
-  </si>
-  <si>
-    <t>135842346</t>
-  </si>
-  <si>
-    <t>135841523</t>
-  </si>
-  <si>
-    <t>135841546</t>
-  </si>
-  <si>
-    <t>135843710</t>
-  </si>
-  <si>
-    <t>135845274</t>
-  </si>
-  <si>
-    <t>135845297</t>
-  </si>
-  <si>
-    <t>135772583</t>
-  </si>
-  <si>
-    <t>135844139</t>
-  </si>
-  <si>
-    <t>135773298</t>
-  </si>
-  <si>
-    <t>135845913</t>
-  </si>
-  <si>
-    <t>135768260</t>
-  </si>
-  <si>
-    <t>135776410</t>
-  </si>
-  <si>
-    <t>135777481</t>
-  </si>
-  <si>
-    <t>135795729</t>
-  </si>
-  <si>
-    <t>135844834</t>
-  </si>
-  <si>
-    <t>135990436</t>
-  </si>
-  <si>
-    <t>135831620</t>
-  </si>
-  <si>
-    <t>135857254</t>
-  </si>
-  <si>
-    <t>134737221</t>
-  </si>
-  <si>
-    <t>135806354</t>
-  </si>
-  <si>
-    <t>135903286</t>
-  </si>
-  <si>
-    <t>133320663</t>
-  </si>
-  <si>
-    <t>135861265</t>
-  </si>
-  <si>
-    <t>135995209</t>
-  </si>
-  <si>
-    <t>131967144</t>
-  </si>
-  <si>
-    <t>135866811</t>
-  </si>
-  <si>
-    <t>135997732</t>
-  </si>
-  <si>
-    <t>135952367</t>
-  </si>
-  <si>
-    <t>135903935</t>
-  </si>
-  <si>
-    <t>135791059</t>
-  </si>
-  <si>
-    <t>136001426</t>
-  </si>
-  <si>
-    <t>135484297</t>
-  </si>
-  <si>
-    <t>136002181</t>
-  </si>
-  <si>
-    <t>135992170</t>
-  </si>
-  <si>
-    <t>134664469</t>
-  </si>
-  <si>
-    <t>135881072</t>
-  </si>
-  <si>
-    <t>135796703</t>
-  </si>
-  <si>
-    <t>136005560</t>
-  </si>
-  <si>
-    <t>135907086</t>
-  </si>
-  <si>
-    <t>135797505</t>
-  </si>
-  <si>
-    <t>135819617</t>
-  </si>
-  <si>
-    <t>135820442</t>
-  </si>
-  <si>
-    <t>135876167</t>
-  </si>
-  <si>
-    <t>135832853</t>
-  </si>
-  <si>
-    <t>135858044</t>
-  </si>
-  <si>
-    <t>135887758</t>
-  </si>
-  <si>
-    <t>135880315</t>
-  </si>
-  <si>
-    <t>135883336</t>
-  </si>
-  <si>
-    <t>135862374</t>
-  </si>
-  <si>
-    <t>135859844</t>
-  </si>
-  <si>
-    <t>135875464</t>
-  </si>
-  <si>
-    <t>135906042</t>
-  </si>
-  <si>
-    <t>135832425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Indexação FG Sicred 23.12 </t>
+    <t>Recusas Sicredi 26/12/2025</t>
+  </si>
+  <si>
+    <t>135284151</t>
+  </si>
+  <si>
+    <t>135843866</t>
+  </si>
+  <si>
+    <t>135839146</t>
+  </si>
+  <si>
+    <t>135834209</t>
+  </si>
+  <si>
+    <t>135858367</t>
+  </si>
+  <si>
+    <t>135893315</t>
+  </si>
+  <si>
+    <t>135883822</t>
+  </si>
+  <si>
+    <t>135892167</t>
+  </si>
+  <si>
+    <t>135893087</t>
+  </si>
+  <si>
+    <t>135891147</t>
+  </si>
+  <si>
+    <t>135876175</t>
+  </si>
+  <si>
+    <t>135889035</t>
+  </si>
+  <si>
+    <t>135853074</t>
+  </si>
+  <si>
+    <t>135892552</t>
+  </si>
+  <si>
+    <t>135889668</t>
+  </si>
+  <si>
+    <t>135907244</t>
+  </si>
+  <si>
+    <t>135927423</t>
+  </si>
+  <si>
+    <t>135890398</t>
+  </si>
+  <si>
+    <t>135934386</t>
+  </si>
+  <si>
+    <t>135937497</t>
+  </si>
+  <si>
+    <t>135931449</t>
+  </si>
+  <si>
+    <t>135917156</t>
+  </si>
+  <si>
+    <t>135933182</t>
+  </si>
+  <si>
+    <t>135939700</t>
+  </si>
+  <si>
+    <t>134380578</t>
+  </si>
+  <si>
+    <t>134727124</t>
+  </si>
+  <si>
+    <t>135954425</t>
+  </si>
+  <si>
+    <t>135947665</t>
+  </si>
+  <si>
+    <t>135960034</t>
+  </si>
+  <si>
+    <t>135960652</t>
+  </si>
+  <si>
+    <t>135962697</t>
+  </si>
+  <si>
+    <t>135947034</t>
+  </si>
+  <si>
+    <t>135877823</t>
+  </si>
+  <si>
+    <t>135947526</t>
+  </si>
+  <si>
+    <t>135948268</t>
+  </si>
+  <si>
+    <t>135948838</t>
+  </si>
+  <si>
+    <t>135915297</t>
+  </si>
+  <si>
+    <t>135912055</t>
+  </si>
+  <si>
+    <t>135866868</t>
+  </si>
+  <si>
+    <t>135972799</t>
+  </si>
+  <si>
+    <t>135880945</t>
+  </si>
+  <si>
+    <t>135979618</t>
+  </si>
+  <si>
+    <t>135976154</t>
+  </si>
+  <si>
+    <t>135986768</t>
+  </si>
+  <si>
+    <t>135969017</t>
+  </si>
+  <si>
+    <t>135946582</t>
+  </si>
+  <si>
+    <t>136000851</t>
+  </si>
+  <si>
+    <t>135993789</t>
+  </si>
+  <si>
+    <t>135946567</t>
+  </si>
+  <si>
+    <t>135994266</t>
+  </si>
+  <si>
+    <t>135925223</t>
+  </si>
+  <si>
+    <t>136000088</t>
+  </si>
+  <si>
+    <t>135997890</t>
+  </si>
+  <si>
+    <t>136012708</t>
+  </si>
+  <si>
+    <t>136011856</t>
+  </si>
+  <si>
+    <t>136014223</t>
+  </si>
+  <si>
+    <t>136015730</t>
+  </si>
+  <si>
+    <t>136017518</t>
+  </si>
+  <si>
+    <t>136011642</t>
+  </si>
+  <si>
+    <t>135834476</t>
+  </si>
+  <si>
+    <t>135838685</t>
+  </si>
+  <si>
+    <t>135833364</t>
+  </si>
+  <si>
+    <t>135834073</t>
+  </si>
+  <si>
+    <t>135839271</t>
+  </si>
+  <si>
+    <t>135841456</t>
+  </si>
+  <si>
+    <t>135819669</t>
+  </si>
+  <si>
+    <t>135834064</t>
+  </si>
+  <si>
+    <t>135834781</t>
+  </si>
+  <si>
+    <t>135858483</t>
+  </si>
+  <si>
+    <t>136022327</t>
+  </si>
+  <si>
+    <t>135839152</t>
+  </si>
+  <si>
+    <t>136022410</t>
+  </si>
+  <si>
+    <t>131714833</t>
+  </si>
+  <si>
+    <t>135840138</t>
+  </si>
+  <si>
+    <t>135846295</t>
+  </si>
+  <si>
+    <t>135904272</t>
+  </si>
+  <si>
+    <t>133364810</t>
+  </si>
+  <si>
+    <t>134010937</t>
+  </si>
+  <si>
+    <t>135921783</t>
+  </si>
+  <si>
+    <t>133705337</t>
+  </si>
+  <si>
+    <t>132697911</t>
+  </si>
+  <si>
+    <t>135852381</t>
+  </si>
+  <si>
+    <t>135883086</t>
+  </si>
+  <si>
+    <t>135856427</t>
+  </si>
+  <si>
+    <t>135857564</t>
+  </si>
+  <si>
+    <t>135868235</t>
+  </si>
+  <si>
+    <t>135861133</t>
+  </si>
+  <si>
+    <t>135863437</t>
+  </si>
+  <si>
+    <t>135864048</t>
+  </si>
+  <si>
+    <t>135859945</t>
+  </si>
+  <si>
+    <t>135865631</t>
+  </si>
+  <si>
+    <t>135924454</t>
+  </si>
+  <si>
+    <t>135935741</t>
+  </si>
+  <si>
+    <t>131745850</t>
+  </si>
+  <si>
+    <t>135867440</t>
+  </si>
+  <si>
+    <t>135868335</t>
+  </si>
+  <si>
+    <t>135868424</t>
+  </si>
+  <si>
+    <t>135869387</t>
+  </si>
+  <si>
+    <t>136027361</t>
+  </si>
+  <si>
+    <t>135873980</t>
+  </si>
+  <si>
+    <t>135878374</t>
+  </si>
+  <si>
+    <t>135875189</t>
+  </si>
+  <si>
+    <t>135875323</t>
+  </si>
+  <si>
+    <t>135885355</t>
+  </si>
+  <si>
+    <t>135875754</t>
+  </si>
+  <si>
+    <t>135876024</t>
+  </si>
+  <si>
+    <t>135876992</t>
+  </si>
+  <si>
+    <t>135877225</t>
+  </si>
+  <si>
+    <t>135878628</t>
+  </si>
+  <si>
+    <t>135879745</t>
+  </si>
+  <si>
+    <t>135880096</t>
+  </si>
+  <si>
+    <t>136029478</t>
+  </si>
+  <si>
+    <t>135882441</t>
+  </si>
+  <si>
+    <t>135863794</t>
+  </si>
+  <si>
+    <t>135901542</t>
+  </si>
+  <si>
+    <t>136027181</t>
+  </si>
+  <si>
+    <t>135884827</t>
+  </si>
+  <si>
+    <t>135887650</t>
+  </si>
+  <si>
+    <t>135888520</t>
+  </si>
+  <si>
+    <t>135889074</t>
+  </si>
+  <si>
+    <t>135890483</t>
+  </si>
+  <si>
+    <t>135890805</t>
+  </si>
+  <si>
+    <t>134599207</t>
+  </si>
+  <si>
+    <t>135950317</t>
+  </si>
+  <si>
+    <t>135893303</t>
+  </si>
+  <si>
+    <t>135893523</t>
+  </si>
+  <si>
+    <t>135954469</t>
+  </si>
+  <si>
+    <t>135875221</t>
+  </si>
+  <si>
+    <t>134001680</t>
+  </si>
+  <si>
+    <t>135900498</t>
+  </si>
+  <si>
+    <t>135947161</t>
+  </si>
+  <si>
+    <t>135961037</t>
+  </si>
+  <si>
+    <t>135923105</t>
+  </si>
+  <si>
+    <t>135922948</t>
+  </si>
+  <si>
+    <t>135909870</t>
+  </si>
+  <si>
+    <t>135951357</t>
+  </si>
+  <si>
+    <t>135955151</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_26.12.2025</t>
+  </si>
+  <si>
+    <t>135929431</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 28/12/2025</t>
+  </si>
+  <si>
+    <t>135987016</t>
+  </si>
+  <si>
+    <t>135836450</t>
+  </si>
+  <si>
+    <t>135911946</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_28.12.2025</t>
+  </si>
+  <si>
+    <t>135753622</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 27/12/2025</t>
+  </si>
+  <si>
+    <t>135855329</t>
+  </si>
+  <si>
+    <t>135866308</t>
+  </si>
+  <si>
+    <t>135886437</t>
+  </si>
+  <si>
+    <t>135910277</t>
+  </si>
+  <si>
+    <t>135855023</t>
+  </si>
+  <si>
+    <t>135975850</t>
+  </si>
+  <si>
+    <t>135842869</t>
+  </si>
+  <si>
+    <t>135851306</t>
+  </si>
+  <si>
+    <t>135855226</t>
+  </si>
+  <si>
+    <t>135859215</t>
+  </si>
+  <si>
+    <t>135866368</t>
+  </si>
+  <si>
+    <t>135890459</t>
+  </si>
+  <si>
+    <t>135914792</t>
+  </si>
+  <si>
+    <t>130768598</t>
+  </si>
+  <si>
+    <t>134780731</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_27.12.2025</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +945,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F180"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -1034,7 +977,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135797706</v>
+        <v>132535282</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1043,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -1079,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1058,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1076,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1094,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1112,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -1205,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -1223,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1241,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1259,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1277,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1295,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1313,7 +1256,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1331,7 +1274,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1349,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1367,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1385,7 +1328,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1403,7 +1346,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1421,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1439,7 +1382,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1457,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1475,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1493,7 +1436,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1511,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1529,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1547,7 +1490,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1565,7 +1508,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1583,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1601,7 +1544,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1619,7 +1562,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1637,7 +1580,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1655,7 +1598,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1673,7 +1616,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1691,7 +1634,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1709,7 +1652,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1727,7 +1670,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1745,7 +1688,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1763,7 +1706,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1781,7 +1724,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1799,7 +1742,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1817,7 +1760,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1835,7 +1778,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1853,7 +1796,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1871,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1889,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1907,7 +1850,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1925,7 +1868,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1934,16 +1877,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1952,16 +1895,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1970,16 +1913,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1988,16 +1931,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -2005,16 +1948,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -2022,16 +1965,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -2039,16 +1982,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -2056,16 +1999,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -2073,16 +2016,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -2090,16 +2033,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -2107,16 +2050,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -2124,16 +2067,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -2141,16 +2084,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -2158,16 +2101,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -2175,16 +2118,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -2192,16 +2135,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -2209,16 +2152,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -2226,16 +2169,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -2243,16 +2186,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
@@ -2260,16 +2203,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
@@ -2277,16 +2220,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
@@ -2294,16 +2237,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
@@ -2311,16 +2254,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
@@ -2328,16 +2271,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
@@ -2345,16 +2288,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
@@ -2362,16 +2305,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
@@ -2379,16 +2322,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
@@ -2396,16 +2339,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
@@ -2413,16 +2356,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
@@ -2430,16 +2373,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
@@ -2447,16 +2390,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
@@ -2464,16 +2407,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>6</v>
@@ -2481,16 +2424,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>6</v>
@@ -2498,16 +2441,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>6</v>
@@ -2515,16 +2458,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>6</v>
@@ -2532,16 +2475,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>6</v>
@@ -2549,16 +2492,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>6</v>
@@ -2566,16 +2509,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>6</v>
@@ -2583,16 +2526,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>6</v>
@@ -2600,16 +2543,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>6</v>
@@ -2617,16 +2560,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>6</v>
@@ -2634,16 +2577,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>6</v>
@@ -2651,16 +2594,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>6</v>
@@ -2668,16 +2611,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>6</v>
@@ -2685,16 +2628,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>6</v>
@@ -2702,16 +2645,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>6</v>
@@ -2719,16 +2662,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>6</v>
@@ -2736,16 +2679,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>6</v>
@@ -2753,16 +2696,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>6</v>
@@ -2770,16 +2713,16 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>6</v>
@@ -2787,16 +2730,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>6</v>
@@ -2804,16 +2747,16 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>6</v>
@@ -2821,16 +2764,16 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>6</v>
@@ -2838,16 +2781,16 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>6</v>
@@ -2855,16 +2798,16 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>6</v>
@@ -2872,16 +2815,16 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>6</v>
@@ -2889,16 +2832,16 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>6</v>
@@ -2906,16 +2849,16 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>6</v>
@@ -2923,16 +2866,16 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>6</v>
@@ -2940,16 +2883,16 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>6</v>
@@ -2957,16 +2900,16 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>6</v>
@@ -2974,16 +2917,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>6</v>
@@ -2991,16 +2934,16 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>6</v>
@@ -3008,16 +2951,16 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>6</v>
@@ -3025,16 +2968,16 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>6</v>
@@ -3042,16 +2985,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>6</v>
@@ -3059,16 +3002,16 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>6</v>
@@ -3076,16 +3019,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>6</v>
@@ -3093,16 +3036,16 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>6</v>
@@ -3110,16 +3053,16 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>6</v>
@@ -3127,16 +3070,16 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>6</v>
@@ -3144,16 +3087,16 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>6</v>
@@ -3161,16 +3104,16 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>6</v>
@@ -3178,16 +3121,16 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>6</v>
@@ -3195,16 +3138,16 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>6</v>
@@ -3212,16 +3155,16 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>6</v>
@@ -3229,16 +3172,16 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>6</v>
@@ -3246,16 +3189,16 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>6</v>
@@ -3263,16 +3206,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>6</v>
@@ -3280,16 +3223,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>6</v>
@@ -3297,16 +3240,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>6</v>
@@ -3314,16 +3257,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>6</v>
@@ -3331,16 +3274,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>6</v>
@@ -3348,16 +3291,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>6</v>
@@ -3365,16 +3308,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>6</v>
@@ -3382,16 +3325,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>6</v>
@@ -3399,16 +3342,16 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>6</v>
@@ -3416,16 +3359,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>6</v>
@@ -3433,16 +3376,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>6</v>
@@ -3450,16 +3393,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>6</v>
@@ -3467,16 +3410,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>6</v>
@@ -3484,16 +3427,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>6</v>
@@ -3501,16 +3444,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>6</v>
@@ -3518,16 +3461,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>6</v>
@@ -3535,16 +3478,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="B146" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="D146" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>6</v>
@@ -3552,16 +3495,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>6</v>
@@ -3569,16 +3512,16 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>6</v>
@@ -3586,16 +3529,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>6</v>
@@ -3603,16 +3546,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>6</v>
@@ -3620,16 +3563,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>6</v>
@@ -3637,16 +3580,16 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>6</v>
@@ -3654,16 +3597,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>6</v>
@@ -3671,16 +3614,16 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>6</v>
@@ -3688,16 +3631,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>60</v>
+        <v>154</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>6</v>
@@ -3705,16 +3648,16 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>6</v>
@@ -3722,16 +3665,16 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>165</v>
+        <v>149</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>6</v>
@@ -3739,16 +3682,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>6</v>
@@ -3756,375 +3699,18 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A160" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A161" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D161" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A162" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D162" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E162" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A163" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A164" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D164" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E164" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A165" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D165" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A166" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="B166" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D166" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A167" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C167" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D167" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E167" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A168" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B168" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D168" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E168" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A169" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D169" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A170" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B170" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C170" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D170" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E170" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A171" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B171" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C171" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D171" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E171" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A172" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B172" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C172" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D172" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E172" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A173" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B173" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C173" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D173" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A174" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B174" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D174" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A175" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B175" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D175" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E175" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A176" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B176" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C176" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A177" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B177" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A178" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B178" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A179" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B179" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A180" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B180" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E180" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -4142,31 +3728,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA0D8FA-FE87-4453-A176-968C5B6021AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1F3257-5B8D-48FF-86B4-99AC981C62EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="180">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,493 +54,520 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 26/12/2025</t>
-  </si>
-  <si>
-    <t>135284151</t>
-  </si>
-  <si>
-    <t>135843866</t>
-  </si>
-  <si>
-    <t>135839146</t>
-  </si>
-  <si>
-    <t>135834209</t>
-  </si>
-  <si>
-    <t>135858367</t>
-  </si>
-  <si>
-    <t>135893315</t>
-  </si>
-  <si>
-    <t>135883822</t>
-  </si>
-  <si>
-    <t>135892167</t>
-  </si>
-  <si>
-    <t>135893087</t>
-  </si>
-  <si>
-    <t>135891147</t>
-  </si>
-  <si>
-    <t>135876175</t>
-  </si>
-  <si>
-    <t>135889035</t>
-  </si>
-  <si>
-    <t>135853074</t>
-  </si>
-  <si>
-    <t>135892552</t>
-  </si>
-  <si>
-    <t>135889668</t>
-  </si>
-  <si>
-    <t>135907244</t>
-  </si>
-  <si>
-    <t>135927423</t>
-  </si>
-  <si>
-    <t>135890398</t>
-  </si>
-  <si>
-    <t>135934386</t>
-  </si>
-  <si>
-    <t>135937497</t>
-  </si>
-  <si>
-    <t>135931449</t>
-  </si>
-  <si>
-    <t>135917156</t>
-  </si>
-  <si>
-    <t>135933182</t>
-  </si>
-  <si>
-    <t>135939700</t>
-  </si>
-  <si>
-    <t>134380578</t>
-  </si>
-  <si>
-    <t>134727124</t>
-  </si>
-  <si>
-    <t>135954425</t>
-  </si>
-  <si>
-    <t>135947665</t>
-  </si>
-  <si>
-    <t>135960034</t>
-  </si>
-  <si>
-    <t>135960652</t>
-  </si>
-  <si>
-    <t>135962697</t>
-  </si>
-  <si>
-    <t>135947034</t>
-  </si>
-  <si>
-    <t>135877823</t>
-  </si>
-  <si>
-    <t>135947526</t>
-  </si>
-  <si>
-    <t>135948268</t>
-  </si>
-  <si>
-    <t>135948838</t>
-  </si>
-  <si>
-    <t>135915297</t>
-  </si>
-  <si>
-    <t>135912055</t>
-  </si>
-  <si>
-    <t>135866868</t>
-  </si>
-  <si>
-    <t>135972799</t>
-  </si>
-  <si>
-    <t>135880945</t>
-  </si>
-  <si>
-    <t>135979618</t>
-  </si>
-  <si>
-    <t>135976154</t>
-  </si>
-  <si>
-    <t>135986768</t>
-  </si>
-  <si>
-    <t>135969017</t>
-  </si>
-  <si>
-    <t>135946582</t>
-  </si>
-  <si>
-    <t>136000851</t>
-  </si>
-  <si>
-    <t>135993789</t>
-  </si>
-  <si>
-    <t>135946567</t>
-  </si>
-  <si>
-    <t>135994266</t>
-  </si>
-  <si>
-    <t>135925223</t>
-  </si>
-  <si>
-    <t>136000088</t>
-  </si>
-  <si>
-    <t>135997890</t>
-  </si>
-  <si>
-    <t>136012708</t>
-  </si>
-  <si>
-    <t>136011856</t>
-  </si>
-  <si>
-    <t>136014223</t>
-  </si>
-  <si>
-    <t>136015730</t>
-  </si>
-  <si>
-    <t>136017518</t>
-  </si>
-  <si>
-    <t>136011642</t>
-  </si>
-  <si>
-    <t>135834476</t>
-  </si>
-  <si>
-    <t>135838685</t>
-  </si>
-  <si>
-    <t>135833364</t>
-  </si>
-  <si>
-    <t>135834073</t>
-  </si>
-  <si>
-    <t>135839271</t>
-  </si>
-  <si>
-    <t>135841456</t>
-  </si>
-  <si>
-    <t>135819669</t>
-  </si>
-  <si>
-    <t>135834064</t>
-  </si>
-  <si>
-    <t>135834781</t>
-  </si>
-  <si>
-    <t>135858483</t>
-  </si>
-  <si>
-    <t>136022327</t>
-  </si>
-  <si>
-    <t>135839152</t>
-  </si>
-  <si>
-    <t>136022410</t>
-  </si>
-  <si>
-    <t>131714833</t>
-  </si>
-  <si>
-    <t>135840138</t>
-  </si>
-  <si>
-    <t>135846295</t>
-  </si>
-  <si>
-    <t>135904272</t>
-  </si>
-  <si>
-    <t>133364810</t>
-  </si>
-  <si>
-    <t>134010937</t>
-  </si>
-  <si>
-    <t>135921783</t>
-  </si>
-  <si>
-    <t>133705337</t>
-  </si>
-  <si>
-    <t>132697911</t>
-  </si>
-  <si>
-    <t>135852381</t>
-  </si>
-  <si>
-    <t>135883086</t>
-  </si>
-  <si>
-    <t>135856427</t>
-  </si>
-  <si>
-    <t>135857564</t>
-  </si>
-  <si>
-    <t>135868235</t>
-  </si>
-  <si>
-    <t>135861133</t>
-  </si>
-  <si>
-    <t>135863437</t>
-  </si>
-  <si>
-    <t>135864048</t>
-  </si>
-  <si>
-    <t>135859945</t>
-  </si>
-  <si>
-    <t>135865631</t>
-  </si>
-  <si>
-    <t>135924454</t>
-  </si>
-  <si>
-    <t>135935741</t>
-  </si>
-  <si>
-    <t>131745850</t>
-  </si>
-  <si>
-    <t>135867440</t>
-  </si>
-  <si>
-    <t>135868335</t>
-  </si>
-  <si>
-    <t>135868424</t>
-  </si>
-  <si>
-    <t>135869387</t>
-  </si>
-  <si>
-    <t>136027361</t>
-  </si>
-  <si>
-    <t>135873980</t>
-  </si>
-  <si>
-    <t>135878374</t>
-  </si>
-  <si>
-    <t>135875189</t>
-  </si>
-  <si>
-    <t>135875323</t>
-  </si>
-  <si>
-    <t>135885355</t>
-  </si>
-  <si>
-    <t>135875754</t>
-  </si>
-  <si>
-    <t>135876024</t>
-  </si>
-  <si>
-    <t>135876992</t>
-  </si>
-  <si>
-    <t>135877225</t>
-  </si>
-  <si>
-    <t>135878628</t>
-  </si>
-  <si>
-    <t>135879745</t>
-  </si>
-  <si>
-    <t>135880096</t>
-  </si>
-  <si>
-    <t>136029478</t>
-  </si>
-  <si>
-    <t>135882441</t>
-  </si>
-  <si>
-    <t>135863794</t>
-  </si>
-  <si>
-    <t>135901542</t>
-  </si>
-  <si>
-    <t>136027181</t>
-  </si>
-  <si>
-    <t>135884827</t>
-  </si>
-  <si>
-    <t>135887650</t>
-  </si>
-  <si>
-    <t>135888520</t>
-  </si>
-  <si>
-    <t>135889074</t>
-  </si>
-  <si>
-    <t>135890483</t>
-  </si>
-  <si>
-    <t>135890805</t>
-  </si>
-  <si>
-    <t>134599207</t>
-  </si>
-  <si>
-    <t>135950317</t>
-  </si>
-  <si>
-    <t>135893303</t>
-  </si>
-  <si>
-    <t>135893523</t>
-  </si>
-  <si>
-    <t>135954469</t>
-  </si>
-  <si>
-    <t>135875221</t>
-  </si>
-  <si>
-    <t>134001680</t>
-  </si>
-  <si>
-    <t>135900498</t>
-  </si>
-  <si>
-    <t>135947161</t>
-  </si>
-  <si>
-    <t>135961037</t>
-  </si>
-  <si>
-    <t>135923105</t>
-  </si>
-  <si>
-    <t>135922948</t>
-  </si>
-  <si>
-    <t>135909870</t>
-  </si>
-  <si>
-    <t>135951357</t>
-  </si>
-  <si>
-    <t>135955151</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_26.12.2025</t>
-  </si>
-  <si>
-    <t>135929431</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 28/12/2025</t>
-  </si>
-  <si>
-    <t>135987016</t>
-  </si>
-  <si>
-    <t>135836450</t>
-  </si>
-  <si>
-    <t>135911946</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_28.12.2025</t>
-  </si>
-  <si>
-    <t>135753622</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 27/12/2025</t>
-  </si>
-  <si>
-    <t>135855329</t>
-  </si>
-  <si>
-    <t>135866308</t>
-  </si>
-  <si>
-    <t>135886437</t>
-  </si>
-  <si>
-    <t>135910277</t>
-  </si>
-  <si>
-    <t>135855023</t>
-  </si>
-  <si>
-    <t>135975850</t>
-  </si>
-  <si>
-    <t>135842869</t>
-  </si>
-  <si>
-    <t>135851306</t>
-  </si>
-  <si>
-    <t>135855226</t>
-  </si>
-  <si>
-    <t>135859215</t>
-  </si>
-  <si>
-    <t>135866368</t>
-  </si>
-  <si>
-    <t>135890459</t>
-  </si>
-  <si>
-    <t>135914792</t>
-  </si>
-  <si>
-    <t>130768598</t>
-  </si>
-  <si>
-    <t>134780731</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_27.12.2025</t>
+    <t>Recusas Sicredi 29/12/2025</t>
+  </si>
+  <si>
+    <t>135904981</t>
+  </si>
+  <si>
+    <t>135908572</t>
+  </si>
+  <si>
+    <t>135912102</t>
+  </si>
+  <si>
+    <t>135909685</t>
+  </si>
+  <si>
+    <t>135912987</t>
+  </si>
+  <si>
+    <t>135914026</t>
+  </si>
+  <si>
+    <t>135915178</t>
+  </si>
+  <si>
+    <t>135926611</t>
+  </si>
+  <si>
+    <t>135932661</t>
+  </si>
+  <si>
+    <t>135933065</t>
+  </si>
+  <si>
+    <t>135936309</t>
+  </si>
+  <si>
+    <t>135937184</t>
+  </si>
+  <si>
+    <t>135938034</t>
+  </si>
+  <si>
+    <t>135915208</t>
+  </si>
+  <si>
+    <t>135932077</t>
+  </si>
+  <si>
+    <t>135926728</t>
+  </si>
+  <si>
+    <t>135936787</t>
+  </si>
+  <si>
+    <t>135959242</t>
+  </si>
+  <si>
+    <t>135954386</t>
+  </si>
+  <si>
+    <t>135959760</t>
+  </si>
+  <si>
+    <t>135953074</t>
+  </si>
+  <si>
+    <t>135959292</t>
+  </si>
+  <si>
+    <t>135955189</t>
+  </si>
+  <si>
+    <t>135956072</t>
+  </si>
+  <si>
+    <t>135956134</t>
+  </si>
+  <si>
+    <t>135957985</t>
+  </si>
+  <si>
+    <t>135960145</t>
+  </si>
+  <si>
+    <t>135958455</t>
+  </si>
+  <si>
+    <t>135911296</t>
+  </si>
+  <si>
+    <t>135976129</t>
+  </si>
+  <si>
+    <t>135976290</t>
+  </si>
+  <si>
+    <t>135981209</t>
+  </si>
+  <si>
+    <t>135969526</t>
+  </si>
+  <si>
+    <t>135975864</t>
+  </si>
+  <si>
+    <t>135980054</t>
+  </si>
+  <si>
+    <t>135974976</t>
+  </si>
+  <si>
+    <t>135973922</t>
+  </si>
+  <si>
+    <t>135984991</t>
+  </si>
+  <si>
+    <t>135978887</t>
+  </si>
+  <si>
+    <t>135990529</t>
+  </si>
+  <si>
+    <t>135918219</t>
+  </si>
+  <si>
+    <t>135979003</t>
+  </si>
+  <si>
+    <t>135996639</t>
+  </si>
+  <si>
+    <t>135973773</t>
+  </si>
+  <si>
+    <t>134664469</t>
+  </si>
+  <si>
+    <t>136003644</t>
+  </si>
+  <si>
+    <t>135960646</t>
+  </si>
+  <si>
+    <t>136008443</t>
+  </si>
+  <si>
+    <t>136007229</t>
+  </si>
+  <si>
+    <t>136005984</t>
+  </si>
+  <si>
+    <t>135877144</t>
+  </si>
+  <si>
+    <t>136006074</t>
+  </si>
+  <si>
+    <t>135994274</t>
+  </si>
+  <si>
+    <t>136005455</t>
+  </si>
+  <si>
+    <t>135999681</t>
+  </si>
+  <si>
+    <t>135994896</t>
+  </si>
+  <si>
+    <t>136007874</t>
+  </si>
+  <si>
+    <t>135996884</t>
+  </si>
+  <si>
+    <t>136013291</t>
+  </si>
+  <si>
+    <t>135980689</t>
+  </si>
+  <si>
+    <t>135938523</t>
+  </si>
+  <si>
+    <t>135901139</t>
+  </si>
+  <si>
+    <t>136025457</t>
+  </si>
+  <si>
+    <t>136026504</t>
+  </si>
+  <si>
+    <t>136033713</t>
+  </si>
+  <si>
+    <t>136027464</t>
+  </si>
+  <si>
+    <t>136028865</t>
+  </si>
+  <si>
+    <t>136019087</t>
+  </si>
+  <si>
+    <t>136033574</t>
+  </si>
+  <si>
+    <t>135935895</t>
+  </si>
+  <si>
+    <t>136038512</t>
+  </si>
+  <si>
+    <t>135985046</t>
+  </si>
+  <si>
+    <t>135568341</t>
+  </si>
+  <si>
+    <t>135866859</t>
+  </si>
+  <si>
+    <t>135901278</t>
+  </si>
+  <si>
+    <t>135906553</t>
+  </si>
+  <si>
+    <t>136040033</t>
+  </si>
+  <si>
+    <t>135952884</t>
+  </si>
+  <si>
+    <t>136042892</t>
+  </si>
+  <si>
+    <t>135958209</t>
+  </si>
+  <si>
+    <t>135928643</t>
+  </si>
+  <si>
+    <t>135911524</t>
+  </si>
+  <si>
+    <t>135927124</t>
+  </si>
+  <si>
+    <t>135905843</t>
+  </si>
+  <si>
+    <t>135907714</t>
+  </si>
+  <si>
+    <t>135978622</t>
+  </si>
+  <si>
+    <t>136046861</t>
+  </si>
+  <si>
+    <t>136047968</t>
+  </si>
+  <si>
+    <t>136047270</t>
+  </si>
+  <si>
+    <t>136047472</t>
+  </si>
+  <si>
+    <t>136047649</t>
+  </si>
+  <si>
+    <t>135904002</t>
+  </si>
+  <si>
+    <t>133648230</t>
+  </si>
+  <si>
+    <t>135904016</t>
+  </si>
+  <si>
+    <t>136049847</t>
+  </si>
+  <si>
+    <t>134083475</t>
+  </si>
+  <si>
+    <t>135632723</t>
+  </si>
+  <si>
+    <t>135947531</t>
+  </si>
+  <si>
+    <t>135949429</t>
+  </si>
+  <si>
+    <t>133780129</t>
+  </si>
+  <si>
+    <t>135933988</t>
+  </si>
+  <si>
+    <t>135959245</t>
+  </si>
+  <si>
+    <t>135887139</t>
+  </si>
+  <si>
+    <t>134263532</t>
+  </si>
+  <si>
+    <t>132627006</t>
+  </si>
+  <si>
+    <t>135898037</t>
+  </si>
+  <si>
+    <t>134964119</t>
+  </si>
+  <si>
+    <t>135895899</t>
+  </si>
+  <si>
+    <t>135895958</t>
+  </si>
+  <si>
+    <t>135899753</t>
+  </si>
+  <si>
+    <t>135959309</t>
+  </si>
+  <si>
+    <t>135900707</t>
+  </si>
+  <si>
+    <t>135900835</t>
+  </si>
+  <si>
+    <t>135902336</t>
+  </si>
+  <si>
+    <t>135902831</t>
+  </si>
+  <si>
+    <t>135904495</t>
+  </si>
+  <si>
+    <t>135904921</t>
+  </si>
+  <si>
+    <t>135905129</t>
+  </si>
+  <si>
+    <t>135906538</t>
+  </si>
+  <si>
+    <t>135979392</t>
+  </si>
+  <si>
+    <t>135986767</t>
+  </si>
+  <si>
+    <t>135909418</t>
+  </si>
+  <si>
+    <t>135909480</t>
+  </si>
+  <si>
+    <t>135909775</t>
+  </si>
+  <si>
+    <t>135910913</t>
+  </si>
+  <si>
+    <t>135912305</t>
+  </si>
+  <si>
+    <t>135913087</t>
+  </si>
+  <si>
+    <t>135914214</t>
+  </si>
+  <si>
+    <t>135914716</t>
+  </si>
+  <si>
+    <t>135924650</t>
+  </si>
+  <si>
+    <t>135924767</t>
+  </si>
+  <si>
+    <t>135925449</t>
+  </si>
+  <si>
+    <t>135925899</t>
+  </si>
+  <si>
+    <t>135857601</t>
+  </si>
+  <si>
+    <t>135926658</t>
+  </si>
+  <si>
+    <t>135928413</t>
+  </si>
+  <si>
+    <t>135928708</t>
+  </si>
+  <si>
+    <t>135929660</t>
+  </si>
+  <si>
+    <t>135929882</t>
+  </si>
+  <si>
+    <t>135929949</t>
+  </si>
+  <si>
+    <t>135930829</t>
+  </si>
+  <si>
+    <t>135933200</t>
+  </si>
+  <si>
+    <t>135935112</t>
+  </si>
+  <si>
+    <t>135935839</t>
+  </si>
+  <si>
+    <t>135936499</t>
+  </si>
+  <si>
+    <t>135936712</t>
+  </si>
+  <si>
+    <t>135937181</t>
+  </si>
+  <si>
+    <t>135940536</t>
+  </si>
+  <si>
+    <t>135945118</t>
+  </si>
+  <si>
+    <t>135945518</t>
+  </si>
+  <si>
+    <t>135946901</t>
+  </si>
+  <si>
+    <t>135948056</t>
+  </si>
+  <si>
+    <t>135948928</t>
+  </si>
+  <si>
+    <t>135950002</t>
+  </si>
+  <si>
+    <t>135950294</t>
+  </si>
+  <si>
+    <t>135950648</t>
+  </si>
+  <si>
+    <t>135952355</t>
+  </si>
+  <si>
+    <t>135952394</t>
+  </si>
+  <si>
+    <t>135952737</t>
+  </si>
+  <si>
+    <t>135953248</t>
+  </si>
+  <si>
+    <t>135954839</t>
+  </si>
+  <si>
+    <t>135955570</t>
+  </si>
+  <si>
+    <t>135957477</t>
+  </si>
+  <si>
+    <t>135957870</t>
+  </si>
+  <si>
+    <t>135957991</t>
+  </si>
+  <si>
+    <t>135959494</t>
+  </si>
+  <si>
+    <t>135960245</t>
+  </si>
+  <si>
+    <t>135960661</t>
+  </si>
+  <si>
+    <t>135961397</t>
+  </si>
+  <si>
+    <t>135961570</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_29.12.2025</t>
   </si>
 </sst>
 </file>
@@ -945,7 +972,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F172"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -977,7 +1004,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>132535282</v>
+        <v>135864329</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -986,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -1004,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -1022,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -1040,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -1058,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -1076,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1121,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -1130,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -1148,7 +1175,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -1166,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1184,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1202,7 +1229,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1220,7 +1247,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1238,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1256,7 +1283,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1274,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1292,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1310,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1328,7 +1355,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1346,7 +1373,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1364,7 +1391,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1382,7 +1409,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1400,7 +1427,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1418,7 +1445,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1436,7 +1463,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1454,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1472,7 +1499,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1490,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1508,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1526,7 +1553,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1544,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1562,7 +1589,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1580,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1598,7 +1625,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1616,7 +1643,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1634,7 +1661,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1652,7 +1679,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1670,7 +1697,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1688,7 +1715,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1706,7 +1733,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1724,7 +1751,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1742,7 +1769,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1760,7 +1787,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1778,7 +1805,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1796,7 +1823,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1814,7 +1841,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1832,7 +1859,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1850,7 +1877,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1868,7 +1895,7 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1886,7 +1913,7 @@
         <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1904,7 +1931,7 @@
         <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1922,7 +1949,7 @@
         <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1940,7 +1967,7 @@
         <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1957,7 +1984,7 @@
         <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1974,7 +2001,7 @@
         <v>8</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1991,7 +2018,7 @@
         <v>8</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -2008,7 +2035,7 @@
         <v>8</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -2025,7 +2052,7 @@
         <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -2042,7 +2069,7 @@
         <v>8</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -2059,7 +2086,7 @@
         <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -2076,7 +2103,7 @@
         <v>8</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -2093,7 +2120,7 @@
         <v>8</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -2110,7 +2137,7 @@
         <v>8</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -2127,7 +2154,7 @@
         <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -2144,7 +2171,7 @@
         <v>8</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -2161,7 +2188,7 @@
         <v>8</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -2178,7 +2205,7 @@
         <v>8</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -2195,7 +2222,7 @@
         <v>8</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
@@ -2212,7 +2239,7 @@
         <v>8</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
@@ -2229,7 +2256,7 @@
         <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
@@ -2246,7 +2273,7 @@
         <v>8</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
@@ -2263,7 +2290,7 @@
         <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
@@ -2280,7 +2307,7 @@
         <v>8</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
@@ -2297,7 +2324,7 @@
         <v>8</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
@@ -2314,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
@@ -2331,7 +2358,7 @@
         <v>8</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
@@ -2348,7 +2375,7 @@
         <v>8</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
@@ -2365,7 +2392,7 @@
         <v>8</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
@@ -2382,7 +2409,7 @@
         <v>8</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
@@ -2399,7 +2426,7 @@
         <v>8</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
@@ -2416,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>6</v>
@@ -2433,7 +2460,7 @@
         <v>8</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>6</v>
@@ -2450,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>6</v>
@@ -2467,7 +2494,7 @@
         <v>8</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>6</v>
@@ -2484,7 +2511,7 @@
         <v>8</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>6</v>
@@ -2501,7 +2528,7 @@
         <v>8</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>6</v>
@@ -2518,7 +2545,7 @@
         <v>8</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>6</v>
@@ -2535,7 +2562,7 @@
         <v>8</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>6</v>
@@ -2552,7 +2579,7 @@
         <v>8</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>6</v>
@@ -2569,7 +2596,7 @@
         <v>8</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>6</v>
@@ -2586,7 +2613,7 @@
         <v>8</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>6</v>
@@ -2603,7 +2630,7 @@
         <v>8</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>6</v>
@@ -2620,7 +2647,7 @@
         <v>8</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>6</v>
@@ -2637,7 +2664,7 @@
         <v>8</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>6</v>
@@ -2654,7 +2681,7 @@
         <v>8</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>6</v>
@@ -2671,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>6</v>
@@ -2688,7 +2715,7 @@
         <v>8</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>6</v>
@@ -2705,7 +2732,7 @@
         <v>8</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>6</v>
@@ -2722,7 +2749,7 @@
         <v>8</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>6</v>
@@ -2739,7 +2766,7 @@
         <v>8</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>6</v>
@@ -2756,7 +2783,7 @@
         <v>8</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>6</v>
@@ -2773,7 +2800,7 @@
         <v>8</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>6</v>
@@ -2790,7 +2817,7 @@
         <v>8</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>6</v>
@@ -2807,7 +2834,7 @@
         <v>8</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>6</v>
@@ -2824,7 +2851,7 @@
         <v>8</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>6</v>
@@ -2841,7 +2868,7 @@
         <v>8</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>6</v>
@@ -2858,7 +2885,7 @@
         <v>8</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>6</v>
@@ -2875,7 +2902,7 @@
         <v>8</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>6</v>
@@ -2892,7 +2919,7 @@
         <v>8</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>6</v>
@@ -2909,7 +2936,7 @@
         <v>8</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>6</v>
@@ -2926,7 +2953,7 @@
         <v>8</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>6</v>
@@ -2943,7 +2970,7 @@
         <v>8</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>6</v>
@@ -2960,7 +2987,7 @@
         <v>8</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>6</v>
@@ -2977,7 +3004,7 @@
         <v>8</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>6</v>
@@ -2994,7 +3021,7 @@
         <v>8</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>6</v>
@@ -3011,7 +3038,7 @@
         <v>8</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>6</v>
@@ -3028,7 +3055,7 @@
         <v>8</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>6</v>
@@ -3045,7 +3072,7 @@
         <v>8</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>6</v>
@@ -3062,7 +3089,7 @@
         <v>8</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>6</v>
@@ -3079,7 +3106,7 @@
         <v>8</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>6</v>
@@ -3096,7 +3123,7 @@
         <v>8</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>6</v>
@@ -3113,7 +3140,7 @@
         <v>8</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>6</v>
@@ -3130,7 +3157,7 @@
         <v>8</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>6</v>
@@ -3147,7 +3174,7 @@
         <v>8</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>6</v>
@@ -3164,7 +3191,7 @@
         <v>8</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>6</v>
@@ -3181,7 +3208,7 @@
         <v>8</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>6</v>
@@ -3198,7 +3225,7 @@
         <v>8</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>6</v>
@@ -3215,7 +3242,7 @@
         <v>8</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>6</v>
@@ -3232,7 +3259,7 @@
         <v>8</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>6</v>
@@ -3249,7 +3276,7 @@
         <v>8</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>6</v>
@@ -3266,7 +3293,7 @@
         <v>8</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>6</v>
@@ -3283,7 +3310,7 @@
         <v>8</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>6</v>
@@ -3300,7 +3327,7 @@
         <v>8</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>6</v>
@@ -3317,7 +3344,7 @@
         <v>8</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>6</v>
@@ -3334,7 +3361,7 @@
         <v>8</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>6</v>
@@ -3351,7 +3378,7 @@
         <v>8</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>6</v>
@@ -3368,7 +3395,7 @@
         <v>8</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>146</v>
+        <v>179</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>6</v>
@@ -3376,16 +3403,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>6</v>
@@ -3393,16 +3420,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>6</v>
@@ -3410,16 +3437,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>6</v>
@@ -3427,16 +3454,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>6</v>
@@ -3444,16 +3471,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>6</v>
@@ -3461,16 +3488,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>6</v>
@@ -3478,16 +3505,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>6</v>
@@ -3495,16 +3522,16 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>6</v>
@@ -3512,16 +3539,16 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>6</v>
@@ -3529,16 +3556,16 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>6</v>
@@ -3546,16 +3573,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>6</v>
@@ -3563,16 +3590,16 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>6</v>
@@ -3580,16 +3607,16 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>6</v>
@@ -3597,16 +3624,16 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>6</v>
@@ -3614,16 +3641,16 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>6</v>
@@ -3631,16 +3658,16 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>6</v>
@@ -3648,16 +3675,16 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>6</v>
@@ -3665,16 +3692,16 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>6</v>
@@ -3682,16 +3709,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>150</v>
+        <v>164</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>6</v>
@@ -3699,18 +3726,239 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>148</v>
+        <v>8</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="E159" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E172" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -3728,31 +3976,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5856C526-C8AD-480F-9387-5999AEA328AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA2353B-D557-45B4-B8B2-9B40B6CE338B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -1060,18 +1060,6 @@
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F29"/>
     </row>
   </sheetData>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA2353B-D557-45B4-B8B2-9B40B6CE338B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6F2546-1FE3-4FB9-A2DC-4E1EC61827AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -136,9 +136,6 @@
   </si>
   <si>
     <t>135566481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recusa Sicredi 25.12.25 </t>
   </si>
 </sst>
 </file>
@@ -584,7 +581,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -602,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -620,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -638,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -656,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -674,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -692,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -710,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -728,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -746,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -764,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -782,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -800,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -818,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -836,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -854,7 +851,7 @@
         <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -872,7 +869,7 @@
         <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -890,7 +887,7 @@
         <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,7 +905,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -926,7 +923,7 @@
         <v>24</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -944,7 +941,7 @@
         <v>24</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,7 +959,7 @@
         <v>24</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -980,7 +977,7 @@
         <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -998,7 +995,7 @@
         <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1013,7 @@
         <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1031,7 @@
         <v>24</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1049,7 @@
         <v>24</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1076,31 +1073,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6F2546-1FE3-4FB9-A2DC-4E1EC61827AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2A1F6F-4F38-4396-9E6D-F17AA1ECEBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="114">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,88 +54,322 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 12.11.2025</t>
-  </si>
-  <si>
-    <t>135159447</t>
-  </si>
-  <si>
-    <t>135182159</t>
-  </si>
-  <si>
-    <t>135219695</t>
-  </si>
-  <si>
-    <t>135221464</t>
-  </si>
-  <si>
-    <t>135265035</t>
-  </si>
-  <si>
-    <t>135259371</t>
-  </si>
-  <si>
-    <t>135265194</t>
-  </si>
-  <si>
-    <t>135258374</t>
-  </si>
-  <si>
-    <t>135248049</t>
-  </si>
-  <si>
-    <t>135276675</t>
-  </si>
-  <si>
-    <t>135286829</t>
-  </si>
-  <si>
-    <t>135284082</t>
-  </si>
-  <si>
-    <t>135278335</t>
-  </si>
-  <si>
-    <t>135273212</t>
-  </si>
-  <si>
-    <t>135723006</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 25.12.2025</t>
-  </si>
-  <si>
-    <t>135819667</t>
-  </si>
-  <si>
-    <t>135803476</t>
-  </si>
-  <si>
-    <t>135807559</t>
-  </si>
-  <si>
-    <t>135808528</t>
-  </si>
-  <si>
-    <t>135811300</t>
-  </si>
-  <si>
-    <t>135811742</t>
-  </si>
-  <si>
-    <t>135811845</t>
-  </si>
-  <si>
-    <t>135812529</t>
-  </si>
-  <si>
-    <t>135814185</t>
-  </si>
-  <si>
-    <t>135820389</t>
-  </si>
-  <si>
-    <t>135566481</t>
+    <t>Relatório de Recusa Sicredi 30/12/2025</t>
+  </si>
+  <si>
+    <t>135882601</t>
+  </si>
+  <si>
+    <t>135882864</t>
+  </si>
+  <si>
+    <t>135937891</t>
+  </si>
+  <si>
+    <t>135899908</t>
+  </si>
+  <si>
+    <t>135937970</t>
+  </si>
+  <si>
+    <t>134727124</t>
+  </si>
+  <si>
+    <t>135959998</t>
+  </si>
+  <si>
+    <t>135876618</t>
+  </si>
+  <si>
+    <t>135878999</t>
+  </si>
+  <si>
+    <t>135979082</t>
+  </si>
+  <si>
+    <t>135985831</t>
+  </si>
+  <si>
+    <t>135981055</t>
+  </si>
+  <si>
+    <t>135982931</t>
+  </si>
+  <si>
+    <t>133320663</t>
+  </si>
+  <si>
+    <t>136006030</t>
+  </si>
+  <si>
+    <t>136001975</t>
+  </si>
+  <si>
+    <t>135991880</t>
+  </si>
+  <si>
+    <t>136006226</t>
+  </si>
+  <si>
+    <t>136002815</t>
+  </si>
+  <si>
+    <t>135999237</t>
+  </si>
+  <si>
+    <t>135998467</t>
+  </si>
+  <si>
+    <t>135995476</t>
+  </si>
+  <si>
+    <t>136007901</t>
+  </si>
+  <si>
+    <t>136006910</t>
+  </si>
+  <si>
+    <t>136013729</t>
+  </si>
+  <si>
+    <t>136016172</t>
+  </si>
+  <si>
+    <t>136013772</t>
+  </si>
+  <si>
+    <t>136021540</t>
+  </si>
+  <si>
+    <t>135995182</t>
+  </si>
+  <si>
+    <t>136023731</t>
+  </si>
+  <si>
+    <t>136024092</t>
+  </si>
+  <si>
+    <t>136024586</t>
+  </si>
+  <si>
+    <t>135997305</t>
+  </si>
+  <si>
+    <t>134290973</t>
+  </si>
+  <si>
+    <t>136030669</t>
+  </si>
+  <si>
+    <t>136002902</t>
+  </si>
+  <si>
+    <t>135998375</t>
+  </si>
+  <si>
+    <t>135897648</t>
+  </si>
+  <si>
+    <t>135986437</t>
+  </si>
+  <si>
+    <t>136050763</t>
+  </si>
+  <si>
+    <t>136039306</t>
+  </si>
+  <si>
+    <t>136040870</t>
+  </si>
+  <si>
+    <t>136029776</t>
+  </si>
+  <si>
+    <t>136046251</t>
+  </si>
+  <si>
+    <t>135873089</t>
+  </si>
+  <si>
+    <t>135875810</t>
+  </si>
+  <si>
+    <t>135882790</t>
+  </si>
+  <si>
+    <t>135883283</t>
+  </si>
+  <si>
+    <t>135884396</t>
+  </si>
+  <si>
+    <t>135887831</t>
+  </si>
+  <si>
+    <t>135887927</t>
+  </si>
+  <si>
+    <t>136056638</t>
+  </si>
+  <si>
+    <t>136057747</t>
+  </si>
+  <si>
+    <t>136059789</t>
+  </si>
+  <si>
+    <t>136061228</t>
+  </si>
+  <si>
+    <t>136057027</t>
+  </si>
+  <si>
+    <t>134880624</t>
+  </si>
+  <si>
+    <t>136065005</t>
+  </si>
+  <si>
+    <t>136066601</t>
+  </si>
+  <si>
+    <t>134425718</t>
+  </si>
+  <si>
+    <t>133076320</t>
+  </si>
+  <si>
+    <t>135980697</t>
+  </si>
+  <si>
+    <t>132941813</t>
+  </si>
+  <si>
+    <t>136069332</t>
+  </si>
+  <si>
+    <t>132564131</t>
+  </si>
+  <si>
+    <t>135976847</t>
+  </si>
+  <si>
+    <t>135995698</t>
+  </si>
+  <si>
+    <t>135984162</t>
+  </si>
+  <si>
+    <t>136067519</t>
+  </si>
+  <si>
+    <t>136071802</t>
+  </si>
+  <si>
+    <t>132840822</t>
+  </si>
+  <si>
+    <t>135920326</t>
+  </si>
+  <si>
+    <t>135929217</t>
+  </si>
+  <si>
+    <t>135952449</t>
+  </si>
+  <si>
+    <t>135978288</t>
+  </si>
+  <si>
+    <t>133411782</t>
+  </si>
+  <si>
+    <t>136061365</t>
+  </si>
+  <si>
+    <t>135873899</t>
+  </si>
+  <si>
+    <t>135883430</t>
+  </si>
+  <si>
+    <t>135896453</t>
+  </si>
+  <si>
+    <t>135905685</t>
+  </si>
+  <si>
+    <t>135750341</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_30.12.2025</t>
+  </si>
+  <si>
+    <t>135934228</t>
+  </si>
+  <si>
+    <t>Relatório de Recusa Sicredi 01/01/2026</t>
+  </si>
+  <si>
+    <t>135938011</t>
+  </si>
+  <si>
+    <t>135938241</t>
+  </si>
+  <si>
+    <t>135917442</t>
+  </si>
+  <si>
+    <t>135919735</t>
+  </si>
+  <si>
+    <t>135957043</t>
+  </si>
+  <si>
+    <t>135925895</t>
+  </si>
+  <si>
+    <t>135934543</t>
+  </si>
+  <si>
+    <t>135906669</t>
+  </si>
+  <si>
+    <t>135907645</t>
+  </si>
+  <si>
+    <t>135931385</t>
+  </si>
+  <si>
+    <t>135925935</t>
+  </si>
+  <si>
+    <t>135933027</t>
+  </si>
+  <si>
+    <t>135958550</t>
+  </si>
+  <si>
+    <t>135956468</t>
+  </si>
+  <si>
+    <t>135956725</t>
+  </si>
+  <si>
+    <t>135958702</t>
+  </si>
+  <si>
+    <t>135952218</t>
+  </si>
+  <si>
+    <t>135950428</t>
+  </si>
+  <si>
+    <t>135949729</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_01.01.2026</t>
   </si>
 </sst>
 </file>
@@ -540,7 +774,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,7 +806,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135166636</v>
+        <v>135887104</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -581,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -599,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -617,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -635,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -653,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -671,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -689,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -707,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -725,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -743,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -761,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -779,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -797,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -815,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -833,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -848,10 +1082,10 @@
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -860,16 +1094,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,16 +1112,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,16 +1130,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -914,16 +1148,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -932,16 +1166,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -950,16 +1184,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -968,16 +1202,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -986,16 +1220,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1238,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1022,16 +1256,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1040,24 +1274,1314 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1073,31 +2597,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2A1F6F-4F38-4396-9E6D-F17AA1ECEBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0881D1-2CF5-42C5-8E7D-1D6DD4638502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="164">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,270 +54,6 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa Sicredi 30/12/2025</t>
-  </si>
-  <si>
-    <t>135882601</t>
-  </si>
-  <si>
-    <t>135882864</t>
-  </si>
-  <si>
-    <t>135937891</t>
-  </si>
-  <si>
-    <t>135899908</t>
-  </si>
-  <si>
-    <t>135937970</t>
-  </si>
-  <si>
-    <t>134727124</t>
-  </si>
-  <si>
-    <t>135959998</t>
-  </si>
-  <si>
-    <t>135876618</t>
-  </si>
-  <si>
-    <t>135878999</t>
-  </si>
-  <si>
-    <t>135979082</t>
-  </si>
-  <si>
-    <t>135985831</t>
-  </si>
-  <si>
-    <t>135981055</t>
-  </si>
-  <si>
-    <t>135982931</t>
-  </si>
-  <si>
-    <t>133320663</t>
-  </si>
-  <si>
-    <t>136006030</t>
-  </si>
-  <si>
-    <t>136001975</t>
-  </si>
-  <si>
-    <t>135991880</t>
-  </si>
-  <si>
-    <t>136006226</t>
-  </si>
-  <si>
-    <t>136002815</t>
-  </si>
-  <si>
-    <t>135999237</t>
-  </si>
-  <si>
-    <t>135998467</t>
-  </si>
-  <si>
-    <t>135995476</t>
-  </si>
-  <si>
-    <t>136007901</t>
-  </si>
-  <si>
-    <t>136006910</t>
-  </si>
-  <si>
-    <t>136013729</t>
-  </si>
-  <si>
-    <t>136016172</t>
-  </si>
-  <si>
-    <t>136013772</t>
-  </si>
-  <si>
-    <t>136021540</t>
-  </si>
-  <si>
-    <t>135995182</t>
-  </si>
-  <si>
-    <t>136023731</t>
-  </si>
-  <si>
-    <t>136024092</t>
-  </si>
-  <si>
-    <t>136024586</t>
-  </si>
-  <si>
-    <t>135997305</t>
-  </si>
-  <si>
-    <t>134290973</t>
-  </si>
-  <si>
-    <t>136030669</t>
-  </si>
-  <si>
-    <t>136002902</t>
-  </si>
-  <si>
-    <t>135998375</t>
-  </si>
-  <si>
-    <t>135897648</t>
-  </si>
-  <si>
-    <t>135986437</t>
-  </si>
-  <si>
-    <t>136050763</t>
-  </si>
-  <si>
-    <t>136039306</t>
-  </si>
-  <si>
-    <t>136040870</t>
-  </si>
-  <si>
-    <t>136029776</t>
-  </si>
-  <si>
-    <t>136046251</t>
-  </si>
-  <si>
-    <t>135873089</t>
-  </si>
-  <si>
-    <t>135875810</t>
-  </si>
-  <si>
-    <t>135882790</t>
-  </si>
-  <si>
-    <t>135883283</t>
-  </si>
-  <si>
-    <t>135884396</t>
-  </si>
-  <si>
-    <t>135887831</t>
-  </si>
-  <si>
-    <t>135887927</t>
-  </si>
-  <si>
-    <t>136056638</t>
-  </si>
-  <si>
-    <t>136057747</t>
-  </si>
-  <si>
-    <t>136059789</t>
-  </si>
-  <si>
-    <t>136061228</t>
-  </si>
-  <si>
-    <t>136057027</t>
-  </si>
-  <si>
-    <t>134880624</t>
-  </si>
-  <si>
-    <t>136065005</t>
-  </si>
-  <si>
-    <t>136066601</t>
-  </si>
-  <si>
-    <t>134425718</t>
-  </si>
-  <si>
-    <t>133076320</t>
-  </si>
-  <si>
-    <t>135980697</t>
-  </si>
-  <si>
-    <t>132941813</t>
-  </si>
-  <si>
-    <t>136069332</t>
-  </si>
-  <si>
-    <t>132564131</t>
-  </si>
-  <si>
-    <t>135976847</t>
-  </si>
-  <si>
-    <t>135995698</t>
-  </si>
-  <si>
-    <t>135984162</t>
-  </si>
-  <si>
-    <t>136067519</t>
-  </si>
-  <si>
-    <t>136071802</t>
-  </si>
-  <si>
-    <t>132840822</t>
-  </si>
-  <si>
-    <t>135920326</t>
-  </si>
-  <si>
-    <t>135929217</t>
-  </si>
-  <si>
-    <t>135952449</t>
-  </si>
-  <si>
-    <t>135978288</t>
-  </si>
-  <si>
-    <t>133411782</t>
-  </si>
-  <si>
-    <t>136061365</t>
-  </si>
-  <si>
-    <t>135873899</t>
-  </si>
-  <si>
-    <t>135883430</t>
-  </si>
-  <si>
-    <t>135896453</t>
-  </si>
-  <si>
-    <t>135905685</t>
-  </si>
-  <si>
-    <t>135750341</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_30.12.2025</t>
-  </si>
-  <si>
-    <t>135934228</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicredi 01/01/2026</t>
-  </si>
-  <si>
-    <t>135938011</t>
-  </si>
-  <si>
-    <t>135938241</t>
-  </si>
-  <si>
     <t>135917442</t>
   </si>
   <si>
@@ -330,27 +66,9 @@
     <t>135925895</t>
   </si>
   <si>
-    <t>135934543</t>
-  </si>
-  <si>
-    <t>135906669</t>
-  </si>
-  <si>
-    <t>135907645</t>
-  </si>
-  <si>
     <t>135931385</t>
   </si>
   <si>
-    <t>135925935</t>
-  </si>
-  <si>
-    <t>135933027</t>
-  </si>
-  <si>
-    <t>135958550</t>
-  </si>
-  <si>
     <t>135956468</t>
   </si>
   <si>
@@ -369,7 +87,439 @@
     <t>135949729</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_01.01.2026</t>
+    <t>Recusas Sicredi 02/01/2026</t>
+  </si>
+  <si>
+    <t>135974357</t>
+  </si>
+  <si>
+    <t>135974699</t>
+  </si>
+  <si>
+    <t>135986347</t>
+  </si>
+  <si>
+    <t>135978555</t>
+  </si>
+  <si>
+    <t>135980732</t>
+  </si>
+  <si>
+    <t>135981022</t>
+  </si>
+  <si>
+    <t>135981227</t>
+  </si>
+  <si>
+    <t>135982940</t>
+  </si>
+  <si>
+    <t>136008909</t>
+  </si>
+  <si>
+    <t>135998310</t>
+  </si>
+  <si>
+    <t>135999466</t>
+  </si>
+  <si>
+    <t>136002114</t>
+  </si>
+  <si>
+    <t>136006694</t>
+  </si>
+  <si>
+    <t>136015180</t>
+  </si>
+  <si>
+    <t>136013209</t>
+  </si>
+  <si>
+    <t>136012414</t>
+  </si>
+  <si>
+    <t>136015866</t>
+  </si>
+  <si>
+    <t>136028803</t>
+  </si>
+  <si>
+    <t>136029415</t>
+  </si>
+  <si>
+    <t>136028877</t>
+  </si>
+  <si>
+    <t>135980025</t>
+  </si>
+  <si>
+    <t>136019840</t>
+  </si>
+  <si>
+    <t>136024341</t>
+  </si>
+  <si>
+    <t>136025787</t>
+  </si>
+  <si>
+    <t>136028854</t>
+  </si>
+  <si>
+    <t>136025146</t>
+  </si>
+  <si>
+    <t>136025776</t>
+  </si>
+  <si>
+    <t>136025013</t>
+  </si>
+  <si>
+    <t>136042938</t>
+  </si>
+  <si>
+    <t>136045299</t>
+  </si>
+  <si>
+    <t>133772326</t>
+  </si>
+  <si>
+    <t>136051885</t>
+  </si>
+  <si>
+    <t>136053960</t>
+  </si>
+  <si>
+    <t>136040886</t>
+  </si>
+  <si>
+    <t>136051655</t>
+  </si>
+  <si>
+    <t>136045767</t>
+  </si>
+  <si>
+    <t>136050934</t>
+  </si>
+  <si>
+    <t>136014976</t>
+  </si>
+  <si>
+    <t>136046468</t>
+  </si>
+  <si>
+    <t>136047665</t>
+  </si>
+  <si>
+    <t>136060605</t>
+  </si>
+  <si>
+    <t>136063672</t>
+  </si>
+  <si>
+    <t>135979325</t>
+  </si>
+  <si>
+    <t>136070120</t>
+  </si>
+  <si>
+    <t>136056448</t>
+  </si>
+  <si>
+    <t>136072868</t>
+  </si>
+  <si>
+    <t>135986015</t>
+  </si>
+  <si>
+    <t>135979816</t>
+  </si>
+  <si>
+    <t>136070628</t>
+  </si>
+  <si>
+    <t>136063355</t>
+  </si>
+  <si>
+    <t>136081045</t>
+  </si>
+  <si>
+    <t>135985302</t>
+  </si>
+  <si>
+    <t>135973896</t>
+  </si>
+  <si>
+    <t>136081208</t>
+  </si>
+  <si>
+    <t>135974203</t>
+  </si>
+  <si>
+    <t>136023678</t>
+  </si>
+  <si>
+    <t>135977738</t>
+  </si>
+  <si>
+    <t>135977915</t>
+  </si>
+  <si>
+    <t>135979743</t>
+  </si>
+  <si>
+    <t>136082836</t>
+  </si>
+  <si>
+    <t>135994081</t>
+  </si>
+  <si>
+    <t>135999226</t>
+  </si>
+  <si>
+    <t>135981513</t>
+  </si>
+  <si>
+    <t>135982516</t>
+  </si>
+  <si>
+    <t>136078765</t>
+  </si>
+  <si>
+    <t>135982952</t>
+  </si>
+  <si>
+    <t>134629361</t>
+  </si>
+  <si>
+    <t>135984603</t>
+  </si>
+  <si>
+    <t>135990167</t>
+  </si>
+  <si>
+    <t>136008492</t>
+  </si>
+  <si>
+    <t>135984977</t>
+  </si>
+  <si>
+    <t>136084077</t>
+  </si>
+  <si>
+    <t>135985119</t>
+  </si>
+  <si>
+    <t>135985175</t>
+  </si>
+  <si>
+    <t>136084886</t>
+  </si>
+  <si>
+    <t>136084725</t>
+  </si>
+  <si>
+    <t>136084519</t>
+  </si>
+  <si>
+    <t>135054204</t>
+  </si>
+  <si>
+    <t>136004443</t>
+  </si>
+  <si>
+    <t>135986952</t>
+  </si>
+  <si>
+    <t>136001712</t>
+  </si>
+  <si>
+    <t>135528624</t>
+  </si>
+  <si>
+    <t>136026968</t>
+  </si>
+  <si>
+    <t>136026266</t>
+  </si>
+  <si>
+    <t>136047108</t>
+  </si>
+  <si>
+    <t>136025290</t>
+  </si>
+  <si>
+    <t>136024795</t>
+  </si>
+  <si>
+    <t>136027746</t>
+  </si>
+  <si>
+    <t>136087489</t>
+  </si>
+  <si>
+    <t>136084387</t>
+  </si>
+  <si>
+    <t>136047497</t>
+  </si>
+  <si>
+    <t>136015242</t>
+  </si>
+  <si>
+    <t>136022568</t>
+  </si>
+  <si>
+    <t>136022897</t>
+  </si>
+  <si>
+    <t>135408798</t>
+  </si>
+  <si>
+    <t>134862292</t>
+  </si>
+  <si>
+    <t>136060200</t>
+  </si>
+  <si>
+    <t>135991887</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_02.01.2026</t>
+  </si>
+  <si>
+    <t>135940326</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 03/01/2026</t>
+  </si>
+  <si>
+    <t>135978742</t>
+  </si>
+  <si>
+    <t>135987058</t>
+  </si>
+  <si>
+    <t>135981904</t>
+  </si>
+  <si>
+    <t>136009013</t>
+  </si>
+  <si>
+    <t>136004821</t>
+  </si>
+  <si>
+    <t>136006844</t>
+  </si>
+  <si>
+    <t>136058368</t>
+  </si>
+  <si>
+    <t>136066110</t>
+  </si>
+  <si>
+    <t>136068080</t>
+  </si>
+  <si>
+    <t>136062716</t>
+  </si>
+  <si>
+    <t>135947124</t>
+  </si>
+  <si>
+    <t>135970482</t>
+  </si>
+  <si>
+    <t>135971759</t>
+  </si>
+  <si>
+    <t>135972737</t>
+  </si>
+  <si>
+    <t>135973248</t>
+  </si>
+  <si>
+    <t>135973497</t>
+  </si>
+  <si>
+    <t>135973926</t>
+  </si>
+  <si>
+    <t>135974087</t>
+  </si>
+  <si>
+    <t>135974294</t>
+  </si>
+  <si>
+    <t>135995612</t>
+  </si>
+  <si>
+    <t>135977632</t>
+  </si>
+  <si>
+    <t>135982640</t>
+  </si>
+  <si>
+    <t>135983439</t>
+  </si>
+  <si>
+    <t>135984334</t>
+  </si>
+  <si>
+    <t>132398496</t>
+  </si>
+  <si>
+    <t>135994843</t>
+  </si>
+  <si>
+    <t>136003618</t>
+  </si>
+  <si>
+    <t>135999549</t>
+  </si>
+  <si>
+    <t>133609934</t>
+  </si>
+  <si>
+    <t>135998602</t>
+  </si>
+  <si>
+    <t>136006962</t>
+  </si>
+  <si>
+    <t>136001483</t>
+  </si>
+  <si>
+    <t>136006445</t>
+  </si>
+  <si>
+    <t>136007475</t>
+  </si>
+  <si>
+    <t>136007699</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_03.01.2026</t>
+  </si>
+  <si>
+    <t>136043422</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 04/01/2026</t>
+  </si>
+  <si>
+    <t>136067135</t>
+  </si>
+  <si>
+    <t>136066805</t>
+  </si>
+  <si>
+    <t>136067432</t>
+  </si>
+  <si>
+    <t>136083489</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_04.01.2026</t>
   </si>
 </sst>
 </file>
@@ -774,7 +924,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -806,16 +956,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135887104</v>
+        <v>134775899</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -824,16 +974,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -842,16 +992,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -860,16 +1010,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -878,16 +1028,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -896,16 +1046,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -914,16 +1064,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -932,16 +1082,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -950,16 +1100,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -968,16 +1118,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -986,16 +1136,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1154,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1022,16 +1172,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1040,16 +1190,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1058,16 +1208,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1076,16 +1226,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1094,16 +1244,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1112,16 +1262,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1130,16 +1280,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1148,16 +1298,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1166,16 +1316,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1184,16 +1334,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1202,16 +1352,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1220,16 +1370,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1238,16 +1388,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1256,16 +1406,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1274,16 +1424,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1292,16 +1442,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1310,16 +1460,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1327,16 +1477,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1344,16 +1494,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1361,16 +1511,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1378,16 +1528,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1395,16 +1545,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1412,16 +1562,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1429,16 +1579,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1446,16 +1596,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1463,16 +1613,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1480,16 +1630,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1497,16 +1647,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1514,16 +1664,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1531,16 +1681,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1548,16 +1698,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1565,16 +1715,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1582,16 +1732,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1599,16 +1749,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1616,16 +1766,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1633,16 +1783,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1650,16 +1800,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1667,16 +1817,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1684,16 +1834,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1701,16 +1851,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1718,16 +1868,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1735,16 +1885,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1752,16 +1902,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1769,16 +1919,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1786,16 +1936,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1803,16 +1953,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1820,16 +1970,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1837,16 +1987,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1854,16 +2004,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1871,16 +2021,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1894,10 +2044,10 @@
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -1911,10 +2061,10 @@
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -1928,10 +2078,10 @@
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -1945,10 +2095,10 @@
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -1962,10 +2112,10 @@
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -1979,10 +2129,10 @@
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -1996,10 +2146,10 @@
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
@@ -2013,10 +2163,10 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
@@ -2030,10 +2180,10 @@
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
@@ -2047,10 +2197,10 @@
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
@@ -2064,10 +2214,10 @@
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
@@ -2081,10 +2231,10 @@
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
@@ -2098,10 +2248,10 @@
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
@@ -2115,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
@@ -2132,10 +2282,10 @@
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
@@ -2149,10 +2299,10 @@
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
@@ -2166,10 +2316,10 @@
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
@@ -2183,10 +2333,10 @@
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
@@ -2200,10 +2350,10 @@
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
@@ -2217,10 +2367,10 @@
         <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>6</v>
@@ -2234,10 +2384,10 @@
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>91</v>
+        <v>19</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>6</v>
@@ -2245,16 +2395,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>6</v>
@@ -2262,16 +2412,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>6</v>
@@ -2279,16 +2429,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>6</v>
@@ -2296,16 +2446,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>6</v>
@@ -2313,16 +2463,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>6</v>
@@ -2330,16 +2480,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>6</v>
@@ -2347,16 +2497,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>6</v>
@@ -2364,16 +2514,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>6</v>
@@ -2381,16 +2531,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>6</v>
@@ -2398,16 +2548,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>6</v>
@@ -2415,16 +2565,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>6</v>
@@ -2432,16 +2582,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>6</v>
@@ -2449,16 +2599,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>6</v>
@@ -2466,16 +2616,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>6</v>
@@ -2483,16 +2633,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>6</v>
@@ -2500,16 +2650,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>6</v>
@@ -2517,16 +2667,16 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>6</v>
@@ -2534,16 +2684,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>6</v>
@@ -2551,16 +2701,16 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>113</v>
+        <v>19</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>6</v>
@@ -2568,20 +2718,848 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D104" s="2" t="s">
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D153" s="1"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D154" s="1"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D155" s="1"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D156" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -2597,31 +3575,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17256066-FF7D-4140-BB8B-A4DBAF4F0C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EBE691-A483-4F3F-8256-EAB6112CA4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="88">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,217 +54,244 @@
     <t>971</t>
   </si>
   <si>
-    <t>Relatório de Recusa MDS 05.01.2026</t>
-  </si>
-  <si>
-    <t>136015026</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 05/01/2026</t>
-  </si>
-  <si>
-    <t>136013440</t>
-  </si>
-  <si>
-    <t>136012300</t>
-  </si>
-  <si>
-    <t>136019863</t>
-  </si>
-  <si>
-    <t>136029652</t>
-  </si>
-  <si>
-    <t>136015895</t>
-  </si>
-  <si>
-    <t>136028423</t>
-  </si>
-  <si>
-    <t>136038699</t>
-  </si>
-  <si>
-    <t>136057786</t>
-  </si>
-  <si>
-    <t>136058219</t>
-  </si>
-  <si>
-    <t>136042036</t>
-  </si>
-  <si>
-    <t>136060040</t>
-  </si>
-  <si>
-    <t>136068326</t>
-  </si>
-  <si>
-    <t>136068477</t>
-  </si>
-  <si>
-    <t>136071474</t>
-  </si>
-  <si>
-    <t>136058752</t>
-  </si>
-  <si>
-    <t>136072864</t>
-  </si>
-  <si>
-    <t>136065774</t>
-  </si>
-  <si>
-    <t>136070802</t>
-  </si>
-  <si>
-    <t>136071586</t>
-  </si>
-  <si>
-    <t>136066498</t>
-  </si>
-  <si>
-    <t>136079068</t>
-  </si>
-  <si>
-    <t>136080370</t>
-  </si>
-  <si>
-    <t>136058277</t>
-  </si>
-  <si>
-    <t>136053502</t>
-  </si>
-  <si>
-    <t>134473932</t>
-  </si>
-  <si>
-    <t>136089884</t>
-  </si>
-  <si>
-    <t>136080585</t>
-  </si>
-  <si>
-    <t>136088643</t>
-  </si>
-  <si>
-    <t>136045819</t>
-  </si>
-  <si>
-    <t>133911066</t>
-  </si>
-  <si>
-    <t>136063932</t>
-  </si>
-  <si>
-    <t>136052337</t>
-  </si>
-  <si>
-    <t>136025637</t>
-  </si>
-  <si>
-    <t>136014042</t>
-  </si>
-  <si>
-    <t>136014617</t>
-  </si>
-  <si>
-    <t>135992503</t>
-  </si>
-  <si>
-    <t>133320663</t>
-  </si>
-  <si>
-    <t>136050435</t>
-  </si>
-  <si>
-    <t>135303359</t>
-  </si>
-  <si>
-    <t>136054149</t>
-  </si>
-  <si>
-    <t>136046629</t>
-  </si>
-  <si>
-    <t>135994723</t>
-  </si>
-  <si>
-    <t>136014124</t>
-  </si>
-  <si>
-    <t>135661513</t>
-  </si>
-  <si>
-    <t>136015974</t>
-  </si>
-  <si>
-    <t>136060654</t>
-  </si>
-  <si>
-    <t>136058686</t>
-  </si>
-  <si>
-    <t>136062850</t>
-  </si>
-  <si>
-    <t>135765063</t>
-  </si>
-  <si>
-    <t>136033253</t>
-  </si>
-  <si>
-    <t>136101354</t>
-  </si>
-  <si>
-    <t>136028086</t>
-  </si>
-  <si>
-    <t>136059146</t>
-  </si>
-  <si>
-    <t>136103210</t>
-  </si>
-  <si>
-    <t>136030700</t>
-  </si>
-  <si>
-    <t>136102872</t>
-  </si>
-  <si>
-    <t>135998148</t>
-  </si>
-  <si>
-    <t>136029928</t>
-  </si>
-  <si>
-    <t>136068273</t>
-  </si>
-  <si>
-    <t>135979609</t>
-  </si>
-  <si>
-    <t>135983337</t>
-  </si>
-  <si>
-    <t>136000820</t>
-  </si>
-  <si>
-    <t>136100964</t>
-  </si>
-  <si>
-    <t>136015076</t>
-  </si>
-  <si>
-    <t>136063517</t>
-  </si>
-  <si>
-    <t>135999837</t>
-  </si>
-  <si>
-    <t>136007895</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_05.01.2026</t>
+    <t>Recusas Sicredi 06/01/2026</t>
+  </si>
+  <si>
+    <t>136004168</t>
+  </si>
+  <si>
+    <t>136006883</t>
+  </si>
+  <si>
+    <t>135989907</t>
+  </si>
+  <si>
+    <t>136011867</t>
+  </si>
+  <si>
+    <t>135994345</t>
+  </si>
+  <si>
+    <t>136024026</t>
+  </si>
+  <si>
+    <t>136026313</t>
+  </si>
+  <si>
+    <t>136030207</t>
+  </si>
+  <si>
+    <t>136030455</t>
+  </si>
+  <si>
+    <t>136028025</t>
+  </si>
+  <si>
+    <t>136027054</t>
+  </si>
+  <si>
+    <t>136022108</t>
+  </si>
+  <si>
+    <t>136023275</t>
+  </si>
+  <si>
+    <t>136019762</t>
+  </si>
+  <si>
+    <t>136052511</t>
+  </si>
+  <si>
+    <t>136014492</t>
+  </si>
+  <si>
+    <t>136016045</t>
+  </si>
+  <si>
+    <t>136063800</t>
+  </si>
+  <si>
+    <t>136073311</t>
+  </si>
+  <si>
+    <t>136066508</t>
+  </si>
+  <si>
+    <t>136078971</t>
+  </si>
+  <si>
+    <t>136083510</t>
+  </si>
+  <si>
+    <t>135999173</t>
+  </si>
+  <si>
+    <t>136043182</t>
+  </si>
+  <si>
+    <t>136085575</t>
+  </si>
+  <si>
+    <t>135982143</t>
+  </si>
+  <si>
+    <t>136078678</t>
+  </si>
+  <si>
+    <t>136041120</t>
+  </si>
+  <si>
+    <t>136070839</t>
+  </si>
+  <si>
+    <t>136103888</t>
+  </si>
+  <si>
+    <t>136108287</t>
+  </si>
+  <si>
+    <t>136108479</t>
+  </si>
+  <si>
+    <t>136103354</t>
+  </si>
+  <si>
+    <t>135990211</t>
+  </si>
+  <si>
+    <t>135990247</t>
+  </si>
+  <si>
+    <t>135993531</t>
+  </si>
+  <si>
+    <t>135991400</t>
+  </si>
+  <si>
+    <t>135994155</t>
+  </si>
+  <si>
+    <t>135992588</t>
+  </si>
+  <si>
+    <t>135993114</t>
+  </si>
+  <si>
+    <t>135998999</t>
+  </si>
+  <si>
+    <t>136000699</t>
+  </si>
+  <si>
+    <t>136002369</t>
+  </si>
+  <si>
+    <t>136006076</t>
+  </si>
+  <si>
+    <t>136012652</t>
+  </si>
+  <si>
+    <t>136014456</t>
+  </si>
+  <si>
+    <t>136015464</t>
+  </si>
+  <si>
+    <t>136015834</t>
+  </si>
+  <si>
+    <t>136016174</t>
+  </si>
+  <si>
+    <t>136062317</t>
+  </si>
+  <si>
+    <t>136107744</t>
+  </si>
+  <si>
+    <t>136112275</t>
+  </si>
+  <si>
+    <t>136072692</t>
+  </si>
+  <si>
+    <t>136112295</t>
+  </si>
+  <si>
+    <t>136117045</t>
+  </si>
+  <si>
+    <t>136066184</t>
+  </si>
+  <si>
+    <t>132631981</t>
+  </si>
+  <si>
+    <t>136022696</t>
+  </si>
+  <si>
+    <t>136051674</t>
+  </si>
+  <si>
+    <t>136022534</t>
+  </si>
+  <si>
+    <t>133722226</t>
+  </si>
+  <si>
+    <t>136067572</t>
+  </si>
+  <si>
+    <t>136025267</t>
+  </si>
+  <si>
+    <t>136030145</t>
+  </si>
+  <si>
+    <t>136073371</t>
+  </si>
+  <si>
+    <t>136023812</t>
+  </si>
+  <si>
+    <t>136046729</t>
+  </si>
+  <si>
+    <t>136041836</t>
+  </si>
+  <si>
+    <t>136123830</t>
+  </si>
+  <si>
+    <t>136063614</t>
+  </si>
+  <si>
+    <t>136128057</t>
+  </si>
+  <si>
+    <t>136048289</t>
+  </si>
+  <si>
+    <t>134597400</t>
+  </si>
+  <si>
+    <t>136024356</t>
+  </si>
+  <si>
+    <t>136024579</t>
+  </si>
+  <si>
+    <t>136027093</t>
+  </si>
+  <si>
+    <t>136027522</t>
+  </si>
+  <si>
+    <t>136014448</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_06.01.2026</t>
   </si>
 </sst>
 </file>
@@ -669,7 +696,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -701,7 +728,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136098436</v>
+        <v>135990715</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -710,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -725,10 +752,10 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -737,16 +764,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -755,16 +782,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -773,16 +800,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -791,16 +818,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -809,16 +836,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -827,16 +854,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -845,16 +872,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -863,16 +890,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -881,16 +908,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -899,16 +926,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -917,16 +944,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -935,16 +962,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -953,16 +980,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -971,16 +998,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -989,16 +1016,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1007,16 +1034,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1025,16 +1052,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1043,16 +1070,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1061,16 +1088,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1079,16 +1106,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1097,16 +1124,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1115,16 +1142,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1133,16 +1160,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1151,16 +1178,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1169,16 +1196,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1187,16 +1214,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1205,16 +1232,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1222,16 +1249,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1239,16 +1266,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1256,16 +1283,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1273,16 +1300,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1290,16 +1317,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1307,16 +1334,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1324,16 +1351,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1341,16 +1368,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1358,16 +1385,16 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1375,16 +1402,16 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1392,16 +1419,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1409,16 +1436,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1426,16 +1453,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1443,16 +1470,16 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1460,16 +1487,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1477,16 +1504,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1494,16 +1521,16 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1511,16 +1538,16 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1528,16 +1555,16 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1545,16 +1572,16 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1562,16 +1589,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1579,16 +1606,16 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1596,16 +1623,16 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1613,16 +1640,16 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1630,16 +1657,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1647,16 +1674,16 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1664,16 +1691,16 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1681,16 +1708,16 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1698,16 +1725,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1715,16 +1742,16 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1732,16 +1759,16 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1749,16 +1776,16 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1766,16 +1793,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -1783,16 +1810,16 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -1800,16 +1827,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -1817,16 +1844,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -1834,16 +1861,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -1851,16 +1878,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -1868,16 +1895,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -1885,18 +1912,188 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1914,31 +2111,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EBE691-A483-4F3F-8256-EAB6112CA4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB899769-E020-4BAF-AC7C-AC411F0B4928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,244 +54,244 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 06/01/2026</t>
-  </si>
-  <si>
-    <t>136004168</t>
-  </si>
-  <si>
-    <t>136006883</t>
-  </si>
-  <si>
-    <t>135989907</t>
-  </si>
-  <si>
-    <t>136011867</t>
-  </si>
-  <si>
-    <t>135994345</t>
-  </si>
-  <si>
-    <t>136024026</t>
-  </si>
-  <si>
-    <t>136026313</t>
-  </si>
-  <si>
-    <t>136030207</t>
-  </si>
-  <si>
-    <t>136030455</t>
-  </si>
-  <si>
-    <t>136028025</t>
-  </si>
-  <si>
-    <t>136027054</t>
-  </si>
-  <si>
-    <t>136022108</t>
-  </si>
-  <si>
-    <t>136023275</t>
-  </si>
-  <si>
-    <t>136019762</t>
-  </si>
-  <si>
-    <t>136052511</t>
-  </si>
-  <si>
-    <t>136014492</t>
-  </si>
-  <si>
-    <t>136016045</t>
-  </si>
-  <si>
-    <t>136063800</t>
-  </si>
-  <si>
-    <t>136073311</t>
-  </si>
-  <si>
-    <t>136066508</t>
-  </si>
-  <si>
-    <t>136078971</t>
-  </si>
-  <si>
-    <t>136083510</t>
-  </si>
-  <si>
-    <t>135999173</t>
-  </si>
-  <si>
-    <t>136043182</t>
-  </si>
-  <si>
-    <t>136085575</t>
-  </si>
-  <si>
-    <t>135982143</t>
-  </si>
-  <si>
-    <t>136078678</t>
-  </si>
-  <si>
-    <t>136041120</t>
-  </si>
-  <si>
-    <t>136070839</t>
-  </si>
-  <si>
-    <t>136103888</t>
-  </si>
-  <si>
-    <t>136108287</t>
-  </si>
-  <si>
-    <t>136108479</t>
-  </si>
-  <si>
-    <t>136103354</t>
-  </si>
-  <si>
-    <t>135990211</t>
-  </si>
-  <si>
-    <t>135990247</t>
-  </si>
-  <si>
-    <t>135993531</t>
-  </si>
-  <si>
-    <t>135991400</t>
-  </si>
-  <si>
-    <t>135994155</t>
-  </si>
-  <si>
-    <t>135992588</t>
-  </si>
-  <si>
-    <t>135993114</t>
-  </si>
-  <si>
-    <t>135998999</t>
-  </si>
-  <si>
-    <t>136000699</t>
-  </si>
-  <si>
-    <t>136002369</t>
-  </si>
-  <si>
-    <t>136006076</t>
-  </si>
-  <si>
-    <t>136012652</t>
-  </si>
-  <si>
-    <t>136014456</t>
-  </si>
-  <si>
-    <t>136015464</t>
-  </si>
-  <si>
-    <t>136015834</t>
-  </si>
-  <si>
-    <t>136016174</t>
-  </si>
-  <si>
-    <t>136062317</t>
-  </si>
-  <si>
-    <t>136107744</t>
-  </si>
-  <si>
-    <t>136112275</t>
-  </si>
-  <si>
-    <t>136072692</t>
-  </si>
-  <si>
-    <t>136112295</t>
-  </si>
-  <si>
-    <t>136117045</t>
-  </si>
-  <si>
-    <t>136066184</t>
-  </si>
-  <si>
-    <t>132631981</t>
-  </si>
-  <si>
-    <t>136022696</t>
-  </si>
-  <si>
-    <t>136051674</t>
-  </si>
-  <si>
-    <t>136022534</t>
-  </si>
-  <si>
-    <t>133722226</t>
-  </si>
-  <si>
-    <t>136067572</t>
-  </si>
-  <si>
-    <t>136025267</t>
-  </si>
-  <si>
-    <t>136030145</t>
-  </si>
-  <si>
-    <t>136073371</t>
-  </si>
-  <si>
-    <t>136023812</t>
-  </si>
-  <si>
-    <t>136046729</t>
-  </si>
-  <si>
-    <t>136041836</t>
-  </si>
-  <si>
-    <t>136123830</t>
-  </si>
-  <si>
-    <t>136063614</t>
-  </si>
-  <si>
-    <t>136128057</t>
-  </si>
-  <si>
-    <t>136048289</t>
-  </si>
-  <si>
-    <t>134597400</t>
-  </si>
-  <si>
-    <t>136024356</t>
-  </si>
-  <si>
-    <t>136024579</t>
-  </si>
-  <si>
-    <t>136027093</t>
-  </si>
-  <si>
-    <t>136027522</t>
-  </si>
-  <si>
-    <t>136014448</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_06.01.2026</t>
+    <t>Recusas Sicredi 07/01/2026</t>
+  </si>
+  <si>
+    <t>136053572</t>
+  </si>
+  <si>
+    <t>136048131</t>
+  </si>
+  <si>
+    <t>136062420</t>
+  </si>
+  <si>
+    <t>136069679</t>
+  </si>
+  <si>
+    <t>136069760</t>
+  </si>
+  <si>
+    <t>136065035</t>
+  </si>
+  <si>
+    <t>136071613</t>
+  </si>
+  <si>
+    <t>136068462</t>
+  </si>
+  <si>
+    <t>136067464</t>
+  </si>
+  <si>
+    <t>136068146</t>
+  </si>
+  <si>
+    <t>136078789</t>
+  </si>
+  <si>
+    <t>136078864</t>
+  </si>
+  <si>
+    <t>136083453</t>
+  </si>
+  <si>
+    <t>136084849</t>
+  </si>
+  <si>
+    <t>136083635</t>
+  </si>
+  <si>
+    <t>136084464</t>
+  </si>
+  <si>
+    <t>136085406</t>
+  </si>
+  <si>
+    <t>136089827</t>
+  </si>
+  <si>
+    <t>136084131</t>
+  </si>
+  <si>
+    <t>136082285</t>
+  </si>
+  <si>
+    <t>136079756</t>
+  </si>
+  <si>
+    <t>136080120</t>
+  </si>
+  <si>
+    <t>136085578</t>
+  </si>
+  <si>
+    <t>136071206</t>
+  </si>
+  <si>
+    <t>136095836</t>
+  </si>
+  <si>
+    <t>136104105</t>
+  </si>
+  <si>
+    <t>136106572</t>
+  </si>
+  <si>
+    <t>136104756</t>
+  </si>
+  <si>
+    <t>136100626</t>
+  </si>
+  <si>
+    <t>136106242</t>
+  </si>
+  <si>
+    <t>136101619</t>
+  </si>
+  <si>
+    <t>136126169</t>
+  </si>
+  <si>
+    <t>136082199</t>
+  </si>
+  <si>
+    <t>136112206</t>
+  </si>
+  <si>
+    <t>136130436</t>
+  </si>
+  <si>
+    <t>136128923</t>
+  </si>
+  <si>
+    <t>136013378</t>
+  </si>
+  <si>
+    <t>136013856</t>
+  </si>
+  <si>
+    <t>136015336</t>
+  </si>
+  <si>
+    <t>136086543</t>
+  </si>
+  <si>
+    <t>136047043</t>
+  </si>
+  <si>
+    <t>136133175</t>
+  </si>
+  <si>
+    <t>136133595</t>
+  </si>
+  <si>
+    <t>136049014</t>
+  </si>
+  <si>
+    <t>136067847</t>
+  </si>
+  <si>
+    <t>136071362</t>
+  </si>
+  <si>
+    <t>134083475</t>
+  </si>
+  <si>
+    <t>136136678</t>
+  </si>
+  <si>
+    <t>136136572</t>
+  </si>
+  <si>
+    <t>135281357</t>
+  </si>
+  <si>
+    <t>136067586</t>
+  </si>
+  <si>
+    <t>136058020</t>
+  </si>
+  <si>
+    <t>136049114</t>
+  </si>
+  <si>
+    <t>136138243</t>
+  </si>
+  <si>
+    <t>136071973</t>
+  </si>
+  <si>
+    <t>134880624</t>
+  </si>
+  <si>
+    <t>136067941</t>
+  </si>
+  <si>
+    <t>136076265</t>
+  </si>
+  <si>
+    <t>136052724</t>
+  </si>
+  <si>
+    <t>136139494</t>
+  </si>
+  <si>
+    <t>136137450</t>
+  </si>
+  <si>
+    <t>136087075</t>
+  </si>
+  <si>
+    <t>136086929</t>
+  </si>
+  <si>
+    <t>136052648</t>
+  </si>
+  <si>
+    <t>133488139</t>
+  </si>
+  <si>
+    <t>136086164</t>
+  </si>
+  <si>
+    <t>136020914</t>
+  </si>
+  <si>
+    <t>136087155</t>
+  </si>
+  <si>
+    <t>136144412</t>
+  </si>
+  <si>
+    <t>136145824</t>
+  </si>
+  <si>
+    <t>135606013</t>
+  </si>
+  <si>
+    <t>135838599</t>
+  </si>
+  <si>
+    <t>136057915</t>
+  </si>
+  <si>
+    <t>136059551</t>
+  </si>
+  <si>
+    <t>136081353</t>
+  </si>
+  <si>
+    <t>136086875</t>
+  </si>
+  <si>
+    <t>136013508</t>
+  </si>
+  <si>
+    <t>136013536</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_07.01.2026</t>
   </si>
 </sst>
 </file>
@@ -696,7 +696,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -728,7 +728,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135990715</v>
+        <v>135640390</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -2096,6 +2096,54 @@
       <c r="E80" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D81" s="1"/>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D82" s="1"/>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D83" s="1"/>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D84" s="1"/>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D85" s="1"/>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D86" s="1"/>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D87" s="1"/>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D88" s="1"/>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D89" s="1"/>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D90" s="1"/>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D91" s="1"/>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D92" s="1"/>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D93" s="1"/>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D94" s="1"/>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D95" s="1"/>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D96" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -2111,31 +2159,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CC297D-A7FA-48B2-8385-D1EDC9EE821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987DAE98-FFE9-48AA-A3BA-2653822AD26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="109">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,94 +51,310 @@
     <t>971</t>
   </si>
   <si>
-    <t>Processado</t>
-  </si>
-  <si>
-    <t>134172760</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 12/01/2026</t>
-  </si>
-  <si>
-    <t>136117131</t>
-  </si>
-  <si>
-    <t>136146752</t>
-  </si>
-  <si>
-    <t>136145273</t>
-  </si>
-  <si>
-    <t>136145106</t>
-  </si>
-  <si>
-    <t>136156756</t>
-  </si>
-  <si>
-    <t>136150626</t>
-  </si>
-  <si>
-    <t>136154044</t>
-  </si>
-  <si>
-    <t>136155273</t>
-  </si>
-  <si>
-    <t>136186213</t>
-  </si>
-  <si>
-    <t>136088372</t>
-  </si>
-  <si>
-    <t>136099794</t>
-  </si>
-  <si>
-    <t>136080882</t>
-  </si>
-  <si>
-    <t>136102494</t>
-  </si>
-  <si>
-    <t>136201261</t>
-  </si>
-  <si>
-    <t>136118277</t>
-  </si>
-  <si>
-    <t>136070978</t>
-  </si>
-  <si>
-    <t>136205039</t>
-  </si>
-  <si>
-    <t>136207499</t>
-  </si>
-  <si>
-    <t>136026066</t>
-  </si>
-  <si>
-    <t>136057668</t>
-  </si>
-  <si>
-    <t>136063955</t>
-  </si>
-  <si>
-    <t>136078883</t>
-  </si>
-  <si>
-    <t>136127711</t>
-  </si>
-  <si>
-    <t>136106662</t>
-  </si>
-  <si>
-    <t>136070203</t>
-  </si>
-  <si>
-    <t>136101329</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_12.01.2026</t>
+    <t>Recusas Sicredi 13/01/2026</t>
+  </si>
+  <si>
+    <t>136088007</t>
+  </si>
+  <si>
+    <t>136088789</t>
+  </si>
+  <si>
+    <t>136087386</t>
+  </si>
+  <si>
+    <t>136080555</t>
+  </si>
+  <si>
+    <t>136094426</t>
+  </si>
+  <si>
+    <t>136117531</t>
+  </si>
+  <si>
+    <t>136123627</t>
+  </si>
+  <si>
+    <t>136143227</t>
+  </si>
+  <si>
+    <t>136141673</t>
+  </si>
+  <si>
+    <t>136082618</t>
+  </si>
+  <si>
+    <t>136151782</t>
+  </si>
+  <si>
+    <t>136171286</t>
+  </si>
+  <si>
+    <t>136177314</t>
+  </si>
+  <si>
+    <t>136190103</t>
+  </si>
+  <si>
+    <t>136187831</t>
+  </si>
+  <si>
+    <t>136188057</t>
+  </si>
+  <si>
+    <t>136173644</t>
+  </si>
+  <si>
+    <t>136060610</t>
+  </si>
+  <si>
+    <t>136064357</t>
+  </si>
+  <si>
+    <t>136064906</t>
+  </si>
+  <si>
+    <t>136056348</t>
+  </si>
+  <si>
+    <t>136057320</t>
+  </si>
+  <si>
+    <t>136111618</t>
+  </si>
+  <si>
+    <t>136214309</t>
+  </si>
+  <si>
+    <t>136107743</t>
+  </si>
+  <si>
+    <t>136116448</t>
+  </si>
+  <si>
+    <t>136079142</t>
+  </si>
+  <si>
+    <t>136080355</t>
+  </si>
+  <si>
+    <t>136080691</t>
+  </si>
+  <si>
+    <t>136082014</t>
+  </si>
+  <si>
+    <t>136082423</t>
+  </si>
+  <si>
+    <t>136082714</t>
+  </si>
+  <si>
+    <t>136083176</t>
+  </si>
+  <si>
+    <t>136084225</t>
+  </si>
+  <si>
+    <t>136084601</t>
+  </si>
+  <si>
+    <t>136085378</t>
+  </si>
+  <si>
+    <t>136086204</t>
+  </si>
+  <si>
+    <t>136086666</t>
+  </si>
+  <si>
+    <t>136086683</t>
+  </si>
+  <si>
+    <t>136087045</t>
+  </si>
+  <si>
+    <t>136087578</t>
+  </si>
+  <si>
+    <t>136088770</t>
+  </si>
+  <si>
+    <t>136114400</t>
+  </si>
+  <si>
+    <t>136220308</t>
+  </si>
+  <si>
+    <t>136101890</t>
+  </si>
+  <si>
+    <t>131808031</t>
+  </si>
+  <si>
+    <t>131204199</t>
+  </si>
+  <si>
+    <t>136126253</t>
+  </si>
+  <si>
+    <t>136126474</t>
+  </si>
+  <si>
+    <t>136119387</t>
+  </si>
+  <si>
+    <t>135763824</t>
+  </si>
+  <si>
+    <t>136125189</t>
+  </si>
+  <si>
+    <t>136082568</t>
+  </si>
+  <si>
+    <t>136083243</t>
+  </si>
+  <si>
+    <t>136134474</t>
+  </si>
+  <si>
+    <t>136096255</t>
+  </si>
+  <si>
+    <t>136162761</t>
+  </si>
+  <si>
+    <t>131815825</t>
+  </si>
+  <si>
+    <t>136101954</t>
+  </si>
+  <si>
+    <t>136230059</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_13.01.2026</t>
+  </si>
+  <si>
+    <t>Processar</t>
+  </si>
+  <si>
+    <t>136078901</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 14/01/2026</t>
+  </si>
+  <si>
+    <t>136083477</t>
+  </si>
+  <si>
+    <t>136096009</t>
+  </si>
+  <si>
+    <t>136130478</t>
+  </si>
+  <si>
+    <t>136140105</t>
+  </si>
+  <si>
+    <t>136101033</t>
+  </si>
+  <si>
+    <t>136164587</t>
+  </si>
+  <si>
+    <t>136164903</t>
+  </si>
+  <si>
+    <t>136166689</t>
+  </si>
+  <si>
+    <t>136183866</t>
+  </si>
+  <si>
+    <t>136179156</t>
+  </si>
+  <si>
+    <t>136177384</t>
+  </si>
+  <si>
+    <t>136198501</t>
+  </si>
+  <si>
+    <t>136230267</t>
+  </si>
+  <si>
+    <t>136216963</t>
+  </si>
+  <si>
+    <t>136226801</t>
+  </si>
+  <si>
+    <t>136236015</t>
+  </si>
+  <si>
+    <t>136236301</t>
+  </si>
+  <si>
+    <t>136160214</t>
+  </si>
+  <si>
+    <t>136242451</t>
+  </si>
+  <si>
+    <t>136159845</t>
+  </si>
+  <si>
+    <t>136158056</t>
+  </si>
+  <si>
+    <t>136124514</t>
+  </si>
+  <si>
+    <t>136161077</t>
+  </si>
+  <si>
+    <t>136167375</t>
+  </si>
+  <si>
+    <t>136243536</t>
+  </si>
+  <si>
+    <t>136244774</t>
+  </si>
+  <si>
+    <t>136123856</t>
+  </si>
+  <si>
+    <t>136245506</t>
+  </si>
+  <si>
+    <t>136246819</t>
+  </si>
+  <si>
+    <t>136247052</t>
+  </si>
+  <si>
+    <t>136158903</t>
+  </si>
+  <si>
+    <t>136126590</t>
+  </si>
+  <si>
+    <t>136244822</t>
+  </si>
+  <si>
+    <t>136249195</t>
+  </si>
+  <si>
+    <t>136251178</t>
+  </si>
+  <si>
+    <t>136250615</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_14.01.2026</t>
   </si>
 </sst>
 </file>
@@ -543,7 +759,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -575,496 +791,1680 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136096960</v>
+        <v>136085691</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="1" t="s">
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D30" s="1"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78FAE8A7-5164-4C35-8745-DCC861316DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,171 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 15/01/2026</t>
+  </si>
+  <si>
+    <t>136101614</t>
+  </si>
+  <si>
+    <t>136103268</t>
+  </si>
+  <si>
+    <t>136144878</t>
+  </si>
+  <si>
+    <t>136162147</t>
+  </si>
+  <si>
+    <t>136165989</t>
+  </si>
+  <si>
+    <t>136181720</t>
+  </si>
+  <si>
+    <t>136186662</t>
+  </si>
+  <si>
+    <t>136181236</t>
+  </si>
+  <si>
+    <t>136174190</t>
+  </si>
+  <si>
+    <t>136198634</t>
+  </si>
+  <si>
+    <t>136210195</t>
+  </si>
+  <si>
+    <t>136198787</t>
+  </si>
+  <si>
+    <t>136224031</t>
+  </si>
+  <si>
+    <t>136229715</t>
+  </si>
+  <si>
+    <t>136244054</t>
+  </si>
+  <si>
+    <t>134919600</t>
+  </si>
+  <si>
+    <t>136249671</t>
+  </si>
+  <si>
+    <t>136250307</t>
+  </si>
+  <si>
+    <t>136250012</t>
+  </si>
+  <si>
+    <t>136205486</t>
+  </si>
+  <si>
+    <t>136031331</t>
+  </si>
+  <si>
+    <t>136071985</t>
+  </si>
+  <si>
+    <t>136187626</t>
+  </si>
+  <si>
+    <t>136244020</t>
+  </si>
+  <si>
+    <t>136258174</t>
+  </si>
+  <si>
+    <t>136258651</t>
+  </si>
+  <si>
+    <t>133540300</t>
+  </si>
+  <si>
+    <t>136258940</t>
+  </si>
+  <si>
+    <t>136167278</t>
+  </si>
+  <si>
+    <t>136261387</t>
+  </si>
+  <si>
+    <t>136260086</t>
+  </si>
+  <si>
+    <t>136261333</t>
+  </si>
+  <si>
+    <t>136261978</t>
+  </si>
+  <si>
+    <t>136262122</t>
+  </si>
+  <si>
+    <t>136104015</t>
+  </si>
+  <si>
+    <t>136262477</t>
+  </si>
+  <si>
+    <t>131677122</t>
+  </si>
+  <si>
+    <t>136189118</t>
+  </si>
+  <si>
+    <t>136266193</t>
+  </si>
+  <si>
+    <t>136267286</t>
+  </si>
+  <si>
+    <t>136266646</t>
+  </si>
+  <si>
+    <t>136269662</t>
+  </si>
+  <si>
+    <t>132937954</t>
+  </si>
+  <si>
+    <t>136096924</t>
+  </si>
+  <si>
+    <t>136099750</t>
+  </si>
+  <si>
+    <t>136103925</t>
+  </si>
+  <si>
+    <t>136105777</t>
+  </si>
+  <si>
+    <t>136106423</t>
+  </si>
+  <si>
+    <t>136106635</t>
+  </si>
+  <si>
+    <t>136107519</t>
+  </si>
+  <si>
+    <t>136110644</t>
+  </si>
+  <si>
+    <t>136107603</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_15.01.2026</t>
   </si>
 </sst>
 </file>
@@ -484,340 +649,966 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136106708</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F46"/>
     </row>
-    <row r="47" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F47"/>
     </row>
-    <row r="48" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="5:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F55"/>
     </row>
-    <row r="56" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F56"/>
     </row>
-    <row r="57" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F57"/>
     </row>
   </sheetData>
@@ -834,31 +1625,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F079ED07-7F2A-4720-90D0-C19B06229BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="44">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,117 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 16/01/2026</t>
+  </si>
+  <si>
+    <t>134473932</t>
+  </si>
+  <si>
+    <t>136082271</t>
+  </si>
+  <si>
+    <t>136145538</t>
+  </si>
+  <si>
+    <t>136166936</t>
+  </si>
+  <si>
+    <t>136165376</t>
+  </si>
+  <si>
+    <t>136188449</t>
+  </si>
+  <si>
+    <t>136186407</t>
+  </si>
+  <si>
+    <t>136208004</t>
+  </si>
+  <si>
+    <t>136226117</t>
+  </si>
+  <si>
+    <t>136231269</t>
+  </si>
+  <si>
+    <t>136231859</t>
+  </si>
+  <si>
+    <t>136256189</t>
+  </si>
+  <si>
+    <t>136273333</t>
+  </si>
+  <si>
+    <t>136086916</t>
+  </si>
+  <si>
+    <t>136087330</t>
+  </si>
+  <si>
+    <t>136155017</t>
+  </si>
+  <si>
+    <t>136278368</t>
+  </si>
+  <si>
+    <t>136139288</t>
+  </si>
+  <si>
+    <t>136124145</t>
+  </si>
+  <si>
+    <t>136283833</t>
+  </si>
+  <si>
+    <t>136284575</t>
+  </si>
+  <si>
+    <t>136138791</t>
+  </si>
+  <si>
+    <t>136141117</t>
+  </si>
+  <si>
+    <t>136286712</t>
+  </si>
+  <si>
+    <t>136187529</t>
+  </si>
+  <si>
+    <t>136286567</t>
+  </si>
+  <si>
+    <t>136116609</t>
+  </si>
+  <si>
+    <t>136120424</t>
+  </si>
+  <si>
+    <t>136125301</t>
+  </si>
+  <si>
+    <t>136126788</t>
+  </si>
+  <si>
+    <t>136290582</t>
+  </si>
+  <si>
+    <t>136288261</t>
+  </si>
+  <si>
+    <t>136176417</t>
+  </si>
+  <si>
+    <t>133208144</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_16.01.2026</t>
   </si>
 </sst>
 </file>
@@ -484,190 +595,669 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136079290</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F45"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F46"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F47"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F48"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.25">
@@ -711,31 +1301,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F079ED07-7F2A-4720-90D0-C19B06229BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04D03A41-3613-4217-85CC-001735C8EEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="90">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,112 +54,250 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 16/01/2026</t>
-  </si>
-  <si>
-    <t>134473932</t>
-  </si>
-  <si>
-    <t>136082271</t>
-  </si>
-  <si>
-    <t>136145538</t>
-  </si>
-  <si>
-    <t>136166936</t>
-  </si>
-  <si>
-    <t>136165376</t>
-  </si>
-  <si>
-    <t>136188449</t>
-  </si>
-  <si>
-    <t>136186407</t>
-  </si>
-  <si>
-    <t>136208004</t>
-  </si>
-  <si>
-    <t>136226117</t>
-  </si>
-  <si>
-    <t>136231269</t>
-  </si>
-  <si>
-    <t>136231859</t>
-  </si>
-  <si>
-    <t>136256189</t>
-  </si>
-  <si>
-    <t>136273333</t>
-  </si>
-  <si>
-    <t>136086916</t>
-  </si>
-  <si>
-    <t>136087330</t>
-  </si>
-  <si>
-    <t>136155017</t>
-  </si>
-  <si>
-    <t>136278368</t>
-  </si>
-  <si>
-    <t>136139288</t>
-  </si>
-  <si>
-    <t>136124145</t>
-  </si>
-  <si>
-    <t>136283833</t>
-  </si>
-  <si>
-    <t>136284575</t>
-  </si>
-  <si>
-    <t>136138791</t>
-  </si>
-  <si>
-    <t>136141117</t>
-  </si>
-  <si>
-    <t>136286712</t>
-  </si>
-  <si>
-    <t>136187529</t>
-  </si>
-  <si>
-    <t>136286567</t>
-  </si>
-  <si>
-    <t>136116609</t>
-  </si>
-  <si>
-    <t>136120424</t>
-  </si>
-  <si>
-    <t>136125301</t>
-  </si>
-  <si>
-    <t>136126788</t>
-  </si>
-  <si>
-    <t>136290582</t>
-  </si>
-  <si>
-    <t>136288261</t>
-  </si>
-  <si>
-    <t>136176417</t>
-  </si>
-  <si>
-    <t>133208144</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_16.01.2026</t>
+    <t>Recusas Sicredi 19/01/2026</t>
+  </si>
+  <si>
+    <t>136117974</t>
+  </si>
+  <si>
+    <t>136154667</t>
+  </si>
+  <si>
+    <t>134599207</t>
+  </si>
+  <si>
+    <t>136177353</t>
+  </si>
+  <si>
+    <t>136189319</t>
+  </si>
+  <si>
+    <t>136188065</t>
+  </si>
+  <si>
+    <t>136175104</t>
+  </si>
+  <si>
+    <t>136187414</t>
+  </si>
+  <si>
+    <t>136174510</t>
+  </si>
+  <si>
+    <t>136172200</t>
+  </si>
+  <si>
+    <t>136117673</t>
+  </si>
+  <si>
+    <t>136210182</t>
+  </si>
+  <si>
+    <t>136207323</t>
+  </si>
+  <si>
+    <t>136220633</t>
+  </si>
+  <si>
+    <t>136220834</t>
+  </si>
+  <si>
+    <t>136228302</t>
+  </si>
+  <si>
+    <t>136214360</t>
+  </si>
+  <si>
+    <t>136222624</t>
+  </si>
+  <si>
+    <t>136223039</t>
+  </si>
+  <si>
+    <t>136239357</t>
+  </si>
+  <si>
+    <t>136239402</t>
+  </si>
+  <si>
+    <t>136253203</t>
+  </si>
+  <si>
+    <t>136248274</t>
+  </si>
+  <si>
+    <t>136253383</t>
+  </si>
+  <si>
+    <t>136253849</t>
+  </si>
+  <si>
+    <t>136239286</t>
+  </si>
+  <si>
+    <t>136254752</t>
+  </si>
+  <si>
+    <t>136254791</t>
+  </si>
+  <si>
+    <t>136254804</t>
+  </si>
+  <si>
+    <t>136239312</t>
+  </si>
+  <si>
+    <t>136240972</t>
+  </si>
+  <si>
+    <t>136254776</t>
+  </si>
+  <si>
+    <t>136249047</t>
+  </si>
+  <si>
+    <t>136249245</t>
+  </si>
+  <si>
+    <t>136242225</t>
+  </si>
+  <si>
+    <t>136237095</t>
+  </si>
+  <si>
+    <t>136220762</t>
+  </si>
+  <si>
+    <t>134295709</t>
+  </si>
+  <si>
+    <t>136272251</t>
+  </si>
+  <si>
+    <t>136267766</t>
+  </si>
+  <si>
+    <t>136275355</t>
+  </si>
+  <si>
+    <t>136274407</t>
+  </si>
+  <si>
+    <t>136275308</t>
+  </si>
+  <si>
+    <t>136275338</t>
+  </si>
+  <si>
+    <t>136272984</t>
+  </si>
+  <si>
+    <t>136278269</t>
+  </si>
+  <si>
+    <t>136274617</t>
+  </si>
+  <si>
+    <t>136281761</t>
+  </si>
+  <si>
+    <t>136282650</t>
+  </si>
+  <si>
+    <t>136287721</t>
+  </si>
+  <si>
+    <t>136287396</t>
+  </si>
+  <si>
+    <t>136294872</t>
+  </si>
+  <si>
+    <t>136273438</t>
+  </si>
+  <si>
+    <t>136282021</t>
+  </si>
+  <si>
+    <t>136288381</t>
+  </si>
+  <si>
+    <t>136293367</t>
+  </si>
+  <si>
+    <t>136282472</t>
+  </si>
+  <si>
+    <t>136114641</t>
+  </si>
+  <si>
+    <t>136095743</t>
+  </si>
+  <si>
+    <t>136305225</t>
+  </si>
+  <si>
+    <t>136153278</t>
+  </si>
+  <si>
+    <t>136190021</t>
+  </si>
+  <si>
+    <t>136123670</t>
+  </si>
+  <si>
+    <t>136225788</t>
+  </si>
+  <si>
+    <t>136312688</t>
+  </si>
+  <si>
+    <t>136313497</t>
+  </si>
+  <si>
+    <t>136313984</t>
+  </si>
+  <si>
+    <t>136187825</t>
+  </si>
+  <si>
+    <t>134926740</t>
+  </si>
+  <si>
+    <t>136206849</t>
+  </si>
+  <si>
+    <t>136210707</t>
+  </si>
+  <si>
+    <t>136318064</t>
+  </si>
+  <si>
+    <t>136110632</t>
+  </si>
+  <si>
+    <t>136137769</t>
+  </si>
+  <si>
+    <t>136152295</t>
+  </si>
+  <si>
+    <t>136155633</t>
+  </si>
+  <si>
+    <t>136176449</t>
+  </si>
+  <si>
+    <t>136182259</t>
+  </si>
+  <si>
+    <t>136189281</t>
+  </si>
+  <si>
+    <t>136189639</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_19.01.2026</t>
   </si>
 </sst>
 </file>
@@ -564,7 +702,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -596,7 +734,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136079290</v>
+        <v>133683889</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -605,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -623,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -641,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -659,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -677,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -695,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -713,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -731,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -749,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -767,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -785,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -803,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -821,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -839,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -857,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -875,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -893,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -911,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -929,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -947,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -965,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -983,7 +1121,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1001,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1019,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1175,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1193,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1211,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1229,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1247,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1283,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1301,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1199,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1217,75 +1355,815 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F44"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F45"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F46"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F47"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F55"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F56"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F57"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B58C66-84F6-4CEC-B959-ED379E26E420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D879603B-F704-4FFD-8E7F-33E24DF6AEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,103 +54,106 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 20/01/2026</t>
-  </si>
-  <si>
-    <t>136222802</t>
-  </si>
-  <si>
-    <t>136222172</t>
-  </si>
-  <si>
-    <t>136244751</t>
-  </si>
-  <si>
-    <t>136238218</t>
-  </si>
-  <si>
-    <t>136227812</t>
-  </si>
-  <si>
-    <t>136293634</t>
-  </si>
-  <si>
-    <t>136271081</t>
-  </si>
-  <si>
-    <t>136302305</t>
-  </si>
-  <si>
-    <t>136305103</t>
-  </si>
-  <si>
-    <t>135974961</t>
-  </si>
-  <si>
-    <t>136304278</t>
-  </si>
-  <si>
-    <t>136111815</t>
-  </si>
-  <si>
-    <t>136112292</t>
-  </si>
-  <si>
-    <t>136112581</t>
-  </si>
-  <si>
-    <t>136113160</t>
-  </si>
-  <si>
-    <t>136114504</t>
-  </si>
-  <si>
-    <t>136115068</t>
-  </si>
-  <si>
-    <t>136121067</t>
-  </si>
-  <si>
-    <t>136123386</t>
-  </si>
-  <si>
-    <t>136116129</t>
-  </si>
-  <si>
-    <t>136146049</t>
-  </si>
-  <si>
-    <t>136222440</t>
-  </si>
-  <si>
-    <t>136215222</t>
-  </si>
-  <si>
-    <t>136246906</t>
-  </si>
-  <si>
-    <t>136328655</t>
-  </si>
-  <si>
-    <t>135447244</t>
-  </si>
-  <si>
-    <t>136328413</t>
-  </si>
-  <si>
-    <t>136335962</t>
-  </si>
-  <si>
-    <t>136337508</t>
-  </si>
-  <si>
-    <t>136141798</t>
-  </si>
-  <si>
-    <t>136138459</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_20.01.2026</t>
+    <t>Recusas Sicredi 21/01/2026</t>
+  </si>
+  <si>
+    <t>136287669</t>
+  </si>
+  <si>
+    <t>136283241</t>
+  </si>
+  <si>
+    <t>136308294</t>
+  </si>
+  <si>
+    <t>136330923</t>
+  </si>
+  <si>
+    <t>136326647</t>
+  </si>
+  <si>
+    <t>136336397</t>
+  </si>
+  <si>
+    <t>136068249</t>
+  </si>
+  <si>
+    <t>136131735</t>
+  </si>
+  <si>
+    <t>136136415</t>
+  </si>
+  <si>
+    <t>136143035</t>
+  </si>
+  <si>
+    <t>136144675</t>
+  </si>
+  <si>
+    <t>136145977</t>
+  </si>
+  <si>
+    <t>136098939</t>
+  </si>
+  <si>
+    <t>136341454</t>
+  </si>
+  <si>
+    <t>136337591</t>
+  </si>
+  <si>
+    <t>136200582</t>
+  </si>
+  <si>
+    <t>136162225</t>
+  </si>
+  <si>
+    <t>136226507</t>
+  </si>
+  <si>
+    <t>136188346</t>
+  </si>
+  <si>
+    <t>136214710</t>
+  </si>
+  <si>
+    <t>136346578</t>
+  </si>
+  <si>
+    <t>136250711</t>
+  </si>
+  <si>
+    <t>136347751</t>
+  </si>
+  <si>
+    <t>136189210</t>
+  </si>
+  <si>
+    <t>136249777</t>
+  </si>
+  <si>
+    <t>136158465</t>
+  </si>
+  <si>
+    <t>136263754</t>
+  </si>
+  <si>
+    <t>136238950</t>
+  </si>
+  <si>
+    <t>136220983</t>
+  </si>
+  <si>
+    <t>136355814</t>
+  </si>
+  <si>
+    <t>136240240</t>
+  </si>
+  <si>
+    <t>136239581</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_21.01.2026</t>
   </si>
 </sst>
 </file>
@@ -555,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -587,7 +590,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136210632</v>
+        <v>136230069</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -596,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -614,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -632,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -650,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -668,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -686,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -704,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -722,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -740,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -758,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -776,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -794,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -812,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -830,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -848,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -866,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -884,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -902,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -920,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -938,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -956,7 +959,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -974,7 +977,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -992,7 +995,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1010,7 +1013,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1028,7 +1031,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1046,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1067,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1082,7 +1085,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1100,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1118,7 +1121,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1136,7 +1139,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1154,12 +1157,78 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F37"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F38"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F41"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F47"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F48"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F50"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D879603B-F704-4FFD-8E7F-33E24DF6AEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76874C77-075C-4C4D-8322-5F0CDB0378D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,106 +54,79 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 21/01/2026</t>
-  </si>
-  <si>
-    <t>136287669</t>
-  </si>
-  <si>
-    <t>136283241</t>
-  </si>
-  <si>
-    <t>136308294</t>
-  </si>
-  <si>
-    <t>136330923</t>
-  </si>
-  <si>
-    <t>136326647</t>
-  </si>
-  <si>
-    <t>136336397</t>
-  </si>
-  <si>
-    <t>136068249</t>
-  </si>
-  <si>
-    <t>136131735</t>
-  </si>
-  <si>
-    <t>136136415</t>
-  </si>
-  <si>
-    <t>136143035</t>
-  </si>
-  <si>
-    <t>136144675</t>
-  </si>
-  <si>
-    <t>136145977</t>
-  </si>
-  <si>
-    <t>136098939</t>
-  </si>
-  <si>
-    <t>136341454</t>
-  </si>
-  <si>
-    <t>136337591</t>
-  </si>
-  <si>
-    <t>136200582</t>
-  </si>
-  <si>
-    <t>136162225</t>
-  </si>
-  <si>
-    <t>136226507</t>
-  </si>
-  <si>
-    <t>136188346</t>
-  </si>
-  <si>
-    <t>136214710</t>
-  </si>
-  <si>
-    <t>136346578</t>
-  </si>
-  <si>
-    <t>136250711</t>
-  </si>
-  <si>
-    <t>136347751</t>
-  </si>
-  <si>
-    <t>136189210</t>
-  </si>
-  <si>
-    <t>136249777</t>
-  </si>
-  <si>
-    <t>136158465</t>
-  </si>
-  <si>
-    <t>136263754</t>
-  </si>
-  <si>
-    <t>136238950</t>
-  </si>
-  <si>
-    <t>136220983</t>
-  </si>
-  <si>
-    <t>136355814</t>
-  </si>
-  <si>
-    <t>136240240</t>
-  </si>
-  <si>
-    <t>136239581</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_21.01.2026</t>
+    <t>Recusas Sicredi 22/01/2026</t>
+  </si>
+  <si>
+    <t>136293599</t>
+  </si>
+  <si>
+    <t>136286895</t>
+  </si>
+  <si>
+    <t>136293879</t>
+  </si>
+  <si>
+    <t>136348464</t>
+  </si>
+  <si>
+    <t>136124116</t>
+  </si>
+  <si>
+    <t>136175200</t>
+  </si>
+  <si>
+    <t>136342301</t>
+  </si>
+  <si>
+    <t>136364265</t>
+  </si>
+  <si>
+    <t>136364186</t>
+  </si>
+  <si>
+    <t>132512611</t>
+  </si>
+  <si>
+    <t>136365234</t>
+  </si>
+  <si>
+    <t>136365401</t>
+  </si>
+  <si>
+    <t>136366028</t>
+  </si>
+  <si>
+    <t>136283620</t>
+  </si>
+  <si>
+    <t>136286158</t>
+  </si>
+  <si>
+    <t>136264493</t>
+  </si>
+  <si>
+    <t>136251945</t>
+  </si>
+  <si>
+    <t>136270817</t>
+  </si>
+  <si>
+    <t>136367568</t>
+  </si>
+  <si>
+    <t>136276538</t>
+  </si>
+  <si>
+    <t>136370763</t>
+  </si>
+  <si>
+    <t>136373058</t>
+  </si>
+  <si>
+    <t>136372965</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_22.01.2026</t>
   </si>
 </sst>
 </file>
@@ -558,7 +531,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,7 +563,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136230069</v>
+        <v>135973496</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -599,7 +572,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -617,7 +590,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -635,7 +608,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -653,7 +626,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -671,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -689,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -707,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -725,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -743,7 +716,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -761,7 +734,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -779,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -797,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -815,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -833,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -851,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -869,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -887,7 +860,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -905,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -923,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -941,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -959,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -977,7 +950,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -995,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1013,222 +986,12 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F37"/>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F38"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F39"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F40"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F41"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F42"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F43"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F44"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F45"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F46"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F47"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F48"/>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F49"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F50"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76874C77-075C-4C4D-8322-5F0CDB0378D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1866181-01B1-48D9-9CE7-BECBCF5F7E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="85">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,79 +54,235 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 22/01/2026</t>
-  </si>
-  <si>
-    <t>136293599</t>
-  </si>
-  <si>
-    <t>136286895</t>
-  </si>
-  <si>
-    <t>136293879</t>
-  </si>
-  <si>
-    <t>136348464</t>
-  </si>
-  <si>
-    <t>136124116</t>
-  </si>
-  <si>
-    <t>136175200</t>
-  </si>
-  <si>
-    <t>136342301</t>
-  </si>
-  <si>
-    <t>136364265</t>
-  </si>
-  <si>
-    <t>136364186</t>
+    <t>Recusas Sicredi 24/01/2026</t>
+  </si>
+  <si>
+    <t>136215949</t>
+  </si>
+  <si>
+    <t>136227458</t>
+  </si>
+  <si>
+    <t>136227908</t>
+  </si>
+  <si>
+    <t>136229641</t>
+  </si>
+  <si>
+    <t>136250205</t>
+  </si>
+  <si>
+    <t>136286552</t>
+  </si>
+  <si>
+    <t>136283813</t>
+  </si>
+  <si>
+    <t>136286123</t>
+  </si>
+  <si>
+    <t>136312841</t>
+  </si>
+  <si>
+    <t>136335400</t>
+  </si>
+  <si>
+    <t>136328283</t>
+  </si>
+  <si>
+    <t>136219362</t>
+  </si>
+  <si>
+    <t>136200911</t>
+  </si>
+  <si>
+    <t>136217122</t>
+  </si>
+  <si>
+    <t>136218641</t>
+  </si>
+  <si>
+    <t>136218675</t>
+  </si>
+  <si>
+    <t>136219019</t>
+  </si>
+  <si>
+    <t>136220734</t>
+  </si>
+  <si>
+    <t>136238819</t>
+  </si>
+  <si>
+    <t>136240520</t>
+  </si>
+  <si>
+    <t>136240601</t>
+  </si>
+  <si>
+    <t>136243301</t>
+  </si>
+  <si>
+    <t>136245978</t>
+  </si>
+  <si>
+    <t>136246140</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_24.01.2026</t>
+  </si>
+  <si>
+    <t>136207720</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 23/01/2026</t>
+  </si>
+  <si>
+    <t>136209206</t>
+  </si>
+  <si>
+    <t>136228118</t>
+  </si>
+  <si>
+    <t>136229835</t>
+  </si>
+  <si>
+    <t>136266796</t>
+  </si>
+  <si>
+    <t>136256582</t>
+  </si>
+  <si>
+    <t>136269727</t>
+  </si>
+  <si>
+    <t>136282110</t>
+  </si>
+  <si>
+    <t>136277556</t>
+  </si>
+  <si>
+    <t>136287456</t>
+  </si>
+  <si>
+    <t>136284071</t>
+  </si>
+  <si>
+    <t>136265959</t>
+  </si>
+  <si>
+    <t>136316220</t>
+  </si>
+  <si>
+    <t>136324130</t>
+  </si>
+  <si>
+    <t>136326461</t>
+  </si>
+  <si>
+    <t>136330566</t>
+  </si>
+  <si>
+    <t>136322210</t>
+  </si>
+  <si>
+    <t>136343672</t>
+  </si>
+  <si>
+    <t>136346641</t>
+  </si>
+  <si>
+    <t>136356010</t>
   </si>
   <si>
     <t>132512611</t>
   </si>
   <si>
-    <t>136365234</t>
-  </si>
-  <si>
-    <t>136365401</t>
-  </si>
-  <si>
-    <t>136366028</t>
-  </si>
-  <si>
-    <t>136283620</t>
-  </si>
-  <si>
-    <t>136286158</t>
-  </si>
-  <si>
-    <t>136264493</t>
-  </si>
-  <si>
-    <t>136251945</t>
-  </si>
-  <si>
-    <t>136270817</t>
-  </si>
-  <si>
-    <t>136367568</t>
-  </si>
-  <si>
-    <t>136276538</t>
-  </si>
-  <si>
-    <t>136370763</t>
-  </si>
-  <si>
-    <t>136373058</t>
-  </si>
-  <si>
-    <t>136372965</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_22.01.2026</t>
+    <t>136314229</t>
+  </si>
+  <si>
+    <t>136375864</t>
+  </si>
+  <si>
+    <t>136375331</t>
+  </si>
+  <si>
+    <t>136179011</t>
+  </si>
+  <si>
+    <t>136208074</t>
+  </si>
+  <si>
+    <t>136226963</t>
+  </si>
+  <si>
+    <t>136286068</t>
+  </si>
+  <si>
+    <t>136202413</t>
+  </si>
+  <si>
+    <t>136372068</t>
+  </si>
+  <si>
+    <t>136208522</t>
+  </si>
+  <si>
+    <t>136381635</t>
+  </si>
+  <si>
+    <t>132467893</t>
+  </si>
+  <si>
+    <t>136385963</t>
+  </si>
+  <si>
+    <t>136386780</t>
+  </si>
+  <si>
+    <t>135678273</t>
+  </si>
+  <si>
+    <t>136214963</t>
+  </si>
+  <si>
+    <t>136219749</t>
+  </si>
+  <si>
+    <t>133729451</t>
+  </si>
+  <si>
+    <t>136227605</t>
+  </si>
+  <si>
+    <t>136389466</t>
+  </si>
+  <si>
+    <t>136317130</t>
+  </si>
+  <si>
+    <t>136384371</t>
+  </si>
+  <si>
+    <t>136392118</t>
+  </si>
+  <si>
+    <t>136392552</t>
+  </si>
+  <si>
+    <t>136392304</t>
+  </si>
+  <si>
+    <t>136351518</t>
+  </si>
+  <si>
+    <t>136295754</t>
+  </si>
+  <si>
+    <t>136264141</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_23.01.2026</t>
   </si>
 </sst>
 </file>
@@ -531,7 +687,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -563,7 +719,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>135973496</v>
+        <v>136208640</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -572,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -734,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -770,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -806,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -824,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -842,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -860,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -914,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -932,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -950,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -968,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -986,12 +1142,863 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1007,31 +2014,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E5065D-3A37-4960-A13A-3496F999C1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,90 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 26/01/2026</t>
+  </si>
+  <si>
+    <t>136248431</t>
+  </si>
+  <si>
+    <t>136248949</t>
+  </si>
+  <si>
+    <t>136265822</t>
+  </si>
+  <si>
+    <t>136333037</t>
+  </si>
+  <si>
+    <t>136306783</t>
+  </si>
+  <si>
+    <t>136342985</t>
+  </si>
+  <si>
+    <t>136363992</t>
+  </si>
+  <si>
+    <t>136375281</t>
+  </si>
+  <si>
+    <t>136375207</t>
+  </si>
+  <si>
+    <t>136374507</t>
+  </si>
+  <si>
+    <t>136379672</t>
+  </si>
+  <si>
+    <t>136383444</t>
+  </si>
+  <si>
+    <t>136391886</t>
+  </si>
+  <si>
+    <t>136393061</t>
+  </si>
+  <si>
+    <t>136210579</t>
+  </si>
+  <si>
+    <t>136309902</t>
+  </si>
+  <si>
+    <t>136336136</t>
+  </si>
+  <si>
+    <t>136406400</t>
+  </si>
+  <si>
+    <t>136256412</t>
+  </si>
+  <si>
+    <t>136329391</t>
+  </si>
+  <si>
+    <t>136407455</t>
+  </si>
+  <si>
+    <t>136412184</t>
+  </si>
+  <si>
+    <t>136255565</t>
+  </si>
+  <si>
+    <t>136295020</t>
+  </si>
+  <si>
+    <t>136327972</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +537,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,218 +568,472 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136211255</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
-    </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F35"/>
-    </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F36"/>
-    </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F37"/>
-    </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F38"/>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F39"/>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F40"/>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F41"/>
-    </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F42"/>
-    </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F43"/>
-    </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F44"/>
-    </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F45"/>
-    </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F46"/>
-    </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F47"/>
-    </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F48"/>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F49"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F50"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F51"/>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F52"/>
-    </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F53"/>
-    </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F55"/>
-    </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F57"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -711,31 +1049,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E5065D-3A37-4960-A13A-3496F999C1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,90 +49,6 @@
   </si>
   <si>
     <t>Processar</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 26/01/2026</t>
-  </si>
-  <si>
-    <t>136248431</t>
-  </si>
-  <si>
-    <t>136248949</t>
-  </si>
-  <si>
-    <t>136265822</t>
-  </si>
-  <si>
-    <t>136333037</t>
-  </si>
-  <si>
-    <t>136306783</t>
-  </si>
-  <si>
-    <t>136342985</t>
-  </si>
-  <si>
-    <t>136363992</t>
-  </si>
-  <si>
-    <t>136375281</t>
-  </si>
-  <si>
-    <t>136375207</t>
-  </si>
-  <si>
-    <t>136374507</t>
-  </si>
-  <si>
-    <t>136379672</t>
-  </si>
-  <si>
-    <t>136383444</t>
-  </si>
-  <si>
-    <t>136391886</t>
-  </si>
-  <si>
-    <t>136393061</t>
-  </si>
-  <si>
-    <t>136210579</t>
-  </si>
-  <si>
-    <t>136309902</t>
-  </si>
-  <si>
-    <t>136336136</t>
-  </si>
-  <si>
-    <t>136406400</t>
-  </si>
-  <si>
-    <t>136256412</t>
-  </si>
-  <si>
-    <t>136329391</t>
-  </si>
-  <si>
-    <t>136407455</t>
-  </si>
-  <si>
-    <t>136412184</t>
-  </si>
-  <si>
-    <t>136255565</t>
-  </si>
-  <si>
-    <t>136295020</t>
-  </si>
-  <si>
-    <t>136327972</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_26.01.2026</t>
   </si>
 </sst>
 </file>
@@ -537,7 +453,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -568,472 +484,218 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
-        <v>136211255</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
+      <c r="A2" s="6"/>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F27"/>
+    </row>
+    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F37"/>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F38"/>
+    </row>
+    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F41"/>
+    </row>
+    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F47"/>
+    </row>
+    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F48"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F50"/>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F51"/>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F52"/>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F53"/>
+    </row>
+    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F54"/>
+    </row>
+    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F55"/>
+    </row>
+    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F56"/>
+    </row>
+    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F57"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1049,31 +711,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C4867E-B5C1-4E44-846E-9DB44BA98C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="77">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,216 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 27/01/2026</t>
+  </si>
+  <si>
+    <t>136281242</t>
+  </si>
+  <si>
+    <t>136334392</t>
+  </si>
+  <si>
+    <t>136329708</t>
+  </si>
+  <si>
+    <t>136333817</t>
+  </si>
+  <si>
+    <t>136341452</t>
+  </si>
+  <si>
+    <t>136342746</t>
+  </si>
+  <si>
+    <t>136347924</t>
+  </si>
+  <si>
+    <t>136334191</t>
+  </si>
+  <si>
+    <t>136345592</t>
+  </si>
+  <si>
+    <t>136341889</t>
+  </si>
+  <si>
+    <t>136364720</t>
+  </si>
+  <si>
+    <t>136374121</t>
+  </si>
+  <si>
+    <t>136281073</t>
+  </si>
+  <si>
+    <t>136384515</t>
+  </si>
+  <si>
+    <t>136394751</t>
+  </si>
+  <si>
+    <t>136394995</t>
+  </si>
+  <si>
+    <t>136343360</t>
+  </si>
+  <si>
+    <t>136409570</t>
+  </si>
+  <si>
+    <t>136410361</t>
+  </si>
+  <si>
+    <t>136410927</t>
+  </si>
+  <si>
+    <t>136411609</t>
+  </si>
+  <si>
+    <t>136412041</t>
+  </si>
+  <si>
+    <t>136412768</t>
+  </si>
+  <si>
+    <t>136413438</t>
+  </si>
+  <si>
+    <t>136413726</t>
+  </si>
+  <si>
+    <t>136414909</t>
+  </si>
+  <si>
+    <t>136414635</t>
+  </si>
+  <si>
+    <t>136414044</t>
+  </si>
+  <si>
+    <t>136414876</t>
+  </si>
+  <si>
+    <t>136418958</t>
+  </si>
+  <si>
+    <t>136416138</t>
+  </si>
+  <si>
+    <t>136412343</t>
+  </si>
+  <si>
+    <t>136244094</t>
+  </si>
+  <si>
+    <t>136246177</t>
+  </si>
+  <si>
+    <t>136247185</t>
+  </si>
+  <si>
+    <t>136268691</t>
+  </si>
+  <si>
+    <t>136256539</t>
+  </si>
+  <si>
+    <t>136250438</t>
+  </si>
+  <si>
+    <t>136238902</t>
+  </si>
+  <si>
+    <t>136330868</t>
+  </si>
+  <si>
+    <t>136420209</t>
+  </si>
+  <si>
+    <t>136419264</t>
+  </si>
+  <si>
+    <t>136423838</t>
+  </si>
+  <si>
+    <t>136423219</t>
+  </si>
+  <si>
+    <t>136314961</t>
+  </si>
+  <si>
+    <t>136426097</t>
+  </si>
+  <si>
+    <t>136427614</t>
+  </si>
+  <si>
+    <t>136347296</t>
+  </si>
+  <si>
+    <t>136428913</t>
+  </si>
+  <si>
+    <t>136419295</t>
+  </si>
+  <si>
+    <t>136432286</t>
+  </si>
+  <si>
+    <t>136432702</t>
+  </si>
+  <si>
+    <t>136285228</t>
+  </si>
+  <si>
+    <t>136430168</t>
+  </si>
+  <si>
+    <t>136312532</t>
+  </si>
+  <si>
+    <t>136429775</t>
+  </si>
+  <si>
+    <t>136434135</t>
+  </si>
+  <si>
+    <t>136352968</t>
+  </si>
+  <si>
+    <t>136265676</t>
+  </si>
+  <si>
+    <t>136281407</t>
+  </si>
+  <si>
+    <t>136258403</t>
+  </si>
+  <si>
+    <t>136285793</t>
+  </si>
+  <si>
+    <t>136290431</t>
+  </si>
+  <si>
+    <t>136292105</t>
+  </si>
+  <si>
+    <t>136292848</t>
+  </si>
+  <si>
+    <t>136293593</t>
+  </si>
+  <si>
+    <t>136415552</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_27.01.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +663,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,218 +694,1216 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136277853</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F46"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F47"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F55"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F56"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F57"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -711,31 +1919,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C4867E-B5C1-4E44-846E-9DB44BA98C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B28D8D-A359-4B44-A924-87A85C9BA094}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="59">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,211 +54,157 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 27/01/2026</t>
-  </si>
-  <si>
-    <t>136281242</t>
-  </si>
-  <si>
-    <t>136334392</t>
-  </si>
-  <si>
-    <t>136329708</t>
-  </si>
-  <si>
-    <t>136333817</t>
-  </si>
-  <si>
-    <t>136341452</t>
-  </si>
-  <si>
-    <t>136342746</t>
-  </si>
-  <si>
-    <t>136347924</t>
-  </si>
-  <si>
-    <t>136334191</t>
-  </si>
-  <si>
-    <t>136345592</t>
-  </si>
-  <si>
-    <t>136341889</t>
-  </si>
-  <si>
-    <t>136364720</t>
-  </si>
-  <si>
-    <t>136374121</t>
-  </si>
-  <si>
-    <t>136281073</t>
-  </si>
-  <si>
-    <t>136384515</t>
-  </si>
-  <si>
-    <t>136394751</t>
-  </si>
-  <si>
-    <t>136394995</t>
-  </si>
-  <si>
-    <t>136343360</t>
-  </si>
-  <si>
-    <t>136409570</t>
-  </si>
-  <si>
-    <t>136410361</t>
-  </si>
-  <si>
-    <t>136410927</t>
-  </si>
-  <si>
-    <t>136411609</t>
-  </si>
-  <si>
-    <t>136412041</t>
-  </si>
-  <si>
-    <t>136412768</t>
-  </si>
-  <si>
-    <t>136413438</t>
-  </si>
-  <si>
-    <t>136413726</t>
-  </si>
-  <si>
-    <t>136414909</t>
-  </si>
-  <si>
-    <t>136414635</t>
-  </si>
-  <si>
-    <t>136414044</t>
-  </si>
-  <si>
-    <t>136414876</t>
-  </si>
-  <si>
-    <t>136418958</t>
-  </si>
-  <si>
-    <t>136416138</t>
-  </si>
-  <si>
-    <t>136412343</t>
-  </si>
-  <si>
-    <t>136244094</t>
-  </si>
-  <si>
-    <t>136246177</t>
-  </si>
-  <si>
-    <t>136247185</t>
-  </si>
-  <si>
-    <t>136268691</t>
-  </si>
-  <si>
-    <t>136256539</t>
-  </si>
-  <si>
-    <t>136250438</t>
-  </si>
-  <si>
-    <t>136238902</t>
-  </si>
-  <si>
-    <t>136330868</t>
-  </si>
-  <si>
-    <t>136420209</t>
-  </si>
-  <si>
-    <t>136419264</t>
-  </si>
-  <si>
-    <t>136423838</t>
-  </si>
-  <si>
-    <t>136423219</t>
-  </si>
-  <si>
-    <t>136314961</t>
-  </si>
-  <si>
-    <t>136426097</t>
-  </si>
-  <si>
-    <t>136427614</t>
-  </si>
-  <si>
-    <t>136347296</t>
-  </si>
-  <si>
-    <t>136428913</t>
-  </si>
-  <si>
-    <t>136419295</t>
-  </si>
-  <si>
-    <t>136432286</t>
-  </si>
-  <si>
-    <t>136432702</t>
-  </si>
-  <si>
-    <t>136285228</t>
-  </si>
-  <si>
-    <t>136430168</t>
-  </si>
-  <si>
-    <t>136312532</t>
-  </si>
-  <si>
-    <t>136429775</t>
-  </si>
-  <si>
-    <t>136434135</t>
-  </si>
-  <si>
-    <t>136352968</t>
-  </si>
-  <si>
-    <t>136265676</t>
-  </si>
-  <si>
-    <t>136281407</t>
-  </si>
-  <si>
-    <t>136258403</t>
-  </si>
-  <si>
-    <t>136285793</t>
-  </si>
-  <si>
-    <t>136290431</t>
-  </si>
-  <si>
-    <t>136292105</t>
-  </si>
-  <si>
-    <t>136292848</t>
-  </si>
-  <si>
-    <t>136293593</t>
-  </si>
-  <si>
-    <t>136415552</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_27.01.2026</t>
+    <t>Recusas Sicredi 28/01/2026</t>
+  </si>
+  <si>
+    <t>136348243</t>
+  </si>
+  <si>
+    <t>136354481</t>
+  </si>
+  <si>
+    <t>136353662</t>
+  </si>
+  <si>
+    <t>136366624</t>
+  </si>
+  <si>
+    <t>136369427</t>
+  </si>
+  <si>
+    <t>136370288</t>
+  </si>
+  <si>
+    <t>136367404</t>
+  </si>
+  <si>
+    <t>136383629</t>
+  </si>
+  <si>
+    <t>136369112</t>
+  </si>
+  <si>
+    <t>136364552</t>
+  </si>
+  <si>
+    <t>136404433</t>
+  </si>
+  <si>
+    <t>136414201</t>
+  </si>
+  <si>
+    <t>136411129</t>
+  </si>
+  <si>
+    <t>136262067</t>
+  </si>
+  <si>
+    <t>136419901</t>
+  </si>
+  <si>
+    <t>136427598</t>
+  </si>
+  <si>
+    <t>136426889</t>
+  </si>
+  <si>
+    <t>136427798</t>
+  </si>
+  <si>
+    <t>136432058</t>
+  </si>
+  <si>
+    <t>136421513</t>
+  </si>
+  <si>
+    <t>136434164</t>
+  </si>
+  <si>
+    <t>136431185</t>
+  </si>
+  <si>
+    <t>136434533</t>
+  </si>
+  <si>
+    <t>136289467</t>
+  </si>
+  <si>
+    <t>136259797</t>
+  </si>
+  <si>
+    <t>136270617</t>
+  </si>
+  <si>
+    <t>136267280</t>
+  </si>
+  <si>
+    <t>136270957</t>
+  </si>
+  <si>
+    <t>136265985</t>
+  </si>
+  <si>
+    <t>136267437</t>
+  </si>
+  <si>
+    <t>136439975</t>
+  </si>
+  <si>
+    <t>136282493</t>
+  </si>
+  <si>
+    <t>136365349</t>
+  </si>
+  <si>
+    <t>134473932</t>
+  </si>
+  <si>
+    <t>136439952</t>
+  </si>
+  <si>
+    <t>136428785</t>
+  </si>
+  <si>
+    <t>136423772</t>
+  </si>
+  <si>
+    <t>136309884</t>
+  </si>
+  <si>
+    <t>136280618</t>
+  </si>
+  <si>
+    <t>134926740</t>
+  </si>
+  <si>
+    <t>136446145</t>
+  </si>
+  <si>
+    <t>136451983</t>
+  </si>
+  <si>
+    <t>136442363</t>
+  </si>
+  <si>
+    <t>136452405</t>
+  </si>
+  <si>
+    <t>136372771</t>
+  </si>
+  <si>
+    <t>136453520</t>
+  </si>
+  <si>
+    <t>136374699</t>
+  </si>
+  <si>
+    <t>136454032</t>
+  </si>
+  <si>
+    <t>136454624</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_28.01.2026</t>
   </si>
 </sst>
 </file>
@@ -663,7 +609,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -695,7 +641,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136277853</v>
+        <v>136293294</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -704,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -722,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -740,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -758,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -776,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -794,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -812,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -830,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -848,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -866,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -884,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -902,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -920,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -938,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -956,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -974,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -992,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1010,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1028,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1046,7 +992,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1064,7 +1010,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1082,7 +1028,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1100,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1118,7 +1064,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1136,7 +1082,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1154,7 +1100,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1172,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1190,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1208,7 +1154,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1226,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1244,7 +1190,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1262,7 +1208,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1280,7 +1226,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1298,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1316,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1334,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1352,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1370,7 +1316,7 @@
         <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1388,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1406,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1424,7 +1370,7 @@
         <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1442,7 +1388,7 @@
         <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1460,7 +1406,7 @@
         <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1478,7 +1424,7 @@
         <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1496,7 +1442,7 @@
         <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1514,7 +1460,7 @@
         <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1532,7 +1478,7 @@
         <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1550,7 +1496,7 @@
         <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1568,7 +1514,7 @@
         <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1586,324 +1532,12 @@
         <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F51"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F52"/>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6637D10-0E7B-45DC-A671-584E008C4A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,123 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 29/01/2026</t>
+  </si>
+  <si>
+    <t>136317099</t>
+  </si>
+  <si>
+    <t>136319422</t>
+  </si>
+  <si>
+    <t>136392982</t>
+  </si>
+  <si>
+    <t>136390757</t>
+  </si>
+  <si>
+    <t>136343080</t>
+  </si>
+  <si>
+    <t>136390462</t>
+  </si>
+  <si>
+    <t>136394720</t>
+  </si>
+  <si>
+    <t>136413877</t>
+  </si>
+  <si>
+    <t>136373689</t>
+  </si>
+  <si>
+    <t>136432968</t>
+  </si>
+  <si>
+    <t>136435027</t>
+  </si>
+  <si>
+    <t>136448230</t>
+  </si>
+  <si>
+    <t>136454481</t>
+  </si>
+  <si>
+    <t>136445169</t>
+  </si>
+  <si>
+    <t>136452776</t>
+  </si>
+  <si>
+    <t>136439438</t>
+  </si>
+  <si>
+    <t>136453442</t>
+  </si>
+  <si>
+    <t>136292802</t>
+  </si>
+  <si>
+    <t>136462496</t>
+  </si>
+  <si>
+    <t>136074396</t>
+  </si>
+  <si>
+    <t>136364639</t>
+  </si>
+  <si>
+    <t>135817969</t>
+  </si>
+  <si>
+    <t>136348117</t>
+  </si>
+  <si>
+    <t>136471845</t>
+  </si>
+  <si>
+    <t>136388943</t>
+  </si>
+  <si>
+    <t>136388944</t>
+  </si>
+  <si>
+    <t>136355028</t>
+  </si>
+  <si>
+    <t>136301506</t>
+  </si>
+  <si>
+    <t>136303750</t>
+  </si>
+  <si>
+    <t>136303904</t>
+  </si>
+  <si>
+    <t>136307334</t>
+  </si>
+  <si>
+    <t>136307342</t>
+  </si>
+  <si>
+    <t>136313059</t>
+  </si>
+  <si>
+    <t>136314878</t>
+  </si>
+  <si>
+    <t>136317270</t>
+  </si>
+  <si>
+    <t>136317315</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_29.01.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,218 +601,670 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136276730</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
-    </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F39"/>
-    </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F40"/>
-    </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F41"/>
-    </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F42"/>
-    </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F43"/>
-    </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F44"/>
-    </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F45"/>
-    </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F46"/>
-    </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F47"/>
-    </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F48"/>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F49"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F50"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F51"/>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F52"/>
-    </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F53"/>
-    </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F55"/>
-    </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F57"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -711,31 +1280,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6637D10-0E7B-45DC-A671-584E008C4A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449905C4-E8BE-48B8-8D36-9F97A2BD62FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="56">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,118 +54,148 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 29/01/2026</t>
-  </si>
-  <si>
-    <t>136317099</t>
-  </si>
-  <si>
-    <t>136319422</t>
-  </si>
-  <si>
-    <t>136392982</t>
-  </si>
-  <si>
-    <t>136390757</t>
-  </si>
-  <si>
-    <t>136343080</t>
-  </si>
-  <si>
-    <t>136390462</t>
-  </si>
-  <si>
-    <t>136394720</t>
-  </si>
-  <si>
-    <t>136413877</t>
-  </si>
-  <si>
-    <t>136373689</t>
-  </si>
-  <si>
-    <t>136432968</t>
-  </si>
-  <si>
-    <t>136435027</t>
-  </si>
-  <si>
-    <t>136448230</t>
-  </si>
-  <si>
-    <t>136454481</t>
-  </si>
-  <si>
-    <t>136445169</t>
-  </si>
-  <si>
-    <t>136452776</t>
-  </si>
-  <si>
-    <t>136439438</t>
-  </si>
-  <si>
-    <t>136453442</t>
-  </si>
-  <si>
-    <t>136292802</t>
-  </si>
-  <si>
-    <t>136462496</t>
-  </si>
-  <si>
-    <t>136074396</t>
-  </si>
-  <si>
-    <t>136364639</t>
-  </si>
-  <si>
-    <t>135817969</t>
-  </si>
-  <si>
-    <t>136348117</t>
-  </si>
-  <si>
-    <t>136471845</t>
-  </si>
-  <si>
-    <t>136388943</t>
-  </si>
-  <si>
-    <t>136388944</t>
-  </si>
-  <si>
-    <t>136355028</t>
-  </si>
-  <si>
-    <t>136301506</t>
-  </si>
-  <si>
-    <t>136303750</t>
-  </si>
-  <si>
-    <t>136303904</t>
-  </si>
-  <si>
-    <t>136307334</t>
-  </si>
-  <si>
-    <t>136307342</t>
-  </si>
-  <si>
-    <t>136313059</t>
-  </si>
-  <si>
-    <t>136314878</t>
-  </si>
-  <si>
-    <t>136317270</t>
-  </si>
-  <si>
-    <t>136317315</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_29.01.2026</t>
+    <t>Recusas Sicredi 30/01/2026</t>
+  </si>
+  <si>
+    <t>136332196</t>
+  </si>
+  <si>
+    <t>136394513</t>
+  </si>
+  <si>
+    <t>136416011</t>
+  </si>
+  <si>
+    <t>136414031</t>
+  </si>
+  <si>
+    <t>136416536</t>
+  </si>
+  <si>
+    <t>136424195</t>
+  </si>
+  <si>
+    <t>136304808</t>
+  </si>
+  <si>
+    <t>136426825</t>
+  </si>
+  <si>
+    <t>136446426</t>
+  </si>
+  <si>
+    <t>136446696</t>
+  </si>
+  <si>
+    <t>136455343</t>
+  </si>
+  <si>
+    <t>136454693</t>
+  </si>
+  <si>
+    <t>136447247</t>
+  </si>
+  <si>
+    <t>136459041</t>
+  </si>
+  <si>
+    <t>136468991</t>
+  </si>
+  <si>
+    <t>136447265</t>
+  </si>
+  <si>
+    <t>136471978</t>
+  </si>
+  <si>
+    <t>136472108</t>
+  </si>
+  <si>
+    <t>136475032</t>
+  </si>
+  <si>
+    <t>136474793</t>
+  </si>
+  <si>
+    <t>135729550</t>
+  </si>
+  <si>
+    <t>136306391</t>
+  </si>
+  <si>
+    <t>136341692</t>
+  </si>
+  <si>
+    <t>136482891</t>
+  </si>
+  <si>
+    <t>135774969</t>
+  </si>
+  <si>
+    <t>136335460</t>
+  </si>
+  <si>
+    <t>136336179</t>
+  </si>
+  <si>
+    <t>136365939</t>
+  </si>
+  <si>
+    <t>136483190</t>
+  </si>
+  <si>
+    <t>136491163</t>
+  </si>
+  <si>
+    <t>136493730</t>
+  </si>
+  <si>
+    <t>136492942</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_30.01.2026</t>
+  </si>
+  <si>
+    <t>136181396</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 31/01/2026</t>
+  </si>
+  <si>
+    <t>136371668</t>
+  </si>
+  <si>
+    <t>136440578</t>
+  </si>
+  <si>
+    <t>136463342</t>
+  </si>
+  <si>
+    <t>136348311</t>
+  </si>
+  <si>
+    <t>136357040</t>
+  </si>
+  <si>
+    <t>136382896</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_31.01.2026</t>
+  </si>
+  <si>
+    <t>136334966</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 01.02.2026</t>
+  </si>
+  <si>
+    <t>136306808</t>
+  </si>
+  <si>
+    <t>136306437</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_01.02.2026</t>
   </si>
 </sst>
 </file>
@@ -570,7 +600,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -602,7 +632,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136276730</v>
+        <v>136334279</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -611,7 +641,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -629,7 +659,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -647,7 +677,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -665,7 +695,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -683,7 +713,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -701,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -719,7 +749,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -737,7 +767,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -755,7 +785,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -773,7 +803,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -791,7 +821,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -809,7 +839,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -827,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -845,7 +875,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -863,7 +893,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -881,7 +911,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -899,7 +929,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -917,7 +947,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -935,7 +965,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -953,7 +983,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -971,7 +1001,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -989,7 +1019,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1007,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1025,7 +1055,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1061,7 +1091,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1079,7 +1109,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1097,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1115,7 +1145,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1133,7 +1163,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1151,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1169,7 +1199,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1187,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1196,75 +1226,173 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F35"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F36"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F37"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F38"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449905C4-E8BE-48B8-8D36-9F97A2BD62FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91029A42-E037-450B-A9A2-BF3DAE097FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,148 +54,82 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 30/01/2026</t>
-  </si>
-  <si>
-    <t>136332196</t>
-  </si>
-  <si>
-    <t>136394513</t>
-  </si>
-  <si>
-    <t>136416011</t>
-  </si>
-  <si>
-    <t>136414031</t>
-  </si>
-  <si>
-    <t>136416536</t>
-  </si>
-  <si>
-    <t>136424195</t>
-  </si>
-  <si>
-    <t>136304808</t>
-  </si>
-  <si>
-    <t>136426825</t>
-  </si>
-  <si>
-    <t>136446426</t>
-  </si>
-  <si>
-    <t>136446696</t>
-  </si>
-  <si>
-    <t>136455343</t>
-  </si>
-  <si>
-    <t>136454693</t>
-  </si>
-  <si>
-    <t>136447247</t>
-  </si>
-  <si>
-    <t>136459041</t>
-  </si>
-  <si>
-    <t>136468991</t>
-  </si>
-  <si>
-    <t>136447265</t>
-  </si>
-  <si>
-    <t>136471978</t>
-  </si>
-  <si>
-    <t>136472108</t>
-  </si>
-  <si>
-    <t>136475032</t>
-  </si>
-  <si>
-    <t>136474793</t>
-  </si>
-  <si>
-    <t>135729550</t>
-  </si>
-  <si>
-    <t>136306391</t>
-  </si>
-  <si>
-    <t>136341692</t>
-  </si>
-  <si>
-    <t>136482891</t>
-  </si>
-  <si>
-    <t>135774969</t>
-  </si>
-  <si>
-    <t>136335460</t>
-  </si>
-  <si>
-    <t>136336179</t>
-  </si>
-  <si>
-    <t>136365939</t>
-  </si>
-  <si>
-    <t>136483190</t>
-  </si>
-  <si>
-    <t>136491163</t>
-  </si>
-  <si>
-    <t>136493730</t>
-  </si>
-  <si>
-    <t>136492942</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_30.01.2026</t>
-  </si>
-  <si>
-    <t>136181396</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 31/01/2026</t>
-  </si>
-  <si>
-    <t>136371668</t>
-  </si>
-  <si>
-    <t>136440578</t>
-  </si>
-  <si>
-    <t>136463342</t>
-  </si>
-  <si>
-    <t>136348311</t>
-  </si>
-  <si>
-    <t>136357040</t>
-  </si>
-  <si>
-    <t>136382896</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_31.01.2026</t>
-  </si>
-  <si>
-    <t>136334966</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 01.02.2026</t>
-  </si>
-  <si>
-    <t>136306808</t>
-  </si>
-  <si>
-    <t>136306437</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_01.02.2026</t>
+    <t>Recusas Sicredi 02/02/2026</t>
+  </si>
+  <si>
+    <t>136350339</t>
+  </si>
+  <si>
+    <t>136404090</t>
+  </si>
+  <si>
+    <t>136413329</t>
+  </si>
+  <si>
+    <t>136431527</t>
+  </si>
+  <si>
+    <t>136435317</t>
+  </si>
+  <si>
+    <t>136433026</t>
+  </si>
+  <si>
+    <t>136443227</t>
+  </si>
+  <si>
+    <t>136451929</t>
+  </si>
+  <si>
+    <t>136492478</t>
+  </si>
+  <si>
+    <t>136487637</t>
+  </si>
+  <si>
+    <t>136328690</t>
+  </si>
+  <si>
+    <t>136507601</t>
+  </si>
+  <si>
+    <t>136508625</t>
+  </si>
+  <si>
+    <t>133663414</t>
+  </si>
+  <si>
+    <t>136510523</t>
+  </si>
+  <si>
+    <t>134295709</t>
+  </si>
+  <si>
+    <t>136511081</t>
+  </si>
+  <si>
+    <t>132331698</t>
+  </si>
+  <si>
+    <t>133372475</t>
+  </si>
+  <si>
+    <t>136428709</t>
+  </si>
+  <si>
+    <t>136513462</t>
+  </si>
+  <si>
+    <t>136409414</t>
+  </si>
+  <si>
+    <t>136413313</t>
+  </si>
+  <si>
+    <t>136413865</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_02.02.2026</t>
   </si>
 </sst>
 </file>
@@ -600,7 +534,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -632,7 +566,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136334279</v>
+        <v>136332080</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -641,7 +575,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -659,7 +593,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -677,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -695,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -713,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -731,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -749,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -767,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -785,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -803,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -821,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -839,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -857,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -875,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -893,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -911,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -929,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -947,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -965,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -983,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1001,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1019,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1037,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1055,7 +989,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1073,326 +1007,12 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33"/>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91029A42-E037-450B-A9A2-BF3DAE097FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D546A541-8E5D-4E65-B7F2-68945C70FF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="31">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,82 +54,73 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 02/02/2026</t>
-  </si>
-  <si>
-    <t>136350339</t>
-  </si>
-  <si>
-    <t>136404090</t>
-  </si>
-  <si>
-    <t>136413329</t>
-  </si>
-  <si>
-    <t>136431527</t>
-  </si>
-  <si>
-    <t>136435317</t>
-  </si>
-  <si>
-    <t>136433026</t>
-  </si>
-  <si>
-    <t>136443227</t>
-  </si>
-  <si>
-    <t>136451929</t>
-  </si>
-  <si>
-    <t>136492478</t>
-  </si>
-  <si>
-    <t>136487637</t>
-  </si>
-  <si>
-    <t>136328690</t>
-  </si>
-  <si>
-    <t>136507601</t>
-  </si>
-  <si>
-    <t>136508625</t>
-  </si>
-  <si>
-    <t>133663414</t>
-  </si>
-  <si>
-    <t>136510523</t>
-  </si>
-  <si>
-    <t>134295709</t>
-  </si>
-  <si>
-    <t>136511081</t>
-  </si>
-  <si>
-    <t>132331698</t>
-  </si>
-  <si>
-    <t>133372475</t>
-  </si>
-  <si>
-    <t>136428709</t>
-  </si>
-  <si>
-    <t>136513462</t>
-  </si>
-  <si>
-    <t>136409414</t>
-  </si>
-  <si>
-    <t>136413313</t>
-  </si>
-  <si>
-    <t>136413865</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_02.02.2026</t>
+    <t>Recusas Sicredi 03/02/2026</t>
+  </si>
+  <si>
+    <t>136393110</t>
+  </si>
+  <si>
+    <t>136095662</t>
+  </si>
+  <si>
+    <t>136433204</t>
+  </si>
+  <si>
+    <t>136448875</t>
+  </si>
+  <si>
+    <t>136459685</t>
+  </si>
+  <si>
+    <t>136460876</t>
+  </si>
+  <si>
+    <t>136493156</t>
+  </si>
+  <si>
+    <t>136500829</t>
+  </si>
+  <si>
+    <t>136495180</t>
+  </si>
+  <si>
+    <t>136511621</t>
+  </si>
+  <si>
+    <t>136507380</t>
+  </si>
+  <si>
+    <t>136502849</t>
+  </si>
+  <si>
+    <t>136440720</t>
+  </si>
+  <si>
+    <t>136432648</t>
+  </si>
+  <si>
+    <t>136391827</t>
+  </si>
+  <si>
+    <t>136360679</t>
+  </si>
+  <si>
+    <t>136379483</t>
+  </si>
+  <si>
+    <t>136393531</t>
+  </si>
+  <si>
+    <t>136534564</t>
+  </si>
+  <si>
+    <t>136427671</t>
+  </si>
+  <si>
+    <t>136432042</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_03.02.2026 (2)</t>
   </si>
 </sst>
 </file>
@@ -534,7 +525,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -566,7 +557,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136332080</v>
+        <v>136381740</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -575,7 +566,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -593,7 +584,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -611,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -629,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -647,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -665,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -683,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -701,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -719,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -737,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -755,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -773,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -791,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -809,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -827,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -863,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -881,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -899,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -917,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -935,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -953,66 +944,12 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D546A541-8E5D-4E65-B7F2-68945C70FF20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD23A117-33C4-4723-ACBC-3D5BC7F4B2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="47">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,73 +54,121 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 03/02/2026</t>
-  </si>
-  <si>
-    <t>136393110</t>
-  </si>
-  <si>
-    <t>136095662</t>
-  </si>
-  <si>
-    <t>136433204</t>
-  </si>
-  <si>
-    <t>136448875</t>
-  </si>
-  <si>
-    <t>136459685</t>
-  </si>
-  <si>
-    <t>136460876</t>
-  </si>
-  <si>
-    <t>136493156</t>
-  </si>
-  <si>
-    <t>136500829</t>
-  </si>
-  <si>
-    <t>136495180</t>
-  </si>
-  <si>
-    <t>136511621</t>
-  </si>
-  <si>
-    <t>136507380</t>
-  </si>
-  <si>
-    <t>136502849</t>
-  </si>
-  <si>
-    <t>136440720</t>
-  </si>
-  <si>
-    <t>136432648</t>
-  </si>
-  <si>
-    <t>136391827</t>
-  </si>
-  <si>
-    <t>136360679</t>
-  </si>
-  <si>
-    <t>136379483</t>
-  </si>
-  <si>
-    <t>136393531</t>
-  </si>
-  <si>
-    <t>136534564</t>
-  </si>
-  <si>
-    <t>136427671</t>
-  </si>
-  <si>
-    <t>136432042</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_03.02.2026 (2)</t>
+    <t>Recusas Sicredi 04/02/2026</t>
+  </si>
+  <si>
+    <t>136431488</t>
+  </si>
+  <si>
+    <t>136445903</t>
+  </si>
+  <si>
+    <t>136454680</t>
+  </si>
+  <si>
+    <t>134963472</t>
+  </si>
+  <si>
+    <t>136487556</t>
+  </si>
+  <si>
+    <t>136477683</t>
+  </si>
+  <si>
+    <t>136484896</t>
+  </si>
+  <si>
+    <t>136492627</t>
+  </si>
+  <si>
+    <t>136504165</t>
+  </si>
+  <si>
+    <t>133990805</t>
+  </si>
+  <si>
+    <t>136512450</t>
+  </si>
+  <si>
+    <t>136420668</t>
+  </si>
+  <si>
+    <t>136344735</t>
+  </si>
+  <si>
+    <t>136359911</t>
+  </si>
+  <si>
+    <t>136362045</t>
+  </si>
+  <si>
+    <t>136372058</t>
+  </si>
+  <si>
+    <t>136372926</t>
+  </si>
+  <si>
+    <t>136373841</t>
+  </si>
+  <si>
+    <t>136352940</t>
+  </si>
+  <si>
+    <t>136395806</t>
+  </si>
+  <si>
+    <t>136423318</t>
+  </si>
+  <si>
+    <t>136453929</t>
+  </si>
+  <si>
+    <t>134903588</t>
+  </si>
+  <si>
+    <t>136545814</t>
+  </si>
+  <si>
+    <t>134311259</t>
+  </si>
+  <si>
+    <t>136548907</t>
+  </si>
+  <si>
+    <t>136439674</t>
+  </si>
+  <si>
+    <t>136463814</t>
+  </si>
+  <si>
+    <t>136384585</t>
+  </si>
+  <si>
+    <t>136385871</t>
+  </si>
+  <si>
+    <t>136386839</t>
+  </si>
+  <si>
+    <t>136467630</t>
+  </si>
+  <si>
+    <t>136470149</t>
+  </si>
+  <si>
+    <t>136423603</t>
+  </si>
+  <si>
+    <t>136439141</t>
+  </si>
+  <si>
+    <t>136473813</t>
+  </si>
+  <si>
+    <t>136556691</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_04.02.2026</t>
   </si>
 </sst>
 </file>
@@ -525,7 +573,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -557,7 +605,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136381740</v>
+        <v>136208612</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -566,7 +614,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -584,7 +632,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -602,7 +650,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -620,7 +668,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -638,7 +686,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -656,7 +704,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -674,7 +722,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -692,7 +740,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -710,7 +758,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -728,7 +776,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -746,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -764,7 +812,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -782,7 +830,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -800,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -818,7 +866,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -836,7 +884,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -854,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -872,7 +920,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -890,7 +938,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -908,7 +956,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -926,7 +974,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -944,12 +992,342 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F38"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F40"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F41"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F42"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F44"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F45"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F46"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F47"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F48"/>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49"/>
+    </row>
+    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F50"/>
+    </row>
+    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F51"/>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F52"/>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F53"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7A1BCE-81F8-4DFE-BA98-B7B9BA784A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,135 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 05/02/2026</t>
+  </si>
+  <si>
+    <t>136492420</t>
+  </si>
+  <si>
+    <t>136495070</t>
+  </si>
+  <si>
+    <t>136492716</t>
+  </si>
+  <si>
+    <t>136487447</t>
+  </si>
+  <si>
+    <t>136477580</t>
+  </si>
+  <si>
+    <t>136516104</t>
+  </si>
+  <si>
+    <t>136386548</t>
+  </si>
+  <si>
+    <t>136522442</t>
+  </si>
+  <si>
+    <t>136522610</t>
+  </si>
+  <si>
+    <t>136529985</t>
+  </si>
+  <si>
+    <t>136530428</t>
+  </si>
+  <si>
+    <t>133268373</t>
+  </si>
+  <si>
+    <t>136488983</t>
+  </si>
+  <si>
+    <t>136523048</t>
+  </si>
+  <si>
+    <t>136524547</t>
+  </si>
+  <si>
+    <t>136524122</t>
+  </si>
+  <si>
+    <t>136530950</t>
+  </si>
+  <si>
+    <t>136550716</t>
+  </si>
+  <si>
+    <t>136555601</t>
+  </si>
+  <si>
+    <t>136541286</t>
+  </si>
+  <si>
+    <t>136549177</t>
+  </si>
+  <si>
+    <t>136556165</t>
+  </si>
+  <si>
+    <t>136557447</t>
+  </si>
+  <si>
+    <t>136547952</t>
+  </si>
+  <si>
+    <t>136394987</t>
+  </si>
+  <si>
+    <t>136394719</t>
+  </si>
+  <si>
+    <t>136370494</t>
+  </si>
+  <si>
+    <t>136369109</t>
+  </si>
+  <si>
+    <t>136389622</t>
+  </si>
+  <si>
+    <t>136533181</t>
+  </si>
+  <si>
+    <t>136565613</t>
+  </si>
+  <si>
+    <t>136392213</t>
+  </si>
+  <si>
+    <t>136567508</t>
+  </si>
+  <si>
+    <t>136439287</t>
+  </si>
+  <si>
+    <t>131686378</t>
+  </si>
+  <si>
+    <t>136406059</t>
+  </si>
+  <si>
+    <t>136576088</t>
+  </si>
+  <si>
+    <t>136454311</t>
+  </si>
+  <si>
+    <t>136236599</t>
+  </si>
+  <si>
+    <t>136422370</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_05.02.2026 (2)</t>
   </si>
 </sst>
 </file>
@@ -484,190 +613,759 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136394587</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F45"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F46"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F47"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F48"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.25">
@@ -711,31 +1409,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C7A1BCE-81F8-4DFE-BA98-B7B9BA784A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FDA38A-7CDC-4194-BAD5-88DCC233A1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="49">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,127 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 05/02/2026</t>
-  </si>
-  <si>
-    <t>136492420</t>
-  </si>
-  <si>
-    <t>136495070</t>
-  </si>
-  <si>
-    <t>136492716</t>
-  </si>
-  <si>
-    <t>136487447</t>
-  </si>
-  <si>
-    <t>136477580</t>
-  </si>
-  <si>
-    <t>136516104</t>
-  </si>
-  <si>
-    <t>136386548</t>
-  </si>
-  <si>
-    <t>136522442</t>
-  </si>
-  <si>
-    <t>136522610</t>
-  </si>
-  <si>
-    <t>136529985</t>
-  </si>
-  <si>
-    <t>136530428</t>
-  </si>
-  <si>
-    <t>133268373</t>
-  </si>
-  <si>
-    <t>136488983</t>
-  </si>
-  <si>
-    <t>136523048</t>
-  </si>
-  <si>
-    <t>136524547</t>
-  </si>
-  <si>
-    <t>136524122</t>
-  </si>
-  <si>
-    <t>136530950</t>
-  </si>
-  <si>
-    <t>136550716</t>
-  </si>
-  <si>
-    <t>136555601</t>
-  </si>
-  <si>
-    <t>136541286</t>
-  </si>
-  <si>
-    <t>136549177</t>
-  </si>
-  <si>
-    <t>136556165</t>
-  </si>
-  <si>
-    <t>136557447</t>
-  </si>
-  <si>
-    <t>136547952</t>
-  </si>
-  <si>
-    <t>136394987</t>
-  </si>
-  <si>
-    <t>136394719</t>
-  </si>
-  <si>
-    <t>136370494</t>
-  </si>
-  <si>
-    <t>136369109</t>
-  </si>
-  <si>
-    <t>136389622</t>
-  </si>
-  <si>
-    <t>136533181</t>
-  </si>
-  <si>
-    <t>136565613</t>
-  </si>
-  <si>
-    <t>136392213</t>
-  </si>
-  <si>
-    <t>136567508</t>
-  </si>
-  <si>
-    <t>136439287</t>
-  </si>
-  <si>
-    <t>131686378</t>
-  </si>
-  <si>
-    <t>136406059</t>
-  </si>
-  <si>
-    <t>136576088</t>
-  </si>
-  <si>
-    <t>136454311</t>
-  </si>
-  <si>
-    <t>136236599</t>
-  </si>
-  <si>
-    <t>136422370</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_05.02.2026 (2)</t>
+    <t>Recusas Sicredi 06/02/2026</t>
+  </si>
+  <si>
+    <t>136409171</t>
+  </si>
+  <si>
+    <t>136406774</t>
+  </si>
+  <si>
+    <t>136471760</t>
+  </si>
+  <si>
+    <t>136379785</t>
+  </si>
+  <si>
+    <t>136477374</t>
+  </si>
+  <si>
+    <t>136528506</t>
+  </si>
+  <si>
+    <t>136511772</t>
+  </si>
+  <si>
+    <t>136561792</t>
+  </si>
+  <si>
+    <t>136432084</t>
+  </si>
+  <si>
+    <t>136572661</t>
+  </si>
+  <si>
+    <t>136575809</t>
+  </si>
+  <si>
+    <t>136579862</t>
+  </si>
+  <si>
+    <t>136579822</t>
+  </si>
+  <si>
+    <t>136380947</t>
+  </si>
+  <si>
+    <t>136390877</t>
+  </si>
+  <si>
+    <t>136445299</t>
+  </si>
+  <si>
+    <t>136488924</t>
+  </si>
+  <si>
+    <t>136588038</t>
+  </si>
+  <si>
+    <t>136594861</t>
+  </si>
+  <si>
+    <t>136595939</t>
+  </si>
+  <si>
+    <t>136493209</t>
+  </si>
+  <si>
+    <t>136487383</t>
+  </si>
+  <si>
+    <t>136601418</t>
+  </si>
+  <si>
+    <t>136420462</t>
+  </si>
+  <si>
+    <t>136425514</t>
+  </si>
+  <si>
+    <t>136427429</t>
+  </si>
+  <si>
+    <t>136428431</t>
+  </si>
+  <si>
+    <t>136433850</t>
+  </si>
+  <si>
+    <t>136434316</t>
+  </si>
+  <si>
+    <t>136607491</t>
+  </si>
+  <si>
+    <t>136601734</t>
+  </si>
+  <si>
+    <t>136415132</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 08/02/2026</t>
+  </si>
+  <si>
+    <t>136416212</t>
+  </si>
+  <si>
+    <t>136408062</t>
+  </si>
+  <si>
+    <t>136598860</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 07/02/2026</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_08.02.2026.xlsx</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_07.02.2026.xlsx</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_06.02.2026.xlsx</t>
   </si>
 </sst>
 </file>
@@ -614,7 +611,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136394587</v>
+        <v>136124680</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -623,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -641,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -659,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -677,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -695,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -713,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -731,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -749,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -767,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -785,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -803,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -821,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -839,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -857,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -875,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -893,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -911,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -929,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -947,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -965,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -983,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1001,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1019,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1037,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1055,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1073,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1091,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1109,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1127,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1145,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1163,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1181,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1196,10 +1193,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1208,16 +1205,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1226,16 +1223,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1244,16 +1241,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1261,93 +1258,18 @@
       <c r="F37"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F38"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F39"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F40"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F41"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F42"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1409,31 +1331,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94FDA38A-7CDC-4194-BAD5-88DCC233A1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8B62C9A-C771-461E-AFC5-BD4419CC0D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -150,6 +150,18 @@
     <t>136601734</t>
   </si>
   <si>
+    <t>Relatório Recusa _ SICREDI_06.02.2026</t>
+  </si>
+  <si>
+    <t>136598860</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 07/02/2026</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_07.02.2026</t>
+  </si>
+  <si>
     <t>136415132</t>
   </si>
   <si>
@@ -162,19 +174,7 @@
     <t>136408062</t>
   </si>
   <si>
-    <t>136598860</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 07/02/2026</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_08.02.2026.xlsx</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_07.02.2026.xlsx</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_06.02.2026.xlsx</t>
+    <t>Relatório Recusa _ SICREDI_08.02.2026</t>
   </si>
 </sst>
 </file>
@@ -579,7 +579,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -620,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -638,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -656,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -674,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -692,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -710,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -728,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -746,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -764,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -782,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -800,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -818,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -836,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -854,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -872,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -890,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -908,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -926,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -944,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -962,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -980,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -998,7 +998,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1016,7 +1016,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1034,7 +1034,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1052,7 +1052,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1070,7 +1070,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1088,7 +1088,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1106,7 +1106,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1124,7 +1124,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1142,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1160,7 +1160,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1178,7 +1178,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1187,16 +1187,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1205,16 +1205,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1223,16 +1223,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -1250,7 +1250,7 @@
         <v>45</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1295,27 +1295,6 @@
     </row>
     <row r="50" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F50"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F51"/>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F52"/>
-    </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F53"/>
-    </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F55"/>
-    </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F57"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2F2C39-3DFE-4493-830B-8290CE788BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="83">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,234 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 09/02/2026</t>
+  </si>
+  <si>
+    <t>136408720</t>
+  </si>
+  <si>
+    <t>136455075</t>
+  </si>
+  <si>
+    <t>136447481</t>
+  </si>
+  <si>
+    <t>136479324</t>
+  </si>
+  <si>
+    <t>136428792</t>
+  </si>
+  <si>
+    <t>136534900</t>
+  </si>
+  <si>
+    <t>136523027</t>
+  </si>
+  <si>
+    <t>136528785</t>
+  </si>
+  <si>
+    <t>136544582</t>
+  </si>
+  <si>
+    <t>136544878</t>
+  </si>
+  <si>
+    <t>136550434</t>
+  </si>
+  <si>
+    <t>136533937</t>
+  </si>
+  <si>
+    <t>136557833</t>
+  </si>
+  <si>
+    <t>136543123</t>
+  </si>
+  <si>
+    <t>136549243</t>
+  </si>
+  <si>
+    <t>136453589</t>
+  </si>
+  <si>
+    <t>136575205</t>
+  </si>
+  <si>
+    <t>136533564</t>
+  </si>
+  <si>
+    <t>136574565</t>
+  </si>
+  <si>
+    <t>136594237</t>
+  </si>
+  <si>
+    <t>136598326</t>
+  </si>
+  <si>
+    <t>136595441</t>
+  </si>
+  <si>
+    <t>136599831</t>
+  </si>
+  <si>
+    <t>136445517</t>
+  </si>
+  <si>
+    <t>136419879</t>
+  </si>
+  <si>
+    <t>136419980</t>
+  </si>
+  <si>
+    <t>136424041</t>
+  </si>
+  <si>
+    <t>136425611</t>
+  </si>
+  <si>
+    <t>136429405</t>
+  </si>
+  <si>
+    <t>132398496</t>
+  </si>
+  <si>
+    <t>136448531</t>
+  </si>
+  <si>
+    <t>136443044</t>
+  </si>
+  <si>
+    <t>136448721</t>
+  </si>
+  <si>
+    <t>133752435</t>
+  </si>
+  <si>
+    <t>136445569</t>
+  </si>
+  <si>
+    <t>136440072</t>
+  </si>
+  <si>
+    <t>136435014</t>
+  </si>
+  <si>
+    <t>136447333</t>
+  </si>
+  <si>
+    <t>136454323</t>
+  </si>
+  <si>
+    <t>136445950</t>
+  </si>
+  <si>
+    <t>136443953</t>
+  </si>
+  <si>
+    <t>136514849</t>
+  </si>
+  <si>
+    <t>136525933</t>
+  </si>
+  <si>
+    <t>136480081</t>
+  </si>
+  <si>
+    <t>136433195</t>
+  </si>
+  <si>
+    <t>136645349</t>
+  </si>
+  <si>
+    <t>136636966</t>
+  </si>
+  <si>
+    <t>136649278</t>
+  </si>
+  <si>
+    <t>136401334</t>
+  </si>
+  <si>
+    <t>132273381</t>
+  </si>
+  <si>
+    <t>132428399</t>
+  </si>
+  <si>
+    <t>136512427</t>
+  </si>
+  <si>
+    <t>136531771</t>
+  </si>
+  <si>
+    <t>136466120</t>
+  </si>
+  <si>
+    <t>136467596</t>
+  </si>
+  <si>
+    <t>136473154</t>
+  </si>
+  <si>
+    <t>136473308</t>
+  </si>
+  <si>
+    <t>136484600</t>
+  </si>
+  <si>
+    <t>136491458</t>
+  </si>
+  <si>
+    <t>136491743</t>
+  </si>
+  <si>
+    <t>136491884</t>
+  </si>
+  <si>
+    <t>136492355</t>
+  </si>
+  <si>
+    <t>136492524</t>
+  </si>
+  <si>
+    <t>136494771</t>
+  </si>
+  <si>
+    <t>136435551</t>
+  </si>
+  <si>
+    <t>136438962</t>
+  </si>
+  <si>
+    <t>136440473</t>
+  </si>
+  <si>
+    <t>136445850</t>
+  </si>
+  <si>
+    <t>136447159</t>
+  </si>
+  <si>
+    <t>136449975</t>
+  </si>
+  <si>
+    <t>136450220</t>
+  </si>
+  <si>
+    <t>136452676</t>
+  </si>
+  <si>
+    <t>136469811</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_09.02.2026</t>
   </si>
 </sst>
 </file>
@@ -453,7 +681,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,218 +712,1318 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>135493048</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F46"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F47"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F55"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F56"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F57"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -711,31 +2039,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D9B4AB0-A465-433B-904E-6484000994DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F06AC22D-FAB7-4C39-B447-97A90B8998EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="51">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,79 +54,133 @@
     <t>971</t>
   </si>
   <si>
-    <t>Recusas Sicredi 10/02/2026</t>
-  </si>
-  <si>
-    <t>136542491</t>
-  </si>
-  <si>
-    <t>136550129</t>
-  </si>
-  <si>
-    <t>136555077</t>
-  </si>
-  <si>
-    <t>136546865</t>
-  </si>
-  <si>
-    <t>136557552</t>
-  </si>
-  <si>
-    <t>136546277</t>
-  </si>
-  <si>
-    <t>133620559</t>
-  </si>
-  <si>
-    <t>136557971</t>
-  </si>
-  <si>
-    <t>136640559</t>
-  </si>
-  <si>
-    <t>136655238</t>
-  </si>
-  <si>
-    <t>136435551</t>
-  </si>
-  <si>
-    <t>136469811</t>
-  </si>
-  <si>
-    <t>136549578</t>
-  </si>
-  <si>
-    <t>136547460</t>
-  </si>
-  <si>
-    <t>136502801</t>
-  </si>
-  <si>
-    <t>136555854</t>
-  </si>
-  <si>
-    <t>136683850</t>
-  </si>
-  <si>
-    <t>136680046</t>
-  </si>
-  <si>
-    <t>136684617</t>
-  </si>
-  <si>
-    <t>136691090</t>
+    <t>Recusas Sicredi 11/02/2026</t>
+  </si>
+  <si>
+    <t>136542211</t>
+  </si>
+  <si>
+    <t>136577763</t>
+  </si>
+  <si>
+    <t>136570013</t>
+  </si>
+  <si>
+    <t>136642675</t>
+  </si>
+  <si>
+    <t>136684385</t>
+  </si>
+  <si>
+    <t>136534789</t>
+  </si>
+  <si>
+    <t>136686683</t>
+  </si>
+  <si>
+    <t>136685638</t>
+  </si>
+  <si>
+    <t>136676488</t>
+  </si>
+  <si>
+    <t>136677988</t>
   </si>
   <si>
     <t>136442753</t>
   </si>
   <si>
+    <t>136459305</t>
+  </si>
+  <si>
+    <t>136459634</t>
+  </si>
+  <si>
+    <t>136461376</t>
+  </si>
+  <si>
+    <t>136461754</t>
+  </si>
+  <si>
+    <t>136461864</t>
+  </si>
+  <si>
     <t>136482942</t>
   </si>
   <si>
     <t>133407614</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_10.02.2026</t>
+    <t>136557938</t>
+  </si>
+  <si>
+    <t>136697138</t>
+  </si>
+  <si>
+    <t>136697023</t>
+  </si>
+  <si>
+    <t>136698066</t>
+  </si>
+  <si>
+    <t>136698170</t>
+  </si>
+  <si>
+    <t>136513142</t>
+  </si>
+  <si>
+    <t>136700652</t>
+  </si>
+  <si>
+    <t>136700920</t>
+  </si>
+  <si>
+    <t>136555871</t>
+  </si>
+  <si>
+    <t>136702786</t>
+  </si>
+  <si>
+    <t>136703036</t>
+  </si>
+  <si>
+    <t>136703466</t>
+  </si>
+  <si>
+    <t>136703961</t>
+  </si>
+  <si>
+    <t>136707003</t>
+  </si>
+  <si>
+    <t>136712050</t>
+  </si>
+  <si>
+    <t>136476760</t>
+  </si>
+  <si>
+    <t>136463996</t>
+  </si>
+  <si>
+    <t>136471788</t>
+  </si>
+  <si>
+    <t>136480637</t>
+  </si>
+  <si>
+    <t>136482822</t>
+  </si>
+  <si>
+    <t>136485842</t>
+  </si>
+  <si>
+    <t>136486545</t>
+  </si>
+  <si>
+    <t>136493058</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_11.02.2026</t>
   </si>
 </sst>
 </file>
@@ -531,7 +585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -563,7 +617,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>136520029</v>
+        <v>136470378</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -572,7 +626,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,7 +644,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,7 +680,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,7 +698,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,7 +716,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,7 +734,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,7 +752,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,7 +770,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -734,7 +788,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -770,7 +824,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -806,7 +860,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -824,7 +878,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -842,7 +896,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -860,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,7 +950,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -914,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -932,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -950,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -968,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -986,108 +1040,354 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F45"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F46"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F47"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F48"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F49"/>
-    </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F50"/>
-    </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F51"/>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F52"/>
-    </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F53"/>
-    </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F54"/>
-    </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F55"/>
-    </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F56"/>
-    </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
-      <c r="F57"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BD3A17-08FF-4F47-B3B2-A8E26446DC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="53">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,144 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 12/02/2026</t>
+  </si>
+  <si>
+    <t>136504722</t>
+  </si>
+  <si>
+    <t>136561402</t>
+  </si>
+  <si>
+    <t>136573767</t>
+  </si>
+  <si>
+    <t>136605583</t>
+  </si>
+  <si>
+    <t>136603691</t>
+  </si>
+  <si>
+    <t>136594080</t>
+  </si>
+  <si>
+    <t>136606623</t>
+  </si>
+  <si>
+    <t>136651677</t>
+  </si>
+  <si>
+    <t>136670049</t>
+  </si>
+  <si>
+    <t>136700370</t>
+  </si>
+  <si>
+    <t>136672227</t>
+  </si>
+  <si>
+    <t>136476760</t>
+  </si>
+  <si>
+    <t>136700968</t>
+  </si>
+  <si>
+    <t>136463996</t>
+  </si>
+  <si>
+    <t>136471788</t>
+  </si>
+  <si>
+    <t>136480637</t>
+  </si>
+  <si>
+    <t>136482822</t>
+  </si>
+  <si>
+    <t>136485842</t>
+  </si>
+  <si>
+    <t>136486545</t>
+  </si>
+  <si>
+    <t>136493058</t>
+  </si>
+  <si>
+    <t>136712417</t>
+  </si>
+  <si>
+    <t>136575132</t>
+  </si>
+  <si>
+    <t>136719628</t>
+  </si>
+  <si>
+    <t>136721122</t>
+  </si>
+  <si>
+    <t>136721759</t>
+  </si>
+  <si>
+    <t>136721410</t>
+  </si>
+  <si>
+    <t>136724023</t>
+  </si>
+  <si>
+    <t>136485034</t>
+  </si>
+  <si>
+    <t>136567819</t>
+  </si>
+  <si>
+    <t>136727638</t>
+  </si>
+  <si>
+    <t>135332666</t>
+  </si>
+  <si>
+    <t>136491524</t>
+  </si>
+  <si>
+    <t>136491923</t>
+  </si>
+  <si>
+    <t>136494217</t>
+  </si>
+  <si>
+    <t>136727587</t>
+  </si>
+  <si>
+    <t>136730554</t>
+  </si>
+  <si>
+    <t>136730578</t>
+  </si>
+  <si>
+    <t>136732247</t>
+  </si>
+  <si>
+    <t>136733586</t>
+  </si>
+  <si>
+    <t>136516719</t>
+  </si>
+  <si>
+    <t>136521888</t>
+  </si>
+  <si>
+    <t>136531555</t>
+  </si>
+  <si>
+    <t>136532042</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_12.02.2026.xlsx</t>
   </si>
 </sst>
 </file>
@@ -484,190 +622,804 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136490908</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F46"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F47"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F48"/>
     </row>
     <row r="49" spans="6:6" x14ac:dyDescent="0.25">

--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms-my.sharepoint.com/personal/victor_novigoext_allpronet_com_br/Documents/Área de Trabalho/indexação/IndexacaoFG/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDD586-5C83-4D1A-97DF-A7CB77E9BB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCD77B84-98F5-4E16-A0D5-E2C1958AD3B6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6CCCB8-DFEC-4256-A147-EBCDA05EB69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="147">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,426 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>971</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 16/02/2026</t>
+  </si>
+  <si>
+    <t>136567054</t>
+  </si>
+  <si>
+    <t>136563260</t>
+  </si>
+  <si>
+    <t>136678572</t>
+  </si>
+  <si>
+    <t>136674958</t>
+  </si>
+  <si>
+    <t>136711149</t>
+  </si>
+  <si>
+    <t>136730669</t>
+  </si>
+  <si>
+    <t>136761924</t>
+  </si>
+  <si>
+    <t>136753553</t>
+  </si>
+  <si>
+    <t>136504725</t>
+  </si>
+  <si>
+    <t>136523412</t>
+  </si>
+  <si>
+    <t>136529397</t>
+  </si>
+  <si>
+    <t>136544285</t>
+  </si>
+  <si>
+    <t>136550564</t>
+  </si>
+  <si>
+    <t>136552361</t>
+  </si>
+  <si>
+    <t>136534495</t>
+  </si>
+  <si>
+    <t>136545701</t>
+  </si>
+  <si>
+    <t>136551941</t>
+  </si>
+  <si>
+    <t>136550465</t>
+  </si>
+  <si>
+    <t>136552246</t>
+  </si>
+  <si>
+    <t>136556392</t>
+  </si>
+  <si>
+    <t>136558271</t>
+  </si>
+  <si>
+    <t>136608395</t>
+  </si>
+  <si>
+    <t>136520138</t>
+  </si>
+  <si>
+    <t>136540886</t>
+  </si>
+  <si>
+    <t>136545967</t>
+  </si>
+  <si>
+    <t>136556415</t>
+  </si>
+  <si>
+    <t>136557375</t>
+  </si>
+  <si>
+    <t>136563073</t>
+  </si>
+  <si>
+    <t>136568097</t>
+  </si>
+  <si>
+    <t>136571389</t>
+  </si>
+  <si>
+    <t>136571538</t>
+  </si>
+  <si>
+    <t>136572110</t>
+  </si>
+  <si>
+    <t>136572253</t>
+  </si>
+  <si>
+    <t>136578477</t>
+  </si>
+  <si>
+    <t>136095662</t>
+  </si>
+  <si>
+    <t>136576296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório Recusa _ SICREDI_16.02.2026 </t>
+  </si>
+  <si>
+    <t>136509386</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 15/02/2026</t>
+  </si>
+  <si>
+    <t>136502120</t>
+  </si>
+  <si>
+    <t>136515754</t>
+  </si>
+  <si>
+    <t>136508536</t>
+  </si>
+  <si>
+    <t>136529341</t>
+  </si>
+  <si>
+    <t>136531412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório Recusa _ SICREDI_15.02.2026 </t>
+  </si>
+  <si>
+    <t>136511323</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 13/02/2026</t>
+  </si>
+  <si>
+    <t>136570164</t>
+  </si>
+  <si>
+    <t>136604726</t>
+  </si>
+  <si>
+    <t>136684070</t>
+  </si>
+  <si>
+    <t>136709234</t>
+  </si>
+  <si>
+    <t>136696198</t>
+  </si>
+  <si>
+    <t>136711074</t>
+  </si>
+  <si>
+    <t>136732431</t>
+  </si>
+  <si>
+    <t>136734776</t>
+  </si>
+  <si>
+    <t>136736437</t>
+  </si>
+  <si>
+    <t>136720997</t>
+  </si>
+  <si>
+    <t>136598303</t>
+  </si>
+  <si>
+    <t>136741068</t>
+  </si>
+  <si>
+    <t>136594964</t>
+  </si>
+  <si>
+    <t>132499766</t>
+  </si>
+  <si>
+    <t>136745274</t>
+  </si>
+  <si>
+    <t>136599404</t>
+  </si>
+  <si>
+    <t>136746791</t>
+  </si>
+  <si>
+    <t>136508389</t>
+  </si>
+  <si>
+    <t>136742013</t>
+  </si>
+  <si>
+    <t>136754219</t>
+  </si>
+  <si>
+    <t>136557604</t>
+  </si>
+  <si>
+    <t>136762433</t>
+  </si>
+  <si>
+    <t>136762900</t>
+  </si>
+  <si>
+    <t>136763289</t>
+  </si>
+  <si>
+    <t>136512721</t>
+  </si>
+  <si>
+    <t>135729146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório Recusa _ SICREDI_13.02.2026 </t>
+  </si>
+  <si>
+    <t>136587663</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 18/02/2026</t>
+  </si>
+  <si>
+    <t>136591181</t>
+  </si>
+  <si>
+    <t>136604924</t>
+  </si>
+  <si>
+    <t>136602185</t>
+  </si>
+  <si>
+    <t>136683167</t>
+  </si>
+  <si>
+    <t>136683199</t>
+  </si>
+  <si>
+    <t>136670171</t>
+  </si>
+  <si>
+    <t>136570261</t>
+  </si>
+  <si>
+    <t>136702780</t>
+  </si>
+  <si>
+    <t>136727140</t>
+  </si>
+  <si>
+    <t>136747408</t>
+  </si>
+  <si>
+    <t>136753248</t>
+  </si>
+  <si>
+    <t>136754275</t>
+  </si>
+  <si>
+    <t>136758791</t>
+  </si>
+  <si>
+    <t>136743932</t>
+  </si>
+  <si>
+    <t>136751936</t>
+  </si>
+  <si>
+    <t>136741941</t>
+  </si>
+  <si>
+    <t>136758197</t>
+  </si>
+  <si>
+    <t>136742629</t>
+  </si>
+  <si>
+    <t>136754383</t>
+  </si>
+  <si>
+    <t>136548812</t>
+  </si>
+  <si>
+    <t>136550440</t>
+  </si>
+  <si>
+    <t>136551067</t>
+  </si>
+  <si>
+    <t>136554310</t>
+  </si>
+  <si>
+    <t>136555903</t>
+  </si>
+  <si>
+    <t>136564856</t>
+  </si>
+  <si>
+    <t>136586645</t>
+  </si>
+  <si>
+    <t>136565335</t>
+  </si>
+  <si>
+    <t>136566658</t>
+  </si>
+  <si>
+    <t>136564905</t>
+  </si>
+  <si>
+    <t>136595207</t>
+  </si>
+  <si>
+    <t>136567349</t>
+  </si>
+  <si>
+    <t>136573397</t>
+  </si>
+  <si>
+    <t>136570397</t>
+  </si>
+  <si>
+    <t>136587545</t>
+  </si>
+  <si>
+    <t>136352237</t>
+  </si>
+  <si>
+    <t>136590231</t>
+  </si>
+  <si>
+    <t>136600145</t>
+  </si>
+  <si>
+    <t>136600162</t>
+  </si>
+  <si>
+    <t>136605043</t>
+  </si>
+  <si>
+    <t>136607168</t>
+  </si>
+  <si>
+    <t>136776971</t>
+  </si>
+  <si>
+    <t>136782315</t>
+  </si>
+  <si>
+    <t>136672621</t>
+  </si>
+  <si>
+    <t>136081909</t>
+  </si>
+  <si>
+    <t>132129987</t>
+  </si>
+  <si>
+    <t>136679774</t>
+  </si>
+  <si>
+    <t>136708228</t>
+  </si>
+  <si>
+    <t>133056421</t>
+  </si>
+  <si>
+    <t>136750598</t>
+  </si>
+  <si>
+    <t>136704216</t>
+  </si>
+  <si>
+    <t>132512611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório Recusa _ SICREDI_18.02.2026 </t>
+  </si>
+  <si>
+    <t>136555539</t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 17/02/2026</t>
+  </si>
+  <si>
+    <t>136710058</t>
+  </si>
+  <si>
+    <t>136722707</t>
+  </si>
+  <si>
+    <t>136729284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório Recusa _ SICREDI_17.02.2026 </t>
+  </si>
+  <si>
+    <t>Recusas Sicredi 14/02/2026</t>
+  </si>
+  <si>
+    <t>136746461</t>
+  </si>
+  <si>
+    <t>136763442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório Recusa _ SICREDI_14.02.2026 </t>
   </si>
 </sst>
 </file>
@@ -453,7 +873,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -484,218 +904,3307 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>136555539</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F36"/>
     </row>
-    <row r="37" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F37"/>
     </row>
-    <row r="38" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F38"/>
     </row>
-    <row r="39" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F39"/>
     </row>
-    <row r="40" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F40"/>
     </row>
-    <row r="41" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F41"/>
     </row>
-    <row r="42" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F46"/>
     </row>
-    <row r="47" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F47"/>
     </row>
-    <row r="48" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F55"/>
     </row>
-    <row r="56" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F56"/>
     </row>
-    <row r="57" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F57"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -711,31 +4220,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6CCCB8-DFEC-4256-A147-EBCDA05EB69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37F8A38-6992-4F7C-BD39-9DD9A6C89FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -165,9 +165,6 @@
     <t>136576296</t>
   </si>
   <si>
-    <t xml:space="preserve">Relatório Recusa _ SICREDI_16.02.2026 </t>
-  </si>
-  <si>
     <t>136509386</t>
   </si>
   <si>
@@ -189,9 +186,6 @@
     <t>136531412</t>
   </si>
   <si>
-    <t xml:space="preserve">Relatório Recusa _ SICREDI_15.02.2026 </t>
-  </si>
-  <si>
     <t>136511323</t>
   </si>
   <si>
@@ -276,9 +270,6 @@
     <t>135729146</t>
   </si>
   <si>
-    <t xml:space="preserve">Relatório Recusa _ SICREDI_13.02.2026 </t>
-  </si>
-  <si>
     <t>136587663</t>
   </si>
   <si>
@@ -438,9 +429,6 @@
     <t>132512611</t>
   </si>
   <si>
-    <t xml:space="preserve">Relatório Recusa _ SICREDI_18.02.2026 </t>
-  </si>
-  <si>
     <t>136555539</t>
   </si>
   <si>
@@ -456,9 +444,6 @@
     <t>136729284</t>
   </si>
   <si>
-    <t xml:space="preserve">Relatório Recusa _ SICREDI_17.02.2026 </t>
-  </si>
-  <si>
     <t>Recusas Sicredi 14/02/2026</t>
   </si>
   <si>
@@ -468,7 +453,22 @@
     <t>136763442</t>
   </si>
   <si>
-    <t xml:space="preserve">Relatório Recusa _ SICREDI_14.02.2026 </t>
+    <t>Relatório Recusa _ SICREDI_16.02.2026 .xlsx</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_15.02.2026 .xlsx</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_13.02.2026 .xlsx</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_18.02.2026 .xlsx</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_17.02.2026 .xlsx</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_14.02.2026 .xlsx</t>
   </si>
 </sst>
 </file>
@@ -914,7 +914,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -932,7 +932,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -950,7 +950,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -968,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -986,7 +986,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -1004,7 +1004,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -1022,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -1040,7 +1040,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -1058,7 +1058,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -1076,7 +1076,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -1094,7 +1094,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -1112,7 +1112,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -1130,7 +1130,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -1148,7 +1148,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -1166,7 +1166,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -1184,7 +1184,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -1202,7 +1202,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1220,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1238,7 +1238,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1256,7 +1256,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1274,7 +1274,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1292,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1310,7 +1310,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1328,7 +1328,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1346,7 +1346,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1382,7 +1382,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1400,7 +1400,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1418,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1436,7 +1436,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1454,7 +1454,7 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1472,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1490,7 +1490,7 @@
         <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1508,7 +1508,7 @@
         <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1526,7 +1526,7 @@
         <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1544,7 +1544,7 @@
         <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1562,7 +1562,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>45</v>
+        <v>141</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1571,16 +1571,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
@@ -1589,16 +1589,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
@@ -1607,16 +1607,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
@@ -1625,16 +1625,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
@@ -1643,16 +1643,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
@@ -1661,16 +1661,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
@@ -1685,10 +1685,10 @@
         <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
@@ -1703,10 +1703,10 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
@@ -1721,10 +1721,10 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
@@ -1739,10 +1739,10 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
@@ -1757,10 +1757,10 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
@@ -1775,10 +1775,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
@@ -1793,10 +1793,10 @@
         <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
@@ -1829,10 +1829,10 @@
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
@@ -1847,10 +1847,10 @@
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
@@ -1865,10 +1865,10 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
@@ -1883,10 +1883,10 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
@@ -1901,10 +1901,10 @@
         <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
@@ -1913,16 +1913,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
@@ -1930,16 +1930,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
@@ -1947,16 +1947,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
@@ -1964,16 +1964,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
@@ -1981,16 +1981,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>6</v>
@@ -1998,16 +1998,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>6</v>
@@ -2015,16 +2015,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>6</v>
@@ -2032,16 +2032,16 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>6</v>
@@ -2049,16 +2049,16 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>6</v>
@@ -2066,16 +2066,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>6</v>
@@ -2083,16 +2083,16 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>6</v>
@@ -2100,16 +2100,16 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>6</v>
@@ -2117,16 +2117,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>6</v>
@@ -2134,16 +2134,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>6</v>
@@ -2151,16 +2151,16 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>6</v>
@@ -2168,16 +2168,16 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>6</v>
@@ -2185,16 +2185,16 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>6</v>
@@ -2202,16 +2202,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>6</v>
@@ -2219,16 +2219,16 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>6</v>
@@ -2236,16 +2236,16 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>6</v>
@@ -2253,16 +2253,16 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>6</v>
@@ -2270,16 +2270,16 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>6</v>
@@ -2287,16 +2287,16 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>6</v>
@@ -2304,16 +2304,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>6</v>
@@ -2321,16 +2321,16 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>6</v>
@@ -2338,16 +2338,16 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>6</v>
@@ -2355,16 +2355,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>6</v>
@@ -2372,16 +2372,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>6</v>
@@ -2389,16 +2389,16 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>6</v>
@@ -2406,16 +2406,16 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>6</v>
@@ -2423,16 +2423,16 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>6</v>
@@ -2440,16 +2440,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>6</v>
@@ -2457,16 +2457,16 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>6</v>
@@ -2474,16 +2474,16 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>6</v>
@@ -2491,16 +2491,16 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>6</v>
@@ -2508,16 +2508,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>6</v>
@@ -2525,16 +2525,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>6</v>
@@ -2542,16 +2542,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>6</v>
@@ -2559,16 +2559,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>6</v>
@@ -2576,16 +2576,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>6</v>
@@ -2593,16 +2593,16 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>6</v>
@@ -2610,16 +2610,16 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>6</v>
@@ -2627,16 +2627,16 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>6</v>
@@ -2644,16 +2644,16 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>6</v>
@@ -2661,16 +2661,16 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>6</v>
@@ -2678,16 +2678,16 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>6</v>
@@ -2695,16 +2695,16 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>6</v>
@@ -2712,16 +2712,16 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>6</v>
@@ -2729,16 +2729,16 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>6</v>
@@ -2746,16 +2746,16 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>6</v>
@@ -2763,16 +2763,16 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>6</v>
@@ -2780,16 +2780,16 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>6</v>
@@ -2797,16 +2797,16 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>6</v>
@@ -2814,16 +2814,16 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>6</v>
@@ -2831,16 +2831,16 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>6</v>
@@ -2848,16 +2848,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>6</v>
@@ -2865,16 +2865,16 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>6</v>
@@ -2882,16 +2882,16 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>6</v>
@@ -2899,16 +2899,16 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>6</v>
@@ -2916,16 +2916,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>6</v>
@@ -2933,16 +2933,16 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>6</v>
@@ -2950,16 +2950,16 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>6</v>
@@ -2967,16 +2967,16 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>6</v>
@@ -2984,16 +2984,16 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>6</v>
@@ -3001,16 +3001,16 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>6</v>
@@ -3018,16 +3018,16 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>6</v>
@@ -3035,16 +3035,16 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>6</v>
@@ -3052,16 +3052,16 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>6</v>
@@ -3069,16 +3069,16 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>6</v>
@@ -3086,16 +3086,16 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>6</v>
@@ -3103,16 +3103,16 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>6</v>
@@ -3120,16 +3120,16 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>6</v>
@@ -3137,16 +3137,16 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>6</v>
@@ -3154,16 +3154,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>6</v>
@@ -3171,16 +3171,16 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>6</v>
@@ -3188,16 +3188,16 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>6</v>
@@ -3205,16 +3205,16 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>6</v>
@@ -3222,16 +3222,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>6</v>
@@ -3239,16 +3239,16 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>6</v>
@@ -3256,16 +3256,16 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>6</v>
@@ -3279,10 +3279,10 @@
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>6</v>
@@ -3290,16 +3290,16 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>6</v>
@@ -3307,16 +3307,16 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>6</v>
@@ -3324,16 +3324,16 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>6</v>
@@ -3341,16 +3341,16 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>6</v>
@@ -3358,16 +3358,16 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>6</v>
@@ -3375,16 +3375,16 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>6</v>
@@ -3392,16 +3392,16 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>6</v>
@@ -3409,16 +3409,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>6</v>
@@ -3432,10 +3432,10 @@
         <v>7</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>6</v>
@@ -3449,10 +3449,10 @@
         <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>6</v>
@@ -3466,10 +3466,10 @@
         <v>7</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>6</v>
@@ -3483,10 +3483,10 @@
         <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>6</v>
@@ -3500,10 +3500,10 @@
         <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>6</v>
@@ -3517,10 +3517,10 @@
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>6</v>
@@ -3534,10 +3534,10 @@
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>6</v>
@@ -3551,10 +3551,10 @@
         <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>6</v>
@@ -3568,10 +3568,10 @@
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>6</v>
@@ -3585,10 +3585,10 @@
         <v>7</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>6</v>
@@ -3602,10 +3602,10 @@
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>6</v>
@@ -3619,10 +3619,10 @@
         <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>6</v>
@@ -3636,10 +3636,10 @@
         <v>7</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>6</v>
@@ -3653,10 +3653,10 @@
         <v>7</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>6</v>
@@ -3664,16 +3664,16 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>6</v>
@@ -3681,16 +3681,16 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>6</v>
@@ -3698,16 +3698,16 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>6</v>
@@ -3715,16 +3715,16 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>6</v>
@@ -3732,16 +3732,16 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>6</v>
@@ -3749,16 +3749,16 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>6</v>
@@ -3766,16 +3766,16 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>6</v>
@@ -3783,16 +3783,16 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>6</v>
@@ -3800,16 +3800,16 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>6</v>
@@ -3817,16 +3817,16 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>6</v>
@@ -3834,16 +3834,16 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>6</v>
@@ -3851,16 +3851,16 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>6</v>
@@ -3868,16 +3868,16 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>6</v>
@@ -3885,16 +3885,16 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>6</v>
@@ -3902,16 +3902,16 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>6</v>
@@ -3919,16 +3919,16 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>6</v>
@@ -3936,16 +3936,16 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>6</v>
@@ -3953,16 +3953,16 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>6</v>
@@ -3970,16 +3970,16 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>6</v>
@@ -3987,16 +3987,16 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>6</v>
@@ -4004,16 +4004,16 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>6</v>
@@ -4021,13 +4021,13 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>146</v>
@@ -4038,13 +4038,13 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>146</v>
@@ -4055,13 +4055,13 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>146</v>
@@ -4072,13 +4072,13 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>146</v>
@@ -4089,13 +4089,13 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>146</v>
@@ -4106,13 +4106,13 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>146</v>
@@ -4123,13 +4123,13 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>146</v>
@@ -4140,13 +4140,13 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>146</v>
@@ -4157,13 +4157,13 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>146</v>
@@ -4174,13 +4174,13 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>146</v>
@@ -4191,13 +4191,13 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>146</v>
@@ -4220,31 +4220,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
+++ b/Treinamento/IndexacaoFG/IndexacaoFG_SIDREDI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37F8A38-6992-4F7C-BD39-9DD9A6C89FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56A45398-FD33-4FD8-AADB-2ED12F3EC159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,6 +54,162 @@
     <t>971</t>
   </si>
   <si>
+    <t>Recusas Sicredi 13/02/2026</t>
+  </si>
+  <si>
+    <t>136570164</t>
+  </si>
+  <si>
+    <t>136604726</t>
+  </si>
+  <si>
+    <t>136684070</t>
+  </si>
+  <si>
+    <t>136709234</t>
+ 